--- a/questoes sem rep.xlsx
+++ b/questoes sem rep.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J212"/>
+  <dimension ref="A1:K212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,11 @@
           <t>notas_revisao</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tema_exame</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -509,6 +514,11 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -546,7 +556,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Capacidade financeira (IMT/DL 257/2007): 9.000 € no 1.º veículo; 5.000 € (pesado) ou 900 € (ligeiro) por cada veículo adicional.</t>
+          <t>Resposta aceite no exame (DL 257/2007 / IMT): 9.000 € no 1.º veículo; 5.000 € (pesado) ou 900 € (ligeiro) por veículo adicional.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -557,6 +567,11 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>Corrigido valor do veículo ligeiro: 1.500 € → 900 € (fonte: imt-ip.pt).</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
         </is>
       </c>
     </row>
@@ -601,6 +616,11 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -643,6 +663,11 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -685,6 +710,11 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -727,6 +757,11 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -769,6 +804,11 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -811,6 +851,11 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -853,6 +898,11 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -895,6 +945,11 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -937,6 +992,11 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -979,6 +1039,11 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1021,6 +1086,11 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1063,6 +1133,11 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1105,6 +1180,11 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1147,6 +1227,11 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1189,6 +1274,11 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1231,6 +1321,11 @@
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1273,6 +1368,11 @@
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1315,6 +1415,11 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1357,6 +1462,11 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1399,6 +1509,11 @@
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1441,6 +1556,11 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1483,6 +1603,11 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1525,6 +1650,11 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1567,6 +1697,11 @@
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1609,6 +1744,11 @@
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1651,6 +1791,11 @@
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1693,6 +1838,11 @@
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1735,6 +1885,11 @@
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1777,6 +1932,11 @@
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1819,6 +1979,11 @@
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1861,6 +2026,11 @@
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1903,6 +2073,11 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1945,6 +2120,11 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1987,6 +2167,11 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2029,6 +2214,11 @@
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2071,6 +2261,11 @@
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2113,6 +2308,11 @@
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2155,6 +2355,11 @@
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2197,6 +2402,11 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2239,6 +2449,11 @@
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2281,6 +2496,11 @@
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2323,6 +2543,11 @@
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2365,6 +2590,11 @@
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2407,6 +2637,11 @@
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2449,6 +2684,11 @@
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2491,6 +2731,11 @@
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2533,6 +2778,11 @@
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2575,6 +2825,11 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2617,6 +2872,11 @@
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2659,6 +2919,11 @@
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2701,6 +2966,11 @@
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2743,6 +3013,11 @@
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2785,6 +3060,11 @@
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2827,6 +3107,11 @@
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2869,6 +3154,11 @@
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2911,6 +3201,11 @@
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2953,6 +3248,11 @@
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2995,6 +3295,11 @@
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3037,6 +3342,11 @@
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3079,6 +3389,11 @@
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3121,6 +3436,11 @@
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3163,6 +3483,11 @@
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3205,6 +3530,11 @@
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3247,6 +3577,11 @@
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3289,6 +3624,11 @@
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3331,6 +3671,11 @@
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3373,6 +3718,11 @@
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>passageiros</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3415,6 +3765,11 @@
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3457,6 +3812,11 @@
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3499,6 +3859,11 @@
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3541,6 +3906,11 @@
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3583,6 +3953,11 @@
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3625,6 +4000,11 @@
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3667,6 +4047,11 @@
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3709,6 +4094,11 @@
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3751,6 +4141,11 @@
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3793,6 +4188,11 @@
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3835,6 +4235,11 @@
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3877,6 +4282,11 @@
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3919,6 +4329,11 @@
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3961,6 +4376,11 @@
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4003,6 +4423,11 @@
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4045,6 +4470,11 @@
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4087,6 +4517,11 @@
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4129,6 +4564,11 @@
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4171,6 +4611,11 @@
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4211,14 +4656,11 @@
           <t>É crime e pode acarretar sanções pesadas.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -4263,6 +4705,11 @@
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4305,6 +4752,11 @@
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4347,6 +4799,11 @@
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4389,6 +4846,11 @@
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4431,6 +4893,11 @@
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4473,6 +4940,11 @@
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4515,6 +4987,11 @@
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4557,6 +5034,11 @@
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4599,6 +5081,11 @@
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4641,6 +5128,11 @@
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4683,6 +5175,11 @@
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4723,14 +5220,11 @@
           <t>É crime com sanções pesadas.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -4775,6 +5269,11 @@
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4817,6 +5316,11 @@
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -4859,6 +5363,11 @@
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -4901,6 +5410,11 @@
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -4943,6 +5457,11 @@
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -4985,6 +5504,11 @@
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5027,6 +5551,11 @@
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5069,6 +5598,11 @@
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5111,6 +5645,11 @@
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5153,6 +5692,11 @@
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5195,6 +5739,11 @@
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5237,6 +5786,11 @@
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5279,6 +5833,11 @@
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5321,6 +5880,11 @@
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -5363,6 +5927,11 @@
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5405,6 +5974,11 @@
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5447,6 +6021,11 @@
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -5489,6 +6068,11 @@
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5531,6 +6115,11 @@
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5573,6 +6162,11 @@
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5615,6 +6209,11 @@
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -5657,6 +6256,11 @@
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -5699,6 +6303,11 @@
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -5741,6 +6350,11 @@
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -5781,14 +6395,11 @@
           <t>Podem ser bilhetes simples ou passes/assina tura.</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -5831,14 +6442,11 @@
           <t>Uniforme e apresentação cuidada são obrigatórios.</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -5883,6 +6491,11 @@
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>passageiros</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -5923,14 +6536,11 @@
           <t>Até 20 kg de bagagem por passageiro é gratuito.</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -5975,6 +6585,11 @@
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -6017,6 +6632,11 @@
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -6057,14 +6677,11 @@
           <t>Transportes públicos bons = menos carros na estrada = menos poluição.</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -6107,14 +6724,11 @@
           <t>Em Portugal, o transporte rodoviário é o mais usado.</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -6157,14 +6771,11 @@
           <t>Pode ser por conta própria ou por conta de outrem.</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>misto</t>
         </is>
       </c>
     </row>
@@ -6209,6 +6820,11 @@
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -6249,14 +6865,11 @@
           <t>Tem de ser alguém com responsabilidade efetiva na gestão.</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>misto</t>
         </is>
       </c>
     </row>
@@ -6299,14 +6912,11 @@
           <t>Várias formas jurídicas são permitidas.</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -6349,14 +6959,11 @@
           <t>Alvará ou licença comunitária válida até 5 anos.</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>misto</t>
         </is>
       </c>
     </row>
@@ -6399,14 +7006,11 @@
           <t>Contrato escrito com a entidade que contrata o serviço.</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -6451,6 +7055,11 @@
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -6493,6 +7102,11 @@
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -6535,6 +7149,11 @@
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -6577,6 +7196,11 @@
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -6617,14 +7241,11 @@
           <t>Serviços regulares = horários e tarifas fixos.</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -6669,6 +7290,11 @@
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -6711,12 +7337,17 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>corrigida; revisar_escopo</t>
+          <t>corrigida</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Preenchida opção D em falta. Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+          <t>Preenchida opção D em falta.</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>misto</t>
         </is>
       </c>
     </row>
@@ -6761,6 +7392,11 @@
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -6803,6 +7439,11 @@
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -6845,6 +7486,11 @@
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -6887,6 +7533,11 @@
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -6929,6 +7580,11 @@
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -6971,6 +7627,11 @@
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -7013,6 +7674,11 @@
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -7055,6 +7721,11 @@
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -7097,6 +7768,11 @@
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -7139,6 +7815,11 @@
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -7181,6 +7862,11 @@
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -7223,6 +7909,11 @@
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>misto</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -7265,6 +7956,11 @@
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -7307,6 +8003,11 @@
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -7349,6 +8050,11 @@
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -7399,6 +8105,11 @@
           <t>Preenchida opção D em falta.</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -7436,7 +8147,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>O airbag é complementar ao cinto de segurança; usado isoladamente pode causar lesões. Todas as afirmações são verdadeiras.</t>
+          <t>Resposta aceite no exame: todas as afirmações sobre o airbag são verdadeiras.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -7447,6 +8158,11 @@
       <c r="J164" t="inlineStr">
         <is>
           <t>Resposta corrigida D→C; opção D preenchida.</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>comum</t>
         </is>
       </c>
     </row>
@@ -7499,6 +8215,11 @@
           <t>Preenchida opção C em falta.</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -7541,6 +8262,11 @@
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -7583,6 +8309,11 @@
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -7625,6 +8356,11 @@
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -7667,6 +8403,11 @@
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -7709,6 +8450,11 @@
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -7759,6 +8505,11 @@
           <t>Preenchida opção D em falta.</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -7801,6 +8552,11 @@
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -7843,6 +8599,11 @@
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -7885,6 +8646,11 @@
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -7927,6 +8693,11 @@
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -7977,6 +8748,11 @@
           <t>Preenchida opção D em falta.</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -8019,6 +8795,11 @@
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -8061,6 +8842,11 @@
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>mercadorias</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -8103,6 +8889,11 @@
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -8145,6 +8936,11 @@
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>passageiros</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -8187,6 +8983,11 @@
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -8229,6 +9030,11 @@
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -8271,6 +9077,11 @@
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -8313,6 +9124,11 @@
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -8355,6 +9171,11 @@
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -8397,6 +9218,11 @@
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -8439,6 +9265,11 @@
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -8479,14 +9310,11 @@
           <t>Autocarro articulado 4+ eixos = 32 toneladas.</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -8529,14 +9357,11 @@
           <t>Veículo &gt; 4 anos = inspeção anual.</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -8579,14 +9404,11 @@
           <t>Requisitos de acesso: idoneidade + capacidade profissional + financeira.</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>misto</t>
         </is>
       </c>
     </row>
@@ -8629,14 +9451,11 @@
           <t>Alta qualidade = 100+ km, categoria III, poucas paragens.</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -8679,14 +9498,11 @@
           <t>Falta não suprida em 1 ano = caducidade do alvará.</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>misto</t>
         </is>
       </c>
     </row>
@@ -8731,6 +9547,11 @@
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -8773,6 +9594,11 @@
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -8813,14 +9639,11 @@
           <t>Balanço ou garantia bancária.</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -8863,14 +9686,11 @@
           <t>Não aprovação = caducidade da licença do veículo.</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -8913,14 +9733,11 @@
           <t>Várias formas jurídicas permitidas.</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -8960,17 +9777,14 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Mínimo € 50 000 para início.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+          <t>Resposta habitualmente aceite nos testes de passageiros do exame CAM/CP. Confirme sempre com o manual da sua entidade formadora.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -9015,6 +9829,11 @@
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>passageiros</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -9055,14 +9874,11 @@
           <t>Verificar sempre (acesso e exercício).</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>misto</t>
         </is>
       </c>
     </row>
@@ -9105,14 +9921,11 @@
           <t>Várias formas de aquisição permitidas.</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -9157,6 +9970,11 @@
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>passageiros</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -9199,6 +10017,11 @@
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>comum</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -9239,14 +10062,11 @@
           <t>Dístico + folha de itinerário.</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -9289,14 +10109,11 @@
           <t>No pedido de acesso.</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -9339,14 +10156,11 @@
           <t>30 dias, sob pena de coima.</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -9389,14 +10203,11 @@
           <t>Interdição profissional = perda de idoneidade.</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>misto</t>
         </is>
       </c>
     </row>
@@ -9439,14 +10250,11 @@
           <t>Serviços regulares especializados = categorias específicas.</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -9489,14 +10297,11 @@
           <t>Ocasionais + regulares especializados nacionais.</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>misto</t>
         </is>
       </c>
     </row>
@@ -9539,14 +10344,11 @@
           <t>Municipais e intermunicipais.</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -9589,14 +10391,11 @@
           <t>Até 20 kg gratuito.</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>passageiros</t>
         </is>
       </c>
     </row>
@@ -9639,14 +10438,11 @@
           <t>Certificado para transportes particulares.</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>revisar_escopo</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>Questão de transporte de passageiros — verificar relevância para exame CAM mercadorias.</t>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>misto</t>
         </is>
       </c>
     </row>

--- a/questoes sem rep.xlsx
+++ b/questoes sem rep.xlsx
@@ -2298,16 +2298,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>b</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>A amarração em laço vai de um lado da carroçaria ao outro por cima da carga.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>Resposta aceite no exame (IMT): amarração em laço liga a carga a um dos lados da carroçaria, para evitar o deslizamento e a inclinação para o lado oposto. A opção D descreve a amarração de topo.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>corrigida</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Resposta corrigida D-&gt;B (manual IMT Acondicionamento de Carga).</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>mercadorias</t>

--- a/questoes sem rep.xlsx
+++ b/questoes sem rep.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Tanto pessoas singulares como coletivas podem obter licença desde que cumpram os requisitos legais (Decreto-Lei n.º 257/2007).</t>
+          <t>Tanto pessoas singulares como coletivas podem obter licença desde que cumpram os requisitos legais (Decreto-Lei n.º 257/2007).</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -566,7 +566,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT (DL 257/2007): 9.000 € no 1.º veículo; 5.000 € (pesado) ou 900 € (ligeiro) por veículo adicional.</t>
+          <t>(DL 257/2007): 9.000 € no 1.º veículo; 5.000 € (pesado) ou 900 € (ligeiro) por veículo adicional.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. A comunicação deve ser feita no prazo de 30 dias após a ocorrência.</t>
+          <t>A comunicação deve ser feita no prazo de 30 dias após a ocorrência.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. A falta deve ser suprida no prazo de 30 dias.</t>
+          <t>A falta deve ser suprida no prazo de 30 dias.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -730,7 +730,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Tanto o transportador como o expedidor respondem solidariamente pela infração.</t>
+          <t>Tanto o transportador como o expedidor respondem solidariamente pela infração.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. A certidão do registo comercial é o documento válido para comprovar o capital social.</t>
+          <t>A certidão do registo comercial é o documento válido para comprovar o capital social.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -834,7 +834,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O IMT é o organismo responsável pela emissão da licença.</t>
+          <t>O IMT é o organismo responsável pela emissão da licença.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. A renovação exige comprovação contínua dos requisitos legais.</t>
+          <t>A renovação exige comprovação contínua dos requisitos legais.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -938,7 +938,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Os requisitos são de verificação permanente.</t>
+          <t>Os requisitos são de verificação permanente.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Tanto o expedidor como o transportador respondem em comparticipação.</t>
+          <t>Tanto o expedidor como o transportador respondem em comparticipação.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O alvará tem validade de 5 anos, devendo ser renovado antes do fim desse prazo.</t>
+          <t>O alvará tem validade de 5 anos, devendo ser renovado antes do fim desse prazo.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. A licença comunitária é necessária para realizar transportes internacionais entre países da União Europeia.</t>
+          <t>A licença comunitária é necessária para realizar transportes internacionais entre países da União Europeia.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O transporte por conta própria não requer licença desde que não haja remuneração por parte de terceiros.</t>
+          <t>O transporte por conta própria não requer licença desde que não haja remuneração por parte de terceiros.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Para veículos de 2 eixos o limite é 18 toneladas (regulamentação europeia).</t>
+          <t>Para veículos de 2 eixos o limite é 18 toneladas (regulamentação europeia).</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Veículos de 3 eixos podem circular até 26 toneladas.</t>
+          <t>Veículos de 3 eixos podem circular até 26 toneladas.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O limite máximo é 44 toneladas para conjuntos com 5 ou mais eixos.</t>
+          <t>O limite máximo é 44 toneladas para conjuntos com 5 ou mais eixos.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. A altura máxima legal é 4 metros do solo.</t>
+          <t>A altura máxima legal é 4 metros do solo.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O comprimento máximo de um veículo isolado é 13,5 metros.</t>
+          <t>O comprimento máximo de um veículo isolado é 13,5 metros.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. É obrigatório o ADR para o transporte de mercadorias perigosas.</t>
+          <t>É obrigatório o ADR para o transporte de mercadorias perigosas.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O limite diário de condução é 9 horas (pode ser estendido para 10 horas duas vezes por semana).</t>
+          <t>O limite diário de condução é 9 horas (pode ser estendido para 10 horas duas vezes por semana).</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O limite semanal de condução é de 56 horas (pode chegar a 60 horas em algumas semanas).</t>
+          <t>O limite semanal de condução é de 56 horas (pode chegar a 60 horas em algumas semanas).</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O descanso diário mínimo é de 11 horas (pode ser reduzido para 9 horas três vezes por semana).</t>
+          <t>O descanso diário mínimo é de 11 horas (pode ser reduzido para 9 horas três vezes por semana).</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Veículos acima de 3,5 t de peso bruto devem ter tacógrafo (analógico ou digital).</t>
+          <t>Veículos acima de 3,5 t de peso bruto devem ter tacógrafo (analógico ou digital).</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Podem ser escritos ou verbais, mas recomenda-se sempre a forma escrita.</t>
+          <t>Podem ser escritos ou verbais, mas recomenda-se sempre a forma escrita.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. A entidade patronal é responsável pelo pagamento no mês seguinte.</t>
+          <t>A entidade patronal é responsável pelo pagamento no mês seguinte.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. A doença é falta justificada, desde que comprovada.</t>
+          <t>A doença é falta justificada, desde que comprovada.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O trabalhador tem direito à reintegração na mesma categoria.</t>
+          <t>O trabalhador tem direito à reintegração na mesma categoria.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O limite semanal normal é de 40 horas.</t>
+          <t>O limite semanal normal é de 40 horas.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O direito a férias é irrenunciável por lei.</t>
+          <t>O direito a férias é irrenunciável por lei.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Todas as situações indicadas são justa causa para o trabalhador.</t>
+          <t>Todas as situações indicadas são justa causa para o trabalhador.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Após 4h30 de condução contínua é obrigatória uma pausa de 45 minutos.</t>
+          <t>Após 4h30 de condução contínua é obrigatória uma pausa de 45 minutos.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O descanso semanal normal é de 45 horas consecutivas.</t>
+          <t>O descanso semanal normal é de 45 horas consecutivas.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O chassis (quadro) é a estrutura principal que suporta todo o veículo.</t>
+          <t>O chassis (quadro) é a estrutura principal que suporta todo o veículo.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. A meia carga causa o maior movimento do líquido (sloshing).</t>
+          <t>A meia carga causa o maior movimento do líquido (sloshing).</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT: altura máxima 4 m a contar do solo.</t>
+          <t>altura máxima 4 m a contar do solo.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Deve-se verificar regularmente o óleo hidráulico e da direção assistida.</t>
+          <t>Deve-se verificar regularmente o óleo hidráulico e da direção assistida.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Indica má combustão, normalmente por excesso de combustível ou filtro de ar sujo.</t>
+          <t>Indica má combustão, normalmente por excesso de combustível ou filtro de ar sujo.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O travamento é quando a carga é colocada contra estruturas fixas do veículo.</t>
+          <t>O travamento é quando a carga é colocada contra estruturas fixas do veículo.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT: amarração em laço liga a carga a um dos lados da carroçaria (manual IMT Acondicionamento de Carga, sec. 3.2.2).</t>
+          <t>amarração em laço liga a carga a um dos lados da carroçaria (manual IMT Acondicionamento de Carga, sec. 3.2.2).</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Parar regularmente é a melhor forma de combater a fadiga noturna.</t>
+          <t>Parar regularmente é a melhor forma de combater a fadiga noturna.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Baixo nível de óleo ou fugas podem causar perda de assistência na direção.</t>
+          <t>Baixo nível de óleo ou fugas podem causar perda de assistência na direção.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Retém as partículas nocivas e as queima periodicamente.</t>
+          <t>Retém as partículas nocivas e as queima periodicamente.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O compressor é movido mecanicamente pelo motor do veículo.</t>
+          <t>O compressor é movido mecanicamente pelo motor do veículo.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Pressão errada + má distribuição da carga aceleram o desgaste.</t>
+          <t>Pressão errada + má distribuição da carga aceleram o desgaste.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. A peação bloqueia o movimento para a frente ou para trás da mercadoria.</t>
+          <t>A peação bloqueia o movimento para a frente ou para trás da mercadoria.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. As amarras em cruz evitam o deslocamento lateral e vertical.</t>
+          <t>As amarras em cruz evitam o deslocamento lateral e vertical.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Planeamento e rotas seguras são essenciais para prevenir roubo.</t>
+          <t>Planeamento e rotas seguras são essenciais para prevenir roubo.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. ABC da reanimação: Consciência → Via aérea → Respiração.</t>
+          <t>ABC da reanimação: Consciência → Via aérea → Respiração.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Compressão direta é o primeiro gesto para controlar hemorragia.</t>
+          <t>Compressão direta é o primeiro gesto para controlar hemorragia.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Mantém as vias aéreas desobstruídas em vítima inconsciente que respira.</t>
+          <t>Mantém as vias aéreas desobstruídas em vítima inconsciente que respira.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Máximo de 13 horas de atividade diária.</t>
+          <t>Máximo de 13 horas de atividade diária.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. 35 horas de formação contínua a cada 5 anos.</t>
+          <t>35 horas de formação contínua a cada 5 anos.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Reduz stocks ao mínimo através de entregas frequentes e precisas.</t>
+          <t>Reduz stocks ao mínimo através de entregas frequentes e precisas.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Postura correta e ajustes do banco evitam dores e fadiga.</t>
+          <t>Postura correta e ajustes do banco evitam dores e fadiga.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Obrigatório em qualquer deslocação.</t>
+          <t>Obrigatório em qualquer deslocação.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Manter o volante reto e esperar que os pneus recuperem aderência.</t>
+          <t>Manter o volante reto e esperar que os pneus recuperem aderência.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Corrige automaticamente derrapagens e perda de controlo.</t>
+          <t>Corrige automaticamente derrapagens e perda de controlo.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Menor consumo e menor manutenção.</t>
+          <t>Menor consumo e menor manutenção.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Inspeção periódica obrigatória de 2 em 2 anos.</t>
+          <t>Inspeção periódica obrigatória de 2 em 2 anos.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Parar em segurança e desligar o motor é prioridade.</t>
+          <t>Parar em segurança e desligar o motor é prioridade.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Útil para simplificar o processo com a seguradora.</t>
+          <t>Útil para simplificar o processo com a seguradora.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Tolerância zero praticamente (0,2 g/l máximo).</t>
+          <t>Tolerância zero praticamente (0,2 g/l máximo).</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Ajuda a manter velocidade constante e económica.</t>
+          <t>Ajuda a manter velocidade constante e económica.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Informa sobre congestionamentos, obras, acidentes, etc.</t>
+          <t>Informa sobre congestionamentos, obras, acidentes, etc.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Deve ser usado com segurança, sem distrair o condutor.</t>
+          <t>Deve ser usado com segurança, sem distrair o condutor.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. É um sistema de apoio à exploração da empresa.</t>
+          <t>É um sistema de apoio à exploração da empresa.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Leitura automática sem contacto.</t>
+          <t>Leitura automática sem contacto.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O ar comprimido é o meio utilizado nos travões pneumáticos de veículos pesados.</t>
+          <t>O ar comprimido é o meio utilizado nos travões pneumáticos de veículos pesados.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Só a altas temperaturas é que o catalisador consegue converter os gases tóxicos.</t>
+          <t>Só a altas temperaturas é que o catalisador consegue converter os gases tóxicos.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Líquido errado afeta todo o desempenho do sistema de travagem.</t>
+          <t>Líquido errado afeta todo o desempenho do sistema de travagem.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. A peação bloqueia o movimento para a frente ou para trás da mercadoria.</t>
+          <t>A peação bloqueia o movimento para a frente ou para trás da mercadoria.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Combina várias direções de força.</t>
+          <t>Combina várias direções de força.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O torniquete é indicado quando a compressão direta não é suficiente.</t>
+          <t>O torniquete é indicado quando a compressão direta não é suficiente.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Sequência atual: 30 compressões + 2 ventilações.</t>
+          <t>Sequência atual: 30 compressões + 2 ventilações.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Pode ser estendido para 10 horas no máximo duas vezes por semana.</t>
+          <t>Pode ser estendido para 10 horas no máximo duas vezes por semana.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Obrigatório guardar durante 2 anos para fiscalização.</t>
+          <t>Obrigatório guardar durante 2 anos para fiscalização.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Obesidade e idade avançada são fatores de risco elevados.</t>
+          <t>Obesidade e idade avançada são fatores de risco elevados.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Muitos medicamentos têm efeito sedativo e são incompatíveis com a condução.</t>
+          <t>Muitos medicamentos têm efeito sedativo e são incompatíveis com a condução.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Com técnicas corretas (mudanças suaves, uso do retardador, etc.) é possível poupar 15-25 %.</t>
+          <t>Com técnicas corretas (mudanças suaves, uso do retardador, etc.) é possível poupar 15-25 %.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Ajuda a manter velocidade constante e económica.</t>
+          <t>Ajuda a manter velocidade constante e económica.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Corrige automaticamente derrapagens e perda de controlo.</t>
+          <t>Corrige automaticamente derrapagens e perda de controlo.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Segurança em primeiro lugar.</t>
+          <t>Segurança em primeiro lugar.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Programar antes evita distrações ao volante.</t>
+          <t>Programar antes evita distrações ao volante.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Informa sobre congestionamentos, obras, acidentes, etc.</t>
+          <t>Informa sobre congestionamentos, obras, acidentes, etc.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Documentos obrigatórios para circulação internacional.</t>
+          <t>Documentos obrigatórios para circulação internacional.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Segurança em primeiro lugar – acionar alarme e pedir ajuda.</t>
+          <t>Segurança em primeiro lugar – acionar alarme e pedir ajuda.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Útil para simplificar o processo com as seguradoras.</t>
+          <t>Útil para simplificar o processo com as seguradoras.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. É o certificado internacional de seguro automóvel.</t>
+          <t>É o certificado internacional de seguro automóvel.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. ABC da reanimação: Consciência, Via Aérea, Respiração, Circulação.</t>
+          <t>ABC da reanimação: Consciência, Via Aérea, Respiração, Circulação.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O descanso diário mínimo obrigatório é de 11 horas consecutivas.</t>
+          <t>O descanso diário mínimo obrigatório é de 11 horas consecutivas.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. A inspeção periódica é obrigatória de 2 em 2 anos.</t>
+          <t>A inspeção periódica é obrigatória de 2 em 2 anos.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT: proibido segurar/manipular; permitido em viva-voz/mãos-livres (art. 82.º CE).</t>
+          <t>proibido segurar/manipular; permitido em viva-voz/mãos-livres (art. 82.º CE).</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Combinação de ritmo circadiano e tempo de condução.</t>
+          <t>Combinação de ritmo circadiano e tempo de condução.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Corrige automaticamente derrapagens e perda de controlo em tempo real.</t>
+          <t>Corrige automaticamente derrapagens e perda de controlo em tempo real.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Deixar os pneus recuperarem aderência naturalmente.</t>
+          <t>Deixar os pneus recuperarem aderência naturalmente.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Mantém velocidade constante e reduz consumo.</t>
+          <t>Mantém velocidade constante e reduz consumo.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. É crime com sanções pesadas.</t>
+          <t>É crime com sanções pesadas.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Facilita o processo com as seguradoras.</t>
+          <t>Facilita o processo com as seguradoras.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Necessário para circular no Espaço Económico Europeu.</t>
+          <t>Necessário para circular no Espaço Económico Europeu.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Sequência atual: 30 compressões + 2 ventilações.</t>
+          <t>Sequência atual: 30 compressões + 2 ventilações.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Torniquete quando a compressão direta não controla a hemorragia.</t>
+          <t>Torniquete quando a compressão direta não controla a hemorragia.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. ABC da reanimação.</t>
+          <t>A resposta correta é a opção A) Avaliar consciência → Via aérea → Respiração → Circulação. No exame CAM do IMT, esta alternativa responde corretamente à questão «O exame primário da vítima segue a regra ABC, que significa».</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Alinhamento incorreto causa desgaste assimétrico.</t>
+          <t>Alinhamento incorreto causa desgaste assimétrico.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Essencial em curvas.</t>
+          <t>A resposta correta é a opção A) As rodas girem a velocidades diferentes em curva. No exame CAM do IMT, esta alternativa responde corretamente à questão «A função do diferencial é permitir que».</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -5950,7 +5950,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Impede deslizamento para a frente/trás.</t>
+          <t>Impede deslizamento para a frente/trás.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Combina várias direções.</t>
+          <t>A resposta correta é a opção D) Todas as anteriores. No exame CAM do IMT, esta alternativa responde corretamente à questão «A amarração em cruz é eficaz contra».</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Exposição múltipla a substâncias.</t>
+          <t>Exposição múltipla a substâncias.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O direito a férias é irrenunciável por lei.</t>
+          <t>O direito a férias é irrenunciável por lei.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Obesidade e idade avançada são fatores de risco elevados.</t>
+          <t>Obesidade e idade avançada são fatores de risco elevados.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Muitos medicamentos são incompatíveis com a condução.</t>
+          <t>Muitos medicamentos são incompatíveis com a condução.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Só a altas temperaturas converte os gases tóxicos.</t>
+          <t>Só a altas temperaturas converte os gases tóxicos.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Além dos acidentes de viação, o motorista também está exposto a acidentes durante carga/descarga.</t>
+          <t>Além dos acidentes de viação, o motorista também está exposto a acidentes durante carga/descarga.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. A descida correta é sempre de costas para a via, com os 3 pontos de apoio.</t>
+          <t>A descida correta é sempre de costas para a via, com os 3 pontos de apoio.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Inexperiência + excesso de confiança = combinação perigosa.</t>
+          <t>Inexperiência + excesso de confiança = combinação perigosa.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Mais de 90% dos acidentes são causados por erro humano.</t>
+          <t>Mais de 90% dos acidentes são causados por erro humano.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Definição legal de acidente de trabalho (Código do Trabalho).</t>
+          <t>Definição legal de acidente de trabalho (Código do Trabalho).</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Proteger as vias respiratórias do frio e do vento é essencial.</t>
+          <t>Proteger as vias respiratórias do frio e do vento é essencial.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Objetos perdidos devem ser entregues na empresa.</t>
+          <t>Objetos perdidos devem ser entregues na empresa.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Definição básica de transporte.</t>
+          <t>Definição básica de transporte.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Unimodal = apenas um modo (ex: só rodoviário).</t>
+          <t>Unimodal = apenas um modo (ex: só rodoviário).</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Podem ser bilhetes simples ou passes/assina tura.</t>
+          <t>Podem ser bilhetes simples ou passes/assina tura.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Uniforme e apresentação cuidada são obrigatórios.</t>
+          <t>Uniforme e apresentação cuidada são obrigatórios.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Expresso = longo curso, poucas paragens, veículos de gama alta.</t>
+          <t>Expresso = longo curso, poucas paragens, veículos de gama alta.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Até 20 kg de bagagem por passageiro é gratuito.</t>
+          <t>Até 20 kg de bagagem por passageiro é gratuito.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Sim, mais de 90% dos acidentes são por erro humano.</t>
+          <t>Sim, mais de 90% dos acidentes são por erro humano.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Transportes + infraestruturas = desenvolvimento.</t>
+          <t>Transportes + infraestruturas = desenvolvimento.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Transportes públicos bons = menos carros na estrada = menos poluição.</t>
+          <t>Transportes públicos bons = menos carros na estrada = menos poluição.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Em Portugal, o transporte rodoviário é o mais usado.</t>
+          <t>Em Portugal, o transporte rodoviário é o mais usado.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Pode ser por conta própria ou por conta de outrem.</t>
+          <t>Pode ser por conta própria ou por conta de outrem.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Sustentabilidade = económico + social + ambiental.</t>
+          <t>Sustentabilidade = económico + social + ambiental.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Tem de ser alguém com responsabilidade efetiva na gestão.</t>
+          <t>Tem de ser alguém com responsabilidade efetiva na gestão.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Várias formas jurídicas são permitidas.</t>
+          <t>Várias formas jurídicas são permitidas.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Alvará ou licença comunitária válida até 5 anos.</t>
+          <t>Alvará ou licença comunitária válida até 5 anos.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Contrato escrito com a entidade que contrata o serviço.</t>
+          <t>Contrato escrito com a entidade que contrata o serviço.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Transportes públicos = por conta de outrem.</t>
+          <t>Transportes públicos = por conta de outrem.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Internacionais = atravessam fronteiras.</t>
+          <t>Internacionais = atravessam fronteiras.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Ambos são transportes terrestres.</t>
+          <t>Ambos são transportes terrestres.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Serviços regulares = horários e tarifas fixos.</t>
+          <t>Serviços regulares = horários e tarifas fixos.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Unipessoal = apenas um sócio.</t>
+          <t>Unipessoal = apenas um sócio.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Várias formas jurídicas são permitidas.</t>
+          <t>Várias formas jurídicas são permitidas.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O objetivo principal é otimizar operações.</t>
+          <t>O objetivo principal é otimizar operações.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Os pesados têm ângulos mortos muito maiores.</t>
+          <t>Os pesados têm ângulos mortos muito maiores.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Danos materiais = danos no veículo.</t>
+          <t>Danos materiais = danos no veículo.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Consequências humanas + materiais + financeiras.</t>
+          <t>Consequências humanas + materiais + financeiras.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. O encosto deve ficar ao nível da parte de trás da cabeça.</t>
+          <t>O encosto deve ficar ao nível da parte de trás da cabeça.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Prejuízo para trabalhador, empresa e sociedade.</t>
+          <t>Prejuízo para trabalhador, empresa e sociedade.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Deve estar bem ajustado, nem largo nem apertado.</t>
+          <t>Deve estar bem ajustado, nem largo nem apertado.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Deve usar sempre o plural (nós/empresa).</t>
+          <t>Deve usar sempre o plural (nós/empresa).</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Dano = perda pessoal ou material.</t>
+          <t>Dano = perda pessoal ou material.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Capacidade de resposta = rapidez e precisão.</t>
+          <t>Capacidade de resposta = rapidez e precisão.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Velocidade que permite controlar o veículo sempre.</t>
+          <t>Velocidade que permite controlar o veículo sempre.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Deve facilitar tudo.</t>
+          <t>A resposta correta é a opção D) Todas as alíneas são verdadeiras. No exame CAM do IMT, esta alternativa responde corretamente à questão «O motorista de uma empresa no decorrer de uma inspeção na estrada deverá».</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Os braços devem estar ligeiramente flexionados.</t>
+          <t>Os braços devem estar ligeiramente flexionados.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. A melhor postura é a que dá melhor eficácia com menos fadiga.</t>
+          <t>A melhor postura é a que dá melhor eficácia com menos fadiga.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Artéria humeral = braço.</t>
+          <t>A resposta correta é a opção B) Pressionar a artéria humeral. No exame CAM do IMT, esta alternativa responde corretamente à questão «Perante uma hemorragia num braço, o procedimento correto é».</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Todos os setores podem ser sancionados.</t>
+          <t>Todos os setores podem ser sancionados.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Exercício físico é fundamental.</t>
+          <t>Exercício físico é fundamental.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Calor excessivo no habitáculo causa sonolência.</t>
+          <t>Calor excessivo no habitáculo causa sonolência.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Todas as afirmações estão corretas.</t>
+          <t>Todas as afirmações estão corretas.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Reino Unido (Inglaterra) não está no Schengen.</t>
+          <t>Reino Unido (Inglaterra) não está no Schengen.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Espanha pertence ao Espaço Schengen.</t>
+          <t>Espanha pertence ao Espaço Schengen.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Nunca dar analgésicos sem orientação médica.</t>
+          <t>Nunca dar analgésicos sem orientação médica.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Cobrir sempre para evitar perda de calor.</t>
+          <t>Cobrir sempre para evitar perda de calor.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Nunca dar comida a feridos.</t>
+          <t>Nunca dar comida a feridos.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Empresa de transporte produz serviços.</t>
+          <t>Empresa de transporte produz serviços.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Ergonomia = postura e condições de trabalho.</t>
+          <t>Ergonomia = postura e condições de trabalho.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Piso molhado = maior risco de aquaplanagem.</t>
+          <t>Piso molhado = maior risco de aquaplanagem.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Motor desligado e quente facilita a drenagem.</t>
+          <t>Motor desligado e quente facilita a drenagem.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Motor desligado e frio para medição correta.</t>
+          <t>Motor desligado e frio para medição correta.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Correntes para cargas pesadas e pontiagudas.</t>
+          <t>Correntes para cargas pesadas e pontiagudas.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Calço não pertence à suspensão.</t>
+          <t>Calço não pertence à suspensão.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Suspensão = absorver irregularidades e estabilizar.</t>
+          <t>Suspensão = absorver irregularidades e estabilizar.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Pedal esponjoso = líquido inadequado.</t>
+          <t>Pedal esponjoso = líquido inadequado.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Binário = força rotacional sobre um eixo.</t>
+          <t>Binário = força rotacional sobre um eixo.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Consumo específico = combustível por potência.</t>
+          <t>Consumo específico = combustível por potência.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Potência = capacidade de realizar trabalho por tempo.</t>
+          <t>Potência = capacidade de realizar trabalho por tempo.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Água destilada para bateria.</t>
+          <t>Água destilada para bateria.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. 3 eixos = até 38 toneladas.</t>
+          <t>3 eixos = até 38 toneladas.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Limitador de velocidade = 85 km/h para pesados.</t>
+          <t>Limitador de velocidade = 85 km/h para pesados.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -9890,7 +9890,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Autocarro articulado 4+ eixos = 32 toneladas.</t>
+          <t>Autocarro articulado 4+ eixos = 32 toneladas.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Veículo &gt; 4 anos = inspeção anual.</t>
+          <t>Veículo &gt; 4 anos = inspeção anual.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Requisitos de acesso: idoneidade + capacidade profissional + financeira.</t>
+          <t>Requisitos de acesso: idoneidade + capacidade profissional + financeira.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Alta qualidade = 100+ km, categoria III, poucas paragens.</t>
+          <t>Alta qualidade = 100+ km, categoria III, poucas paragens.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Falta não suprida em 1 ano = caducidade do alvará.</t>
+          <t>Falta não suprida em 1 ano = caducidade do alvará.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Folha de itinerário para serviços ocasionais.</t>
+          <t>Folha de itinerário para serviços ocasionais.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Comunicar em 30 dias.</t>
+          <t>A resposta correta é a opção C) No prazo de 30 dias a contar da data da ocorrência. No exame CAM do IMT, esta alternativa responde corretamente à questão «A cessação de funções do administrador, diretor ou gerente da empresa, que assegure o requisito de capacidade profiss...».</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Balanço ou garantia bancária.</t>
+          <t>Balanço ou garantia bancária.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Não aprovação = caducidade da licença do veículo.</t>
+          <t>Não aprovação = caducidade da licença do veículo.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Várias formas jurídicas permitidas.</t>
+          <t>Várias formas jurídicas permitidas.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -10410,7 +10410,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Resposta habitualmente aceite nos testes de passageiros do exame CAM/CP. Confirme sempre com o manual da sua entidade formadora.</t>
+          <t>Resposta habitualmente aceite nos testes de passageiros do exame CAM/CP. Confirme sempre com o manual da sua entidade formadora.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Contrato escrito obrigatório.</t>
+          <t>Contrato escrito obrigatório.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Verificar sempre (acesso e exercício).</t>
+          <t>Verificar sempre (acesso e exercício).</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Várias formas de aquisição permitidas.</t>
+          <t>Várias formas de aquisição permitidas.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -10622,7 +10622,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Itinerário, frequência, paragens, categoria.</t>
+          <t>Itinerário, frequência, paragens, categoria.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Cabotagem = transportes nacionais por não residentes.</t>
+          <t>Cabotagem = transportes nacionais por não residentes.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Dístico + folha de itinerário.</t>
+          <t>Dístico + folha de itinerário.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. No pedido de acesso.</t>
+          <t>A resposta correta é a opção C) Com o pedido de acesso à atividade. No exame CAM do IMT, esta alternativa responde corretamente à questão «A comprovação do requisito de idoneidade, é exigida aos administradores diretores ou gerentes de empresas de transpor...».</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. 30 dias, sob pena de coima.</t>
+          <t>30 dias, sob pena de coima.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Interdição profissional = perda de idoneidade.</t>
+          <t>Interdição profissional = perda de idoneidade.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Serviços regulares especializados = categorias específicas.</t>
+          <t>Serviços regulares especializados = categorias específicas.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Ocasionais + regulares especializados nacionais.</t>
+          <t>Ocasionais + regulares especializados nacionais.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Municipais e intermunicipais.</t>
+          <t>Municipais e intermunicipais.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Até 20 kg gratuito.</t>
+          <t>A resposta correta é a opção B) 20 kg por passageiro. No exame CAM do IMT, esta alternativa responde corretamente à questão «É obrigatório o transporte gratuito da bagagem pessoal do passageiro, em veículos afetos a carreiras interurbanas e a...».</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Certificado para transportes particulares.</t>
+          <t>Certificado para transportes particulares.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Caduca o alvará. No exame CAM do IMT, esta alternativa responde corretamente à questão «Decorrido um ano após a falta superveniente de qualquer um dos requisitos de idoneidade, capacidade profissional e ca...».</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) É intransmissível. No exame CAM do IMT, esta alternativa responde corretamente à questão «O alvará ou licença comunitária para o exerc ício da atividade de transportes rodoviários de mercadorias por conta de...».</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) O veículo é utilizado no conjunto da sua capacidade de carga por um único expedidor. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para efeitos do Decreto -Lei n.º 257/2007, de 16 de Julho, são considerados transportes em regime de carga completa o...».</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Desde que tenha havido anterior condenação pela prática da mesma infração. No exame CAM do IMT, esta alternativa responde corretamente à questão «Com a aplicação da coima pela realização de transportes rodoviários de mercadorias por entidade diversa do titular do...».</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Duplicado ou cópia autenticada do último balanço apresentado para efeitos de IRC. No exame CAM do IMT, esta alternativa responde corretamente à questão «A prova do cumprimento do requisito de capacidade financeira, durante o exercício da atividade, pode ser feita atravé...».</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) A guia de transporte. No exame CAM do IMT, esta alternativa responde corretamente à questão «Qual dos documentos seguintes deve estar a bordo do veículo durante a realização de um transporte rodoviário de merca...».</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Um transportador celebra com outro transportador um novo contrato baseado nos direitos que lhe advêm de um primeiro contrato. No exame CAM do IMT, esta alternativa responde corretamente à questão «No âmbito do transporte rodoviário de mercadorias, há subcontratação quando».</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Nome ou denominação social, sede e número de alvará. No exame CAM do IMT, esta alternativa responde corretamente à questão «São elementos de preenchimento obrigatório pelo transportador, na guia de transporte».</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -11674,7 +11674,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Estão sujeitos a licenciamento, desde que afetos ao transporte rodoviário de mercadorias por conta de outrem. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nos termos do Decreto-Lei n.º 257/2007, de 16 de Julho, os veículos automóveis com peso bruto igual ou superior a 2,5...».</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Prestação do serviço de transporte com faturação ou recibo em regime de atividade liberal ou existência de contrato para utilização do veículo entre a empresa titular do alvará e um terceiro. No exame CAM do IMT, esta alternativa responde corretamente à questão «São considerados como  efetuados por entidade diversa do titular do alvará, os transportes em que se verifique alguma...».</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Não é necessário obter qualquer autorização ou licenciamento. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para realizar uma largada de pombos correio em Bragança, foi cedido a título gratuito, à Associação Columbófila do Po...».</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Quando se trate da recolha de mercadorias destinadas a serem agrupadas no armazém do transportador para posterior distribuição. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os transportes rodoviários de mercadorias por conta de outrem são descritos numa guia de transporte que deve acompanh...».</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Sancionamento com coima. No exame CAM do IMT, esta alternativa responde corretamente à questão «Considerando que o licenciamento dos veículos automóveis de mercadorias é uma condição de acesso ao mercado de transp...».</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -11974,7 +11974,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Caducam todas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando ocorrer a caducidade da licença para o exercício da atividade, as licenças dos veículos».</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Formular reservas na guia de transporte. No exame CAM do IMT, esta alternativa responde corretamente à questão «Na operação de carga sempre que o transportador verifique defeito na mercadoria, pode».</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Forma retangular, inscrição “TP” e indicação do número de alvará do transportador. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os veículos automóveis licenciados para o transporte rodoviário de mercadorias por conta de outrém, devem ostentar di...».</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Apenas sociedades comerciais. No exame CAM do IMT, esta alternativa responde corretamente à questão «Podem aceder ao exercício da atividade de transporte rodoviário de mercadorias por conta de outrem, através de veícul...».</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Tem um prazo de validade não superior a 5 anos, renovável mediante comprovação de que se mantêm os requisitos de acesso e de exercício à atividade. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nos termos do D ecreto-Lei n.º 257/2007, de 16 de Julho, o alvará que habilita a empresa para o exercício da atividad...».</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Por duplicado ou cópia autenticada do último balanço apresentado para efeitos do imposto sobre o rendimento das pessoas colectivas (IRC) ou garantia bancária. No exame CAM do IMT, esta alternativa responde corretamente à questão «Durante o exercício da atividade, a comprovação do requisito de capacidade financeira faz-se».</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Identificação do expedidor, do transportador e do destinatário. No exame CAM do IMT, esta alternativa responde corretamente à questão «A guia de transporte é um docum ento que prova a existência de um contrato de transporte de mercadorias por conta de ...».</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Preencher total ou parcialmente a guia de transporte, considerando -se que o faz em nome do expedidor. No exame CAM do IMT, esta alternativa responde corretamente à questão «A guia de transporte contém elementos de preenchimento obrigatório, sendo um a identificação do expedidor e do tr ans...».</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) A guia de transporte. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para efeitos de prova de que estamos perante um transporte rodoviário de merc adorias por conta de outrem,  as entida...».</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Quando se trate de recolha de mercadorias no armazém do transportador para posterior distribuição. No exame CAM do IMT, esta alternativa responde corretamente à questão «A guia de remessa exigida pela lei fi scal para controlo do Imposto sobre o Valor Acrescentado (IVA) pode substituir ...».</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Instituto da Mobilidade e dos Transportes. No exame CAM do IMT, esta alternativa responde corretamente à questão «O registo das empresas licenciadas para o exercicio da atividade de transportes rodoviarios de mercadorias por conta ...».</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Sempre que seja solicitado à empresa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os requisitos de acesso e de exercício da atividade de transportes rodoviários de mercadorias por conta de outrem, de...».</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) O infrator. No exame CAM do IMT, esta alternativa responde corretamente à questão «Numa situação de excesso de carga em que a entidade fiscalizadora determina a imobilização do veículo até que a carga...».</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Não estão abrangidos pelo regime de licenciamento na atividade de transporte rodoviário de mercadorias por conta de outrem. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os veículos aos quais estejam ligados, de forma permanente e exclusiva, equipamentos ou máquinas».</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) € 125 000. No exame CAM do IMT, esta alternativa responde corretamente à questão «mercadorias por conta de outrem A empresa XP, Ldª, deve, para início da atividade de  transporte rodoviário de mercad...».</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) € 254 000. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma empresa licenciada na atividade de transportes rodoviários de mercadorias por conta de outrem qu e no desenvolvim...».</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -12934,7 +12934,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Sempre que se verificar a caducidade do alvará ou da licença comunitária e no caso de transmissão da propriedade ou posse do veículo. No exame CAM do IMT, esta alternativa responde corretamente à questão «As licenças dos veículos afetos ao transporte rodoviário de mercadorias  por conta de outrem caducam».</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Por todos os gerentes, administradores ou diretores da sociedade. No exame CAM do IMT, esta alternativa responde corretamente à questão «O requisito de idoneidade, numa sociedade que tenha como objeto a atividade de transporte rodoviário de mercadorias p...».</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Nos veículos automóveis de mercadorias licenciados para transportes rodoviários de mercadorias por conta de outrem. No exame CAM do IMT, esta alternativa responde corretamente à questão «A colocação de distintivos de identificação - TP - em veículos de transporte de mercadorias, utilizados em regime de ...».</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Mantendo o veículo dentro das condições e recomendações do fabricante. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um condutor de um veículo pesado pode contribuir para reduzir a poluição».</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) 37 toneladas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O peso bruto máximo para os conjuntos veículo a motor-reboque de quatro eixos é de».</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) 25% do peso bruto do veículo ou conjunto de veículos. No exame CAM do IMT, esta alternativa responde corretamente à questão «O peso bruto no eixo ou eixos motores de um veículo ou conjunto de veículos não pode ser inferior a».</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -13294,7 +13294,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) 32 toneladas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O peso bruto máximo para os veículos de quatro eixos é de».</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) 32 toneladas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O peso bruto máximo de um veículo (trator e semi-reboque) com 3 eixos é de».</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) 15% do peso bruto total. No exame CAM do IMT, esta alternativa responde corretamente à questão «Num veículo que tenha mais de um eixo à retaguarda, o peso bruto que incide sobre o eixo da frente não pode ser infer...».</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) 26 toneladas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O peso bruto máximo para veículos de 3 eixos, é de».</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Verdadeira para todos os veículos pesados. No exame CAM do IMT, esta alternativa responde corretamente à questão «O peso bruto máximo dos v eículos aumenta, até determinado limite, em função do maior 'número de eixos desses veículo...».</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) A um conjunto de operações regulares, nos termos da manutenção preventiva. No exame CAM do IMT, esta alternativa responde corretamente à questão «A utilização de um veículo conduz ao desgaste e/ou a avaria de alguns dos sistemas que o constituem. A fim de manter ...».</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Garantir a integridade física dos trabalhadores intervenientes na operação, a segurança rodoviária e evitar avarias nas mercadorias transportadas. No exame CAM do IMT, esta alternativa responde corretamente à questão «A estiva ou arrumação da carga num veículo deverá obedecer a um planeamento prévio. A peação e ou travamento da carga...».</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) A carga máxima admissível, determinada pelo peso ou cubicagem máxima admitida. No exame CAM do IMT, esta alternativa responde corretamente à questão «No planeamento do enchimento da caixa de carga do veículo é imperativo considerar-se».</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -13774,7 +13774,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Preencher os espaços com madeiras, esferovite, cartão prensado ou outro tipo de materiais que absorvam os choques criados ao longo da viagem. No exame CAM do IMT, esta alternativa responde corretamente à questão «Após a estiva de uma determinada carga geral num veículo, verifico u-se a existência de espaços entre as mercadorias....».</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -13834,7 +13834,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Controlar o seu veículo todos os dias, antes da partida (pneus, luzes, travões, combustível, níveis de óleo, bateria, etc...). No exame CAM do IMT, esta alternativa responde corretamente à questão «Para garantia, quer da própria segurança, quer da segurança dos outros utentes, o condutor de um veículo de mercadori...».</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Do expedidor, do transportador e do destinatário. No exame CAM do IMT, esta alternativa responde corretamente à questão «São elementos essenciais do contrato de transporte, devendo ser obrigatoriamente descritas na guia de transporte, a s...».</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Oito horas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nos termos do estabelecido no Código do Trabalho, o período normal de trabalho diário não pode exceder».</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) No mês seguinte ao do início do trabalho. No exame CAM do IMT, esta alternativa responde corretamente à questão «A inscrição dos trabalhadores no Regime da Segurança Social deve ser efetuada».</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Trabalho a termo, certo ou incerto. No exame CAM do IMT, esta alternativa responde corretamente à questão «Regra geral, os contratos de trabalho são consensuais ou verba is, contudo a lei prevê exceções a esta regra, exigind...».</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -14134,7 +14134,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) A entidade empregadora. No exame CAM do IMT, esta alternativa responde corretamente à questão «A responsabilidade pela inscrição dos trabalhadores no Regime da Segurança Social recai sobre».</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -14194,7 +14194,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Todo o trabalho efetuado entre as 21 horas de um dia e as 9 horas do dia seguinte. No exame CAM do IMT, esta alternativa responde corretamente à questão «Considera-se período de trabalho noturno o compreendido entre».</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) 25%. No exame CAM do IMT, esta alternativa responde corretamente à questão «O período de trabalho noturno é remunerado, relativamente à retribuição fi xada para trabalho equivalente prestado du...».</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -14314,7 +14314,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Ser um acordo celebrado livremen te entre as partes contratantes, podendo ou não ser reduzido a escrito. No exame CAM do IMT, esta alternativa responde corretamente à questão «Regra geral, o contrato de trabalho subordinado caracteriza-se por».</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -14374,7 +14374,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Com a celebração do contrato de trabalho. No exame CAM do IMT, esta alternativa responde corretamente à questão «O direito a férias é adquirido pelo trabalhador».</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) A uma retribuição igual à que receberia se estivesse a trabalhar, acrescida de um montante igual a essa retribuição. No exame CAM do IMT, esta alternativa responde corretamente à questão «Durante o período de férias a retribuição do trabalhador por conta de outrem corresponde».</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -14494,7 +14494,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Exercer o direito de contratação coletiva em nome dos interesses dos seus associados. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os sindicatos, de acordo com o estipulado na Constituição da República Portuguesa, têm competência para».</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -14554,7 +14554,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Pela entidade patronal através de guia de pagamento. No exame CAM do IMT, esta alternativa responde corretamente à questão «As contribuições para a Segurança Social da responsabilidade dos trabalhadores devem ser pagas».</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) É controlado através de um livrete individual aprovado pelo organismo responsável pelas condições de trabalho. No exame CAM do IMT, esta alternativa responde corretamente à questão «O horário de trabalho de um motorista de uma empresa que conduza veículos automóveis com peso bruto inferior a 3,5 to...».</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -14674,7 +14674,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) As férias são interrompidas, desde que o trabalhador participe a doença à entidade patronal. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se o trabalhador adoecer durante o gozo das férias».</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -14734,7 +14734,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Contrato de trabalho. No exame CAM do IMT, esta alternativa responde corretamente à questão «O contrato pelo qual uma pessoa s e obriga, mediante retribuição, a prestar a sua atividade intelectual ou manual a o...».</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) O termo do prazo. No exame CAM do IMT, esta alternativa responde corretamente à questão «A caducidade é um a das formas de cessação do contrato de trabalho, que ocorre quando se verifica uma das seguintes s...».</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) No caso de ocorrer justa causa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um trabalhador pode fazer cessar o seu contrato de trabalho, sem observância de aviso prévio».</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) O comportamento culposo do trabalh ador que inviabilize  a manutenção da relação de trabalho. No exame CAM do IMT, esta alternativa responde corretamente à questão «Constitui justa causa de despedimento promovido pela entidade empregadora».</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) A conversão do contrato em contrato sem termo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se um contrato de trabalho a termo certo for celebrado sem indicação do pra zo estipulado e do motivo justificativo, ...».</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -15034,7 +15034,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Pode exercer qualquer outra atividade remunerada se a entidade patronal o autorizar a isso. No exame CAM do IMT, esta alternativa responde corretamente à questão «Durante o gozo das férias, o trabalhador».</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) 40 horas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Regra geral, o limite máximo do período normal de trabalho semanal a que um trabalhador se pode obrigar a prestar é de».</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Realiza um trabalho autónomo e apresenta o respetivo resultado. No exame CAM do IMT, esta alternativa responde corretamente à questão «Tendo um estatuto diferente do trabalhador por conta de outrem, o prestador de serviços».</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Um conjunto de trabalhadores e um conjunto de entidades patronais, através das respetivas associações sindicais e patronais. No exame CAM do IMT, esta alternativa responde corretamente à questão «O traba lho subordinado, não obstante ter subjacente uma relação individual de trabalho, pode ser regulado por conven...».</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) É considerada falta justificada. No exame CAM do IMT, esta alternativa responde corretamente à questão «A não comparência do trabalhador no local de trabalho por motivo de doença, não devidamente comprovada».</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Pelo trabalhador e pela entidade patronal. No exame CAM do IMT, esta alternativa responde corretamente à questão «A contribuição q ue incide sobre a remuneração do trabalhador, no âmbito do financiamento do regime geral da seguranç...».</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) O despedimento for considerado injustificado pelo trabalhador e pelo sindicato. No exame CAM do IMT, esta alternativa responde corretamente à questão «O trabalhador, após ter sido objeto de despedimento promovido pela entidade empregadora, tem direito a ser reintegrad...».</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) A realização de transportes nacionais por transportadores não residentes. No exame CAM do IMT, esta alternativa responde corretamente à questão «No âmbito de um transporte rodoviário de mercadorias, cabotagem é».</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) 18 toneladas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O peso máximo autorizado de um reboque de 2 eixos é de».</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -15574,7 +15574,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) 1 ano. No exame CAM do IMT, esta alternativa responde corretamente à questão «De acordo com o Regulamento (CE) nº 561/2006, do Parlamento Europeu e do Conselho, de 15 de março, Conselho, de 20 de...».</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Cuja velocidade máxima autorizada ultrapasse os 40 km/hora. No exame CAM do IMT, esta alternativa responde corretamente à questão «É obrigatória a instalação e utilização do tacógrafo nos veículos destinados ao transporte rodoviário de mercadorias».</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Particular ou por conta própria. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um transporte em que as mercadorias transportadas, tenham sido compradas pelo proprietário do veículo e este for por ...».</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -15754,7 +15754,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Idoneidade, capacidade profissional e capacidade financeira. No exame CAM do IMT, esta alternativa responde corretamente à questão «As empresas que pretendam aceder ao transporte rodoviário de mercadorias por conta de outrem devem reunir os requisitos».</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) 14 dias úteis de férias. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se um trabalhador for contratado em 1/03/2009, no dia 2/10/2009, tem direito a gozar».</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -15874,7 +15874,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) 6 metros. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os veículos devem ser sinalizad os lateralmente com luzes ou reflectores de cor âmbar, sempre que o respetivo comprim...».</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -15934,7 +15934,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) 18 meses. No exame CAM do IMT, esta alternativa responde corretamente à questão «A duração máxima de um contrato de trabalho a termo certo, incluindo renovações, com um trabalhador à procura do prim...».</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -15994,7 +15994,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Tiver concluído a escolaridade obrigatória e se tratar de trabalhos leves. No exame CAM do IMT, esta alternativa responde corretamente à questão «O menor com idade inferior a 16 anos não pode ser contratado para realizar uma atividade remunerada prestada com auto...».</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) 90 dias. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nos contratos por tempo indeterminado, para a generalidade dos trabalhadores, o período experimental tem a seguinte d...».</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Se destinarem ao transporte de determinadas categorias de passageiros, com exclusão de  outros, nomeadamente os estudantes entre o domicílio e a escola. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os serviços regulares especializados de transporte coletivo de passageiros, em veículos pesados, caracterizam-se por».</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -16174,7 +16174,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Automóveis de passageiros com lotação até 9 lugares e peso bruto superior a 5 ton.. No exame CAM do IMT, esta alternativa responde corretamente à questão «transportes existentes Na classificação europeia de veículos, a categoria M1 corresponde a».</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Estão obrigatoriamente sujeitos à forma escrita. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os contratos de trabalho a termo».</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -16294,7 +16294,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Pela entidade patronal, no mês seguinte aquele a que disserem respeito. No exame CAM do IMT, esta alternativa responde corretamente à questão «O pagamento à Segurança Social das contrib uições dos trabalhadores por conta de outrém deve ser efetuado».</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -16354,7 +16354,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) É considerada falta justificada. No exame CAM do IMT, esta alternativa responde corretamente à questão «A ausência do trabalhador do local de trabalho, por motivo de doença».</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) O tribunal decidir que o despedimento é ilícito. No exame CAM do IMT, esta alternativa responde corretamente à questão «Após ter sido objeto de despedimento promovido pela entidade empregadora, o trabalhador tem direito a ser reintegrado...».</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Capacidade Profissional. No exame CAM do IMT, esta alternativa responde corretamente à questão «A capacidade técnica ou profissional, como requisito de acesso à atividade de transportes rodoviários de mercadorias ...».</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) 2 anos. No exame CAM do IMT, esta alternativa responde corretamente à questão «A interdição do exercício da actividade de transportes rodoviários de mercadorias por conta de outrém, como sanção ac...».</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Estar legalmente proibidos do exercício do comércio. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para efeito de comprovação do requisito de idoneidade no acesso e exercício da atividade de transportes rodoviários d...».</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -16654,7 +16654,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Não está sujeito a licenciamento na atividade de transporte público rodoviário de mercadorias por conta de outrem. No exame CAM do IMT, esta alternativa responde corretamente à questão «O transporte de envios postais, realizado no âmbito da atividade de prestador de serviços postais».</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) 15 dias. No exame CAM do IMT, esta alternativa responde corretamente à questão «conta de outrem O contrato de trabalho a termo certo c aduca no final do prazo estipulado desde que o empregador comu...».</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Para satisfação de necessidades temporárias da empresa e pelo período estritamente necessário. No exame CAM do IMT, esta alternativa responde corretamente à questão «O contrato de trabalho a termo certo pode ser celebrado».</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -16834,7 +16834,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) 5 dias. No exame CAM do IMT, esta alternativa responde corretamente à questão «As faltas justificadas, quando sejam previsíveis,  devem ser comunicadas ao empregador com a antecedência mínima de».</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -16894,7 +16894,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Não inferior a uma hora, nem superior a duas horas. No exame CAM do IMT, esta alternativa responde corretamente à questão «A jornada de trabalho diária deve ser interrompida por um intervalo de descanso, de duração».</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Tem direito a gozar dois dias úteis de férias por cada mês completo de duração do contrato. No exame CAM do IMT, esta alternativa responde corretamente à questão «O trabalhador admitido com contrato cuja duração total não atinja seis meses».</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) 2 membros. No exame CAM do IMT, esta alternativa responde corretamente à questão «Numa empresa que tenha 60 trabalhadores sindicalizados, o número máximo de delegados sindicais que beneficiam do regi...».</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -17074,7 +17074,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Entre as 22 horas de um dia e as sete horas do dia seguinte. No exame CAM do IMT, esta alternativa responde corretamente à questão «Na ausência de fixação por instrumento de regulamentação coletiva de trabalho, considera -se período de trabalho notu...».</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) 30 dias por ano. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para prestar assistência inadiável e imprescindível, em caso de doença ou acidente, a filhos, adotados ou a enteados ...».</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -17194,7 +17194,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Cinco dias úteis seguidos, obrigatoriamente gozados na primeira semana a seguir ao nascimento do filho. No exame CAM do IMT, esta alternativa responde corretamente à questão «De acordo com o Código do Trabalho, a licença por paternidade, correspondente a».</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -17254,7 +17254,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Início do período experimental. No exame CAM do IMT, esta alternativa responde corretamente à questão «de avaliação Nos termos do Código do Trabalho, a antiguidade dos trabalhadores é contada a partir do».</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -17314,7 +17314,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Quando se trate de recolha de me rcadoria destinada a ser agrupada no armazém do transportador para posterior distribuição. No exame CAM do IMT, esta alternativa responde corretamente à questão «A guia de remessa exigida pela lei fiscal para controlo do imposto sobre o valor acrescentado (IVA) pode substituir a...».</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Por duplicado ou cópia autenticada do último balanço apresentado para efeitos de IRC. No exame CAM do IMT, esta alternativa responde corretamente à questão «A comprovação do requisito de capacidade financeira de exercício de uma empresa de transportes organizada sob a forma...».</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Automóveis de passageiros com lotação até 9 lugares e peso bruto superior a 5 ton.. No exame CAM do IMT, esta alternativa responde corretamente à questão «Na classificação europeia de veículos, a categoria m2 corresponde a».</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -17494,7 +17494,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Cumpre os requisitos de acesso à at ividade (idoneidade, capacidade profissional e capacidade financeira). No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma sociedade por quotas, unipessoal que pretenda obter o alvará para o exercício da atividade de transporte pú blico...».</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -17554,7 +17554,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) A caducidade da respetiva licença. No exame CAM do IMT, esta alternativa responde corretamente à questão «rendimento das pessoas coletivas (IRC) ou por garantia bancária A não aprovação em inspeção periódica de um veículo a...».</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -17614,7 +17614,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Resposta habitualmente aceite nos testes de passageiros do exame CAM/CP. Confirme sempre com o manual da sua entidade formadora.</t>
+          <t>Resposta habitualmente aceite nos testes de passageiros do exame CAM/CP. Confirme sempre com o manual da sua entidade formadora.</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -17674,7 +17674,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Itinerário, frequência, paragens, categoria.</t>
+          <t>Itinerário, frequência, paragens, categoria.</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -17734,7 +17734,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Cabotagem. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os serviços de transporte nacionais realizados por t ransportadores não estabelecidos no território português, design...».</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Dístico + folha de itinerário.</t>
+          <t>Dístico + folha de itinerário.</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. No pedido de acesso.</t>
+          <t>A resposta correta é a opção C) Com o pedido de acesso à atividade. No exame CAM do IMT, esta alternativa responde corretamente à questão «A comprovação do requisito de idoneidade , é exigida aos administradores diretores ou geren tes de empresas de transp...».</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -17914,7 +17914,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Interdição profissional = perda de idoneidade.</t>
+          <t>Interdição profissional = perda de idoneidade.</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -17974,7 +17974,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Serviços regulares e serviços expresso. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nos termos do Regime Jurídico do Serviço Público de Tra nsportes de Passageiros (RIISPTP) as carreiras de serviço púb...».</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Nenhuma das anteriores respostas é correcta. No exame CAM do IMT, esta alternativa responde corretamente à questão «O binário do motor é».</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -18094,7 +18094,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) O mais baixo possível. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para aumentar a estabilidade de circulação dos veículos pesados, torna -se conveniente que o centro de gravidade do c...».</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -18154,7 +18154,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Implica na instabilidade do veículo e diminui a eficácia do seu sistema de travagem. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se concentrar a carga a  transportar no limite traseiro da caixa de carga de um veículo pesado de dois eixos».</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Suportar o motor, a carroçaria e a caixa de carga do veículo. No exame CAM do IMT, esta alternativa responde corretamente à questão «A função do quadro ou chassis nos automóveis, é de».</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -18274,7 +18274,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Transformar os gases provenientes do motor em produtos menos poluentes. No exame CAM do IMT, esta alternativa responde corretamente à questão «A função do catalisador catalítico aplicado ao sistema de escape dos automóveis tem como função».</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -18334,7 +18334,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) São muito prejudiciais para meio ambiente e para o ser humano. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os gases resultantes da combustão e libertados para a atmosfera pelos veículos a motor».</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -18394,7 +18394,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) O motor está a poluir mais que o normal, porque está a consumir óleo em excesso. No exame CAM do IMT, esta alternativa responde corretamente à questão «Verificando-se frequente necessidade de acrescentar óleo no motor, pode concluir-se que».</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -18454,7 +18454,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Verificar se esta está bem fixa à carroçaria e se o líquido se encontra a cobrir as placas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um dos cuidados a ter com as baterias é».</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Condutor. No exame CAM do IMT, esta alternativa responde corretamente à questão «A manutenção dos pneumáticos de uma viatura compete sempre ao».</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -18574,7 +18574,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) 4 kg sem travar o travão de pé. No exame CAM do IMT, esta alternativa responde corretamente à questão «No painel de instrumentos de um pesado em andamento, os manómetros de ar devem indicar uma pressão de».</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Sempre que possível, utilizar com a mudança mais alta engrenada, com o motor no binário máximo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para economizar combustível e diminuir a poluição dos motores o condutor deve».</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -18694,7 +18694,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Verificar se a alavanca da caixa automática se encontra na posição D. No exame CAM do IMT, esta alternativa responde corretamente à questão «Ao colocar o motor de um veículo pesado a trabalhar o condutor deve».</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Gerando um campo magnético com a produção de correntes induzidas que reagindo se opõem ao movimento dos dois discos montados no veio da transmissão. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nos veículos pesados, de um modo geral, o retardador ou travão eléctrico funciona».</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -18814,7 +18814,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Obrigatoriamente por ação mecânica. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nos veículos pesados com sistema pneumático da travagem o travão de mão atua».</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -18874,7 +18874,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Inicia uma longa descida de inclinação acentuada. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se o veiculo está equipado com o retardador eléctrico (travão auxiliar elétrico), o seu condutor deve ligá - lo sempr...».</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -18934,7 +18934,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Fuga na tubagem do circuito hidráulico. No exame CAM do IMT, esta alternativa responde corretamente à questão «Num veiculo com travões de disco equipado com o sistema de travagem tipo hi dráulico, uma falta súbita de travões pod...».</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -18994,7 +18994,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Se o líquido refrigerante está entre os parâmetros recomendados. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um dos vários cuidados que o condutor deve ter antes de iniciar uma viagem, é verificar, nomeadamente, se».</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) O nível de óleo de lubrificação do motor está muito baixo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando um automóvel pesado descreve uma cu rva apertada ou quando trava de emergência, se a luz avisadora da lubrific...».</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -19114,7 +19114,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Não esforçar o motor. No exame CAM do IMT, esta alternativa responde corretamente à questão «O objetivo da condução dentro da “faixa verde “ é».</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -19174,7 +19174,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) 4 ciclos. No exame CAM do IMT, esta alternativa responde corretamente à questão «O ciclo de operação de um motor diesel de um veículo pesado, é composto de».</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -19234,7 +19234,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Admissão, compressão, explosão/expansão, escape. No exame CAM do IMT, esta alternativa responde corretamente à questão «As fases do ciclo do motor diesel num veículo pesado são».</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -19294,7 +19294,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Em caso de falha do sistema, possa ainda existir algum poder de travagem. No exame CAM do IMT, esta alternativa responde corretamente à questão «O tipo de sistema de travagem cruzado serve para».</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -19354,7 +19354,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Reduzir e utilizar os meios de travagem auxiliar. No exame CAM do IMT, esta alternativa responde corretamente à questão «Numa eminente falha de travões o motorista deverá».</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -19414,7 +19414,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Detetar a origem do problema e a atitude a tomar. No exame CAM do IMT, esta alternativa responde corretamente à questão «No caso de uma baixa súbita no nível do fluido de travões, o motorista deverá».</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Que permite desacoplar o motor do resto da transmissão. No exame CAM do IMT, esta alternativa responde corretamente à questão «A embraiagem é um tipo de mecanismo que».</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -19534,7 +19534,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Que as rodas motrizes rolem a diferentes velocidades. No exame CAM do IMT, esta alternativa responde corretamente à questão «A função de um diferencial consiste em permitir».</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -19594,7 +19594,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Longitudinal e atrás do mesmo. No exame CAM do IMT, esta alternativa responde corretamente à questão «A localização de uma caixa de velocidades num veículo pesado é, respetivamente ao motor visto de frente».</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Aumentar a curva de binário do motor. No exame CAM do IMT, esta alternativa responde corretamente à questão «O objetivo do conversor de binário é».</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -19714,7 +19714,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Antes do binário máximo. No exame CAM do IMT, esta alternativa responde corretamente à questão «No que respeita a curva de consumo específico, para um motor de um veículo pesado, o consumo de combustível é menor».</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -19774,7 +19774,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) O uso de velas de ignição. No exame CAM do IMT, esta alternativa responde corretamente à questão «A principal diferença entre um motor a diesel e um a gasolina é».</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -19834,7 +19834,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Retirar a humidade ao ar. No exame CAM do IMT, esta alternativa responde corretamente à questão «Num sistema de travagem pneumática, a função do secador de ar é».</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Sempre que possível, andar com a mudança mais alta engrenada e com o motor no binário máximo. No exame CAM do IMT, esta alternativa responde corretamente à questão «A zona de utilização óptima do conta-rotações consegue-se».</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -19954,7 +19954,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Terceiro tempo. No exame CAM do IMT, esta alternativa responde corretamente à questão «O motor de combustão difere do motor de explosão no».</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Aumentar o controlo e a eficiência de travagem durante as descidas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O retardador é um travão auxiliar que trabalha sem utilizar o sistema n ormal de travagem tendo como principal função».</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -20074,7 +20074,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Tirar antecipadamente o pé do acelerador. No exame CAM do IMT, esta alternativa responde corretamente à questão «O aproveitamento da inércia do veículo irá traduzir-se num menor consumo pelo que, o condutor deverá».</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Obrigatoriamente por acção mecânica. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nos veículos pesados com sistema pneumático da travagem o travão de mão actua».</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -20194,7 +20194,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Fuga na tubagem do circuito hidráulico. No exame CAM do IMT, esta alternativa responde corretamente à questão «Num veiculo com travões de disco equipado com o sistema de travagem tipo hidráulico, uma falta súbita de travões pode...».</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -20254,7 +20254,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Evitar o bloqueio das rodas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema de travagem ABS utilizado nos autocarros destina-se a».</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Radiador, válvula termostática, bomba de água, canais de refrigeração no interior do bloco de cilindros e canais de refrigeração na cabeça do motor. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema de refrigeração por líquido refrigerante de um motor é composto por».</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Pneumático. No exame CAM do IMT, esta alternativa responde corretamente à questão «cilindros e canais de refrigeração na cabeça do motor Os veículos de elevado peso bruto utilizam sistema de travagem».</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -20434,7 +20434,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Ar. No exame CAM do IMT, esta alternativa responde corretamente à questão «Durante a admissão de um motor de ciclo diesel, entra».</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -20494,7 +20494,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Ao binário máximo do motor. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um baixo consumo de combustível é conseguido utilizando o motor na rotação a que equivale».</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -20554,7 +20554,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Bomba injectora, common rail ou injector-bomba. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema de alimentação de um motor diesel pode adotar as seguintes opções».</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -20614,7 +20614,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Escape e tem por função a reutilização dos gases de escape para compress ão do ar de admissão. No exame CAM do IMT, esta alternativa responde corretamente à questão «O EGR está integrado no sistema de».</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -20674,7 +20674,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Depende do valor binário e da rotação a que o motor está a trabalhar. No exame CAM do IMT, esta alternativa responde corretamente à questão «A potência de um motor».</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Da rotação do motor e da velocidade do veículo e da posição do acelerador. No exame CAM do IMT, esta alternativa responde corretamente à questão «A seleção da mudança num veículo equipado com caixa de velocidades automática depende».</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -20794,7 +20794,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Monitorizar a rotação de cada roda, a inclinação do veículo e a aceleração, atuando em conformidade a fim de estabilizar o veículo em situações de instabilidade. No exame CAM do IMT, esta alternativa responde corretamente à questão «O controlo de estabilidade tem por função».</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -20854,7 +20854,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Circular com uma mudança baixa de modo a utilizar o motor como travão. No exame CAM do IMT, esta alternativa responde corretamente à questão «Numa descida de acentuada inclinação o condutor deve».</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -20914,7 +20914,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Transporte terrestre, transporte aquaviário, transporte aéreo e transporte tubular ou dutoviário. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os modos de transportes dividem-se em».</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -20974,7 +20974,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) A responsabilidade social de uma empresa de transportes incide sobre os seus clientes, e não sobre os seus trabalhadores. No exame CAM do IMT, esta alternativa responde corretamente à questão «Atendendo aos princípios de organização e funcionamento de uma empresa de transportes de mercadorias, indique qual da...».</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) A atividade transitária só pode ser exercida por empresas titulares de alvará emitido pelo IMT. No exame CAM do IMT, esta alternativa responde corretamente à questão «Assinale a afirmação verdadeira».</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Matriculados, que não se encontrem avariados ou sinistrados, nem se destinem a substituir veículos sinistrados ou avariados. No exame CAM do IMT, esta alternativa responde corretamente à questão «Não podem ser transportados por empresas prestadoras de serviços através de veículos tipo pronto - socorro os veículos».</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) No transporte multimodal há um único documento cont ratual para todo o transporte qualquer que seja o número de modos envolvidos, enquanto no intermodal podem existir vários documentos contratuais mas o transporte é realizado sem rutura de carga. No exame CAM do IMT, esta alternativa responde corretamente à questão «A diferença entre transporte intermodal e transporte multimodal é que».</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -21214,7 +21214,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Os transportes rodoviários de mercadorias por conta de outrem são mais eficientes que os transportes por conta própria. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma das medidas da eficiência nos transportes é dada pela percentagem de quilómetros em carga. Quanto a este aspeto, ...».</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -21266,7 +21266,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) No conjunto da sua capacidade de carga por um único expedidor. No exame CAM do IMT, esta alternativa responde corretamente à questão «Transporte em regime de carga completa é o transporte por conta de outrem em que o veículo é utilizado».</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Isotérmico, com uma fonte de frio, que permite regular a temperatura até -20º C. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um veículo de temperatura controlada refrigerado é um veículo».</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -21386,7 +21386,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Alvará, emitido pelo IMTT. No exame CAM do IMT, esta alternativa responde corretamente à questão «horas, constante ou superior a 12ºC Uma empresa de aluguer de veículos sem condutor é titulada por».</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) A poluição atmosférica, os acidentes, os riscos de alterações climatéricas, o ruído e os custos para a natureza e para a paisagem. No exame CAM do IMT, esta alternativa responde corretamente à questão «Pode dizer-se que os componentes dos custos externos dos transportes são».</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -21506,7 +21506,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Maior rapidez (porta-a-porta). No exame CAM do IMT, esta alternativa responde corretamente à questão «natureza e para a paisagem Das vantagens do transporte rodoviário de mercadorias, pode-se assinalar».</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -21566,7 +21566,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Necessidade de transbordo para chegar junto do cliente final. No exame CAM do IMT, esta alternativa responde corretamente à questão «Das desvantagens do transporte ferroviário de mercadorias pode assinalar-se».</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Ideal para o envio de mercadorias com pouco peso e volume. No exame CAM do IMT, esta alternativa responde corretamente à questão «Das vantagens do transporte aéreo de mercadorias pode-se assinalar».</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Prazos e entregas atempadas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os carregadores valorizam, sobretudo».</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -21746,7 +21746,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Triagem, Recolha, distribuição secundária, reporting, distribuição primária. No exame CAM do IMT, esta alternativa responde corretamente à questão «As sub-operações da “Operação de Transporte” devem seguir esta ordem».</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -21806,7 +21806,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) O retorno das embalagens vazias, produtos danificados ou obsoletos para recuperação ou reciclagem.. No exame CAM do IMT, esta alternativa responde corretamente à questão «Logística inversa é».</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -21866,7 +21866,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Redução imediata da necessidade de stock. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma das principais vantagens do “Just in Time” é».</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -21926,7 +21926,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Transporte público ou por conta de outrem. No exame CAM do IMT, esta alternativa responde corretamente à questão «O transporte rodoviário de me rcadorias realizado como actividade empresarial, cujo acesso é condicionado, no que diz...».</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -21986,7 +21986,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Transporte em regime de carga completa. No exame CAM do IMT, esta alternativa responde corretamente à questão «O tipo de serviço prestado quando se afecta um veículo em exclusividade a um em expedidor, em que todas as operações ...».</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -22046,7 +22046,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Transporte a granel. No exame CAM do IMT, esta alternativa responde corretamente à questão «O transporte de matérias sólidas ou de objectos não embalados, em veículos ou contentores, denomina-se por».</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -22106,7 +22106,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Grande flexibilidade de carga e de destinos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Das afirmações seguintes, indique a que melhor se identifica com o transporte rodoviário».</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -22166,7 +22166,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) A cada indivíduo o equilíbrio entre as exigências da tarefa e suas capacidades individuais. No exame CAM do IMT, esta alternativa responde corretamente à questão «A introdução dos princípios da ergonomia permite».</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Remete para dois tipos de interacção: as acções sobre o veículo e entre o condutor e os outros utentes da via. No exame CAM do IMT, esta alternativa responde corretamente à questão «A interacção homem-máquina na condução de veículos».</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Sempre que o foco de desvio da atenção é interno. No exame CAM do IMT, esta alternativa responde corretamente à questão «utentes da via A atenção é uma função cognitiva fundamental na tarefa da condução. Considera-se inatenção».</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -22346,7 +22346,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Zonas não urbanas. No exame CAM do IMT, esta alternativa responde corretamente à questão «pensamentos A fadiga na condução é responsável por inúmeros acidentes, podendo aparecer mais frequentemente na conduç...».</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -22406,7 +22406,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) O stress, a postura sentada prolongada, a manipulação de cargas e o ruído. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os fatores de maior risco inerentes à profissão de motorista são».</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -22466,7 +22466,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Negativamente, uma vez que aumenta o tempo de reacção. No exame CAM do IMT, esta alternativa responde corretamente à questão «O álcool, medicamentos, cafeína podem alterar o comportamento do condutor».</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -22526,7 +22526,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Devem fazer-se horários de refeições irregulares. No exame CAM do IMT, esta alternativa responde corretamente à questão «Na profissão de motorista uma alimentação saudável pode contribuir entre outros aspeto s para uma melhoria na produti...».</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -22586,7 +22586,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) A afirmação é correta pois drogas e determinados medicamentos como os relaxantes interferem na condução. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os motoristas devem ter especial atenção ao consumo de substâncias, na medida que podem influenciar a tarefa da condução».</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -22646,7 +22646,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Um efeito semelhante ao consumo de bebidas alcoólicas. No exame CAM do IMT, esta alternativa responde corretamente à questão «A fadiga e a sonolência têm sobre a condução».</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -22706,7 +22706,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Três tipos de atividades: perceptiva, cognitiva e motora. No exame CAM do IMT, esta alternativa responde corretamente à questão «forte A condução de um veículo comporta».</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -22766,7 +22766,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Com o veículo parado. No exame CAM do IMT, esta alternativa responde corretamente à questão «A inserção de dados num sistema de navegação (GPS) deve ser realizada».</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -22826,7 +22826,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Um permanente processamento de informação num envolvimento dinâmico e interações com os restantes utentes da via, de modo a permitir a tomada de decisão em tempo útil. No exame CAM do IMT, esta alternativa responde corretamente à questão «A tarefa da condução impõe».</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -22886,7 +22886,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Um permanente processamento de informação num envolvimento dinâmico e interações com os restantes utentes da via, de modo a permitir a tomada de decisão em tempo útil. No exame CAM do IMT, esta alternativa responde corretamente à questão «A tarefa da condução impõe».</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) São da responsabilidade da entidade patronal, devendo os próprios motoristas gerir a sua saúde, adoptando comportamentos em prol de uma vida saudável. No exame CAM do IMT, esta alternativa responde corretamente à questão «As condições para manutenção da saúde física e psicológica dos motoristas».</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -23006,7 +23006,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Dois tipos de interações: interações sociais e interação homem-máquina. No exame CAM do IMT, esta alternativa responde corretamente à questão «Durante a condução verificam-se».</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -23066,7 +23066,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) De comportamentos habituais, cometidos regularmente e que se torna m práticas automáticas e frequentemente toleradas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Algumas das transgressões cometidas durante a condução resultam».</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -23126,7 +23126,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Riscos psicossociais, riscos biológicos, riscos físicos ambientais, riscos biológicos e riscos derivados da manutenção da postura sentada. No exame CAM do IMT, esta alternativa responde corretamente à questão «A profissão de motorista tem inerentes».</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -23186,7 +23186,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Interferem com a segurança da condução. No exame CAM do IMT, esta alternativa responde corretamente à questão «As distrações e inatenções durante a tarefa de condução são fatores que».</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -23246,7 +23246,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Não, qualquer que seja a quantidade ingerida tem efeito negativo na condução. No exame CAM do IMT, esta alternativa responde corretamente à questão «Comente a afirmação: Só quando bebo em excesso é que corro riscos se conduzir».</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -23306,7 +23306,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Dormir, nem que seja por um pequeno período de tempo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando estou cansado devo».</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Todas as situações anteriores. No exame CAM do IMT, esta alternativa responde corretamente à questão «Podem ser indicadores de stress».</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -23426,7 +23426,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Refeições substanciais para não ter que conduzir de “barriga vazia”. No exame CAM do IMT, esta alternativa responde corretamente à questão «Indique quais os fatores que diminuem o risco de fadiga».</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -23486,7 +23486,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Dificultar de avaliação das distâncias. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os efeitos do álcool no cérebro são».</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT: proibido segurar/manipular; permitido em viva-voz/mãos-livres.</t>
+          <t>proibido segurar/manipular; permitido em viva-voz/mãos-livres.</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -23606,7 +23606,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Todas as respostas anteriores estão corretas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quais são os principais sintomas da fadiga?».</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -23666,7 +23666,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) 7 Grupos de Alimentos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Por quantos grupos de alimentos é constituída a Nova Roda de alimentos?».</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -23726,7 +23726,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) O grupo que deve ser consumido em maior quantidade diária é o dos cereais, derivados e tubérculos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Relativamente à Roda dos Alimentos».</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -23786,7 +23786,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Consumir alimentos com muita gordura regularmente. No exame CAM do IMT, esta alternativa responde corretamente à questão «Não é uma recomendação para uma alimentação saudável».</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -23846,7 +23846,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Alcoolemia acima de 0,5 g/l é frequentemente mortal. No exame CAM do IMT, esta alternativa responde corretamente à questão «Assinale a afirmação falsa».</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -23906,7 +23906,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Aumento do tempo de reação. No exame CAM do IMT, esta alternativa responde corretamente à questão «reação e de concentração Alguns medicamentos podem provocar».</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Igual ou superior a 0,5 g/l. No exame CAM do IMT, esta alternativa responde corretamente à questão «Considera-se condução sob efeito do álcool, quando o condutor apresenta uma taxa de álcool no sangue».</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -24026,7 +24026,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Enchidos e carnes fumadas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O colesterol é provocado principalmente pela ingestão de».</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -24086,7 +24086,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Técnicas para a prevenção de ac identes de trabalho, quer eliminando condições inseguras do ambiente, quer educando para a prática de atitudes preventivas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Entende-se por segurança no trabalho um conjunto de».</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -24146,7 +24146,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Triangular, pictograma negro, sobre fundo amarelo e margem negra. No exame CAM do IMT, esta alternativa responde corretamente à questão «profissionais A sinalização de perigo visa advertir para uma situação objeto ou ação susceptível de dano ou lesão pes...».</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -24206,7 +24206,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Contraída por um trabalhador em razão especificamente do seu exercício profissional. No exame CAM do IMT, esta alternativa responde corretamente à questão «Entende-se por doença profissional a doença».</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -24266,7 +24266,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) As interações entre os seres humanos e os outros elementos de um sistema como intuito de otimizar o sistema homem – trabalho. No exame CAM do IMT, esta alternativa responde corretamente à questão «A ergonomia é uma disciplina científica que estuda».</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT: permitido em viva-voz/mãos-livres.</t>
+          <t>permitido em viva-voz/mãos-livres.</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Parar 10 a 15 minutos de todas as 2 ou 3 horas de condução, ou então após 150 km. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para evitar a fadiga, aconselha-se».</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -24446,7 +24446,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Pressões de tempo relacionadas com horário de trabalho ou prazos de entrega de mercadorias. No exame CAM do IMT, esta alternativa responde corretamente à questão «Consideram-se situações indutoras de stress».</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -24506,7 +24506,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Alargar a base de sustentação, colocar o objeto o mais próximo possível  do corpo e flectir os joelhos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Considera-se como uma boa postura no levantamento de uma carga».</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -24566,7 +24566,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Manter as costas o mais vertical possível fletindo as pernas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Ao fazer o levantamento manual de uma carga deve».</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -24626,7 +24626,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Na posição sentada, a postura, ligeiramente inclinada para frente, é mais natural e menos fatigante que a ereta. O assento deve permitir mudanças frequente s de postura, para retardar o aparecimento da fadiga. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma má  postura corporal poderá implicar várias consequências no trabalhador. Assinale a afirmação correta».</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -24686,7 +24686,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) A perda de controlo do veículo, em curva, é, quase sempre, originada por inabilidade do condutor ou por velocidade excessiva para as condições do veículo e da via. No exame CAM do IMT, esta alternativa responde corretamente à questão «Considerando a influência dos fatores humanos na condução, indique qual das seguintes afirmações é verdadeira».</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -24746,7 +24746,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Uma alimentação saudável e equilibrada é fundamental na prevenção de certas doenças (obesidade, doenças cardiovasculares, diabetes, certos tipo de cancro). No exame CAM do IMT, esta alternativa responde corretamente à questão «Indique qual das afirmações é a verdadeira».</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -24806,7 +24806,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Radiações Ópticas (Infra-vermelho, Visível e Ultra Violetas). No exame CAM do IMT, esta alternativa responde corretamente à questão «As principais radiações a que os condutores de veículos pesados de passageiros e de mercadorias estão expostos são».</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -24866,7 +24866,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Todas as respostas anteriores estão corretas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O assento do motorista deve».</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -24926,7 +24926,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Promover uma convivência pacífica e harmoniosa entre condutores e peões. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para minimizar os efeitos do stress posso».</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -24986,7 +24986,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Implica sempre não comer determinados alimentos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma alimentação saudável e equilibrada».</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -25046,7 +25046,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Provoca redução efetiva das capacidades necessárias para conduzir. No exame CAM do IMT, esta alternativa responde corretamente à questão «O consumo de álcool».</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -25106,7 +25106,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Tem influência na condução, e por isso deve ser regulado por um médico. No exame CAM do IMT, esta alternativa responde corretamente à questão «O uso de medicamentos».</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -25166,7 +25166,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Todas as respostas anteriores estão correctas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Sob o efeito de drogas, um motorista».</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -25226,7 +25226,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Devem estar colocados de forma a minimizar os impactos na condução. No exame CAM do IMT, esta alternativa responde corretamente à questão «O uso de sistemas de comunicação e informação embarcados».</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -25286,7 +25286,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Tem impacto na prestação de um serviço de qualidade. No exame CAM do IMT, esta alternativa responde corretamente à questão «A higiene, saúde e segurança no trabalho».</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -25346,7 +25346,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Parar o motor sempre que a demora se preveja ser superior a 1 minuto. No exame CAM do IMT, esta alternativa responde corretamente à questão «Na chegada ao terminal do serviço, caso o veículo se encontre sem problemas, a atuação do Motorista deve ser».</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -25406,7 +25406,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) No regime de rotações económicas do motor. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma redução de apenas 5% de consumo de combustível representa poupança energética e evita a emissão de várias tonelad...».</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -25466,7 +25466,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Ao binário máximo do motor. No exame CAM do IMT, esta alternativa responde corretamente à questão «O regime de rotações que permite ao motor desenvolver maior força com menor consumo corresponde».</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -25526,7 +25526,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Aproveitar a força da inércia nas descidas. No exame CAM do IMT, esta alternativa responde corretamente à questão «É um comportamento de condução económica».</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -25586,7 +25586,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Todas as afirmações anteriores. No exame CAM do IMT, esta alternativa responde corretamente à questão «Conduzir economicamente significa».</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -25646,7 +25646,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Todas as causas referidas nas alíneas anteriores “A escolha correcta dos pneus do veículo e a respetiva manutenção, influenciam o consumo de. No exame CAM do IMT, esta alternativa responde corretamente à questão «As principais causas para o aumento do consumo de combustível são».</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -25706,7 +25706,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Sim é importante, pois os dois fatores influenciam os consumos. No exame CAM do IMT, esta alternativa responde corretamente à questão «“A escolha correcta dos pneus do veículo e a respetiva manutenção, influenciam o consumo de combustível”. Identifique...».</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -25766,7 +25766,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) A um menor consumo de combustível. No exame CAM do IMT, esta alternativa responde corretamente à questão «O binário máximo de um automóvel corresponde».</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -25826,7 +25826,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Sistema de Escape. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema do veículo que tem por função tratar a emissão de gases poluentes é».</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -25886,7 +25886,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Conduzir com os vidros abertos, quando se circula a maiores velocidades. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para uma condução económica constitui má prática».</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -25946,7 +25946,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) As emissões do veículo, diminuir a eficiência do motor e aumentar o consumo de combustível. No exame CAM do IMT, esta alternativa responde corretamente à questão «Caso o catalisador do sistema de exaustão esteja obstruído, pode influenciar».</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -26006,7 +26006,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) 65% do seu curso. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para diminuir o consumo de combustível no início da marcha deve-se pressionar o pedal de acelerador a».</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -26066,7 +26066,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Desacelerar, prevendo o aparecimento de peões. No exame CAM do IMT, esta alternativa responde corretamente à questão «Ao aproximar-se de uma passadeira, o comportamento do motorista deve ser».</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -26126,7 +26126,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Conduzir sempre com baixa velocidade. No exame CAM do IMT, esta alternativa responde corretamente à questão «A fim de poder evitar acidentes, o motorista deve».</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -26186,7 +26186,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Qualquer uma das respostas anteriores está correta. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um dos cuidados a ter aquando da utilização do espelho retrovisor é».</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) A afirmação é verdadeira. No exame CAM do IMT, esta alternativa responde corretamente à questão «Em mais de 90 % dos acidentes rodoviários, o erro do condutor é o fator determinante. Comente».</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -26306,7 +26306,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) A afirmação é verdadeira. No exame CAM do IMT, esta alternativa responde corretamente à questão «Ter um descanso correto e uma alimentação equilibrada são p rincípios básicos para uma condução mais segura.».</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -26366,7 +26366,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) O coeficiente de atrito no eixo dianteiro é menor que no eixo traseiro. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma situação de sobreviragem surge quando».</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -26426,7 +26426,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Ligar as luzes de cruzamento. No exame CAM do IMT, esta alternativa responde corretamente à questão «De noite, sempre que o condutor circule a menos de 100 metros do veículo da frente deve».</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -26486,7 +26486,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) No máximo do binário. No exame CAM do IMT, esta alternativa responde corretamente à questão «A engrenagem das mudanças deve ser feita».</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -26546,7 +26546,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Não, o sistema de travagem dos veículos pesados corresponde a uma forma de segurança ativa, enquanto que o capacete de proteção corresponde a uma medida de segurança passiva. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema de travagem dos veículos pesados de passageiros e o capacete de protecção dos motociclistas correspondem am...».</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -26606,7 +26606,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Cerca de 1 segundos. No exame CAM do IMT, esta alternativa responde corretamente à questão «O tempo médio de reação de um condutor é, em condições normais».</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -26666,7 +26666,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Análise, Percepção, Decisão, Ação. No exame CAM do IMT, esta alternativa responde corretamente à questão «A função “condução” divide-se em 4 fases, sendo a ordem correcta».</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -26726,7 +26726,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Espelho – Sinal – Espelho – Manobra. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nas manobras que implicam deslocação lateral dos veículos devo verificar o seguinte procedimento».</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -26786,7 +26786,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) 4 Vezes mais. No exame CAM do IMT, esta alternativa responde corretamente à questão «A distância necessária para assegurar uma travagem forte num piso de alcatrão molhado de um veículo à velocidade de 6...».</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -26846,7 +26846,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Abdicar da prioridade para evitar o acidente. No exame CAM do IMT, esta alternativa responde corretamente à questão «Fazer uma condução defensiva é».</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -26906,7 +26906,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) A visão. No exame CAM do IMT, esta alternativa responde corretamente à questão «Qual é o órgão dos sentidos que é mais importante para desempenharmos corretamente a tarefa da condução?».</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -26966,7 +26966,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) A velocidade. No exame CAM do IMT, esta alternativa responde corretamente à questão «Dos fatores que se seguem, o mais determinante para o capotamento de veículos pesados é».</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Adapta a marcha do veículo às condições do tráfego. No exame CAM do IMT, esta alternativa responde corretamente à questão «A condução económica ocorre quando o motorista».</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -27086,7 +27086,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Antecipar as situações de trânsito, guardando a distância de segurança, de modo a evitar as acelerações e as travagens bruscas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma condução económica caracteriza-se por».</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -27146,7 +27146,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Ajustar, ao máximo, a velocidade à circulação viária existente no momento. No exame CAM do IMT, esta alternativa responde corretamente à questão «A forma de condução que devemos utilizar para reduzir o número de “pára -arranca”, mesmo estando numa fila de trânsit...».</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Deixar o motor ao ralenti. No exame CAM do IMT, esta alternativa responde corretamente à questão «Com o motor em funcionamento, a fim de carregar o sistema pneumático, o motorista deve».</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -27266,7 +27266,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Diminuir a resistência aerodinâmica.. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os reboques e/ou semi-reboques acoplados possuem dimensão, em altura, superior ao do trator. A colocação de deflector...».</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -27326,7 +27326,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Utilização da inércia do veículo o que i rá traduzir-se numa menor necessidade de usar o acelerador, logo, menores consumos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Como exemplo de algumas das regras para a prática de uma cond ução económica e mais amiga do ambiente pode referir-se».</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -27386,7 +27386,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Em subida, selecione a relação da caixa de velocidades que permite subir conservando um regime de motor entre 1300 e 1400 rpm;. No exame CAM do IMT, esta alternativa responde corretamente à questão «A utilização correta da caixa de velocidades, irá permitir um menor consumo de combustível e menor desgaste de pneus ...».</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -27446,7 +27446,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Determinar a massa de carga máxima que pode ser carregada no veículo, ao longo da plataforma. No exame CAM do IMT, esta alternativa responde corretamente à questão «A elaboração de um plano de distribuição da carga serve para».</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -27506,7 +27506,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Amarração de topo. No exame CAM do IMT, esta alternativa responde corretamente à questão «As cintas são frequentemente utilizadas para».</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -27566,7 +27566,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Num sistema de fixação em que as amarrações são posicionadas por cima da parte superior das mercadorias e fixas a dois pontos de amarração do veículo (opostos). No exame CAM do IMT, esta alternativa responde corretamente à questão «A amarração de topo consiste».</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -27626,7 +27626,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Desacelerar prevendo o aparecimento de peões. No exame CAM do IMT, esta alternativa responde corretamente à questão «mercadorias e fixas a dois pontos de amarração do veículo (opostos) Ao aproximar-se de uma passadeira, o comportament...».</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -27686,7 +27686,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Fadiga e sonolência. No exame CAM do IMT, esta alternativa responde corretamente à questão «Dos factores abaixo indicados, assinale aquele que pode contribuir para a ocorrência de acidentes».</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -27746,7 +27746,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Aumentar a distância de segurança em relação ao veículo da frente. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para conduzir com antecipação, deve».</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -27806,7 +27806,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Levantar o pé do pedal do acelerador. No exame CAM do IMT, esta alternativa responde corretamente à questão «Numa curva, deve».</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -27866,7 +27866,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Reduzir a velocidade. No exame CAM do IMT, esta alternativa responde corretamente à questão «Ao aproximar-se de uma rotunda, a forma mais adequada de proceder é».</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -27926,7 +27926,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Travamento ou bloqueio. No exame CAM do IMT, esta alternativa responde corretamente à questão «O acondicionamento da carga pode ser feito através do método de».</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -27986,7 +27986,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) O conjunto do peso da tara e da carga que o veículo pode transportar. No exame CAM do IMT, esta alternativa responde corretamente à questão «O peso bruto de um veículo é».</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -28046,7 +28046,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) 29 toneladas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O peso bruto máximo de um conjunto veículo trator-semi-reboque de três eixos é».</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -28106,7 +28106,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) De topo, em laço, com lançantes, envolvente e directa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os tipos de amarração que existem são».</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -28166,7 +28166,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Proteção de cargas que soltem grãos ou poeiras. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os toldos a colocar nos veículos de caixa aberta, devem ser utilizados para».</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -28226,7 +28226,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) O trator deve iniciar o processo de travagem primeiro que o reboque e / ou semi-reboque.. No exame CAM do IMT, esta alternativa responde corretamente à questão «No processo de travagem de veículos pe sados com reboque ou semi -reboque, indique a afirmação verdadeira».</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Força que se opõe à deslocação do veículo, tendo este que a vencer para se deslocar. No exame CAM do IMT, esta alternativa responde corretamente à questão «Sobre o veículo automóvel pesado incidem um conjunto de forças que poderão colocar em causa a sua segurança. Entende-...».</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Diminuir a velocidade de cada um dos veículos, encostando-os o mais à direita possível.. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando ocorre o cruzamento de dois veículos pesados com mais do que 8 metros de comprimento, que circulam em sentido ...».</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -28406,7 +28406,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Maior for a distância entre eixos.. No exame CAM do IMT, esta alternativa responde corretamente à questão «A amplitude de raio de viragem de um veículo pesado de mercadorias é tanto maior quanto».</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -28466,7 +28466,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) No transporte com depósito não completamente atestado, o motorista deve ter especial atenção ao efetuar uma curva e ao travar. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os veículos automóveis pesados de mercadorias que transportem cargas móveis (ex: líquido em cisternas) devem ter dete...».</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -28526,7 +28526,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Posição inadequada ao volante. No exame CAM do IMT, esta alternativa responde corretamente à questão «Como causas potenciadoras de fadiga pode referir-se».</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -28586,7 +28586,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) 4 m. No exame CAM do IMT, esta alternativa responde corretamente à questão «A altura máxima permitida para os veículos de mercadorias (carga geral) é de».</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -28646,7 +28646,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Inclinar-se quando sujeita a forças horizontais. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quanto mais elevado for o centro de gravidade de uma carga mais esta tenderá a».</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Desacelerar à distância conveniente, reduzindo a carga no acelerador. No exame CAM do IMT, esta alternativa responde corretamente à questão «Num piso irregular e com pouca aderência, o motorista deve».</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -28766,7 +28766,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Evitar o deslocamento de objetos cilíndricos ao longo da plataforma de carga. No exame CAM do IMT, esta alternativa responde corretamente à questão «O travamento com calços é utilizado para».</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Ensaio da embraiagem e sistema de travagem. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para a salvaguarda da sua segurança, e dos outros utentes da via o motorista deve fazer diariamente antes de iniciar ...».</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -28886,7 +28886,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Sim, sempre. No exame CAM do IMT, esta alternativa responde corretamente à questão «Comente a afirmação: “A distribuição do peso na caixa de carga pode influenciar o consumo de combustível”».</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -28946,7 +28946,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) A comodidade dos passageiros que transporta. No exame CAM do IMT, esta alternativa responde corretamente à questão «A correta utilização do acelerador por um motorista contribui para».</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -29006,7 +29006,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) 61% dos assaltos ocorreram nos parques ou áreas de serviço. No exame CAM do IMT, esta alternativa responde corretamente à questão «De acordo com a IRU».</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -29066,7 +29066,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) A maior parte são urbanas ou fronteiriças. A Roménia, a Hungria, a Polónia e a Rússia têm as mais elevadas taxas de agressões. No exame CAM do IMT, esta alternativa responde corretamente à questão «No que respeita a criminalidade, as zonas sensíveis na Europa são».</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -29126,7 +29126,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) A planificação detalhada do itinerário. No exame CAM do IMT, esta alternativa responde corretamente à questão «Antes de iniciar o transporte, entende -se como uma boa prática, com vista a evitar situações de criminalidade e vand...».</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -29186,7 +29186,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Antes de iniciar a viagem. No exame CAM do IMT, esta alternativa responde corretamente à questão «A verificação do correcto funcionamento dos dispositivos de alarme da viatura deve ser feita».</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -29246,7 +29246,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) A prevenção. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma das características fundamentais para a segurança de um condutor e».</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -29306,7 +29306,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Evitar falar do conteúdo e valor do transporte e dos itinerários escolhidos, com pessoas estranhas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Entende-se como uma boa prática, durante o abastecimento da viatura, com vista a evitar situações de criminalidade e ...».</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -29366,7 +29366,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Evitar parques de estacionamento isolados. No exame CAM do IMT, esta alternativa responde corretamente à questão «Durante o estacionamento da viatura, o condutor deve».</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -29426,7 +29426,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Avisar as autoridades e o proprietário do veículo em causa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Em caso de desaparecimento da viatura o condutor deve».</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -29486,7 +29486,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Avisar as autoridades e o proprietário do veículo em causa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se a viatura que conduz for sujeita a atos de vandalismo, deve».</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -29546,7 +29546,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Possua vigilância e os veículos sejam controlados à entrada e à saída. No exame CAM do IMT, esta alternativa responde corretamente à questão «Parque de estacionamento seguro é o que».</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -29606,7 +29606,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Roménia, Hungria, Polónia e Rússia. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os países europeus que representam maior risco por possuírem taxas elevadas no que diz respeito a índices de agressão...».</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -29666,7 +29666,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) A afirmação é verdadeira. No exame CAM do IMT, esta alternativa responde corretamente à questão «As entradas e saídas de um parque de estacionamento seguro são, regra geral, controladas por vídeo vigilância e apena...».</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -29726,7 +29726,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Da polícia, autoridade anti-terrorismo e proteção civil e da embaixada. No exame CAM do IMT, esta alternativa responde corretamente à questão «No que se refere a segurança, o condutor que se desloque a outro país  deve conhecer sempre os números de contacto».</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -29786,7 +29786,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Transportar consigo objetos de valor e grandes quantias de dinheiro. No exame CAM do IMT, esta alternativa responde corretamente à questão «O motorista deve evitar».</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -29846,7 +29846,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Saber onde são os parques de estacionamento mais seguros para estacionar a viatura e descansar em segurança.. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nas viagens internacionais deve».</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -29906,7 +29906,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Preferir os parques de estacionamento bem iluminados e onde já estejam algumas viaturas também. No exame CAM do IMT, esta alternativa responde corretamente à questão «em segurança. Durante a noite, quando tiver de parar para descansar, o motorista deve».</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -29966,7 +29966,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Voltaram todos a entrar e verificar através de uma listagem se são as mesmas pessoas. No exame CAM do IMT, esta alternativa responde corretamente à questão «estacionadas Numa viagem internacional, após uma paragem, o motorista deve, antes de dar continuidade à viagem, verif...».</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -30026,7 +30026,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Entrega as bagagens certas aos respetivos passageiros e que não existe nada de estranho entre elas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando se dirigir à bagageira para retirar ou colocar as bagagens o motorista deve certificar-se que».</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -30086,7 +30086,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Os dispositivos de segurança estão todos a funcionar corretamente. No exame CAM do IMT, esta alternativa responde corretamente à questão «veículo qualquer pessoa estranha Antes de iniciar uma viagem internacional o motorista deve certificar-se que».</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -30146,7 +30146,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Todas as alíneas anteriores estão certas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Durante uma viagem, a bordo da viatura deve estar uma lista de verificações que serve para».</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -30206,7 +30206,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Chamar de imediato as autoridades competentes. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se o motorista se aperceber que leva um clandestino a bordo qual o procedimento adequado».</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -30266,7 +30266,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Pela via rodoviária, marítima e raramente por via aérea. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os clandestinos procuram introduzir-se na Europa por uma ou mais vias. Indique quais».</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -30326,7 +30326,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Necessidade de ligação constante com a empresa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nas deslocações em território nacional deve ter sempre presente».</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -30386,7 +30386,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Antes de entrar no veículo verifique se há pessoas a passear na área. No exame CAM do IMT, esta alternativa responde corretamente à questão «Relativamente à segurança passiva, quais as ações que preventivamente deve tomar».</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -30446,7 +30446,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Busca sumária ao exterior depois ao interior, em todos os locais susceptíveis de esconder um objeto ou pessoa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Antes e depois de entrar no veículo qual é a tarefa que deve dar especial atenção à».</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -30506,7 +30506,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Manter bom relacionamento e controlo dos passageiros, capacidade do saber ouvir para assim, responder adequadamente e evitar a discussão. No exame CAM do IMT, esta alternativa responde corretamente à questão «Durante o percurso para evitar e prevenir situações de risco, sobretudo, em situações de conflito violento, deve».</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -30566,7 +30566,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Tráfico e consumo de estupefacientes e substâncias psicotrópicas tipificados no Dec-Lei n.º 15/93 de 22 de Janeiro. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os motoristas estão sujeitos a determinadas consequências por cometerem determinados tipos de crime relativamente à s...».</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -30626,7 +30626,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Nos locais de estacionamento e áreas de serviço. No exame CAM do IMT, esta alternativa responde corretamente à questão «De acordo com os dados do International Road Transport Union, a maioria dos ataques aos veículos de transporte ocorrem».</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -30686,7 +30686,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) De noite. No exame CAM do IMT, esta alternativa responde corretamente à questão «Mais de 50 % dos ataques aos veículos de transporte ocorrem».</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -30746,7 +30746,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Estacionar em locais isolados, com o menor número de veículos pesados possíveis. No exame CAM do IMT, esta alternativa responde corretamente à questão «Na paragem para descanso, no decorrer do transporte, indique que medida não adoptaria».</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -30806,7 +30806,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Verificar os danos provocados no veículo, avaliar as perdas da carga e comunicar imediatamente á entidade patronal e à polícia, ajudando no relatório do roubo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Diga o que fazer em caso de emergência de roubo ou assalto».</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Verificar os danos provocados no veículo, avaliar as perdas da carga e comunicar imediatamente á entidade patronal e à polícia, ajudando no relatório do roubo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Diga o que fazer em caso de emergência de roubo ou assalto».</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -30926,7 +30926,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Entrar na cabine do veículo e sair do local o mais rápido possível. No exame CAM do IMT, esta alternativa responde corretamente à questão «No caso de sofrer uma agressão, indique quais dos seguintes procedimentos não adotaria».</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -30986,7 +30986,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Mantenha a calma, não abra o vidro, e se necessário contacte a polícia. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se durante uma paragem na via for abordado por um estranho, qual dos procedimentos adotaria».</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -31046,7 +31046,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Se no decorrer de um transporte, um utente i nsistir entrar sem documento de embarque, deixar entrar, se houver lugares disponíveis. No exame CAM do IMT, esta alternativa responde corretamente à questão «No transporte de pesados de passageiros, indique que procedimento não adoptaria».</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -31106,7 +31106,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Descansar e aguardar que seja efetuada a descarga. No exame CAM do IMT, esta alternativa responde corretamente à questão «entrar, se houver lugares disponíveis Quando da chegada ao destinatário, o motorista não deve».</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -31166,7 +31166,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Planear os detalhes do itinerário e não seguir sempre o mesmo percurso. No exame CAM do IMT, esta alternativa responde corretamente à questão «todas retiradas Uma das formas de prevenir a criminalidade é, antes da viagem».</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -31226,7 +31226,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) O norte de França. No exame CAM do IMT, esta alternativa responde corretamente à questão «no local programado Das zonas abaixo referidas, uma das mais sensíveis da Europa no que respeita a segurança é».</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -31286,7 +31286,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Legumes. No exame CAM do IMT, esta alternativa responde corretamente à questão «No que se refere a segurança, não é considerada uma “mercadoria sensível”».</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -31346,7 +31346,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Hungria. No exame CAM do IMT, esta alternativa responde corretamente à questão «Dos países abaixo referidos, a taxa de agressão a motoristas é maior na».</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -31406,7 +31406,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Colocar cintas de segurança, trancas/fechaduras e o cabo de segurança TIR ou fechar bem o veículo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para impedir o roubo do veículo ou da carga, deve».</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -31466,7 +31466,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Deve observar todas as anteriores respostas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando estaciona o veículo num parque deve».</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -31526,7 +31526,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Três anos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quem favorecer ou facilitar a entrada ou o trânsito ilegais de cidadão estrangeiro em território português, incorre n...».</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -31586,7 +31586,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Revela comportamento negligente ao não empreender pessoalmente quaisquer verificações do veículo durante a viagem. No exame CAM do IMT, esta alternativa responde corretamente à questão «Perante o transporte de passageiros clandestinos, as autoridades britânicas aplicarão a sanção máxima ao motorista que».</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -31646,7 +31646,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Lista de Verificações do Home Office. No exame CAM do IMT, esta alternativa responde corretamente à questão «A Lista de Verificações que dá mais gar antias de evitar a aplicação de coimas, caso o motorista transporte clandesti...».</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -31706,7 +31706,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) O motorista. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quem é o principal responsável pela implementação prática de um sistema eficaz de prevenção do transporte de clandest...».</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -31766,7 +31766,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Antecipar eventuais situações de risco para poder reagir adequadamente. No exame CAM do IMT, esta alternativa responde corretamente à questão «A utilização responsável da rede de estradas implica».</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -31826,7 +31826,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Sinalizar o veículo, alertar as autoridades e parar o motor do veículo. No exame CAM do IMT, esta alternativa responde corretamente à questão «As regras gerais de actuação em caso de acidente são».</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -31886,7 +31886,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) 112. No exame CAM do IMT, esta alternativa responde corretamente à questão «Em caso de acidente e suspeita de vítimas acidentadas com lesões deverá ligar para o».</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -31946,7 +31946,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Entre o combustível e o oxigénio do ar (comburente), face a uma fonte de calor. No exame CAM do IMT, esta alternativa responde corretamente à questão «Fogo é uma reação química».</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -32006,7 +32006,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Todas as respostas anteriores estão correctas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O 1º Socorro é a primeira assistência ou ajuda prestada a qualquer indivíduo vítima de acidente ou doença súbita, com...».</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -32066,7 +32066,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Pode ser realizado apenas por um condutor. No exame CAM do IMT, esta alternativa responde corretamente à questão «O preenchimento da Declaração Amigável de Acidente Automóvel (DAAA)».</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -32126,7 +32126,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Convenção internacional, denominada Convenção Multilateral de Garantias. No exame CAM do IMT, esta alternativa responde corretamente à questão «“Carta Verde” é uma».</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -32186,7 +32186,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Escolho áreas de estacionamento vigiadas e seguras. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para prevenir atos de vandalismo, roubo ou sequestro num veículo».</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -32246,7 +32246,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Sim. No exame CAM do IMT, esta alternativa responde corretamente à questão «O seguro obrigatório automóvel garante as indemnizações devidas por danos pessoais ou materiais causados a terceiros ...».</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -32306,7 +32306,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) 30 compressões para 2 insuflações (30:2). No exame CAM do IMT, esta alternativa responde corretamente à questão «Na Reanimação Cardio-Respiratória, a razão entre as compressões torácicas e as insuflações é».</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -32366,7 +32366,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Mulheres grávidas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Não devem ser aplicadas compressões abdominais em».</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -32426,7 +32426,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Deve ser provocada nas vítimas que respiram normalmente. No exame CAM do IMT, esta alternativa responde corretamente à questão «A posição lateral de segurança».</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -32486,7 +32486,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Não tocar na lesão. No exame CAM do IMT, esta alternativa responde corretamente à questão «Em caso de queimadura deve-se».</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -32546,7 +32546,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Se a vítima estiver contaminada com tóxicos ou venenos o socorrista deve usar proteções do corpo e da roupa (luvas e avental). No exame CAM do IMT, esta alternativa responde corretamente à questão «Em caso de intoxicação».</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -32606,7 +32606,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Deve ser sucinto e relatar resumidamente o que aconteceu. No exame CAM do IMT, esta alternativa responde corretamente à questão «No preenchimento da Declaração Amigável de Acidente Automóvel».</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -32666,7 +32666,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Não movimentar a vítima, exceto se existir perigo iminente de incêndio, explosão ou qualquer outra situação que ponha em risco a vida da vítima. No exame CAM do IMT, esta alternativa responde corretamente à questão «Perante uma vítima de acidente o procedimento adequado é».</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -32726,7 +32726,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Prevenir, alertar e socorrer. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os princípios gerais de socorrismo são».</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -32786,7 +32786,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Com realização de pancadas interescapulares ou manobra de Heimlich. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma vítima de asfixia por obstr ução das vias respiratórias devido à presença de um corpo estranho deve ser socorrida».</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -32846,7 +32846,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Desobstruir as vias aéreas, fazer a extensão da cabeça, pedir ajuda e verificar se está a respirar. No exame CAM do IMT, esta alternativa responde corretamente à questão «No caso da vítima não responder aos estímulos do socorrista, o procedimento correto é».</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -32906,7 +32906,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Estacionar o veículo depois do local do acidente, ligar as luzes de perigo, vestir o colete e colocar o sinal de pré-sinalização de perigo a pelo menos 30m da retaguarda do veículo ou da carga a sinalizar.. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para sinalizar corretamente o local do acidente o motorista deve».</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -32966,7 +32966,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Estacionar o veículo antes do local do acidente, ligar as luzes de perigo, vestir o colet e e colocar o sinal de pré-sinalização de perigo a pelo menos 30m da retaguarda do veículo ou da carga a sinalizar.. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para sinalizar corretamente o local do acidente o motorista deve».</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -33026,7 +33026,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Colocar a vítima sentada com a cabeça direita e fazer compressão com o polegar e o indicador em pinça apertando as extremidades do nariz. No exame CAM do IMT, esta alternativa responde corretamente à questão «Numa situação de epistaxis (hemorragia pelo nariz), o socorrista deve».</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -33086,7 +33086,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Todas as respostas anteriores estão correctas. No exame CAM do IMT, esta alternativa responde corretamente à questão «pinça apertando as extremidades do nariz Quando se liga 112».</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -33146,7 +33146,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Devem ser referidas todas as informações anteriores. No exame CAM do IMT, esta alternativa responde corretamente à questão «Ao ligar 112, o mais importante é».</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -33206,7 +33206,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Deve-se esperar durante 10 segundos para ver se a vítima respira ou não. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para perceber se alguém está em paragem cardio-respiratória».</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -33266,7 +33266,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) O melhor método é fazer compressão direta. No exame CAM do IMT, esta alternativa responde corretamente à questão «Perante uma ferida simples numa zona sem fraturas».</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -33326,7 +33326,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Todas as respostas anteriores estão corretas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Numa situação de queimadura, os cuidados de emergência visam».</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -33386,7 +33386,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Todas as respostas anteriores estão correctas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Em caso de incêndio, um motorista».</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -33446,7 +33446,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Os atos do motorista devem basear-se em evitar sempre o confronto. No exame CAM do IMT, esta alternativa responde corretamente à questão «Em caso de tentativa de agressão ou agressão ao motorista».</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -33506,7 +33506,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Não desligar a ignição dos veículos acidentados. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um condutor que assista a um acidente no qual existam pessoas ou haja veículos danificados tem o dever de prestar o a...».</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -33566,7 +33566,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Abandonar o local. No exame CAM do IMT, esta alternativa responde corretamente à questão «preparados para dar resposta e prestar primeiros socorros aos que deles necessitam Em caso de acidente com a sua viat...».</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -33626,7 +33626,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Manter o veículo em funcionamento. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando ocorre um incêndio num veículo, o motorista deve adotar certos procedimentos. Das seguintes hipóteses, qual é ...».</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -33686,7 +33686,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) 8 Dias. No exame CAM do IMT, esta alternativa responde corretamente à questão «A participação da declaração amigável de acidente deve ser entregue ou enviada à seguradora no período de».</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -33746,7 +33746,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Não, apenas quando os condutores estiverem de acordo. No exame CAM do IMT, esta alternativa responde corretamente à questão «A participação da declaração amigável de acidente deve ser sempre preenchida».</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -33806,7 +33806,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Avaliar se a vítima está consciente/inconsciente. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para iniciar o socorro das vítimas é necessária a avaliaç ão desta, através do exame primário, o qual consiste em».</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -33866,7 +33866,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Tentar prever potenciais situações de conflito e identificar potenciais agressores, assim como controlar as emoções e tomar decisões. No exame CAM do IMT, esta alternativa responde corretamente à questão «No contexto do transporte  rodoviário os riscos de agressão e violência aos motoristas e respetivos veículos tem vind...».</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -33926,7 +33926,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Avaliação em primeiro lugar do estado de consciência da vítima. No exame CAM do IMT, esta alternativa responde corretamente à questão «O exame primário da vítima consiste na».</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -33986,7 +33986,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Deteção Alerta e Pré-socorro. No exame CAM do IMT, esta alternativa responde corretamente à questão «Perante uma situação de acidente, a sequência adequada na aplicação nas diversas fases do Sistema Integrado de Emergê...».</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Utilizar água para lavar os olhos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se um produto tóxico atingir o condutor nos olhos, este deverá imediatamente».</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -34106,7 +34106,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Envolver a vítima com um cobertor ou rolá-la pelo chão. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se numa situação de incêndio a roupa da vítima estiver a arder deve-se».</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -34166,7 +34166,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Custo de reparação ou perda total, e reboque. No exame CAM do IMT, esta alternativa responde corretamente à questão «A “Convenção IDS” (indemnização direta ao segurado), assinada por quase todas as seguradoras que operam em Portugal a...».</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -34226,7 +34226,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Humana, material e financeira. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes rodoviários com veículos pesados de passageiros têm consequências de ordem».</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -34286,7 +34286,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Dentro das localidades. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes com veículos pesados de passageiros ocorrem, sobretudo».</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -34346,7 +34346,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) 50 metros. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes rodoviários envolvendo veículos pesados de passageiros traduzem-se fundamentalmente em colisões, despist...».</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -34406,7 +34406,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Iniciar encostado ao eixo da via, curvando próximo do mesmo; ao sair da curva manter o veículo mais próximo do eixo da via. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para evitar alguns acidentes, os condutores de veículos pesados de passageiros deverão proceder da seguinte forma par...».</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -34466,7 +34466,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Maior velocidade de circulação. No exame CAM do IMT, esta alternativa responde corretamente à questão «curva, onde as rodas esquerdas devem estar pró ximas do eixo da via; ao sair da curva deve afastar - se do eixo da vi...».</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Colisões. No exame CAM do IMT, esta alternativa responde corretamente à questão «A maior incidência de mortes envolvendo veículos pesados de passageiros é devida».</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -34586,7 +34586,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Os acidentes envolvendo veículos pesados de passageiros têm consequências mais graves para terceiros do que para os utentes. No exame CAM do IMT, esta alternativa responde corretamente à questão «Atendendo aos dados estatísticos da sinistralidade rodoviária, indique qual das afirmações é verdadeira».</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -34646,7 +34646,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Que o retrator ajuste automaticamente o comprimento do cinto, e em caso de aceleração brusca o mesmo seja bloqueado. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os cintos de segurança equipados com retrator de bloqueio automático de emergência por inércia permitem».</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -34706,7 +34706,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Sinalizar a eventual s úbita redução de velocidade, procurar uma escapatória possível, parar em segurança, sinalizar o acidente e solicitar auxílio. No exame CAM do IMT, esta alternativa responde corretamente à questão «O condutor de um automóvel pesado que assista a um acidente na via em que circula, deve».</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -34766,7 +34766,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Reduzir a velocidade, encostar-se o mais à direita possível e ligar os quatro indicadores de mudança de direção em funcionamento simultâneo. No exame CAM do IMT, esta alternativa responde corretamente à questão «O condutor que ao circular em auto-estrada veja que 200 m à sua frente ocorreu um acidente, deve, como procedimento m...».</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -34826,7 +34826,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Aumentar a distância do veículo da frente de forma a, se necessário, conseguir parar em segurança. No exame CAM do IMT, esta alternativa responde corretamente à questão «Sempre que a faixa de rodagem se encontre molhada o condutor deve».</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -34886,7 +34886,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Certificar-se de que a visibilidade para a condução não é afetada e circular só nestas condições. No exame CAM do IMT, esta alternativa responde corretamente à questão «Sempre que o condutor verifique que o sistema de limpa para - brisas apresente deficiências no seu funcionamento o co...».</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -34946,7 +34946,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Reduzir a velocidade e aumentar a distância de segurança do veículo que circula à sua frente. No exame CAM do IMT, esta alternativa responde corretamente à questão «Sempre que as condições atmosféricas sejam adversas o condutor deve».</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -35006,7 +35006,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Deve-se a um conjunto de medidas concertadas, associadas à evolução do parque automóvel, à qualidade das vias e, essencialmente, às alterações de atitudes e comportamentos que se têm vindo a verificar nos utentes. No exame CAM do IMT, esta alternativa responde corretamente à questão «A redução da sinistralidade rodoviária em Portugal nos últimos anos».</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -35066,7 +35066,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) As consequências dos acidentes envolvendo veículos pesados são superiores às consequências dos acidentes que não envolvem este tipo de veículos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando observamos as estatísticas de sinistralidade podemos concluir que».</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -35126,7 +35126,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Menor volume de tráfego e menor número de acidentes. No exame CAM do IMT, esta alternativa responde corretamente à questão «relativamente às consequências dos acidentes que não envolvem este tipo de veículos Os períodos do dia que apresenta ...».</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -35186,7 +35186,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Têm consequências mais graves para terceiros do que para os utentes dos veículos pesados. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes que envolvem veículos pesados».</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -35246,7 +35246,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Baixou substancialmente nos últimos anos, sendo a mais baixa quando comparada com a dos restantes veículos. No exame CAM do IMT, esta alternativa responde corretamente à questão «A taxa de implicação de veículos pesados de passageiros em acidentes com vítimas».</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -35306,7 +35306,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Sim, de acordo com os resultados apresentados o nú mero de mortos e feridos graves diminuiu consideravelmente.. No exame CAM do IMT, esta alternativa responde corretamente à questão «De acordo com o Observatório de Segurança Rodoviária o nosso país tem vindo a diminuir o número de mortos e feridos g...».</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -35366,7 +35366,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) A apneia do sono tem efeitos muito graves na condução, porque os  condutores não se apercebem de que estão com a vigilância diminuída e, devido a esse facto, com a atenção, a concentração e os reflexos diminuídos. No exame CAM do IMT, esta alternativa responde corretamente à questão «A apneia do sono é um problema que tem efeitos muito graves na condução».</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -35426,7 +35426,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) A apneia do sono tem efeitos muito graves na condução, porque os  condutores não se apercebem de que estão com a vigilância diminuída e, devido a esse facto, com a atenção, a concentração e os reflexos diminuídos. No exame CAM do IMT, esta alternativa responde corretamente à questão «A apneia do sono é um problema que tem efeitos muito graves na condução».</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -35486,7 +35486,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Sim, usando o cinto de segurança, o condutor, em caso de acidente, tem mais probabilidades de não sofrer lesões graves. No exame CAM do IMT, esta alternativa responde corretamente à questão «O uso do cinto de segurança, usado pelos condutores dos veículos pesados, diminui o número de condutores mortos. Comente».</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -35546,7 +35546,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Sim, os acidentes por despiste nos ligeiros de passageiros foi de bastante superior aos despistes de veículos pesados de passageiros. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes, por despiste, são, segundo o Observatório de Segurança Rodoviário de 2009, em número superior nos ligeiros».</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -35606,7 +35606,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Sim, além dos custos ma teriais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos autocarros estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes rodoviários envolvendo pesados de passageiros têm custos para as próprias empresas».</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -35666,7 +35666,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Sim, além dos custos ma teriais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos autocarros estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes rodoviários envolvendo pesados de passageiros têm custos para as próprias empresas».</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -35726,7 +35726,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Sim, além dos custos materiais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos veículos estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes rodoviários envolvendo pesados de mercadorias têm custos para as próprias empresas».</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -35786,7 +35786,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Sim, além dos custos materiais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos veículos estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes rodoviários envolvendo pesados de mercadorias têm custos para as próprias empresas».</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -35846,7 +35846,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Envolve grande diversidade de riscos, para além dos associados à condução. No exame CAM do IMT, esta alternativa responde corretamente à questão «A profissão de motoristas de veículos pesados de passageiros».</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Certa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Pode considerar-se que o risco químico se encontra associado à profissão de condução. A afirmação está».</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -35966,7 +35966,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Pode ser uma medida correta, desde que não incentive a prática de velocidades mais elevadas e de menores tempos de descanso. No exame CAM do IMT, esta alternativa responde corretamente à questão «A existência nas empresas empregadoras de sistemas de prémios de desempenho que tenham em conta o tempo que o motoris...».</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -36026,7 +36026,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) É sempre um fator de risco para o motorista. No exame CAM do IMT, esta alternativa responde corretamente à questão «A existência de deficiências ao nível da manutenção e equipamentos do veículo».</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -36086,7 +36086,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Traduzem-se num aumento da gravidade em caso de acidente. No exame CAM do IMT, esta alternativa responde corretamente à questão «tráfego As características dos veículos pesados de passageiros relacionadas com o seu peso».</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -36146,7 +36146,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Traduzem-se num aumento da gravidade em caso de acidente. No exame CAM do IMT, esta alternativa responde corretamente à questão «completamente lotado As características dos veículos pesados de mercadorias relacionadas com o seu peso».</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -36206,7 +36206,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) A afirmação está certa apenas se se referir a condução noturna. No exame CAM do IMT, esta alternativa responde corretamente à questão «As ultrapassagens efetuadas por veículos pesados de passageiros oferecem maior risco relativame nte às realizadas por...».</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -36266,7 +36266,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Não é permitido ao motorista ´dar boleias´. No exame CAM do IMT, esta alternativa responde corretamente à questão «Das afirmações abaixo referidas, identifique uma normas de segurança ativa».</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -36326,7 +36326,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Cobrir todas as consequências dos acidentes de viação (materiais, físicos, psicológicos e sociais). No exame CAM do IMT, esta alternativa responde corretamente à questão «A avaliação efetuada pelas seguradoras e sentenças dos tribunais em caso de acidente de viação, permite».</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -36386,7 +36386,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Morte de passageiros. No exame CAM do IMT, esta alternativa responde corretamente à questão «São consequências materiais de acidentes de viação».</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -36446,7 +36446,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Colisões. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes rodoviários com veículos pesados de mercadorias são, principalmente, devidos a».</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -36506,7 +36506,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Nas ultrapassagens indevidas. No exame CAM do IMT, esta alternativa responde corretamente à questão «A colisão com um veículo em sentido contrário ocorre, de modo geral».</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -36566,7 +36566,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Circula demasiado perto do veículo da frente. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma colisão com o veículo da frente pode ocorrer quando o condutor».</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -36626,7 +36626,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Desrespeito da regra de cedência de passagem. No exame CAM do IMT, esta alternativa responde corretamente à questão «As colisões num cruzamento ocorrem fundamentalmente por».</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -36686,7 +36686,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Fazer sinal com o indicador de mudança de direção à esquerda. No exame CAM do IMT, esta alternativa responde corretamente à questão «A realização de uma ultrapassagem em segurança, implica».</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -36746,7 +36746,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) À velocidade de impacto dos veículos. No exame CAM do IMT, esta alternativa responde corretamente à questão «A gravidade dos acidentes com veículos pesados de mercadorias está associada».</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -36806,7 +36806,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) À velocidade a que o veículo circula. No exame CAM do IMT, esta alternativa responde corretamente à questão «A gravidade dos acidentes com veículos pesados de passageiros está associada».</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -36866,7 +36866,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Consequências de acidentes. No exame CAM do IMT, esta alternativa responde corretamente à questão «No contexto de acidentes de viação, quando se fala de mortos, feridos, derrames ou custos, referimo -nos a».</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -36926,7 +36926,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Suécia. No exame CAM do IMT, esta alternativa responde corretamente à questão «O país que regista menor sinistralidade rodoviária com veículos pesados de mercadorias é a».</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -36986,7 +36986,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) No veículo, na via e no homem. No exame CAM do IMT, esta alternativa responde corretamente à questão «As condições ambientais têm impacto».</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -37046,7 +37046,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Sim, sempre. No exame CAM do IMT, esta alternativa responde corretamente à questão «A distribuição do peso na caixa de carga pode influenciar o domínio do veículo em segurança».</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -37106,7 +37106,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) O uso do corta-vento na janela do condutor e a condução, sempre que possível, com o vidro fechado. No exame CAM do IMT, esta alternativa responde corretamente à questão «Algumas das medidas tendentes a reduzir o aparecim ento de otites e doenças das vias respiratórias nos motoristas são».</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -37166,7 +37166,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) 10 kg por passageiro. No exame CAM do IMT, esta alternativa responde corretamente à questão «É obrigatório o transporte gratuito da bagagem pessoal do passageiro, em veículos afetos a carreiras interurbanas e a...».</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -37226,7 +37226,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Sim, pois uma boa rede de transportes públicos eficiente e pontual, fazia com que as pessoas a utilizassem mais e isto iria contribuir para um decréscimo da poluição atmosférica e diminuição dos engarrafamentos de trânsito. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma boa rede de transportes públicos de passageiros pode evitar as deslocações em viaturas particulares e melhoria da...».</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -37286,7 +37286,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Alvará ou licença comunitária válida até 5 anos.</t>
+          <t>Alvará ou licença comunitária válida até 5 anos.</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -37346,7 +37346,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Transportes públicos = por conta de outrem.</t>
+          <t>Transportes públicos = por conta de outrem.</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -37406,7 +37406,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Os transportes regulares e ocasionais. No exame CAM do IMT, esta alternativa responde corretamente à questão «metropolitana de transportes Constituem categorias do transporte interno».</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -37466,7 +37466,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Sociedades comerciais, cooperativas e empresas públicas ou de capitais públicos que comprovem reunir os requisitos de acesso à actividade. No exame CAM do IMT, esta alternativa responde corretamente à questão «A ativid ade de transporte público rodoviário de passageiros ou por conta de outrem nacional  ou internacional pode s...».</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -37526,7 +37526,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Sociedades anónimas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O capital social está dividido em ações num dos seguintes tipos de sociedades».</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -37586,7 +37586,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Empresas públicas de transporte rodoviário. No exame CAM do IMT, esta alternativa responde corretamente à questão «As empresas de transportes rodoviários de passgeiros cujo capital social é detido maioritariamente pelo Estado ou por...».</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -37646,7 +37646,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) O “Aluguer ocasional” é um serviço prestado mediante a cedência de um autocarro com um condutor para a realização de uma deslocação de um grupo de passageiros.. No exame CAM do IMT, esta alternativa responde corretamente à questão «Em relação ao transporte rodoviário de passageiros, assinale a afirmação verdadeira».</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -37706,7 +37706,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Em carreiras regulares, com origem, destino, pontos de passagem e horários previamente estabelecidos, devidamente autorizados e divulgados junto dos utentes. No exame CAM do IMT, esta alternativa responde corretamente à questão «O serviço público de transporte de passageiros é um serviço prestado».</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -37766,7 +37766,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Mais rápido que o transporte público, com menor número de paragens, normalmente aplicável a médio-longo curso. No exame CAM do IMT, esta alternativa responde corretamente à questão «O serviço “Expresso” é um serviço».</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -37826,7 +37826,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Estes serviços asseguram o transporte de grupos constituídos por iniciativa de um comitente ou do próprio transportador e estão isentos de qualquer autorização, sendo efetuados ao abri go de folhas de itinerário. No exame CAM do IMT, esta alternativa responde corretamente à questão «Considerando as caraterísticas de transporte dos «serviços ocasionais», indique qual das seguintes afirmações é verda...».</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -37886,7 +37886,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Exige condições físicas, psíquicas, humanas específicas ao candidato a motorista. No exame CAM do IMT, esta alternativa responde corretamente à questão «transportes nacionais no território de outro Estado A profissão de motorista de pesados».</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) A visão global do público dos serviços da empresa. No exame CAM do IMT, esta alternativa responde corretamente à questão «A imagem de uma empresa é».</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -38006,7 +38006,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Preservar a imagem da viatura como a limpeza e adequação dos equipamentos. No exame CAM do IMT, esta alternativa responde corretamente à questão «O motorista deverá ter como características pessoais».</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -38066,7 +38066,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Todas as respostas anteriores estão corretas. No exame CAM do IMT, esta alternativa responde corretamente à questão «As necessidades essenciais do cliente são».</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -38126,7 +38126,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Estabilidade emocional e manter uma comunicação assertiva com os interlocutores. No exame CAM do IMT, esta alternativa responde corretamente à questão «O motorista deve ter como sua característica».</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -38186,7 +38186,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Estabilidade emocional e manter uma comunicação assertiva com os interlocutores. No exame CAM do IMT, esta alternativa responde corretamente à questão «O motorista deve ter como sua característica».</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Falta de organização gerando pouco trabalho e produtividade assim como aspetos físicos ambientais. No exame CAM do IMT, esta alternativa responde corretamente à questão «para o exercício da função e ético Um dos fatores que prejudica o bom relacionamento interpessoal nas empresas é».</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -38306,7 +38306,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) O conjunto de deveres, princípios e normas adoptadas por um determinado grupo profissional. No exame CAM do IMT, esta alternativa responde corretamente à questão «A deontologia profissional é».</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -38366,7 +38366,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Ser independente no trabalho com os colegas/ colaboradores. No exame CAM do IMT, esta alternativa responde corretamente à questão «No trabalho em equipa, o profissional não deve».</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -38426,7 +38426,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Emissor, mensagem, canal e recetor. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os elementos do processo de comunicação são».</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -38486,7 +38486,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Assertivo, agressivo, manipulador e passivo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Podemos identificar quatro estilos de comunicação no relacionamento interpessoal».</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -38546,7 +38546,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Há uma atitude de auto-afirmação. No exame CAM do IMT, esta alternativa responde corretamente à questão «Na comunicação assertiva».</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -38606,7 +38606,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Verdadeiro. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um dos problemas inerentes ao processo de comunicação reside no facto de o recetor atribuir à mensagem um significado...».</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -38666,7 +38666,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) O olhar para o chão. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um dos erros mais comuns quando falamos é».</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -38726,7 +38726,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Todas as outras respostas estão corretas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Ao prestar um serviço, deve».</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -38786,7 +38786,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Todas as outras respostas estão corretas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Perante uma reclamação do cliente devo».</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -38846,7 +38846,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Todas as outras respostas estão corretas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Perante uma reclamação do cliente devo».</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -38906,7 +38906,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) O nosso comportamento vai influenciar o comportamento daqueles que interagem connosco. No exame CAM do IMT, esta alternativa responde corretamente à questão «Numa correta conduta».</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -38966,7 +38966,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Ter o cliente como a razão de ser do seu desempenho. No exame CAM do IMT, esta alternativa responde corretamente à questão «Desenvolver uma postura comercial junto do cliente significa».</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -39026,7 +39026,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Ajuda os clientes com dificuldade de mobilização (grávidas, idosos). No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma das maneiras de aferir a competência relacional do motorista é verificar se o mesmo».</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -39086,7 +39086,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Uma oportunidade para poder melhorar o serviço e o desempenho. No exame CAM do IMT, esta alternativa responde corretamente à questão «As reclamações dos clientes devem ser entendidas como».</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -39146,7 +39146,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Ter a capacidade de escutar o cliente dando informações corretas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Perante a manifestação de insatisfação do cliente, é mais eficaz».</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -39206,7 +39206,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Facilitar a comunicação e cordialidade. No exame CAM do IMT, esta alternativa responde corretamente à questão «Comunicar de forma assertiva é».</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -39266,7 +39266,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Aproveitar a situação para trocar impressões com o colega. No exame CAM do IMT, esta alternativa responde corretamente à questão «No acto de rendição o motorista deve».</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -39326,7 +39326,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) É um dever do motorista. No exame CAM do IMT, esta alternativa responde corretamente à questão «A manutenção do veículo por parte do motorista».</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -39386,7 +39386,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Procurar perceber o que está realmente em causa, sem personalizar ou julgar. No exame CAM do IMT, esta alternativa responde corretamente à questão «A melhor forma de gerir um conflito entre colegas é».</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -39446,7 +39446,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Sentir-se bloqueado e paralisado quando é apresentado um problema para resolver. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um tipo de comportamento passivo é».</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -39506,7 +39506,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Os motoristas devem estar conscientes da importância do cargo que ocupam e o significado que seu trabalho tem para a organização. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os serviços de uma organização alcançam vantagens competitivas quando a qualid ade é definida como uma questão estrat...».</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -39566,7 +39566,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Formar um grupo coeso, eficiente e motivado. No exame CAM do IMT, esta alternativa responde corretamente à questão «tempos e condução aplicáveis A boa comunicação é importante entre os membros dentro de uma organização para».</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -39626,7 +39626,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Dar a confiança e satisfação aos clientes. No exame CAM do IMT, esta alternativa responde corretamente à questão «A qualidade do serviço serve para».</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -39686,7 +39686,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Técnicas, de relacionamento e organizacionais. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os três tipos de competências do motorista são».</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -39746,7 +39746,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Aumento da fadiga. No exame CAM do IMT, esta alternativa responde corretamente à questão «Qual a principal dificuldade da condução noturna é».</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -39806,7 +39806,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) A qualidade de serviço implica obrigatoriamente aumentar os custos da empresa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Não está correto afirmar que».</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -39866,7 +39866,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Organizacional. No exame CAM do IMT, esta alternativa responde corretamente à questão «A capacidade de integração na estrutura de uma empresa é uma competência do tipo».</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -39926,7 +39926,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Tangibilidade, fiabilidade, confiança, pró atividade, e empatia. No exame CAM do IMT, esta alternativa responde corretamente à questão «As características de um serviço de qualidade são».</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -39986,7 +39986,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) O motorista. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para os clientes de uma firma de transportes, a face visível da empresa é».</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -40046,7 +40046,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Estão insatisfeitos com a qualidade do atendimento. No exame CAM do IMT, esta alternativa responde corretamente à questão «Estudos indicam que, na maior parte dos casos, os clientes abandonam uma empresa ou serviço, porque».</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -40106,7 +40106,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Afastando-se do cliente, deixando-o a falar sozinho. No exame CAM do IMT, esta alternativa responde corretamente à questão «serviço Um dos seguintes comportamentos deve ser evitado, pois prejudica a comunicação com o cliente. Indique qual».</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -40166,7 +40166,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Processos de tratamento, controlo e comunicação de informação. No exame CAM do IMT, esta alternativa responde corretamente à questão «fazemos As Tecnologias de Informação e Comunicação dizem respeito a».</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -40226,7 +40226,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Os clientes que reclamam só causam problemas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma reclamação pode ser vista como uma oportunidade”. Uma das frases seguintes é falsa. Indique qual».</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -40286,7 +40286,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Os clientes que reclamam só causam problemas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma reclamação pode ser vista como uma oportunidade”. Uma das frases seguintes é falsa. Indique qual».</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -40346,7 +40346,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Um conjunto de veículos pertencentes a uma mesma empresa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Gestão de frota significa administrar ou gerir».</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -40406,7 +40406,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Poupar tempo, dinheiro e aumentar a satisfação dos clientes. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema de bilhética permite aos operadores de transporte público».</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -40466,7 +40466,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Telemóveis. No exame CAM do IMT, esta alternativa responde corretamente à questão «A utilização do Sistema SOS reduziu significativamente, após o aparecimento de».</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -40526,7 +40526,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Móveis. No exame CAM do IMT, esta alternativa responde corretamente à questão «GSM é o Sistema Global para Comunicações».</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -40586,7 +40586,7 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Posicionamento Global. No exame CAM do IMT, esta alternativa responde corretamente à questão «O GPS é um Sistema de».</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -40646,7 +40646,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) O tempo estimado para a chegada do próximo veículo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os painéis de informação destinam-se a apresentar, em cada instante, informação sobre».</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -40706,7 +40706,7 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Bilhética Electrónica e SMS. No exame CAM do IMT, esta alternativa responde corretamente à questão «O SAE permite a interligação entre outros sistemas, como».</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -40766,7 +40766,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Altitude, longitude e latitude. No exame CAM do IMT, esta alternativa responde corretamente à questão «O principio de funcionamento do GPS baseia-se em ».</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -40826,7 +40826,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) A coleção de documentos electrónicos interligados por uma infindável  rede ou teia (Web) de aranha, armazenados em computadores designados por servidores Web espalhados por todo o mundo. No exame CAM do IMT, esta alternativa responde corretamente à questão «A World Wide Web (WWW) é».</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -40886,7 +40886,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Permite aos motoristas estar em contacto com a empresa, colegas, clientes e outros contactos, tais como serviços de manutenção e reparação e centros de controlo de tráfego. No exame CAM do IMT, esta alternativa responde corretamente à questão «A evolução da s tecnologias de informação e comunicação tem tido influência nos transportes de pesados de passageiros...».</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -40946,7 +40946,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) O processamento de informação, mapas, bases de dados, comunicações e dados em tempo real recolhidos a partir de uma variedade de sensores. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os sistemas inteligentes de transportes (ITS) permitem».</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -41006,7 +41006,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Proporcionam o acesso a informação em tempo real relativa à viagem e ao tráfego. No exame CAM do IMT, esta alternativa responde corretamente à questão «As tecnologias de informação e comunicação contribuem para a segurança rodoviária porque».</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -41066,7 +41066,7 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Permite fiscalizar os passageiros no veículo. No exame CAM do IMT, esta alternativa responde corretamente à questão «A bilhética sem contacto (indique a afirmação verdadeira)».</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -41126,7 +41126,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Os custos de manutenção do sistema são mais altos comparativamente com outros sistemas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Relativamente à bilhética sem contacto, indique qual das seguintes afirmações é falsa».</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -41186,7 +41186,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Ter permanentemente a bordo informação sobre o estado da via e condições do tráfego. No exame CAM do IMT, esta alternativa responde corretamente à questão «As tecnologias de informação permitem ao condutor».</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -41246,7 +41246,7 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) O condutor possa agir de forma a evitar o acidente. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema de alerta à eminência de colisão permite que».</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
@@ -41306,7 +41306,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Durante um determinado percurso sem que seja necessário pressionar o acelerador do veículo. No exame CAM do IMT, esta alternativa responde corretamente à questão «O regulador de velocidade é um sistema que permite manter uma velocidade constante».</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -41366,7 +41366,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Reduzir largamente o congestionamento nessas áreas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os sistemas de pagamento eletrónico de portagens têm como principal vantagem».</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -41426,7 +41426,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Reduzir o volume de tráfego e, consequentemente, o correspondente impacto ambiental. No exame CAM do IMT, esta alternativa responde corretamente à questão «A criação de uma taxa de circulação em áreas urbanas congestionadas tem vindo a ser implementada em várias cidades eu...».</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -41486,7 +41486,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Veículos (através da respectiva matrícula). No exame CAM do IMT, esta alternativa responde corretamente à questão «Os sistemas de controlo automático do comportamento em estrada visam a identificação de».</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -41546,7 +41546,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) A promoção da segurança. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma das vantagens da utilização dos sistemas inteligentes de transporte é».</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -41606,7 +41606,7 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) A emissão de informações aos condutores, permitindo -lhes uma melhor gestão da viagem em função das ocorrências assinaladas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os painéis de mensagens variáveis são painéis eletrónicos que permitem».</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -41666,7 +41666,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Evitar o acidente. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema de aviso de aproximação de obstáculos em manobras de marcha-atrás visa».</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -41726,7 +41726,7 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Constitui um útil auxiliar de navegação para o condutor. No exame CAM do IMT, esta alternativa responde corretamente à questão «A correcta utilização do GPS numa viagem pela Europa».</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
@@ -41786,7 +41786,7 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Velocidade média, localização de áreas de serviço e de locais de interesse turístico, bem como o valor da correspondente altitude. No exame CAM do IMT, esta alternativa responde corretamente à questão «O GPS permite que o condutor obtenha, entre outras, as seguintes informações».</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -41846,7 +41846,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Um recetor GPS. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para um utente receber sinal através dum sistema de navegação GPS, é necessário que possua».</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -41906,7 +41906,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Sintetizadores de voz que permitem a indicação do caminho ou rumo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Sempre que durante a condução se utiliza o GPS, é mais seguro recorrer à função que permite a utilização de».</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -41966,7 +41966,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Deter dados estatísticos mais fiáveis sobre a evolução das necessidades de mobilidade dos cidadãos. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema da bilhética sem contacto permite à entidade transportadora».</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -42026,7 +42026,7 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Inteligentes, seguros e com a possibilidade de garantirem serviços transversais. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os Smart Cards são».</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
@@ -42086,7 +42086,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) O conjunto de quaisquer registos quantificáveis relativos a um fenómeno ou acontecimento. No exame CAM do IMT, esta alternativa responde corretamente à questão «O conceito de “dados” representa».</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -42146,7 +42146,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) A aplicação das tecnologias de informação e comunicação aos transportes. No exame CAM do IMT, esta alternativa responde corretamente à questão «Sistemas  Inteligentes de Transportes são».</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -42206,7 +42206,7 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Não, cada vez há mais sistemas de informática embarcada, fáceis de utilizar e amigos do ambiente. No exame CAM do IMT, esta alternativa responde corretamente à questão «A gestão da frota só é possível com recurso a complicados sistemas informáticos».</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
@@ -42266,7 +42266,7 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Internet. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma rede de computadores, pública, global, de uso múltiplo é denominada».</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
@@ -42326,7 +42326,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Aumentar a produtividade e a competitividade. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um sistema de informação para fins operacionais e fins de gestão pode».</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -42386,7 +42386,7 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Registar os tempos de condução e de repouso. No exame CAM do IMT, esta alternativa responde corretamente à questão «O tacógrafo digital tem a função de».</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -42446,7 +42446,7 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Este equipamento requer a inserção de u m cartão inteligente (com um chip incorporado), que tem carácter pessoal, contém a identificação do condutor e permite a memorização dos dados relativos às suas actividades. No exame CAM do IMT, esta alternativa responde corretamente à questão «Relativamente ao tacógrafo digital, indique qual é a afirmação verdadeira».</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
@@ -42506,7 +42506,7 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Cada condutor poderá ser titular de um ou mais cartões. No exame CAM do IMT, esta alternativa responde corretamente à questão «Relativamente ao tacógrafo digital, indique qual é a afirmação verdadeira».</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -42566,7 +42566,7 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Sistemas inteligentes de transportes. No exame CAM do IMT, esta alternativa responde corretamente à questão «As siglas ITS significam».</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -42626,7 +42626,7 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Falsa, uma vez que o dispositivo que permite manter a velocidade constante é o regulador activo de velocidade. No exame CAM do IMT, esta alternativa responde corretamente à questão «O limitador de velocidade permite manter uma velocidade constante sem que seja necessário pressionar o acelerador do ...».</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -42686,7 +42686,7 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) GPS/Telemap. No exame CAM do IMT, esta alternativa responde corretamente à questão «As aplicações operacionais são sistemas de informação dedicados às necessidades específicas das empresas. São daquela...».</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
@@ -42746,7 +42746,7 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) A obtenção de informação em tempo real sobre a localização dos produtos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma das vantagens do RFID na área da logística é».</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -42806,7 +42806,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Sistema de comunicação “wireless” (sem fios). No exame CAM do IMT, esta alternativa responde corretamente à questão «O RFID (Radio Frequency Identification) é um».</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -42866,7 +42866,7 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Europeu de radionavegação e de posicionamento por satélite. No exame CAM do IMT, esta alternativa responde corretamente à questão «O “Programa GALILEO” é um programa».</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -42926,7 +42926,7 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) 80%. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nos transportes nacionais por rodoviária a percentagem das cargas que viaja apenas até 100 km é».</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -42986,7 +42986,7 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Sim, mas nem sempre foi assim. No exame CAM do IMT, esta alternativa responde corretamente à questão «O modo rodoviário é o maior elo de ligação do nosso país ao espaço europeu».</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -43046,7 +43046,7 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) O centro da gravidade da carga (total de passageiros e bagagem) e superfície da caixa de carga coincidirem. No exame CAM do IMT, esta alternativa responde corretamente à questão «O equilíbrio de um veículo pesado de passageiros esta relacionado com o respetivo centro de gravidade. A estabilidade...».</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -43106,7 +43106,7 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Encontrar-se em boas condições físicas como psíquicas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para a prática de uma condução correta, cómoda e segura, o motorista de um pesado de passageiro deve».</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -43166,7 +43166,7 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Submeter-se a prévio controlo médico e a acompanhamento adequado para monitoriz ação de eventuais efeitos negativos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Perante a necessidade de um profissional da condução recorrer a medicamentos que possam atuar sobre o sistema nervoso...».</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -43226,7 +43226,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Capacidade de resposta = rapidez e precisão.</t>
+          <t>Capacidade de resposta = rapidez e precisão.</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -43286,7 +43286,7 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) ABS. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema antibloqueio das rodas de uma viatura é conhecido através das siglas».</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -43346,7 +43346,7 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Em condições normais, o gasto de combustível não depende do tipo de caixa de velocidades mas do tipo de condução. No exame CAM do IMT, esta alternativa responde corretamente à questão «É gasto mais combustível com uma caixa de velocidades do tipo».</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -43406,7 +43406,7 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) As três hipóteses estão corretas, dependendo da situação concreta. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para otimizar o gasto de combustível, o motorista deve».</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -43466,7 +43466,7 @@
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Nas descidas, utilizar o ponto morto. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para racionalizar o consumo de combustível, o motorista não deve».</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -43526,7 +43526,7 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Guiar com os vidros abertos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Indique qual o fator indicativo de má prática em termos de condução económica».</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -43586,7 +43586,7 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Os atrasos e maior consumo de energia. No exame CAM do IMT, esta alternativa responde corretamente à questão «O principais custos dos congestionamentos de trânsito, são».</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -43646,7 +43646,7 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) É todo o transporte que se realiza entre locais de um mesmo país estrangeiro. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para um veículo de matrícula portuguesa, cabotagem é».</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
@@ -43706,7 +43706,7 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Que se realiza entre locais de países diferentes, distintos de Portugal. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para um veículo de matrícula portuguesa o transporte de cross-trade é o transporte».</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -43766,7 +43766,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Serve a empresa proprietária do veículo no exercício das suas atividades. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um veículo que efetua transporte por conta própria».</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -43826,7 +43826,7 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Mais de 95% das toneladas movimentadas e a ferrovia menos de 5%. No exame CAM do IMT, esta alternativa responde corretamente à questão «Analisando a produção dos vários modos de transporte de mercadorias observamos que, nos tráfegos nacionais os transpo...».</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -43886,7 +43886,7 @@
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) A massa de carga máxima que pode ser carregada no veículo, ao longo da plataforma. No exame CAM do IMT, esta alternativa responde corretamente à questão «A elaboração de um plano de distribuição da carga serve para determinar».</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -43946,7 +43946,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Reduzir o consumo de combustível, as emissões poluentes e aumentar a segurança rodoviária. No exame CAM do IMT, esta alternativa responde corretamente à questão «e fixas a dois pontos de amarração do veículo (opostos) A condução económica possibilita».</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -44006,7 +44006,7 @@
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Maior for a velocidade a que se circula assim como no caso de má visibilidade ou piso escorregadio. No exame CAM do IMT, esta alternativa responde corretamente à questão «A distância de segurança em relação ao veículo da frente deve ser maior quando».</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
@@ -44066,7 +44066,7 @@
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Poliéster, poliamida ou polipropileno. No exame CAM do IMT, esta alternativa responde corretamente à questão «As cintas de amarração são normalmente feitas de».</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
@@ -44126,7 +44126,7 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Numa forma de amarração da carga com ligação a um dos lados da carroçaria do veículo, a fim de evitar o deslizamento e a inclinação da carga para o lado oposto. No exame CAM do IMT, esta alternativa responde corretamente à questão «A amarração em laço consiste».</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
@@ -44186,7 +44186,7 @@
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) A carga máxima admissível, determinada pelo peso ou cubicagem máxima admitida. No exame CAM do IMT, esta alternativa responde corretamente à questão «No planeamento do enchimento da caixa de carga do veículo é imperativo considerar-se».</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
@@ -44246,7 +44246,7 @@
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Pneumático. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os veículos de elevado peso bruto utilizam sistema de travagem».</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
@@ -44306,7 +44306,7 @@
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) A atividade transitária só pode ser exercida por empresas titulares de alvará emitido pelo IMT. No exame CAM do IMT, esta alternativa responde corretamente à questão «Assinale a afirmação verdadeira».</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
@@ -44366,7 +44366,7 @@
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Uma forma de cooperação ao nível da actividade de uma empresa (contratante ou empresa principal) que entrega a outra (subcontratada ou empresa auxiliar) a execução da totalidade ou de uma parte da sua actividade dentro de determinadas condições. No exame CAM do IMT, esta alternativa responde corretamente à questão «A subcontratação nas empresas de transporte rodoviário é».</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
@@ -44426,7 +44426,7 @@
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Não coloca em perigo a saúde pública e os ecossistemas e que respeita as necessidades de mobilidade. No exame CAM do IMT, esta alternativa responde corretamente à questão «Transporte sustentável é o que».</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
@@ -44486,7 +44486,7 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Alvará, emitido pelo IMTT. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma empresa de aluguer de veículos sem condutor é titulada por».</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -44546,7 +44546,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Maior rapidez (porta-a-porta). No exame CAM do IMT, esta alternativa responde corretamente à questão «Das vantagens do transporte rodoviário de mercadorias, pode-se assinalar».</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -44606,7 +44606,7 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Um dos principais fatores encontrados na origem de acidentes rodoviários. No exame CAM do IMT, esta alternativa responde corretamente à questão «A perda de controlo associada à fadiga é».</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -44666,7 +44666,7 @@
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Aumento do tempo de reação. No exame CAM do IMT, esta alternativa responde corretamente à questão «Alguns medicamentos podem provocar».</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
@@ -44726,7 +44726,7 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Aos veículos de duas rodas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Sob a influência de vento lateral o condutor deve dar especial atenção».</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -44786,7 +44786,7 @@
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Os dispositivos de segurança estão todos a funcionar corretamente. No exame CAM do IMT, esta alternativa responde corretamente à questão «Antes de iniciar uma viagem internacional o motorista deve certificar-se que».</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
@@ -44846,7 +44846,7 @@
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) Verificar os danos provocados no veículo, avaliar as perdas da carga e comunicar imediatamente á entidade patronal e à polícia, ajudando no relatório do roubo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Diga o que fazer em caso de emergência de roubo ou assalto».</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">
@@ -44906,7 +44906,7 @@
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Descansar e aguardar que seja efetuada a descarga. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando da chegada ao destinatário, o motorista não deve».</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
@@ -44966,7 +44966,7 @@
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Planear os detalhes do itinerário e não seguir sempre o mesmo percurso. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma das formas de prevenir a criminalidade é, antes da viagem».</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
@@ -45026,7 +45026,7 @@
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Contactar imediatamente as autoridades locais e identificar -se, b em como ao veículo, dando referências da localização. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se suspeitar que transporta um passageiro clandestino, deve».</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
@@ -45086,7 +45086,7 @@
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) A base das chamas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Em caso de incêndio, o jacto do extintor deve ser direcionado para».</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
@@ -45146,7 +45146,7 @@
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Todas as respostas anteriores estão correctas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando se liga 112».</t>
         </is>
       </c>
       <c r="I772" t="inlineStr">
@@ -45206,7 +45206,7 @@
       </c>
       <c r="H773" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Abandonar o local. No exame CAM do IMT, esta alternativa responde corretamente à questão «Em caso de acidente com a sua viatura, qual o procedimento que não deve ser adoptado».</t>
         </is>
       </c>
       <c r="I773" t="inlineStr">
@@ -45266,7 +45266,7 @@
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Maior velocidade de circulação. No exame CAM do IMT, esta alternativa responde corretamente à questão «A principal causa para o índice de gravidade dos acidentes com veículo pesados de passageiros ser superior fora das l...».</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
@@ -45326,7 +45326,7 @@
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Menor volume de tráfego e menor número de acidentes. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os períodos do dia que apresenta maior gravidade nos acidentes correspondem aos períodos com».</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
@@ -45386,7 +45386,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Os transportes interurbanos, regionais, locais e urbanos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Constituem categorias do transporte interno».</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -45446,7 +45446,7 @@
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção C) Falta de organização gerando pouco trabalho e produtividade assim como aspetos físicos ambientais. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um dos fatores que prejudica o bom relacionamento interpessoal nas empresas é».</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">
@@ -45506,7 +45506,7 @@
       </c>
       <c r="H778" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Formar um grupo coeso, eficiente e motivado. No exame CAM do IMT, esta alternativa responde corretamente à questão «A boa comunicação é importante entre os membros dentro de uma organização para».</t>
         </is>
       </c>
       <c r="I778" t="inlineStr">
@@ -45566,7 +45566,7 @@
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Permite aos motoristas estar em contacto com a empresa, colegas, clientes e outros contactos, tais como serviços de manutenção e reparação e centros de controlo de tráfego. No exame CAM do IMT, esta alternativa responde corretamente à questão «A evolução da s tecnologias de informação e comunicação tem tido influência nos transportes de pesados de passageiros...».</t>
         </is>
       </c>
       <c r="I779" t="inlineStr">
@@ -45626,7 +45626,7 @@
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção A) Permite fiscalizar os passageiros no veículo. No exame CAM do IMT, esta alternativa responde corretamente à questão «A bilhética sem contacto (indique a afirmação verdadeira)».</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
@@ -45686,7 +45686,7 @@
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção D) Avaliação em primeiro lugar do estado de consciência da vítima. No exame CAM do IMT, esta alternativa responde corretamente à questão «O exame primário da vítima consiste na».</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
@@ -45746,7 +45746,7 @@
       </c>
       <c r="H782" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT.</t>
+          <t>A resposta correta é a opção B) A instalação de televisões na cabine do veículo ou na caixa de carga. No exame CAM do IMT, esta alternativa responde corretamente à questão «A telemática é».</t>
         </is>
       </c>
       <c r="I782" t="inlineStr">
@@ -45806,7 +45806,7 @@
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Integra localização, dados de condução e gestão de frota.</t>
+          <t>Integra localização, dados de condução e gestão de frota.</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Cartões ou dispositivos que funcionam por proximidade.</t>
+          <t>Cartões ou dispositivos que funcionam por proximidade.</t>
         </is>
       </c>
       <c r="I784" t="inlineStr">
@@ -45926,7 +45926,7 @@
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Permite que as rodas exteriores e interiores girem a velocidades diferentes.</t>
+          <t>Permite que as rodas exteriores e interiores girem a velocidades diferentes.</t>
         </is>
       </c>
       <c r="I785" t="inlineStr">
@@ -45986,7 +45986,7 @@
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. É crime e pode acarretar sanções pesadas.</t>
+          <t>É crime e pode acarretar sanções pesadas.</t>
         </is>
       </c>
       <c r="I786" t="inlineStr">
@@ -46046,7 +46046,7 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>Resposta aceite no exame IMT. Afeta todo o sistema de travagem.</t>
+          <t>Afeta todo o sistema de travagem.</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">

--- a/questoes sem rep.xlsx
+++ b/questoes sem rep.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(DL 257/2007): 9.000 € no 1.º veículo; 5.000 € (pesado) ou 900 € (ligeiro) por veículo adicional.</t>
+          <t>(DL 257/2007): 9.000 € no 1.º veículo; 5.000 € (pesado) ou 900 € (ligeiro) por veículo adicional. Relativamente a «Durante o exercício da atividade das empresas de transportes públicos de mercadorias por…», a resposta adequada é D): Não pode ser inferior a € 9 000 pelo primeiro veículo automóvel licenciado ou € 5 000 ou € 900 por cada veículo adicional, consoante se trate de veículo pesado ou ligeiro. Por exemplo, a opção A) indica valores (Não pode ser superior a € 8 987,36 pelo primeiro veículo automóvel licenci…) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>A comunicação deve ser feita no prazo de 30 dias após a ocorrência.</t>
+          <t>O valor ou limite legal aplicável é 30 dias a contar da data da sua ocorrência, indicado em C).  Por exemplo, a opção A) indica valores (10 dias a contar da sua ocorrência) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>A falta deve ser suprida no prazo de 30 dias.</t>
+          <t>O procedimento adequado é No prazo de 30 dias a contar da data da sua ocorrência (A)). Por exemplo, D) («Aquando da renovação da licença ou alvará») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -730,7 +730,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tanto o transportador como o expedidor respondem solidariamente pela infração.</t>
+          <t>Transporte em regime de carga completa significa que o veículo é utilizado na totalidade da sua capacidade por um único expedidor (um cliente por serviço). A opção C) exprime isso. A opção A) descreve carga fracionada, em que vários expedidores partilham o mesmo veículo.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>A certidão do registo comercial é o documento válido para comprovar o capital social.</t>
+          <t>A certidão do registo comercial é o documento válido para comprovar o capital social. Na situação «Uma sociedade unipessoal por quotas, no início da atividade, deve fazer prova da…», o procedimento correto é Certidão do registo comercial da qual conste o capital social (opção B)). Por exemplo, D) («Declaração do IRC referente ao ano anterior.») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -834,7 +834,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>O IMT é o organismo responsável pela emissão da licença.</t>
+          <t>Pelo Instituto da Mobilidade e dos Transportes — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Câmara Municipal da residência do proprietário do veículo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>A renovação exige comprovação contínua dos requisitos legais.</t>
+          <t>Mediante comprovação de que se mantêm os requisitos de acesso e de exercício de atividade — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Apenas mediante prova da capacidade profissional») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -938,7 +938,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Os requisitos são de verificação permanente.</t>
+          <t>Em qualquer momento porque os requisitos são de verificação permanente — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Só pode fiscalizar mediante participação das autoridades policiais») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tanto o expedidor como o transportador respondem em comparticipação.</t>
+          <t>Transporte em regime de carga completa significa que o veículo é utilizado na totalidade da sua capacidade por um único expedidor (um cliente por serviço). A opção D) exprime isso. A opção A) descreve carga fracionada, em que vários expedidores partilham o mesmo veículo.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>O alvará tem validade de 5 anos, devendo ser renovado antes do fim desse prazo.</t>
+          <t>5 anos — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (1 ano) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Para veículos de 2 eixos o limite é 18 toneladas (regulamentação europeia).</t>
+          <t>O valor ou limite legal aplicável é 18 toneladas, indicado em A).  Por exemplo, a opção B) indica valores (20 toneladas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Veículos de 3 eixos podem circular até 26 toneladas.</t>
+          <t>O valor ou limite legal aplicável é 26 toneladas, indicado em B).  Por exemplo, a opção A) indica valores (22 toneladas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>O limite máximo é 44 toneladas para conjuntos com 5 ou mais eixos.</t>
+          <t>O valor ou limite legal aplicável é 44 toneladas, indicado em C).  Por exemplo, a opção A) indica valores (38 toneladas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>A altura máxima legal é 4 metros do solo.</t>
+          <t>4 metros — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (3,5 metros) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>O comprimento máximo de um veículo isolado é 13,5 metros.</t>
+          <t>13,5 metros — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (12 metros) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>É obrigatório o ADR para o transporte de mercadorias perigosas.</t>
+          <t>ADR (Acordo Europeu relativo ao transporte de mercadorias perigosas) — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Certificado de capacidade profissional adicional») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>O limite diário de condução é 9 horas (pode ser estendido para 10 horas duas vezes por semana).</t>
+          <t>O limite diário de condução é 9 horas (pode ser estendido para 10 horas duas vezes por semana). Relativamente a «O tempo máximo de condução diária para um condutor profissional (sem interrupções) é de», a resposta adequada é B): 9 horas. Por exemplo, a opção A) indica valores (8 horas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>O limite semanal de condução é de 56 horas (pode chegar a 60 horas em algumas semanas).</t>
+          <t>O limite semanal de condução é de 56 horas (pode chegar a 60 horas em algumas semanas). Relativamente a «O tempo máximo de condução semanal (sem interrupções) para um condutor profissional é de», a resposta adequada é B): 56 horas. Por exemplo, a opção A) indica valores (45 horas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>O descanso diário mínimo é de 11 horas (pode ser reduzido para 9 horas três vezes por semana).</t>
+          <t>O descanso diário mínimo é de 11 horas (pode ser reduzido para 9 horas três vezes por semana). Relativamente a «O período mínimo de descanso diário obrigatório para um condutor profissional é de», a resposta adequada é B): 11 horas. Por exemplo, a opção A) indica valores (9 horas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Veículos acima de 3,5 t de peso bruto devem ter tacógrafo (analógico ou digital).</t>
+          <t>O valor ou limite legal aplicável é 3,5 toneladas, indicado em B).  Por exemplo, a opção A) indica valores (2,5 toneladas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Podem ser escritos ou verbais, mas recomenda-se sempre a forma escrita.</t>
+          <t>Escrita ou verbal — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Apenas por tempo indeterminado») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>A entidade patronal é responsável pelo pagamento no mês seguinte.</t>
+          <t>O procedimento adequado é Pela entidade patronal no mês seguinte (B)). Por exemplo, A) («Pelo trabalhador mensalmente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>A doença é falta justificada, desde que comprovada.</t>
+          <t>Relativamente a «A ausência do trabalhador por motivo de doença é considerada», a resposta adequada é B): Falta justificada.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>O trabalhador tem direito à reintegração na mesma categoria.</t>
+          <t>Reintegração na empresa — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Apenas pagamento de salários em atraso») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>O limite semanal normal é de 40 horas.</t>
+          <t>40 horas — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (35 horas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>O direito a férias é irrenunciável por lei.</t>
+          <t>Nunca pode acontecer (é irrenunciável) — é o que melhor responde ao enunciado (opção B)). Por exemplo, A) («Pode acontecer se a entidade pagar em dobro») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Todas as situações indicadas são justa causa para o trabalhador.</t>
+          <t>As alternativas anteriores são corretas em separado; por isso D) («Todas as anteriores») é a resposta completa. Por exemplo, C) («Recusar tarefas que não estão no contrato») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Após 4h30 de condução contínua é obrigatória uma pausa de 45 minutos.</t>
+          <t>4 horas e 30 minutos — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (4 horas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>O descanso semanal normal é de 45 horas consecutivas.</t>
+          <t>O procedimento adequado é 45 horas (C)). Por exemplo, a opção A) indica valores (24 horas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>O chassis (quadro) é a estrutura principal que suporta todo o veículo.</t>
+          <t>Quadro ou Chassis — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Longarinas ou Travessas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>A meia carga causa o maior movimento do líquido (sloshing).</t>
+          <t>Com metade da sua capacidade — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Não existe diferença em qualquer dos casos assinalados») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>altura máxima 4 m a contar do solo.</t>
+          <t>4 metros a contar do solo — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (3,5 metros a contar do solo) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Deve-se verificar regularmente o óleo hidráulico e da direção assistida.</t>
+          <t>O procedimento adequado é O nível do óleo do comando da embraiagem e o do sistema hidráulico da direção assistida (C)). Por exemplo, D) («Nenhum dos itens anteriores») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Indica má combustão, normalmente por excesso de combustível ou filtro de ar sujo.</t>
+          <t>Excesso de combustível não queimado devido má mistura de combustível — é o que melhor responde ao enunciado (opção D)). Por exemplo, B) («Fugas de combustível na alta pressão») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>O travamento é quando a carga é colocada contra estruturas fixas do veículo.</t>
+          <t>Trata-se de uma definição: Num sistema de retenção em que a carga é estivada contra estruturas fixas ou elementos do porta-cargas (opção D)).  Por exemplo, C) («Num sistema para prender vários volumes e deve sempre ser combinada com ou…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Parar regularmente é a melhor forma de combater a fadiga noturna.</t>
+          <t>O procedimento adequado é Parar de 2 em 2 horas e, imperativamente, após os primeiros sintomas de fadiga (A)). Por exemplo, D) («Circular com maior velocidade até encontrar uma área de serviço aberta») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Baixo nível de óleo ou fugas podem causar perda de assistência na direção.</t>
+          <t>Baixo nível de óleo ou fugas podem causar perda de assistência na direção. Na situação «O sistema de direção assistida hidráulica deve ser verificado periodicamente quanto ao», o procedimento correto é Nível de óleo e estado das mangueiras (opção A)).</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Retém as partículas nocivas e as queima periodicamente.</t>
+          <t>Reduzir as partículas de fuligem no escape — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Aquecer o motor mais rápido») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>O compressor é movido mecanicamente pelo motor do veículo.</t>
+          <t>Motor de combustão através de correia — é o que melhor responde ao enunciado (opção B)). Por exemplo, A) («Motor elétrico auxiliar») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Pressão errada + má distribuição da carga aceleram o desgaste.</t>
+          <t>As alternativas anteriores são corretas em separado; por isso D) («Todas as anteriores») é a resposta completa. Por exemplo, C) («Carga mal distribuída») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>A peação bloqueia o movimento para a frente ou para trás da mercadoria.</t>
+          <t>Evitar o movimento longitudinal da carga — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Melhorar a aerodinâmica») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>As amarras em cruz evitam o deslocamento lateral e vertical.</t>
+          <t>Trata-se de uma definição: Amarras diagonais sobre a carga (opção A)).  Por exemplo, C) («Amarras apenas laterais») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Planeamento e rotas seguras são essenciais para prevenir roubo.</t>
+          <t>O procedimento adequado é Evitar paragens desnecessárias e escolher rotas seguras (A)). Por exemplo, D) («Ignorar o plano de segurança») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>ABC da reanimação: Consciência → Via aérea → Respiração.</t>
+          <t>Avaliar o estado de consciência — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Colocar em posição lateral de segurança») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Compressão direta é o primeiro gesto para controlar hemorragia.</t>
+          <t>O procedimento adequado é Fazer compressão direta sobre a ferida (B)). Por exemplo, D) («Deixar sangrar para limpar») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Mantém as vias aéreas desobstruídas em vítima inconsciente que respira.</t>
+          <t>O procedimento adequado é Está inconsciente mas respira (B)). Por exemplo, D) («Está em paragem cardiorrespiratória») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Máximo de 13 horas de atividade diária.</t>
+          <t>13 horas — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (10 horas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>35 horas de formação contínua a cada 5 anos.</t>
+          <t>O procedimento adequado é 5 anos (B)). Por exemplo, a opção A) indica valores (3 anos) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Reduz stocks ao mínimo através de entregas frequentes e precisas.</t>
+          <t>Produção e entrega com stocks mínimos — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Gestão de combustível») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Postura correta e ajustes do banco evitam dores e fadiga.</t>
+          <t>Reduzir o esforço físico e prevenir lesões — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Aumentar o espaço de carga») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Obrigatório em qualquer deslocação.</t>
+          <t>Obrigatório sempre que o veículo estiver em movimento — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Obrigatório apenas em cidade») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Manter o volante reto e esperar que os pneus recuperem aderência.</t>
+          <t>O procedimento adequado é Soltar o acelerador e não travar (C)). Por exemplo, D) («Virar o volante rapidamente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Corrige automaticamente derrapagens e perda de controlo.</t>
+          <t>O veículo começa a derrapar ou perder estabilidade — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O condutor usa o travão de mão») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Menor consumo e menor manutenção.</t>
+          <t>Reduzir o consumo de combustível e o desgaste — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Chegar mais rápido ao destino») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Inspeção periódica obrigatória de 2 em 2 anos.</t>
+          <t>O procedimento adequado é 2 anos (B)). Por exemplo, a opção A) indica valores (6 meses) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Parar em segurança e desligar o motor é prioridade.</t>
+          <t>O procedimento adequado é Parar o veículo em local seguro e desligar o motor (B)). Por exemplo, C) («Telefonar imediatamente para o 112») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Útil para simplificar o processo com a seguradora.</t>
+          <t>O procedimento adequado é Sempre que haja danos materiais e as partes concordem (B)). Por exemplo, D) («Apenas em autoestrada») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Tolerância zero praticamente (0,2 g/l máximo).</t>
+          <t>0,2 g/l — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (0,5 g/l) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Ajuda a manter velocidade constante e económica.</t>
+          <t>O procedimento adequado é Sempre que possível em autoestrada (A)). Por exemplo, D) («Nunca em veículos pesados») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Informa sobre congestionamentos, obras, acidentes, etc.</t>
+          <t>Informar sobre condições de trânsito em tempo real — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Indicar postos de combustível») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Deve ser usado com segurança, sem distrair o condutor.</t>
+          <t>O procedimento adequado é Como apoio, nunca desviando a atenção da estrada (B)). Por exemplo, D) («Apenas em viagens internacionais») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>É um sistema de apoio à exploração da empresa.</t>
+          <t>Apoiar a gestão da empresa (rotas, horários, bilhética) — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Substituir o tacógrafo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Leitura automática sem contacto.</t>
+          <t>Identificação automática de veículos e cargas — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Controlar a velocidade») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>O ar comprimido é o meio utilizado nos travões pneumáticos de veículos pesados.</t>
+          <t>O ar comprimido é o meio utilizado nos travões pneumáticos de veículos pesados. Relativamente a «O sistema de travagem pneumática utiliza como meio de transmissão de força», a resposta adequada é B): Ar comprimido.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Só a altas temperaturas é que o catalisador consegue converter os gases tóxicos.</t>
+          <t>O procedimento adequado é 600-800 °C (C)). Por exemplo, a opção A) indica valores (100-200 °C) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Líquido errado afeta todo o desempenho do sistema de travagem.</t>
+          <t>As alternativas anteriores são corretas em separado; por isso D) («Todas as anteriores») é a resposta completa. Por exemplo, C) («Aumento da distância de travagem») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>A peação bloqueia o movimento para a frente ou para trás da mercadoria.</t>
+          <t>Aumentar a altura da carga — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Melhorar a aerodinâmica») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Combina várias direções de força.</t>
+          <t>As alternativas anteriores são corretas em separado; por isso D) («Todas as anteriores») é a resposta completa. Por exemplo, B) («Movimento para a frente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>O torniquete é indicado quando a compressão direta não é suficiente.</t>
+          <t>O procedimento adequado é Torniquete comercial (A)). Por exemplo, D) («Nada, só esperar ajuda») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sequência atual: 30 compressões + 2 ventilações.</t>
+          <t>O procedimento adequado é 30 compressões torácicas (A)). Por exemplo, a opção B) indica valores (2 insuflações) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Pode ser estendido para 10 horas no máximo duas vezes por semana.</t>
+          <t>10 horas — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (9 horas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Obrigatório guardar durante 2 anos para fiscalização.</t>
+          <t>O procedimento adequado é 2 anos (B)). Por exemplo, a opção A) indica valores (1 ano) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Obesidade e idade avançada são fatores de risco elevados.</t>
+          <t>Condutores com excesso de peso — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Condutores que fazem pausas frequentes») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Muitos medicamentos têm efeito sedativo e são incompatíveis com a condução.</t>
+          <t>É proibido durante a condução — é o que melhor responde ao enunciado (opção B)). Por exemplo, A) («É permitido se tomar só meio comprimido») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Com técnicas corretas (mudanças suaves, uso do retardador, etc.) é possível poupar 15-25 %.</t>
+          <t>Com técnicas corretas (mudanças suaves, uso do retardador, etc.) é possível poupar 15-25 %. Relativamente a «A condução económica permite reduzir o consumo de combustível em até», a resposta adequada é C): 15-25 %. Por exemplo, a opção A) indica valores (5 %) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Ajuda a manter velocidade constante e económica.</t>
+          <t>O procedimento adequado é Sempre que possível em autoestrada (A)). Por exemplo, D) («Nunca em veículos pesados») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Corrige automaticamente derrapagens e perda de controlo.</t>
+          <t>O veículo derrapa ou perde aderência — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O condutor usa o telemóvel») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Segurança em primeiro lugar.</t>
+          <t>O procedimento adequado é Reduzir velocidade e aumentar distância de segurança (B)). Por exemplo, C) («Usar luzes de máximos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Programar antes evita distrações ao volante.</t>
+          <t>Na situação «O GPS profissional deve ser programado», o procedimento correto é Antes de iniciar a viagem (opção A)).</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Informa sobre congestionamentos, obras, acidentes, etc.</t>
+          <t>Informar sobre condições de trânsito em tempo real — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Indicar postos de combustível») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Documentos obrigatórios para circulação internacional.</t>
+          <t>O procedimento adequado é Carta Verde, documentos do veículo e carga (A)). Na situação «Antes de uma viagem internacional o condutor deve verificar», o procedimento correto é Carta Verde, documentos do veículo e carga (opção A)).</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Segurança em primeiro lugar – acionar alarme e pedir ajuda.</t>
+          <t>Trata-se de uma definição: Ativar o botão de alarme e ligar 112 (opção A)).  Por exemplo, C) («Parar e sair do veículo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Útil para simplificar o processo com as seguradoras.</t>
+          <t>Sempre que haja danos e as partes concordem — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Apenas em autoestrada») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>É o certificado internacional de seguro automóvel.</t>
+          <t>Circular em países do Espaço Económico Europeu — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Apenas em viagens de longa distância») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>ABC da reanimação: Consciência, Via Aérea, Respiração, Circulação.</t>
+          <t>Avaliar consciência → Via aérea → Respiração → Circulação — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Nenhuma das anteriores») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>O descanso diário mínimo obrigatório é de 11 horas consecutivas.</t>
+          <t>O procedimento adequado é 11 horas (B)). Por exemplo, a opção A) indica valores (9 horas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>A inspeção periódica é obrigatória de 2 em 2 anos.</t>
+          <t>O procedimento adequado é 2 em 2 anos (B)). Por exemplo, a opção A) indica valores (6 em 6 meses) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>proibido segurar/manipular; permitido em viva-voz/mãos-livres (art. 82.º CE).</t>
+          <t>O Código da Estrada (art. 82.º) proíbe segurar ou manipular o telemóvel enquanto se conduz; o uso em viva-voz ou mãos-livres é o permitido. Por isso A) está correta: Permitido em viva-voz.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Combinação de ritmo circadiano e tempo de condução.</t>
+          <t>Em todas as situações acima — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Após 4 horas de condução contínua») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Corrige automaticamente derrapagens e perda de controlo em tempo real.</t>
+          <t>O veículo derrapa ou perde estabilidade — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O condutor usa o travão de mão») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Deixar os pneus recuperarem aderência naturalmente.</t>
+          <t>O procedimento adequado é Soltar o acelerador e manter o volante reto (C)). Na situação «Em caso de aquaplanagem o condutor deve», o procedimento correto é Soltar o acelerador e manter o volante reto (opção C)).</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Mantém velocidade constante e reduz consumo.</t>
+          <t>Na situação «O limitador de velocidade (cruzeiro) deve ser usado principalmente em», o procedimento correto é Autoestrada e estradas nacionais (opção B)).</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>É crime com sanções pesadas.</t>
+          <t>Proibido e pode ter consequências graves — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Permitido se pagar em dinheiro») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Facilita o processo com as seguradoras.</t>
+          <t>O procedimento adequado é Sempre que haja danos e as partes concordem (A)). Por exemplo, C) («Apenas em autoestrada») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Necessário para circular no Espaço Económico Europeu.</t>
+          <t>Internacional de seguro automóvel — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («De capacidade profissional») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Sequência atual: 30 compressões + 2 ventilações.</t>
+          <t>30 compressões torácicas — é o que melhor responde ao enunciado (opção A)). Por exemplo, a opção B) indica valores (2 insuflações) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Torniquete quando a compressão direta não controla a hemorragia.</t>
+          <t>O procedimento adequado é Torniquete comercial (A)). Por exemplo, B) («Compressa improvisada») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Avaliar consciência → Via aérea → Respiração → Circulação. No exame CAM do IMT, esta alternativa responde corretamente à questão «O exame primário da vítima segue a regra ABC, que significa».</t>
+          <t>Avaliar consciência → Via aérea → Respiração → Circulação — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Nenhuma das anteriores») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Alinhamento incorreto causa desgaste assimétrico.</t>
+          <t>Alinhamento incorreto das rodas — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Carga bem distribuída») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) As rodas girem a velocidades diferentes em curva. No exame CAM do IMT, esta alternativa responde corretamente à questão «A função do diferencial é permitir que».</t>
+          <t>As rodas girem a velocidades diferentes em curva — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O motor aumente o binário») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -5950,7 +5950,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Impede deslizamento para a frente/trás.</t>
+          <t>Movimento longitudinal da mercadoria — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Melhoria da visibilidade») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Todas as anteriores. No exame CAM do IMT, esta alternativa responde corretamente à questão «A amarração em cruz é eficaz contra».</t>
+          <t>As alternativas anteriores são corretas em separado; por isso D) («Todas as anteriores») é a resposta completa. Por exemplo, B) («Movimento para a frente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Exposição múltipla a substâncias.</t>
+          <t>As alternativas anteriores são corretas em separado; por isso D) («Todas as anteriores») é a resposta completa.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>O direito a férias é irrenunciável por lei.</t>
+          <t>Em caso algum, porque o direito a férias é irrenunciável — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Desde que o trabalhador concorde») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Obesidade e idade avançada são fatores de risco elevados.</t>
+          <t>Com excesso de peso — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Que fazem pausas frequentes») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Muitos medicamentos são incompatíveis com a condução.</t>
+          <t>Proibido durante a condução — é o que melhor responde ao enunciado (opção B)). Por exemplo, A) («Permitido se tomar meio comprimido») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Só a altas temperaturas converte os gases tóxicos.</t>
+          <t>600-800 °C — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (100-200 °C) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Além dos acidentes de viação, o motorista também está exposto a acidentes durante carga/descarga.</t>
+          <t>Além dos acidentes de viação, o motorista também está exposto a acidentes durante carga/descarga. Relativamente a «O motorista de um veículo pesado de mercadorias está, no âmbito da sua profissão,…», a resposta adequada é B): Acidentes relacionados com a carga e descarga de veículos. Por exemplo, D) («Não está sujeito a acidentes») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>A descida correta é sempre de costas para a via, com os 3 pontos de apoio.</t>
+          <t>O procedimento adequado é De costas para a via, utilizando sempre todos os apoios de mãos e de pés (A)). Por exemplo, D) («Não é necessário cumprir qualquer regra para o efeito») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Inexperiência + excesso de confiança = combinação perigosa.</t>
+          <t>O desconhecimento da via e o excesso de confiança — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («Apenas o desconhecimento da via») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Mais de 90% dos acidentes são causados por erro humano.</t>
+          <t>O comportamento dos condutores — é o que melhor responde ao enunciado (opção A)). Relativamente a «Qual a principal causa de sinistralidade rodoviária», a resposta adequada é A): O comportamento dos condutores.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Definição legal de acidente de trabalho (Código do Trabalho).</t>
+          <t>Um acontecimento sú bito e imprevisto, sofrido pelo trabalhador que se verifique no local e tempo de trabalho — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Um acidente ocorrido na rua que implique hospitalização») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Proteger as vias respiratórias do frio e do vento é essencial.</t>
+          <t>O uso do corta-vento na janela do condutor e a condução sempre que possível com o vidro fechado — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («A condução com as janelas abertas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Objetos perdidos devem ser entregues na empresa.</t>
+          <t>O procedimento adequado é Na sede ou agente da empresa (B)). Por exemplo, D) («Na residência do condutor da viatura») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Definição básica de transporte.</t>
+          <t>Meio de deslocação de pessoas ou bens a partir de um lugar para outro — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Movimentação entre dois modos de transporte») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Unimodal = apenas um modo (ex: só rodoviário).</t>
+          <t>Envolver apenas um modo de transporte — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Envolver transbordos para veículos da mesma modalidade») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Podem ser bilhetes simples ou passes/assina tura.</t>
+          <t>Simples ou de assinatura — é o que melhor responde ao enunciado (opção B)). Relativamente a «Nas carreiras urbanas e interurbanas de transporte de passageiros os bilhetes poderão ser», a resposta adequada é B): Simples ou de assinatura.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Uniforme e apresentação cuidada são obrigatórios.</t>
+          <t>Apresentar-se devidamente uniformizado e com aspecto cuidado — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Importunar os passageiros com exigências não justificadas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Expresso = longo curso, poucas paragens, veículos de gama alta.</t>
+          <t>Os serviços com distâncias não inferiores a 50 km, com  um número limitado de paragens intermédias e que utilizam exclusivamente veículos de classes II ou III — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Apenas serviços classificados como regulares especializados.») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Até 20 kg de bagagem por passageiro é gratuito.</t>
+          <t>20 Kg por passageiro — é o que melhor responde ao enunciado (opção D)). Por exemplo, a opção A) indica valores (40 Kg por passageiro) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Sim, mais de 90% dos acidentes são por erro humano.</t>
+          <t>A afirmação é verdadeira — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («A afirmação é falsa, porque a maior causa de acidente são as condições met…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Transportes + infraestruturas = desenvolvimento.</t>
+          <t>Sim, aliados a uma boa rede de infraestruturas viárias — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Sim, se for efetuado por autoestradas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Transportes públicos bons = menos carros na estrada = menos poluição.</t>
+          <t>Sim, pois uma boa rede de transportes públicos eficiente e pontual, fazia com que as pessoas a utilizassem mais e isto iria contribuir para um decréscimo da poluição atmosférica e diminuição dos engarrafamentos de trânsito — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Não, pois ninguém está interessado em utilizar os transportes públicos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Em Portugal, o transporte rodoviário é o mais usado.</t>
+          <t>Relativamente a «No que se refere ao transporte de passageiros, a rede de transporte mais utilizada no…», a resposta adequada é C): Rodoviária.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Pode ser por conta própria ou por conta de outrem.</t>
+          <t>Por conta própria e por conta de outrem — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Não se encontra regulamentado») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Sustentabilidade = económico + social + ambiental.</t>
+          <t>O procedimento adequado é Económico, social e ambiental (C)). Por exemplo, D) («Não é aplicável o conceito de sustentabilidade») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Tem de ser alguém com responsabilidade efetiva na gestão.</t>
+          <t>O procedimento adequado é Um administrador, diretor ou gerente que dirija a empresa em permanência e efetividade (D)). Por exemplo, B) («Pelo sócio maioritário da empresa») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Várias formas jurídicas são permitidas.</t>
+          <t>Sociedades comerciais, cooperativas e empresas públicas ou de capitais públicos — é o que melhor responde ao enunciado (opção D)). Por exemplo, A) («Apenas sociedades comerciais») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Alvará ou licença comunitária válida até 5 anos.</t>
+          <t>Um alvará ou licença comunitária emitidos por um prazo não superior a cinco anos. — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A atividade de transporte rodoviário de passageiros em autocarro não neces…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Contrato escrito com a entidade que contrata o serviço.</t>
+          <t>Um contrato escrito entre a empresa transportadora e a entidade interessada na prestação do serviço — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Um acordo entre duas pessoas: gerente da empresa de transportes e  o Presi…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Transportes públicos = por conta de outrem.</t>
+          <t>Transportes públicos ou por conta de outrem — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Transportes interurbanos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Internacionais = atravessam fronteiras.</t>
+          <t>Os que implicando atravessamento de fronteiras se desenvolvem parcialm ente em território português — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Os que visam satisfazer as necessidades de deslocação dentro de um municíp…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Ambos são transportes terrestres.</t>
+          <t>Trata-se de uma definição: Modos de transportes terrestres (opção A)). Na definição pedida («O transporte rodoviário e o transporte ferroviário são»), o conceito correto é Modos de transportes terrestres (opção A)).</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Serviços regulares = horários e tarifas fixos.</t>
+          <t>Transportes que asseguram o tr ansporte de passageiros segundo itinerário, frequência, horário e tarifas predeterminadas e em que podem ser tomados e largados passageiros em paragens previamente estabelecidas — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Transportes efetuados sem fins lucrativos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Unipessoal = apenas um sócio.</t>
+          <t>Uma sociedade por quotas, constituída por um único sócio — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Uma sociedade em que as quotas estão repartidas por uma pessoa singular e …») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Várias formas jurídicas são permitidas.</t>
+          <t>Sociedades comerciais, cooperativas, empresas públicas e outras entidades que reúnam os requisitos de acesso — é o que melhor responde ao enunciado (opção D)). Por exemplo, B) («Unicamente por sociedades comerciais») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>O objetivo principal é otimizar operações.</t>
+          <t>Optimizar o funcionamento operacional — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Melhorar a qualidade das paragens») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Os pesados têm ângulos mortos muito maiores.</t>
+          <t>O ângulos mortos são maiores — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A afirmação está certa apenas se se referir à condução nocturna») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Danos materiais = danos no veículo.</t>
+          <t>Danos no veículo acidentado — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Incapacidade parcial definitiva do condutor do veículo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Consequências humanas + materiais + financeiras.</t>
+          <t>Humana, material e financeira — é o que melhor responde ao enunciado (opção D)). Relativamente a «Os acidentes rodoviários com veículos pesados de mercadorias têm consequências de ordem», a resposta adequada é D): Humana, material e financeira.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>O encosto deve ficar ao nível da parte de trás da cabeça.</t>
+          <t>O procedimento adequado é À mesma altura da parte posterior da cabeça do motorista (D)). Por exemplo, B) («Debaixo da nuca do motorista») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Prejuízo para trabalhador, empresa e sociedade.</t>
+          <t>Todas as resposta são corretas — é o que melhor responde ao enunciado (opção D)). Relativamente a «Os acidentes laborais causam prejuízo», a resposta adequada é D): Todas as resposta são corretas.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Deve estar bem ajustado, nem largo nem apertado.</t>
+          <t>O procedimento adequado é Nem muito largo, nem muito apertado, ajustado ao corpo e bem fechado (C)). Por exemplo, D) («O cinto de segurança não é necessário em veiculos pesados») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Deve usar sempre o plural (nós/empresa).</t>
+          <t>O procedimento adequado é Utilizar o singular e não o plural referindo-se à empresa (C)). Por exemplo, B) («Ter sempre uma atitude respeitosa») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Dano = perda pessoal ou material.</t>
+          <t>Na definição pedida («A perda pessoal ou material consequente a um sinistro rodoviário denomina-se»), o conceito correto é Dano (opção C)).</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Capacidade de resposta = rapidez e precisão.</t>
+          <t>Trata-se de uma definição: Capacidade de resposta (opção D)).  Por exemplo, B) («Condicionantes da condução») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Velocidade que permite controlar o veículo sempre.</t>
+          <t>Velocidade que permite dominar o veículo perante qualquer obstáculo — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Límite inferior de velocidade permitido para a vía onde se circula») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Todas as alíneas são verdadeiras. No exame CAM do IMT, esta alternativa responde corretamente à questão «O motorista de uma empresa no decorrer de uma inspeção na estrada deverá».</t>
+          <t>O procedimento adequado é Todas as alíneas são verdadeiras (D)). Por exemplo, C) («Facilitar o exame dos documentos relacionados com o transporte») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Os braços devem estar ligeiramente flexionados.</t>
+          <t>Durante a condução, os braços do condutor não devem estar ligeiramente flexionados — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Durante a condução, não convém cruzar as mãos quando se gira o volante») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>A melhor postura é a que dá melhor eficácia com menos fadiga.</t>
+          <t>O enunciado pede a afirmação errada. C) é a incorreta porque: Deve-se tratar os clientes educadamente, dizendo: “o Senhor”, “a Senhora”, “Obrigado(a)”, “Por favor”. As alternativas A) A apresentação do motorista (higiene pessoal, cuidados com a roupa, etc.) … e B) O olhar amável e o sorriso são dois dos maiores trunfos de que o motorista… são afirmações corretas ou recomendadas.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Pressionar a artéria humeral. No exame CAM do IMT, esta alternativa responde corretamente à questão «Perante uma hemorragia num braço, o procedimento correto é».</t>
+          <t>Na situação «Perante uma hemorragia num braço, o procedimento correto é», o procedimento correto é Pressionar a artéria humeral (opção B)).</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Todos os setores podem ser sancionados.</t>
+          <t>Verdadeira, para todos os setores, incluindo o setor de transportes — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Falsa — não existe sanção para a contratação de imigrantes em situação irr…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Exercício físico é fundamental.</t>
+          <t>O procedimento adequado é Fazer exercício físico (D)). Por exemplo, C) («Consumir exclusivamente alimentos ricos em gordura animal») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Calor excessivo no habitáculo causa sonolência.</t>
+          <t>Ambiente muito quente no habitáculo do condutor — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Descansar regularmente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Todas as afirmações estão corretas.</t>
+          <t>Todas as respostas anteriores estão certas — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Os motoristas profissionais estão expostos a estas lesões») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Reino Unido (Inglaterra) não está no Schengen.</t>
+          <t>Relativamente a «Indique qual dos países abaixo indicados não pertence ao Espaço Schengen», a resposta adequada é A): Inglaterra.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Espanha pertence ao Espaço Schengen.</t>
+          <t>Relativamente a «Indique qual dos países abaixo indicados pertence ao Espaço Schengen», a resposta adequada é A): Espanha.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Nunca dar analgésicos sem orientação médica.</t>
+          <t>Em caso algum se deve ministrar analgésicos aos feridos — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Cobrir sempre para evitar perda de calor.</t>
+          <t>Deve tapá-los com um cobertor, tanto de verão como de inverno para evitar perdas de calor — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Deve evitar cobrir os feridos para não provocar choque térmico») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Nunca dar comida a feridos.</t>
+          <t>O procedimento adequado é Dar comida aos feridos (A)). Por exemplo, D) («Perguntar como se sentem») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Empresa de transporte produz serviços.</t>
+          <t>Produz serviços — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Apenas pode prestar serviços em território internacional») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Ergonomia = postura e condições de trabalho.</t>
+          <t>Relativamente a «A ergonomia tem por âmbito recomendar», a resposta adequada é A): Postura física.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Piso molhado = maior risco de aquaplanagem.</t>
+          <t>O procedimento adequado é Depois do pavimento estar bem molhado (C)). Por exemplo, D) («A chuva não causa a perda de aderência do pneus») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Motor desligado e quente facilita a drenagem.</t>
+          <t>O procedimento adequado é Desligado e quente, para que o óleo a substituir esteja mais diluído (B)). Por exemplo, D) («Ligado e frio, para o óleo estar mais viscoso») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Motor desligado e frio para medição correta.</t>
+          <t>O procedimento adequado é Desligado e frio (C)). Por exemplo, D) («Não importa o motor, o veículo é que deve estar num sítio plano») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Correntes para cargas pesadas e pontiagudas.</t>
+          <t>Mercadorias com arestas pontiagudas e pesadas — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Fardos de papel e de algodão») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Calço não pertence à suspensão.</t>
+          <t>Relativamente a «Dos seguintes órgãos do veículo, não pertence à suspensão», a resposta adequada é C): O calço.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Suspensão = absorver irregularidades e estabilizar.</t>
+          <t>Absorver irregularidades do piso e estabilizar os movimentos — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Diminuir o desgaste dos pneus») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Pedal esponjoso = líquido inadequado.</t>
+          <t>Um pedal esponjoso na travagem — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Um esforço excessivo na travagem») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Binário = força rotacional sobre um eixo.</t>
+          <t>O binário do motor é o momento de rotação (torque) aplicado ao veículo. A opção A) refere-se à potência; a B) aproxima-se do conceito de binário, mas no gabarito IMT a resposta aceite é D) porque nenhuma das três primeiras definições descreve o binário de forma completa e isolada.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Consumo específico = combustível por potência.</t>
+          <t>A quantidade de combustível utilizado para obter uma unidade de potência (kW ou CV) numa unidade de tempo — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O máximo esforço que podemos obter do motor a um determinado número ou fai…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Potência = capacidade de realizar trabalho por tempo.</t>
+          <t>A capacidade de realizar trabalho na unidade de tempo — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Nenhuma das respostas anteriores») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Água destilada para bateria.</t>
+          <t>O procedimento adequado é Adicionar água destilada (D)). Por exemplo, C) («Adicionar electrólito») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>3 eixos = até 38 toneladas.</t>
+          <t>O valor ou limite legal aplicável é 38 toneladas, indicado em D).  Por exemplo, a opção A) indica valores (26 toneladas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Limitador de velocidade = 85 km/h para pesados.</t>
+          <t>O valor ou limite legal aplicável é 85 Kms/hora, indicado em B).  Por exemplo, a opção A) indica valores (50 Kms/hora) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -9890,7 +9890,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Autocarro articulado 4+ eixos = 32 toneladas.</t>
+          <t>O valor ou limite legal aplicável é 32 toneladas, indicado em A).  Por exemplo, a opção B) indica valores (28 toneladas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Veículo &gt; 4 anos = inspeção anual.</t>
+          <t>O procedimento adequado é Anualmente (C)). Por exemplo, B) («De três em três meses») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Requisitos de acesso: idoneidade + capacidade profissional + financeira.</t>
+          <t>O procedimento adequado é Cumpre os requisitos de acesso à atividade (idoneidade capacidade profissional e capacidade financeira) (B)). Por exemplo, D) («Não tem dívidas ao fisco nem à Segurança Social») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Alta qualidade = 100+ km, categoria III, poucas paragens.</t>
+          <t>Percurso não inferior a 100 kms, veículos da categoria III, número limitado de paragens e assistente de bordo — é o que melhor responde ao enunciado (opção A)). Por exemplo, a opção B) indica valores (Percurso não inferior a 200 kms, sem paragens intermédias e veículos da ca…) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Falta não suprida em 1 ano = caducidade do alvará.</t>
+          <t>Caduca o alvará para o exercício da atividade — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Caducam as concessões que a empresa seja titular») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Folha de itinerário para serviços ocasionais.</t>
+          <t>Trata-se de uma definição: Documento descritivo do serviço ou folha de itinerário (opção A)).  Por exemplo, D) («Certificado do serviço») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) No prazo de 30 dias a contar da data da ocorrência. No exame CAM do IMT, esta alternativa responde corretamente à questão «A cessação de funções do administrador, diretor ou gerente da empresa, que assegure o requisito de capacidade profiss...».</t>
+          <t>O procedimento adequado é No prazo de 30 dias a contar da data da ocorrência (C)). Por exemplo, a opção A) indica valores (No prazo de 20 dias a contar da data da ocorrência) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Balanço ou garantia bancária.</t>
+          <t>Por duplicado ou cópia autenticada do último balanço apresentado para efeitos do imposto sob re o rendimento das pessoas coletivas (IRC) ou por garantia bancária — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Pelo extracto da conta bancária de qualquer dos gerentes») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Não aprovação = caducidade da licença do veículo.</t>
+          <t>A caducidade da respetiva licença — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A cessação da exploração da carreira à qual o veículo esteja adstrito») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Várias formas jurídicas permitidas.</t>
+          <t>Sociedades comerciais, cooperativas e empresas públicas ou de capitais públicos — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Apenas sociedades em nome colectivo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Contrato escrito obrigatório.</t>
+          <t>O procedimento adequado é Estabelecer um contrato reduzido a escrito com a entidade interessada no serviço (A)). Por exemplo, D) («Preencher previamente uma folha de itinerário») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Verificar sempre (acesso e exercício).</t>
+          <t>O procedimento adequado é No acesso e durante o exercício da atividade (D)). Por exemplo, C) («Somente quando for requerido o acesso à atividade») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Várias formas de aquisição permitidas.</t>
+          <t>Adquiridos em regime de locação financeira ou outro contrato de locação, ou em regime de propriedade plena. — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Mediante exclusivo financiamento público») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -10622,7 +10622,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Itinerário, frequência, paragens, categoria.</t>
+          <t>O procedimento adequado é A categoria dos passageiros a transportar, itinerário, frequência e paragens (A)). Por exemplo, D) («A origem e destino, número de passageiros e locais da sua tomada e largada») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Cabotagem = transportes nacionais por não residentes.</t>
+          <t>Cabotagem — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Transportes combinados») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Dístico + folha de itinerário.</t>
+          <t>O procedimento adequado é Dístico identificativo do serviço e folha de itinerário (C)). Por exemplo, D) («Cópia do contrato de transporte e cópia certificada de licença comunitária») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Com o pedido de acesso à atividade. No exame CAM do IMT, esta alternativa responde corretamente à questão «A comprovação do requisito de idoneidade, é exigida aos administradores diretores ou gerentes de empresas de transpor...».</t>
+          <t>Com o pedido de acesso à atividade — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Com o pedido de admissão a exame de capacidade profissional») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>30 dias, sob pena de coima.</t>
+          <t>O procedimento adequado é No prazo de trinta dias sob pena de aplicação de uma coima (A)). Por exemplo, D) («No prazo de cinco anos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Interdição profissional = perda de idoneidade.</t>
+          <t>Na medida de interdição do exercício da profissão independentemente da natureza do crime — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Na pena acessória de inibição de conduzir») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Serviços regulares especializados = categorias específicas.</t>
+          <t>Serviços regulares especializados — é o que melhor responde ao enunciado (opção D)). Por exemplo, B) («Transportes de cabotagem») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Ocasionais + regulares especializados nacionais.</t>
+          <t>Serviços ocasionais e serviços regulares especializados de âmbito nacional — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Todo o tipo de transportes») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Municipais e intermunicipais.</t>
+          <t>Municipais e intermunicipais — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Serviços regulares e serviços expresso») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) 20 kg por passageiro. No exame CAM do IMT, esta alternativa responde corretamente à questão «É obrigatório o transporte gratuito da bagagem pessoal do passageiro, em veículos afetos a carreiras interurbanas e a...».</t>
+          <t>20 kg por passageiro — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (10 kg por passageiro) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Certificado para transportes particulares.</t>
+          <t>Na situação «Uma empresa que efetue transportes nacionais particulares ou por conta própria, dos seus…», o procedimento correto é Certificado (opção A)).</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Caduca o alvará. No exame CAM do IMT, esta alternativa responde corretamente à questão «Decorrido um ano após a falta superveniente de qualquer um dos requisitos de idoneidade, capacidade profissional e ca...».</t>
+          <t>Caduca o alvará — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («A empresa é obrigada a duplicar o capital social») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) É intransmissível. No exame CAM do IMT, esta alternativa responde corretamente à questão «O alvará ou licença comunitária para o exerc ício da atividade de transportes rodoviários de mercadorias por conta de...».</t>
+          <t>O alvará ou licença comunitária de transporte rodoviário de mercadorias por conta de outrem é pessoal e intransmissível — não passa com a venda da empresa ou dos veículos. Daí a opção D) (É intransmissível).</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) O veículo é utilizado no conjunto da sua capacidade de carga por um único expedidor. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para efeitos do Decreto -Lei n.º 257/2007, de 16 de Julho, são considerados transportes em regime de carga completa o...».</t>
+          <t>Transporte em regime de carga completa significa que o veículo é utilizado na totalidade da sua capacidade por um único expedidor (um cliente por serviço). A opção D) exprime isso. A opção A) descreve carga fracionada, em que vários expedidores partilham o mesmo veículo.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Desde que tenha havido anterior condenação pela prática da mesma infração. No exame CAM do IMT, esta alternativa responde corretamente à questão «Com a aplicação da coima pela realização de transportes rodoviários de mercadorias por entidade diversa do titular do...».</t>
+          <t>Desde que tenha havido anterior condenação pela prática da mesma infração — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («Desde que não cumpra os requisitos de acesso e exercício da atividade») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Duplicado ou cópia autenticada do último balanço apresentado para efeitos de IRC. No exame CAM do IMT, esta alternativa responde corretamente à questão «A prova do cumprimento do requisito de capacidade financeira, durante o exercício da atividade, pode ser feita atravé...».</t>
+          <t>Duplicado ou cópia autenticada do último balanço apresentado para efeitos de IRC — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Certificado passado por uma associação de transportadores») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) A guia de transporte. No exame CAM do IMT, esta alternativa responde corretamente à questão «Qual dos documentos seguintes deve estar a bordo do veículo durante a realização de um transporte rodoviário de merca...».</t>
+          <t>O procedimento adequado é A guia de transporte (C)). Por exemplo, A) («O bilhete de identidade /cartão do cidadão») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Um transportador celebra com outro transportador um novo contrato baseado nos direitos que lhe advêm de um primeiro contrato. No exame CAM do IMT, esta alternativa responde corretamente à questão «No âmbito do transporte rodoviário de mercadorias, há subcontratação quando».</t>
+          <t>Um transportador celebra com outro transportador um novo contrato baseado nos direitos que lhe advêm de um primeiro contrato — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Não existe a figura do subcontrato») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Nome ou denominação social, sede e número de alvará. No exame CAM do IMT, esta alternativa responde corretamente à questão «São elementos de preenchimento obrigatório pelo transportador, na guia de transporte».</t>
+          <t>Nome ou denominação social, sede e número de alvará — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A identificação do expedidor») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -11674,7 +11674,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Estão sujeitos a licenciamento, desde que afetos ao transporte rodoviário de mercadorias por conta de outrem. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nos termos do Decreto-Lei n.º 257/2007, de 16 de Julho, os veículos automóveis com peso bruto igual ou superior a 2,5...».</t>
+          <t>Estão sujeitos a licenciamento, desde que afetos ao transporte rodoviário de mercadorias por conta de outrem — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Só podem ser licenciados se estiverem afetos à realização de transportes p…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Prestação do serviço de transporte com faturação ou recibo em regime de atividade liberal ou existência de contrato para utilização do veículo entre a empresa titular do alvará e um terceiro. No exame CAM do IMT, esta alternativa responde corretamente à questão «São considerados como  efetuados por entidade diversa do titular do alvará, os transportes em que se verifique alguma...».</t>
+          <t>Prestação do serviço de transporte com faturação ou recibo em regime de atividade liberal ou existência de contrato para utilização do veículo entre a empresa titular do alvará e um terceiro — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Prestação de serviço de transpor te não acompanhado de fatura, guia de rem…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Não é necessário obter qualquer autorização ou licenciamento. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para realizar uma largada de pombos correio em Bragança, foi cedido a título gratuito, à Associação Columbófila do Po...».</t>
+          <t>Não é necessário obter qualquer autorização ou licenciamento — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («É suficiente proceder ao licenciamento do veículo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Quando se trate da recolha de mercadorias destinadas a serem agrupadas no armazém do transportador para posterior distribuição. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os transportes rodoviários de mercadorias por conta de outrem são descritos numa guia de transporte que deve acompanh...».</t>
+          <t>O procedimento adequado é Quando se trate da recolha de mercadorias destinadas a serem agrupadas no armazém do transportador para posterior distribuição (B)). Por exemplo, D) («Quando o percurso do transporte não for superior a 100 quilómetros») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Sancionamento com coima. No exame CAM do IMT, esta alternativa responde corretamente à questão «Considerando que o licenciamento dos veículos automóveis de mercadorias é uma condição de acesso ao mercado de transp...».</t>
+          <t>Sancionamento com coima — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Pagamento imediato de coima») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -11974,7 +11974,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Caducam todas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando ocorrer a caducidade da licença para o exercício da atividade, as licenças dos veículos».</t>
+          <t>Caducam todas — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Mantêm-se válidas apenas por um ano») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Formular reservas na guia de transporte. No exame CAM do IMT, esta alternativa responde corretamente à questão «Na operação de carga sempre que o transportador verifique defeito na mercadoria, pode».</t>
+          <t>Formular reservas na guia de transporte — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Denunciar os defeitos ao destinatário no ato da entrega») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Forma retangular, inscrição “TP” e indicação do número de alvará do transportador. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os veículos automóveis licenciados para o transporte rodoviário de mercadorias por conta de outrém, devem ostentar di...».</t>
+          <t>O procedimento adequado é Forma retangular, inscrição “TP” e indicação do número de alvará do transportador (B)). Por exemplo, A) («Forma retangular, inscrição “TP” e designação da empresa proprietária do v…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Apenas sociedades comerciais. No exame CAM do IMT, esta alternativa responde corretamente à questão «Podem aceder ao exercício da atividade de transporte rodoviário de mercadorias por conta de outrem, através de veícul...».</t>
+          <t>Apenas sociedades comerciais — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Qualquer pessoa coletiva ou singular») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Tem um prazo de validade não superior a 5 anos, renovável mediante comprovação de que se mantêm os requisitos de acesso e de exercício à atividade. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nos termos do D ecreto-Lei n.º 257/2007, de 16 de Julho, o alvará que habilita a empresa para o exercício da atividad...».</t>
+          <t>Tem um prazo de validade não superior a 5 anos, renovável mediante comprovação de que se mantêm os requisitos de acesso e de exercício à atividade — é o que melhor responde ao enunciado (opção A)). Por exemplo, a opção C) indica valores (Tem um prazo de validade de 10 anos, renovável mediante a comprovação de q…) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Por duplicado ou cópia autenticada do último balanço apresentado para efeitos do imposto sobre o rendimento das pessoas colectivas (IRC) ou garantia bancária. No exame CAM do IMT, esta alternativa responde corretamente à questão «Durante o exercício da atividade, a comprovação do requisito de capacidade financeira faz-se».</t>
+          <t>Por duplicado ou cópia autenticada do último balanço apresentado para efeitos do imposto sobre o rendimento das pessoas colectivas (IRC) ou garantia bancária — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Pelo livro de registo das contas da empresa») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Identificação do expedidor, do transportador e do destinatário. No exame CAM do IMT, esta alternativa responde corretamente à questão «A guia de transporte é um docum ento que prova a existência de um contrato de transporte de mercadorias por conta de ...».</t>
+          <t>O procedimento adequado é Identificação do expedidor, do transportador e do destinatário (C)). Por exemplo, D) («Instruções do expedidor relativamente a procedimentos de manuseamento da m…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Preencher total ou parcialmente a guia de transporte, considerando -se que o faz em nome do expedidor. No exame CAM do IMT, esta alternativa responde corretamente à questão «A guia de transporte contém elementos de preenchimento obrigatório, sendo um a identificação do expedidor e do tr ans...».</t>
+          <t>O procedimento adequado é Preencher total ou parcialmente a guia de transporte, considerando -se que o faz em nome do expedidor (C)). Por exemplo, D) («Utilizar a guia de um contrato anterior») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) A guia de transporte. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para efeitos de prova de que estamos perante um transporte rodoviário de merc adorias por conta de outrem,  as entida...».</t>
+          <t>O procedimento adequado é A guia de transporte (A)). Por exemplo, D) («Os documentos de constituição da empresa») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Quando se trate de recolha de mercadorias no armazém do transportador para posterior distribuição. No exame CAM do IMT, esta alternativa responde corretamente à questão «A guia de remessa exigida pela lei fi scal para controlo do Imposto sobre o Valor Acrescentado (IVA) pode substituir ...».</t>
+          <t>Quando se trate de recolha de mercadorias no armazém do transportador para posterior distribuição — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Nos casos em que haja acordo entre expedidor e destinatário») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Instituto da Mobilidade e dos Transportes. No exame CAM do IMT, esta alternativa responde corretamente à questão «O registo das empresas licenciadas para o exercicio da atividade de transportes rodoviarios de mercadorias por conta ...».</t>
+          <t>Instituto da Mobilidade e dos Transportes — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Conservatoria do Registo Automovel») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Sempre que seja solicitado à empresa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os requisitos de acesso e de exercício da atividade de transportes rodoviários de mercadorias por conta de outrem, de...».</t>
+          <t>O procedimento adequado é Sempre que seja solicitado à empresa (C)). Por exemplo, D) («Apenas de cinco em cinco anos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) O infrator. No exame CAM do IMT, esta alternativa responde corretamente à questão «Numa situação de excesso de carga em que a entidade fiscalizadora determina a imobilização do veículo até que a carga...».</t>
+          <t>O infrator — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («O Instituto da Mobilidade e dos Transportes») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Não estão abrangidos pelo regime de licenciamento na atividade de transporte rodoviário de mercadorias por conta de outrem. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os veículos aos quais estejam ligados, de forma permanente e exclusiva, equipamentos ou máquinas».</t>
+          <t>Não estão abrangidos pelo regime de licenciamento na atividade de transporte rodoviário de mercadorias por conta de outrem — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Só estão sujeitos a licenciame nto obrigatório quando o peso bruto dos veí…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) € 125 000. No exame CAM do IMT, esta alternativa responde corretamente à questão «mercadorias por conta de outrem A empresa XP, Ldª, deve, para início da atividade de  transporte rodoviário de mercad...».</t>
+          <t>O procedimento adequado é € 125 000 (A)). Por exemplo, a opção B) indica valores (€ 50 000) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) € 254 000. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma empresa licenciada na atividade de transportes rodoviários de mercadorias por conta de outrem qu e no desenvolvim...».</t>
+          <t>€ 254 000 — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (€ 150 000) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -12934,7 +12934,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Sempre que se verificar a caducidade do alvará ou da licença comunitária e no caso de transmissão da propriedade ou posse do veículo. No exame CAM do IMT, esta alternativa responde corretamente à questão «As licenças dos veículos afetos ao transporte rodoviário de mercadorias  por conta de outrem caducam».</t>
+          <t>Sempre que se verificar a caducidade do alvará ou da licença comunitária e no caso de transmissão da propriedade ou posse do veículo — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Quando o veículo completar vinte anos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Por todos os gerentes, administradores ou diretores da sociedade. No exame CAM do IMT, esta alternativa responde corretamente à questão «O requisito de idoneidade, numa sociedade que tenha como objeto a atividade de transporte rodoviário de mercadorias p...».</t>
+          <t>O procedimento adequado é Por todos os gerentes, administradores ou diretores da sociedade (D)). Por exemplo, C) («Somente pelos sócios que possuam mais de 30% do capital social») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Nos veículos automóveis de mercadorias licenciados para transportes rodoviários de mercadorias por conta de outrem. No exame CAM do IMT, esta alternativa responde corretamente à questão «A colocação de distintivos de identificação - TP - em veículos de transporte de mercadorias, utilizados em regime de ...».</t>
+          <t>Nos veículos automóveis de mercadorias licenciados para transportes rodoviários de mercadorias por conta de outrem — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Em todo o tipo de veículos, desde que alugados em regime de “aluguer de lo…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Mantendo o veículo dentro das condições e recomendações do fabricante. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um condutor de um veículo pesado pode contribuir para reduzir a poluição».</t>
+          <t>Mantendo o veículo dentro das condições e recomendações do fabricante — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Viajando a alta velocidade, de modo a que o tempo de duração da viagem dim…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) 37 toneladas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O peso bruto máximo para os conjuntos veículo a motor-reboque de quatro eixos é de».</t>
+          <t>O valor ou limite legal aplicável é 37 toneladas, indicado em B).  Por exemplo, a opção A) indica valores (29 toneladas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) 25% do peso bruto do veículo ou conjunto de veículos. No exame CAM do IMT, esta alternativa responde corretamente à questão «O peso bruto no eixo ou eixos motores de um veículo ou conjunto de veículos não pode ser inferior a».</t>
+          <t>O valor ou limite legal aplicável é 25% do peso bruto do veículo ou conjunto de veículos, indicado em C).  Por exemplo, a opção A) indica valores (15% do peso bruto do veículo ou conjunto de veículos) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -13294,7 +13294,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) 32 toneladas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O peso bruto máximo para os veículos de quatro eixos é de».</t>
+          <t>O valor ou limite legal aplicável é 32 toneladas, indicado em B).  Por exemplo, a opção A) indica valores (38 toneladas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) 32 toneladas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O peso bruto máximo de um veículo (trator e semi-reboque) com 3 eixos é de».</t>
+          <t>O valor ou limite legal aplicável é 32 toneladas, indicado em C).  Por exemplo, a opção A) indica valores (22 toneladas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) 15% do peso bruto total. No exame CAM do IMT, esta alternativa responde corretamente à questão «Num veículo que tenha mais de um eixo à retaguarda, o peso bruto que incide sobre o eixo da frente não pode ser infer...».</t>
+          <t>O valor ou limite legal aplicável é 15% do peso bruto total, indicado em A).  Por exemplo, a opção B) indica valores (20% do peso bruto total) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) 26 toneladas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O peso bruto máximo para veículos de 3 eixos, é de».</t>
+          <t>O valor ou limite legal aplicável é 26 toneladas, indicado em C).  Por exemplo, a opção A) indica valores (18 toneladas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Verdadeira para todos os veículos pesados. No exame CAM do IMT, esta alternativa responde corretamente à questão «O peso bruto máximo dos v eículos aumenta, até determinado limite, em função do maior 'número de eixos desses veículo...».</t>
+          <t>Verdadeira para todos os veículos pesados — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Falsa porque o peso bruto não está relacionado com o número de eixos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) A um conjunto de operações regulares, nos termos da manutenção preventiva. No exame CAM do IMT, esta alternativa responde corretamente à questão «A utilização de um veículo conduz ao desgaste e/ou a avaria de alguns dos sistemas que o constituem. A fim de manter ...».</t>
+          <t>O procedimento adequado é A um conjunto de operações regulares, nos termos da manutenção preventiva (A)). Por exemplo, D) («Ao parqueamento dos veículos que apresentem problemas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Garantir a integridade física dos trabalhadores intervenientes na operação, a segurança rodoviária e evitar avarias nas mercadorias transportadas. No exame CAM do IMT, esta alternativa responde corretamente à questão «A estiva ou arrumação da carga num veículo deverá obedecer a um planeamento prévio. A peação e ou travamento da carga...».</t>
+          <t>O procedimento adequado é Garantir a integridade física dos trabalhadores intervenientes na operação, a segurança rodoviária e evitar avarias nas mercadorias transportadas (D)). Por exemplo, C) («Utilizar os diversos equipamentos existentes no veículo (argolas, ganchos,…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) A carga máxima admissível, determinada pelo peso ou cubicagem máxima admitida. No exame CAM do IMT, esta alternativa responde corretamente à questão «No planeamento do enchimento da caixa de carga do veículo é imperativo considerar-se».</t>
+          <t>A carga máxima admissível, determinada pelo peso ou cubicagem máxima admitida — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O espaço entre os lotes da mercadoria a fim de garantir o equilíbrio do ve…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -13774,7 +13774,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Preencher os espaços com madeiras, esferovite, cartão prensado ou outro tipo de materiais que absorvam os choques criados ao longo da viagem. No exame CAM do IMT, esta alternativa responde corretamente à questão «Após a estiva de uma determinada carga geral num veículo, verifico u-se a existência de espaços entre as mercadorias....».</t>
+          <t>Trata-se de uma definição: Preencher os espaços com madeiras, esferovite, cartão prensado ou outro tipo de materiais que absorvam os choques criados ao longo da viagem (opção A)).  Por exemplo, D) («Voltar a arrumar os volumes, de modo a não deixar espaço entre o topo dos …») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -13834,7 +13834,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Controlar o seu veículo todos os dias, antes da partida (pneus, luzes, travões, combustível, níveis de óleo, bateria, etc...). No exame CAM do IMT, esta alternativa responde corretamente à questão «Para garantia, quer da própria segurança, quer da segurança dos outros utentes, o condutor de um veículo de mercadori...».</t>
+          <t>O procedimento adequado é Controlar o seu veículo todos os dias, antes da partida (pneus, luzes, travões, combustível, níveis de óleo, bateria, etc...) (C)). Por exemplo, D) («Verificar todas as semanas a pressão dos pneus») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Do expedidor, do transportador e do destinatário. No exame CAM do IMT, esta alternativa responde corretamente à questão «São elementos essenciais do contrato de transporte, devendo ser obrigatoriamente descritas na guia de transporte, a s...».</t>
+          <t>O procedimento adequado é Do expedidor, do transportador e do destinatário (C)). Por exemplo, D) («Apenas do destinatário») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Oito horas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nos termos do estabelecido no Código do Trabalho, o período normal de trabalho diário não pode exceder».</t>
+          <t>Relativamente a «Nos termos do estabelecido no Código do Trabalho, o período normal de trabalho diário…», a resposta adequada é C): Oito horas.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) No mês seguinte ao do início do trabalho. No exame CAM do IMT, esta alternativa responde corretamente à questão «A inscrição dos trabalhadores no Regime da Segurança Social deve ser efetuada».</t>
+          <t>O procedimento adequado é No mês seguinte ao do início do trabalho (C)). Por exemplo, D) («Quando o trabalhador adoecer») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Trabalho a termo, certo ou incerto. No exame CAM do IMT, esta alternativa responde corretamente à questão «Regra geral, os contratos de trabalho são consensuais ou verba is, contudo a lei prevê exceções a esta regra, exigind...».</t>
+          <t>Trabalho a termo, certo ou incerto — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Trabalho independente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -14134,7 +14134,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) A entidade empregadora. No exame CAM do IMT, esta alternativa responde corretamente à questão «A responsabilidade pela inscrição dos trabalhadores no Regime da Segurança Social recai sobre».</t>
+          <t>A entidade empregadora — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («O próprio trabalhador») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -14194,7 +14194,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Todo o trabalho efetuado entre as 21 horas de um dia e as 9 horas do dia seguinte. No exame CAM do IMT, esta alternativa responde corretamente à questão «Considera-se período de trabalho noturno o compreendido entre».</t>
+          <t>Todo o trabalho efetuado entre as 21 horas de um dia e as 9 horas do dia seguinte — é o que melhor responde ao enunciado (opção D)). Por exemplo, a opção A) indica valores (As 22 horas de um dia e as 7 horas do dia seguinte) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) 25%. No exame CAM do IMT, esta alternativa responde corretamente à questão «O período de trabalho noturno é remunerado, relativamente à retribuição fi xada para trabalho equivalente prestado du...».</t>
+          <t>25% — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (10%) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -14314,7 +14314,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Ser um acordo celebrado livremen te entre as partes contratantes, podendo ou não ser reduzido a escrito. No exame CAM do IMT, esta alternativa responde corretamente à questão «Regra geral, o contrato de trabalho subordinado caracteriza-se por».</t>
+          <t>Ser um acordo celebrado livremen te entre as partes contratantes, podendo ou não ser reduzido a escrito — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Ser um contrato que pode ser celebrado por pessoa de idade inferior a 16 a…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -14374,7 +14374,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Com a celebração do contrato de trabalho. No exame CAM do IMT, esta alternativa responde corretamente à questão «O direito a férias é adquirido pelo trabalhador».</t>
+          <t>Com a celebração do contrato de trabalho — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Após um período de trabalho efetivo a combinar com o empregador») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) A uma retribuição igual à que receberia se estivesse a trabalhar, acrescida de um montante igual a essa retribuição. No exame CAM do IMT, esta alternativa responde corretamente à questão «Durante o período de férias a retribuição do trabalhador por conta de outrem corresponde».</t>
+          <t>A uma retribuição igual à que receberia se estivesse a trabalhar, acrescida de um montante igual a essa retribuição — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Ao seu vencimento mensal acrescida de uma gratificação em função do seu de…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -14494,7 +14494,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Exercer o direito de contratação coletiva em nome dos interesses dos seus associados. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os sindicatos, de acordo com o estipulado na Constituição da República Portuguesa, têm competência para».</t>
+          <t>Exercer o direito de contratação coletiva em nome dos interesses dos seus associados — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Desenvolver uma qualquer atividade empresarial») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -14554,7 +14554,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Pela entidade patronal através de guia de pagamento. No exame CAM do IMT, esta alternativa responde corretamente à questão «As contribuições para a Segurança Social da responsabilidade dos trabalhadores devem ser pagas».</t>
+          <t>O procedimento adequado é Pela entidade patronal através de guia de pagamento (B)). Por exemplo, D) («Por declaração de rendimentos no final de cada ano civil») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) É controlado através de um livrete individual aprovado pelo organismo responsável pelas condições de trabalho. No exame CAM do IMT, esta alternativa responde corretamente à questão «O horário de trabalho de um motorista de uma empresa que conduza veículos automóveis com peso bruto inferior a 3,5 to...».</t>
+          <t>É controlado através de um livrete individual aprovado pelo organismo responsável pelas condições de trabalho — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Não carece de qualquer controle em virtude do trabalho decorrer fora da em…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -14674,7 +14674,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) As férias são interrompidas, desde que o trabalhador participe a doença à entidade patronal. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se o trabalhador adoecer durante o gozo das férias».</t>
+          <t>As férias são interrompidas, desde que o trabalhador participe a doença à entidade patronal — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Os dias de doença são descontados nas férias do ano seguinte») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -14734,7 +14734,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Contrato de trabalho. No exame CAM do IMT, esta alternativa responde corretamente à questão «O contrato pelo qual uma pessoa s e obriga, mediante retribuição, a prestar a sua atividade intelectual ou manual a o...».</t>
+          <t>Contrato de trabalho — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Contrato de prestação de serviços») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) O termo do prazo. No exame CAM do IMT, esta alternativa responde corretamente à questão «A caducidade é um a das formas de cessação do contrato de trabalho, que ocorre quando se verifica uma das seguintes s...».</t>
+          <t>O termo do prazo — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A falta do trabalhador por mais de três dias consecutivos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) No caso de ocorrer justa causa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um trabalhador pode fazer cessar o seu contrato de trabalho, sem observância de aviso prévio».</t>
+          <t>No caso de ocorrer justa causa — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Se a empresa não pagar as quotas ao seu sindicato») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) O comportamento culposo do trabalh ador que inviabilize  a manutenção da relação de trabalho. No exame CAM do IMT, esta alternativa responde corretamente à questão «Constitui justa causa de despedimento promovido pela entidade empregadora».</t>
+          <t>O comportamento culposo do trabalh ador que inviabilize  a manutenção da relação de trabalho — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Não existe o conceito de justa causa na legislação laboral nacional») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) A conversão do contrato em contrato sem termo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se um contrato de trabalho a termo certo for celebrado sem indicação do pra zo estipulado e do motivo justificativo, ...».</t>
+          <t>A conversão do contrato em contrato sem termo — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A punição da entidade empregadora através de multa») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -15034,7 +15034,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Pode exercer qualquer outra atividade remunerada se a entidade patronal o autorizar a isso. No exame CAM do IMT, esta alternativa responde corretamente à questão «Durante o gozo das férias, o trabalhador».</t>
+          <t>Pode exercer qualquer outra atividade remunerada se a entidade patronal o autorizar a isso — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Não pode sair do concelho da sede da empresa sem autorização da entidade p…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) 40 horas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Regra geral, o limite máximo do período normal de trabalho semanal a que um trabalhador se pode obrigar a prestar é de».</t>
+          <t>40 horas — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (36 horas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Realiza um trabalho autónomo e apresenta o respetivo resultado. No exame CAM do IMT, esta alternativa responde corretamente à questão «Tendo um estatuto diferente do trabalhador por conta de outrem, o prestador de serviços».</t>
+          <t>Realiza um trabalho autónomo e apresenta o respetivo resultado — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Tem direito ao gozo de férias remuneradas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Um conjunto de trabalhadores e um conjunto de entidades patronais, através das respetivas associações sindicais e patronais. No exame CAM do IMT, esta alternativa responde corretamente à questão «O traba lho subordinado, não obstante ter subjacente uma relação individual de trabalho, pode ser regulado por conven...».</t>
+          <t>Um conjunto de trabalhadores e um conjunto de entidades patronais, através das respetivas associações sindicais e patronais — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Um trabalhador e uma entidade patronal») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) É considerada falta justificada. No exame CAM do IMT, esta alternativa responde corretamente à questão «A não comparência do trabalhador no local de trabalho por motivo de doença, não devidamente comprovada».</t>
+          <t>É considerada falta justificada — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («É considerado trabalho efetivo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Pelo trabalhador e pela entidade patronal. No exame CAM do IMT, esta alternativa responde corretamente à questão «A contribuição q ue incide sobre a remuneração do trabalhador, no âmbito do financiamento do regime geral da seguranç...».</t>
+          <t>Pelo trabalhador e pela entidade patronal — é o que melhor responde ao enunciado (opção C)). Relativamente a «A contribuição q ue incide sobre a remuneração do trabalhador, no âmbito do…», a resposta adequada é C): Pelo trabalhador e pela entidade patronal.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) O despedimento for considerado injustificado pelo trabalhador e pelo sindicato. No exame CAM do IMT, esta alternativa responde corretamente à questão «O trabalhador, após ter sido objeto de despedimento promovido pela entidade empregadora, tem direito a ser reintegrad...».</t>
+          <t>O despedimento for considerado injustificado pelo trabalhador e pelo sindicato — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A ilicitude do despedimento seja declarada por tribunal judicial em ação i…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) A realização de transportes nacionais por transportadores não residentes. No exame CAM do IMT, esta alternativa responde corretamente à questão «No âmbito de um transporte rodoviário de mercadorias, cabotagem é».</t>
+          <t>A realização de transportes nacionais por transportadores não residentes — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («A realização de qualquer transporte desde que o veículo esteja vazio») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) 18 toneladas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O peso máximo autorizado de um reboque de 2 eixos é de».</t>
+          <t>18 toneladas — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (15 toneladas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -15574,7 +15574,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) 1 ano. No exame CAM do IMT, esta alternativa responde corretamente à questão «De acordo com o Regulamento (CE) nº 561/2006, do Parlamento Europeu e do Conselho, de 15 de março, Conselho, de 20 de...».</t>
+          <t>O procedimento adequado é 1 ano (D)). Por exemplo, a opção A) indica valores (5 anos) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Cuja velocidade máxima autorizada ultrapasse os 40 km/hora. No exame CAM do IMT, esta alternativa responde corretamente à questão «É obrigatória a instalação e utilização do tacógrafo nos veículos destinados ao transporte rodoviário de mercadorias».</t>
+          <t>Cuja velocidade máxima autorizada ultrapasse os 40 km/hora — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção C) indica valores (Afetos ao transporte de mercadorias e cujo peso máximo autorizado, incluin…) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Particular ou por conta própria. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um transporte em que as mercadorias transportadas, tenham sido compradas pelo proprietário do veículo e este for por ...».</t>
+          <t>Particular ou por conta própria — é o que melhor responde ao enunciado (opção C)). Por exemplo, A) («Público ou por conta de outrem») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -15754,7 +15754,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Idoneidade, capacidade profissional e capacidade financeira. No exame CAM do IMT, esta alternativa responde corretamente à questão «As empresas que pretendam aceder ao transporte rodoviário de mercadorias por conta de outrem devem reunir os requisitos».</t>
+          <t>O procedimento adequado é Idoneidade, capacidade profissional e capacidade financeira (B)). Por exemplo, D) («Estar obrigatoriamente constituídas como sociedades por quotas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) 14 dias úteis de férias. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se um trabalhador for contratado em 1/03/2009, no dia 2/10/2009, tem direito a gozar».</t>
+          <t>14 dias úteis de férias — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (22 dias úteis de férias) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -15874,7 +15874,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) 6 metros. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os veículos devem ser sinalizad os lateralmente com luzes ou reflectores de cor âmbar, sempre que o respetivo comprim...».</t>
+          <t>A questão relaciona-se com condução segura, prevenção de acidentes e comportamento ao volante. No caso «Os veículos devem ser sinalizad os lateralmente com luzes ou reflectores de cor âmbar, sempre que o…», a opção A) é a alternativa que melhor se aplica ao caso: 6 metros. A opção B) («12 metros») apresenta valores diferentes dos exigidos nesta situação A opção C) («16 metros») apresenta valores diferentes dos exigidos nesta situação.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -15934,7 +15934,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) 18 meses. No exame CAM do IMT, esta alternativa responde corretamente à questão «A duração máxima de um contrato de trabalho a termo certo, incluindo renovações, com um trabalhador à procura do prim...».</t>
+          <t>18 meses — é o que melhor responde ao enunciado (opção D)). Por exemplo, a opção A) indica valores (6 meses) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -15994,7 +15994,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Tiver concluído a escolaridade obrigatória e se tratar de trabalhos leves. No exame CAM do IMT, esta alternativa responde corretamente à questão «O menor com idade inferior a 16 anos não pode ser contratado para realizar uma atividade remunerada prestada com auto...».</t>
+          <t>Tiver concluído a escolaridade obrigatória e se tratar de trabalhos leves — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («O contrato for reduzido a escrito») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) 90 dias. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nos contratos por tempo indeterminado, para a generalidade dos trabalhadores, o período experimental tem a seguinte d...».</t>
+          <t>90 dias — é o que melhor responde ao enunciado (opção A)). Por exemplo, a opção B) indica valores (180 dias) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Se destinarem ao transporte de determinadas categorias de passageiros, com exclusão de  outros, nomeadamente os estudantes entre o domicílio e a escola. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os serviços regulares especializados de transporte coletivo de passageiros, em veículos pesados, caracterizam-se por».</t>
+          <t>Se destinarem ao transporte de determinadas categorias de passageiros, com exclusão de  outros, nomeadamente os estudantes entre o domicílio e a escola — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Assegurarem o transporte de passageiros, quando se revelarem insuficientes…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -16174,7 +16174,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Automóveis de passageiros com lotação até 9 lugares e peso bruto superior a 5 ton.. No exame CAM do IMT, esta alternativa responde corretamente à questão «transportes existentes Na classificação europeia de veículos, a categoria M1 corresponde a».</t>
+          <t>A questão relaciona-se com condução segura, prevenção de acidentes e comportamento ao volante. No caso «transportes existentes Na classificação europeia de veículos, a categoria M1 corresponde a», a opção B) é a alternativa que melhor se aplica ao caso: Automóveis de passageiros com lotação até 9 lugares e peso bruto superior a 5 ton.. A opção A) («Automóveis de passageiros com lotação até 9 lugares, incluindo o co…») apresenta valores diferentes dos exigidos nesta situação A opção C) («Reboques com peso bruto até 0,75 ton.») apresenta valores diferentes dos exigidos nesta situação.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Estão obrigatoriamente sujeitos à forma escrita. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os contratos de trabalho a termo».</t>
+          <t>Estão obrigatoriamente sujeitos à forma escrita — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Só podem ter a forma verbal») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -16294,7 +16294,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Pela entidade patronal, no mês seguinte aquele a que disserem respeito. No exame CAM do IMT, esta alternativa responde corretamente à questão «O pagamento à Segurança Social das contrib uições dos trabalhadores por conta de outrém deve ser efetuado».</t>
+          <t>O procedimento adequado é Pela entidade patronal, no mês seguinte aquele a que disserem respeito (A)). Por exemplo, B) («Mensalmente, pelo próprio trabalhador») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -16354,7 +16354,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) É considerada falta justificada. No exame CAM do IMT, esta alternativa responde corretamente à questão «A ausência do trabalhador do local de trabalho, por motivo de doença».</t>
+          <t>É considerada falta justificada — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («É considerado um ilícito») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) O tribunal decidir que o despedimento é ilícito. No exame CAM do IMT, esta alternativa responde corretamente à questão «Após ter sido objeto de despedimento promovido pela entidade empregadora, o trabalhador tem direito a ser reintegrado...».</t>
+          <t>O tribunal decidir que o despedimento é ilícito — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O trabalhador consentir numa redução da sua remuneração») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Capacidade Profissional. No exame CAM do IMT, esta alternativa responde corretamente à questão «A capacidade técnica ou profissional, como requisito de acesso à atividade de transportes rodoviários de mercadorias ...».</t>
+          <t>Capacidade Profissional — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Admissibilidade de Firma») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) 2 anos. No exame CAM do IMT, esta alternativa responde corretamente à questão «A interdição do exercício da actividade de transportes rodoviários de mercadorias por conta de outrém, como sanção ac...».</t>
+          <t>2 anos — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (1 ano) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Estar legalmente proibidos do exercício do comércio. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para efeito de comprovação do requisito de idoneidade no acesso e exercício da atividade de transportes rodoviários d...».</t>
+          <t>Estar legalmente proibidos do exercício do comércio — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Ter sido condenado por duas infrações ao Código da Estrada») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -16654,7 +16654,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Não está sujeito a licenciamento na atividade de transporte público rodoviário de mercadorias por conta de outrem. No exame CAM do IMT, esta alternativa responde corretamente à questão «O transporte de envios postais, realizado no âmbito da atividade de prestador de serviços postais».</t>
+          <t>Não está sujeito a licenciamento na atividade de transporte público rodoviário de mercadorias por conta de outrem — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Está sujeito apenas ao licenciamento dos veículos ligeiros») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) 15 dias. No exame CAM do IMT, esta alternativa responde corretamente à questão «conta de outrem O contrato de trabalho a termo certo c aduca no final do prazo estipulado desde que o empregador comu...».</t>
+          <t>O valor ou limite legal aplicável é 15 dias, indicado em B).  Por exemplo, a opção A) indica valores (30 dias) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Para satisfação de necessidades temporárias da empresa e pelo período estritamente necessário. No exame CAM do IMT, esta alternativa responde corretamente à questão «O contrato de trabalho a termo certo pode ser celebrado».</t>
+          <t>Para satisfação de necessidades temporárias da empresa e pelo período estritamente necessário — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Sempre que o prazo seja superior a 5 anos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -16834,7 +16834,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) 5 dias. No exame CAM do IMT, esta alternativa responde corretamente à questão «As faltas justificadas, quando sejam previsíveis,  devem ser comunicadas ao empregador com a antecedência mínima de».</t>
+          <t>O procedimento adequado é 5 dias (A)). Por exemplo, a opção B) indica valores (10 dias) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -16894,7 +16894,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Não inferior a uma hora, nem superior a duas horas. No exame CAM do IMT, esta alternativa responde corretamente à questão «A jornada de trabalho diária deve ser interrompida por um intervalo de descanso, de duração».</t>
+          <t>O procedimento adequado é Não inferior a uma hora, nem superior a duas horas (B)). Na situação «A jornada de trabalho diária deve ser interrompida por um intervalo de descanso, de…», o procedimento correto é Não inferior a uma hora, nem superior a duas horas (opção B)).</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Tem direito a gozar dois dias úteis de férias por cada mês completo de duração do contrato. No exame CAM do IMT, esta alternativa responde corretamente à questão «O trabalhador admitido com contrato cuja duração total não atinja seis meses».</t>
+          <t>Tem direito a gozar dois dias úteis de férias por cada mês completo de duração do contrato — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Só terá direito a férias se esse direito estiver consignado no contrato») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) 2 membros. No exame CAM do IMT, esta alternativa responde corretamente à questão «Numa empresa que tenha 60 trabalhadores sindicalizados, o número máximo de delegados sindicais que beneficiam do regi...».</t>
+          <t>2 membros — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (5 membros) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -17074,7 +17074,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Entre as 22 horas de um dia e as sete horas do dia seguinte. No exame CAM do IMT, esta alternativa responde corretamente à questão «Na ausência de fixação por instrumento de regulamentação coletiva de trabalho, considera -se período de trabalho notu...».</t>
+          <t>Entre as 22 horas de um dia e as sete horas do dia seguinte — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (Entre as 0 e as 5 horas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) 30 dias por ano. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para prestar assistência inadiável e imprescindível, em caso de doença ou acidente, a filhos, adotados ou a enteados ...».</t>
+          <t>O procedimento adequado é 30 dias por ano (D)). Por exemplo, a opção A) indica valores (20 dias por ano) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -17194,7 +17194,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Cinco dias úteis seguidos, obrigatoriamente gozados na primeira semana a seguir ao nascimento do filho. No exame CAM do IMT, esta alternativa responde corretamente à questão «De acordo com o Código do Trabalho, a licença por paternidade, correspondente a».</t>
+          <t>Cinco dias úteis seguidos, obrigatoriamente gozados na primeira semana a seguir ao nascimento do filho — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Quinze dias úteis, só em caso de morte ou incapacidade física da mãe») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -17254,7 +17254,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Início do período experimental. No exame CAM do IMT, esta alternativa responde corretamente à questão «de avaliação Nos termos do Código do Trabalho, a antiguidade dos trabalhadores é contada a partir do».</t>
+          <t>Início do período experimental — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Dia acordado pela entidade patronal e trabalhador») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -17314,7 +17314,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Quando se trate de recolha de me rcadoria destinada a ser agrupada no armazém do transportador para posterior distribuição. No exame CAM do IMT, esta alternativa responde corretamente à questão «A guia de remessa exigida pela lei fiscal para controlo do imposto sobre o valor acrescentado (IVA) pode substituir a...».</t>
+          <t>Quando se trate de recolha de me rcadoria destinada a ser agrupada no armazém do transportador para posterior distribuição — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Quando não seja possível formular reservas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Por duplicado ou cópia autenticada do último balanço apresentado para efeitos de IRC. No exame CAM do IMT, esta alternativa responde corretamente à questão «A comprovação do requisito de capacidade financeira de exercício de uma empresa de transportes organizada sob a forma...».</t>
+          <t>Por duplicado ou cópia autenticada do último balanço apresentado para efeitos de IRC — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Pelas atas das reuniões realizadas no ano anterior») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Automóveis de passageiros com lotação até 9 lugares e peso bruto superior a 5 ton.. No exame CAM do IMT, esta alternativa responde corretamente à questão «Na classificação europeia de veículos, a categoria m2 corresponde a».</t>
+          <t>A questão relaciona-se com condução segura, prevenção de acidentes e comportamento ao volante. No caso «Na classificação europeia de veículos, a categoria m2 corresponde a», a opção B) é a alternativa que melhor se aplica ao caso: Automóveis de passageiros com lotação até 9 lugares e peso bruto superior a 5 ton.. A opção A) («Automóveis de passageiros com lotação até 9 lugares, incluindo o co…») apresenta valores diferentes dos exigidos nesta situação A opção C) («Reboques com peso bruto superior a 3,5 ton. e até 10 ton.») apresenta valores diferentes dos exigidos nesta situação.</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -17494,7 +17494,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Cumpre os requisitos de acesso à at ividade (idoneidade, capacidade profissional e capacidade financeira). No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma sociedade por quotas, unipessoal que pretenda obter o alvará para o exercício da atividade de transporte pú blico...».</t>
+          <t>O procedimento adequado é Cumpre os requisitos de acesso à at ividade (idoneidade, capacidade profissional e capacidade financeira) (B)). Por exemplo, D) («Não tem dívidas ao fisco nem à Segurança Social») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -17554,7 +17554,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) A caducidade da respetiva licença. No exame CAM do IMT, esta alternativa responde corretamente à questão «rendimento das pessoas coletivas (IRC) ou por garantia bancária A não aprovação em inspeção periódica de um veículo a...».</t>
+          <t>A caducidade da respetiva licença — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A cessação da exploração da carreira à qual o veículo esteja adstrito») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -17674,7 +17674,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Itinerário, frequência, paragens, categoria.</t>
+          <t>O procedimento adequado é A categoria dos passageiros a transportar, itinerário, frequência e paragens (A)). Por exemplo, D) («A origem e destino, número de passageiros e locais da sua tomada e largada») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -17734,7 +17734,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Cabotagem. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os serviços de transporte nacionais realizados por t ransportadores não estabelecidos no território português, design...».</t>
+          <t>Cabotagem — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Transportes combinados») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Dístico + folha de itinerário.</t>
+          <t>O procedimento adequado é Dístico identificativo do serviço e folha de itinerário (C)). Por exemplo, D) («Cópia do contrato de transporte e cópia certificada de licença comunitária») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Com o pedido de acesso à atividade. No exame CAM do IMT, esta alternativa responde corretamente à questão «A comprovação do requisito de idoneidade , é exigida aos administradores diretores ou geren tes de empresas de transp...».</t>
+          <t>Com o pedido de acesso à atividade — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Com o pedido de admissão a exame de capacidade profissional») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -17914,7 +17914,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Interdição profissional = perda de idoneidade.</t>
+          <t>Na medida de interdição do exercício da profissão, independentemente da natureza do crime — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Na pena acessória de inibição de conduzir») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -17974,7 +17974,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Serviços regulares e serviços expresso. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nos termos do Regime Jurídico do Serviço Público de Tra nsportes de Passageiros (RIISPTP) as carreiras de serviço púb...».</t>
+          <t>Serviços regulares e serviços expresso — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Independentes, concorrentes e afluentes») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Nenhuma das anteriores respostas é correcta. No exame CAM do IMT, esta alternativa responde corretamente à questão «O binário do motor é».</t>
+          <t>O binário do motor é o momento de rotação (torque) aplicado ao veículo. A opção A) refere-se à potência; a B) aproxima-se do conceito de binário, mas no gabarito IMT a resposta aceite é D) porque nenhuma das três primeiras definições descreve o binário de forma completa e isolada.</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -18094,7 +18094,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) O mais baixo possível. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para aumentar a estabilidade de circulação dos veículos pesados, torna -se conveniente que o centro de gravidade do c...».</t>
+          <t>O mais baixo possível — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Qualquer altura, pois não tem interferência no centro de gravidade») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -18154,7 +18154,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Implica na instabilidade do veículo e diminui a eficácia do seu sistema de travagem. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se concentrar a carga a  transportar no limite traseiro da caixa de carga de um veículo pesado de dois eixos».</t>
+          <t>Implica na instabilidade do veículo e diminui a eficácia do seu sistema de travagem — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A carga pode ser colocada em qualquer parte da caixa de carga») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Suportar o motor, a carroçaria e a caixa de carga do veículo. No exame CAM do IMT, esta alternativa responde corretamente à questão «A função do quadro ou chassis nos automóveis, é de».</t>
+          <t>Suportar o motor, a carroçaria e a caixa de carga do veículo — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Suportar o peso do veículo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -18274,7 +18274,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Transformar os gases provenientes do motor em produtos menos poluentes. No exame CAM do IMT, esta alternativa responde corretamente à questão «A função do catalisador catalítico aplicado ao sistema de escape dos automóveis tem como função».</t>
+          <t>Transformar os gases provenientes do motor em produtos menos poluentes — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Diminuir a temperatura do motor») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -18334,7 +18334,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) São muito prejudiciais para meio ambiente e para o ser humano. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os gases resultantes da combustão e libertados para a atmosfera pelos veículos a motor».</t>
+          <t>São muito prejudiciais para meio ambiente e para o ser humano — é o que melhor responde ao enunciado (opção B)). Por exemplo, A) («São absorvidos pela atmosfera sem consequências negativas para o meio ambi…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -18394,7 +18394,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) O motor está a poluir mais que o normal, porque está a consumir óleo em excesso. No exame CAM do IMT, esta alternativa responde corretamente à questão «Verificando-se frequente necessidade de acrescentar óleo no motor, pode concluir-se que».</t>
+          <t>O motor está a poluir mais que o normal, porque está a consumir óleo em excesso — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («O cárter e ou a respetiva junta estão a vedar bem») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -18454,7 +18454,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Verificar se esta está bem fixa à carroçaria e se o líquido se encontra a cobrir as placas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um dos cuidados a ter com as baterias é».</t>
+          <t>Verificar se esta está bem fixa à carroçaria e se o líquido se encontra a cobrir as placas — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Adicionar, se necessário, água destilada até ao enchimento completo da bat…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Condutor. No exame CAM do IMT, esta alternativa responde corretamente à questão «A manutenção dos pneumáticos de uma viatura compete sempre ao».</t>
+          <t>Condutor — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Proprietário da viatura») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -18574,7 +18574,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) 4 kg sem travar o travão de pé. No exame CAM do IMT, esta alternativa responde corretamente à questão «No painel de instrumentos de um pesado em andamento, os manómetros de ar devem indicar uma pressão de».</t>
+          <t>O valor ou limite legal aplicável é 4 kg sem travar o travão de pé, indicado em B).  Por exemplo, a opção A) indica valores (3 kg sempre que se utilize o travão de pé) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Sempre que possível, utilizar com a mudança mais alta engrenada, com o motor no binário máximo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para economizar combustível e diminuir a poluição dos motores o condutor deve».</t>
+          <t>O procedimento adequado é Sempre que possível, utilizar com a mudança mais alta engrenada, com o motor no binário máximo (B)). Por exemplo, D) («Nas descidas, desengatar a caixa de velocidades») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -18694,7 +18694,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Verificar se a alavanca da caixa automática se encontra na posição D. No exame CAM do IMT, esta alternativa responde corretamente à questão «Ao colocar o motor de um veículo pesado a trabalhar o condutor deve».</t>
+          <t>O procedimento adequado é Verificar se a alavanca da caixa automática se encontra na posição D (D)). Por exemplo, C) («Verificar todas as luzes do veículo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Gerando um campo magnético com a produção de correntes induzidas que reagindo se opõem ao movimento dos dois discos montados no veio da transmissão. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nos veículos pesados, de um modo geral, o retardador ou travão eléctrico funciona».</t>
+          <t>Gerando um campo magnético com a produção de correntes induzidas que reagindo se opõem ao movimento dos dois discos montados no veio da transmissão — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Através de correntes alternas que provocam um atrito entre os discos e o v…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -18814,7 +18814,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Obrigatoriamente por ação mecânica. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nos veículos pesados com sistema pneumático da travagem o travão de mão atua».</t>
+          <t>Obrigatoriamente por ação mecânica — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Por ação dos cabos do travão de mão») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -18874,7 +18874,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Inicia uma longa descida de inclinação acentuada. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se o veiculo está equipado com o retardador eléctrico (travão auxiliar elétrico), o seu condutor deve ligá - lo sempr...».</t>
+          <t>O procedimento adequado é Inicia uma longa descida de inclinação acentuada (C)). Por exemplo, B) («Transitando em patamar, efetue uma travagem de emergência») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -18934,7 +18934,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Fuga na tubagem do circuito hidráulico. No exame CAM do IMT, esta alternativa responde corretamente à questão «Num veiculo com travões de disco equipado com o sistema de travagem tipo hi dráulico, uma falta súbita de travões pod...».</t>
+          <t>O procedimento adequado é Fuga na tubagem do circuito hidráulico (B)). Por exemplo, C) («Calços do travão muito gastos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -18994,7 +18994,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Se o líquido refrigerante está entre os parâmetros recomendados. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um dos vários cuidados que o condutor deve ter antes de iniciar uma viagem, é verificar, nomeadamente, se».</t>
+          <t>O procedimento adequado é Se o líquido refrigerante está entre os parâmetros recomendados (B)). Por exemplo, D) («O filtro do ar tem impurezas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) O nível de óleo de lubrificação do motor está muito baixo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando um automóvel pesado descreve uma cu rva apertada ou quando trava de emergência, se a luz avisadora da lubrific...».</t>
+          <t>O nível de óleo de lubrificação do motor está muito baixo — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («O nível do líquido de limpeza do pára-brisas está baixo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -19114,7 +19114,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Não esforçar o motor. No exame CAM do IMT, esta alternativa responde corretamente à questão «O objetivo da condução dentro da “faixa verde “ é».</t>
+          <t>Não esforçar o motor — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Circular dentro das velocidades recomendadas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -19174,7 +19174,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) 4 ciclos. No exame CAM do IMT, esta alternativa responde corretamente à questão «O ciclo de operação de um motor diesel de um veículo pesado, é composto de».</t>
+          <t>4 ciclos — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (2 ciclos) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -19234,7 +19234,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Admissão, compressão, explosão/expansão, escape. No exame CAM do IMT, esta alternativa responde corretamente à questão «As fases do ciclo do motor diesel num veículo pesado são».</t>
+          <t>Admissão, compressão, explosão/expansão, escape — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Admissão, injecção, ignição, escape») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -19294,7 +19294,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Em caso de falha do sistema, possa ainda existir algum poder de travagem. No exame CAM do IMT, esta alternativa responde corretamente à questão «O tipo de sistema de travagem cruzado serve para».</t>
+          <t>Em caso de falha do sistema, possa ainda existir algum poder de travagem — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Evitar que as rodas bloqueiem») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -19354,7 +19354,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Reduzir e utilizar os meios de travagem auxiliar. No exame CAM do IMT, esta alternativa responde corretamente à questão «Numa eminente falha de travões o motorista deverá».</t>
+          <t>O procedimento adequado é Reduzir e utilizar os meios de travagem auxiliar (D)). Por exemplo, C) («Bombear consecutivamente o travão») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -19414,7 +19414,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Detetar a origem do problema e a atitude a tomar. No exame CAM do IMT, esta alternativa responde corretamente à questão «No caso de uma baixa súbita no nível do fluido de travões, o motorista deverá».</t>
+          <t>O procedimento adequado é Detetar a origem do problema e a atitude a tomar (B)). Por exemplo, D) («Ignorar e evitar declives inclinados») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Que permite desacoplar o motor do resto da transmissão. No exame CAM do IMT, esta alternativa responde corretamente à questão «A embraiagem é um tipo de mecanismo que».</t>
+          <t>Que permite desacoplar o motor do resto da transmissão — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Permite adotar o regime do motor») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -19534,7 +19534,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Que as rodas motrizes rolem a diferentes velocidades. No exame CAM do IMT, esta alternativa responde corretamente à questão «A função de um diferencial consiste em permitir».</t>
+          <t>Trata-se de uma definição: Que as rodas motrizes rolem a diferentes velocidades (opção B)). Na definição pedida («A função de um diferencial consiste em permitir»), o conceito correto é Que as rodas motrizes rolem a diferentes velocidades (opção B)).</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -19594,7 +19594,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Longitudinal e atrás do mesmo. No exame CAM do IMT, esta alternativa responde corretamente à questão «A localização de uma caixa de velocidades num veículo pesado é, respetivamente ao motor visto de frente».</t>
+          <t>Longitudinal e atrás do mesmo — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («Transversalmente ao mesmo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Aumentar a curva de binário do motor. No exame CAM do IMT, esta alternativa responde corretamente à questão «O objetivo do conversor de binário é».</t>
+          <t>Aumentar a curva de binário do motor — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Definir um modelo da gestão do motor») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -19714,7 +19714,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Antes do binário máximo. No exame CAM do IMT, esta alternativa responde corretamente à questão «No que respeita a curva de consumo específico, para um motor de um veículo pesado, o consumo de combustível é menor».</t>
+          <t>Antes do binário máximo — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A partir do encontro das linhas de binário e potência») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -19774,7 +19774,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) O uso de velas de ignição. No exame CAM do IMT, esta alternativa responde corretamente à questão «A principal diferença entre um motor a diesel e um a gasolina é».</t>
+          <t>O uso de velas de ignição — é o que melhor responde ao enunciado (opção D)). Por exemplo, B) («O número de cilindros») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -19834,7 +19834,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Retirar a humidade ao ar. No exame CAM do IMT, esta alternativa responde corretamente à questão «Num sistema de travagem pneumática, a função do secador de ar é».</t>
+          <t>Retirar a humidade ao ar — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Manter o ar à temperatura ideal») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Sempre que possível, andar com a mudança mais alta engrenada e com o motor no binário máximo. No exame CAM do IMT, esta alternativa responde corretamente à questão «A zona de utilização óptima do conta-rotações consegue-se».</t>
+          <t>Sempre que possível, andar com a mudança mais alta engrenada e com o motor no binário máximo — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Esticando o motor logo no início da marcha») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -19954,7 +19954,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Terceiro tempo. No exame CAM do IMT, esta alternativa responde corretamente à questão «O motor de combustão difere do motor de explosão no».</t>
+          <t>Relativamente a «O motor de combustão difere do motor de explosão no», a resposta adequada é C): Terceiro tempo.</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Aumentar o controlo e a eficiência de travagem durante as descidas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O retardador é um travão auxiliar que trabalha sem utilizar o sistema n ormal de travagem tendo como principal função».</t>
+          <t>Aumentar o controlo e a eficiência de travagem durante as descidas — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Estabilizar o veículo em situações de condução perigosa») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -20074,7 +20074,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Tirar antecipadamente o pé do acelerador. No exame CAM do IMT, esta alternativa responde corretamente à questão «O aproveitamento da inércia do veículo irá traduzir-se num menor consumo pelo que, o condutor deverá».</t>
+          <t>O procedimento adequado é Tirar antecipadamente o pé do acelerador (B)). Por exemplo, D) («Acelerar o veículo de forma agressiva») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Obrigatoriamente por acção mecânica. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nos veículos pesados com sistema pneumático da travagem o travão de mão actua».</t>
+          <t>Obrigatoriamente por acção mecânica — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Por acção dos cabos do travão de mão») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -20194,7 +20194,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Fuga na tubagem do circuito hidráulico. No exame CAM do IMT, esta alternativa responde corretamente à questão «Num veiculo com travões de disco equipado com o sistema de travagem tipo hidráulico, uma falta súbita de travões pode...».</t>
+          <t>O procedimento adequado é Fuga na tubagem do circuito hidráulico (B)). Por exemplo, C) («Calços do travão muito gastos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -20254,7 +20254,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Evitar o bloqueio das rodas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema de travagem ABS utilizado nos autocarros destina-se a».</t>
+          <t>Evitar o bloqueio das rodas — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Permitir uma melhor repartição da travagem») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Radiador, válvula termostática, bomba de água, canais de refrigeração no interior do bloco de cilindros e canais de refrigeração na cabeça do motor. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema de refrigeração por líquido refrigerante de um motor é composto por».</t>
+          <t>Radiador, válvula termostática, bomba de água, canais de refrigeração no interior do bloco de cilindros e canais de refrigeração na cabeça do motor — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Apenas por ventoinha, termóstato e alhetas do motor») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Pneumático. No exame CAM do IMT, esta alternativa responde corretamente à questão «cilindros e canais de refrigeração na cabeça do motor Os veículos de elevado peso bruto utilizam sistema de travagem».</t>
+          <t>Relativamente a «cilindros e canais de refrigeração na cabeça do motor Os veículos de elevado peso bruto…», a resposta adequada é B): Pneumático.</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -20434,7 +20434,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Ar. No exame CAM do IMT, esta alternativa responde corretamente à questão «Durante a admissão de um motor de ciclo diesel, entra».</t>
+          <t>Ar — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Ar e gás de petróleo liquefeito») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -20494,7 +20494,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Ao binário máximo do motor. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um baixo consumo de combustível é conseguido utilizando o motor na rotação a que equivale».</t>
+          <t>Ao binário máximo do motor — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («À rotação em que quer o binário quer a potência são máximos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -20554,7 +20554,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Bomba injectora, common rail ou injector-bomba. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema de alimentação de um motor diesel pode adotar as seguintes opções».</t>
+          <t>Bomba injectora, common rail ou injector-bomba — é o que melhor responde ao enunciado (opção B)). Por exemplo, A) («Carburador e sistema injector-bomba») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -20614,7 +20614,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Escape e tem por função a reutilização dos gases de escape para compress ão do ar de admissão. No exame CAM do IMT, esta alternativa responde corretamente à questão «O EGR está integrado no sistema de».</t>
+          <t>Escape e tem por função a reutilização dos gases de escape para compress ão do ar de admissão — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Distribuição dos gases de escape») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -20674,7 +20674,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Depende do valor binário e da rotação a que o motor está a trabalhar. No exame CAM do IMT, esta alternativa responde corretamente à questão «A potência de um motor».</t>
+          <t>Depende do valor binário e da rotação a que o motor está a trabalhar — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Depende apenas do binário») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Da rotação do motor e da velocidade do veículo e da posição do acelerador. No exame CAM do IMT, esta alternativa responde corretamente à questão «A seleção da mudança num veículo equipado com caixa de velocidades automática depende».</t>
+          <t>Da rotação do motor e da velocidade do veículo e da posição do acelerador — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Apenas da posição do acelerador») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -20794,7 +20794,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Monitorizar a rotação de cada roda, a inclinação do veículo e a aceleração, atuando em conformidade a fim de estabilizar o veículo em situações de instabilidade. No exame CAM do IMT, esta alternativa responde corretamente à questão «O controlo de estabilidade tem por função».</t>
+          <t>Monitorizar a rotação de cada roda, a inclinação do veículo e a aceleração, atuando em conformidade a fim de estabilizar o veículo em situações de instabilidade — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Limitar o escorregamento em caso de travagem brusca») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -20854,7 +20854,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Circular com uma mudança baixa de modo a utilizar o motor como travão. No exame CAM do IMT, esta alternativa responde corretamente à questão «Numa descida de acentuada inclinação o condutor deve».</t>
+          <t>O procedimento adequado é Circular com uma mudança baixa de modo a utilizar o motor como travão (C)). Por exemplo, D) («Circular com o pé sempre em cima do pedal de travão») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -20914,7 +20914,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Transporte terrestre, transporte aquaviário, transporte aéreo e transporte tubular ou dutoviário. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os modos de transportes dividem-se em».</t>
+          <t>Transporte terrestre, transporte aquaviário, transporte aéreo e transporte tubular ou dutoviário — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -20974,7 +20974,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) A responsabilidade social de uma empresa de transportes incide sobre os seus clientes, e não sobre os seus trabalhadores. No exame CAM do IMT, esta alternativa responde corretamente à questão «Atendendo aos princípios de organização e funcionamento de uma empresa de transportes de mercadorias, indique qual da...».</t>
+          <t>A responsabilidade social de uma empresa de transportes incide sobre os seus clientes, e não sobre os seus trabalhadores — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Uma boa comunicação, a cortesia, prontidão e a competência são alguns dos …») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) A atividade transitária só pode ser exercida por empresas titulares de alvará emitido pelo IMT. No exame CAM do IMT, esta alternativa responde corretamente à questão «Assinale a afirmação verdadeira».</t>
+          <t>A atividade transitária só pode ser exercida por empresas titulares de alvará emitido pelo IMT — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («As empresas que realizam transporte rodoviário de mercadorias perigosas ca…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Matriculados, que não se encontrem avariados ou sinistrados, nem se destinem a substituir veículos sinistrados ou avariados. No exame CAM do IMT, esta alternativa responde corretamente à questão «Não podem ser transportados por empresas prestadoras de serviços através de veículos tipo pronto - socorro os veículos».</t>
+          <t>Matriculados, que não se encontrem avariados ou sinistrados, nem se destinem a substituir veículos sinistrados ou avariados — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Que se destinem a exposições ou manifestações desportivas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) No transporte multimodal há um único documento cont ratual para todo o transporte qualquer que seja o número de modos envolvidos, enquanto no intermodal podem existir vários documentos contratuais mas o transporte é realizado sem rutura de carga. No exame CAM do IMT, esta alternativa responde corretamente à questão «A diferença entre transporte intermodal e transporte multimodal é que».</t>
+          <t>No transporte multimodal há um único documento cont ratual para todo o transporte qualquer que seja o número de modos envolvidos, enquanto no intermodal podem existir vários documentos contratuais mas o transporte é realizado sem rutura de carga — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («No transporte intermodal só participam dois modos de transport e enquanto …») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -21214,7 +21214,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Os transportes rodoviários de mercadorias por conta de outrem são mais eficientes que os transportes por conta própria. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma das medidas da eficiência nos transportes é dada pela percentagem de quilómetros em carga. Quanto a este aspeto, ...».</t>
+          <t>Os transportes rodoviários de mercadorias por conta de outrem são mais eficientes que os transportes por conta própria — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -21266,7 +21266,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) No conjunto da sua capacidade de carga por um único expedidor. No exame CAM do IMT, esta alternativa responde corretamente à questão «Transporte em regime de carga completa é o transporte por conta de outrem em que o veículo é utilizado».</t>
+          <t>Transporte em regime de carga completa significa que o veículo é utilizado na totalidade da sua capacidade por um único expedidor (um cliente por serviço). A opção B) exprime isso. A opção A) descreve carga fracionada, em que vários expedidores partilham o mesmo veículo.</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Isotérmico, com uma fonte de frio, que permite regular a temperatura até -20º C. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um veículo de temperatura controlada refrigerado é um veículo».</t>
+          <t>Isotérmico, com uma fonte de frio, que permite regular a temperatura até -20º C — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (Isotérmico, com um mecanismo capaz de produzir frio, reduzindo assim a tem…) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -21386,7 +21386,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Alvará, emitido pelo IMTT. No exame CAM do IMT, esta alternativa responde corretamente à questão «horas, constante ou superior a 12ºC Uma empresa de aluguer de veículos sem condutor é titulada por».</t>
+          <t>Alvará, emitido pelo IMTT — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Não carece de qualquer alvará») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) A poluição atmosférica, os acidentes, os riscos de alterações climatéricas, o ruído e os custos para a natureza e para a paisagem. No exame CAM do IMT, esta alternativa responde corretamente à questão «Pode dizer-se que os componentes dos custos externos dos transportes são».</t>
+          <t>A poluição atmosférica, os acidentes, os riscos de alterações climatéricas, o ruído e os custos para a natureza e para a paisagem — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Apenas a poluição atmosférica») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -21506,7 +21506,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Maior rapidez (porta-a-porta). No exame CAM do IMT, esta alternativa responde corretamente à questão «natureza e para a paisagem Das vantagens do transporte rodoviário de mercadorias, pode-se assinalar».</t>
+          <t>Maior rapidez (porta-a-porta) — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Maior competitividade para produtos com baixo custo de tonelada por quilóm…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -21566,7 +21566,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Necessidade de transbordo para chegar junto do cliente final. No exame CAM do IMT, esta alternativa responde corretamente à questão «Das desvantagens do transporte ferroviário de mercadorias pode assinalar-se».</t>
+          <t>Necessidade de transbordo para chegar junto do cliente final — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Custos bastante elevados em relação aos outros meios de transporte») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Ideal para o envio de mercadorias com pouco peso e volume. No exame CAM do IMT, esta alternativa responde corretamente à questão «Das vantagens do transporte aéreo de mercadorias pode-se assinalar».</t>
+          <t>Ideal para o envio de mercadorias com pouco peso e volume — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Maior capacidade de carga») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Prazos e entregas atempadas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os carregadores valorizam, sobretudo».</t>
+          <t>Prazos e entregas atempadas — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Custos administrativos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -21746,7 +21746,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Triagem, Recolha, distribuição secundária, reporting, distribuição primária. No exame CAM do IMT, esta alternativa responde corretamente à questão «As sub-operações da “Operação de Transporte” devem seguir esta ordem».</t>
+          <t>O procedimento adequado é Triagem, Recolha, distribuição secundária, reporting, distribuição primária (A)).</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -21806,7 +21806,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) O retorno das embalagens vazias, produtos danificados ou obsoletos para recuperação ou reciclagem.. No exame CAM do IMT, esta alternativa responde corretamente à questão «Logística inversa é».</t>
+          <t>O retorno das embalagens vazias, produtos danificados ou obsoletos para recuperação ou reciclagem. — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A chegada da carga ao cliente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -21866,7 +21866,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Redução imediata da necessidade de stock. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma das principais vantagens do “Just in Time” é».</t>
+          <t>Redução imediata da necessidade de stock — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Aumento dos tempos de produção») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -21926,7 +21926,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Transporte público ou por conta de outrem. No exame CAM do IMT, esta alternativa responde corretamente à questão «O transporte rodoviário de me rcadorias realizado como actividade empresarial, cujo acesso é condicionado, no que diz...».</t>
+          <t>Trata-se de uma definição: Transporte público ou por conta de outrem (opção D)). Na definição pedida («O transporte rodoviário de me rcadorias realizado como actividade empresarial, cujo…»), o conceito correto é Transporte público ou por conta de outrem (opção D)).</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -21986,7 +21986,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Transporte em regime de carga completa. No exame CAM do IMT, esta alternativa responde corretamente à questão «O tipo de serviço prestado quando se afecta um veículo em exclusividade a um em expedidor, em que todas as operações ...».</t>
+          <t>Transporte em regime de carga completa — é o que melhor responde ao enunciado (opção C)). Relativamente a «O tipo de serviço prestado quando se afecta um veículo em exclusividade a um em…», a resposta adequada é C): Transporte em regime de carga completa.</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -22046,7 +22046,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Transporte a granel. No exame CAM do IMT, esta alternativa responde corretamente à questão «O transporte de matérias sólidas ou de objectos não embalados, em veículos ou contentores, denomina-se por».</t>
+          <t>Na definição pedida («O transporte de matérias sólidas ou de objectos não embalados, em veículos ou…»), o conceito correto é Transporte a granel (opção B)).</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -22106,7 +22106,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Grande flexibilidade de carga e de destinos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Das afirmações seguintes, indique a que melhor se identifica com o transporte rodoviário».</t>
+          <t>Grande flexibilidade de carga e de destinos — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Elevados custos de terminal») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -22166,7 +22166,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) A cada indivíduo o equilíbrio entre as exigências da tarefa e suas capacidades individuais. No exame CAM do IMT, esta alternativa responde corretamente à questão «A introdução dos princípios da ergonomia permite».</t>
+          <t>A cada indivíduo o equilíbrio entre as exigências da tarefa e suas capacidades individuais — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Apenas o aumento da produtividade») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Remete para dois tipos de interacção: as acções sobre o veículo e entre o condutor e os outros utentes da via. No exame CAM do IMT, esta alternativa responde corretamente à questão «A interacção homem-máquina na condução de veículos».</t>
+          <t>Remete para dois tipos de interacção: as acções sobre o veículo e entre o condutor e os outros utentes da via — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Sempre que o foco de desvio da atenção é interno. No exame CAM do IMT, esta alternativa responde corretamente à questão «utentes da via A atenção é uma função cognitiva fundamental na tarefa da condução. Considera-se inatenção».</t>
+          <t>Sempre que o foco de desvio da atenção é interno — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Quando o foco de desvio da atenção é externo, sendo que o indivíduo está a…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -22346,7 +22346,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Zonas não urbanas. No exame CAM do IMT, esta alternativa responde corretamente à questão «pensamentos A fadiga na condução é responsável por inúmeros acidentes, podendo aparecer mais frequentemente na conduç...».</t>
+          <t>Zonas não urbanas — é o que melhor responde ao enunciado (opção A)). Por exemplo, B) («Vias com perfil sinuoso») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -22406,7 +22406,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) O stress, a postura sentada prolongada, a manipulação de cargas e o ruído. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os fatores de maior risco inerentes à profissão de motorista são».</t>
+          <t>O stress, a postura sentada prolongada, a manipulação de cargas e o ruído — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Apenas o stress e o ruído») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -22466,7 +22466,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Negativamente, uma vez que aumenta o tempo de reacção. No exame CAM do IMT, esta alternativa responde corretamente à questão «O álcool, medicamentos, cafeína podem alterar o comportamento do condutor».</t>
+          <t>Negativamente, uma vez que aumenta o tempo de reacção — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Positivamente, uma vez que diminui o tempo de reacção e permite uma melhor…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -22526,7 +22526,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Devem fazer-se horários de refeições irregulares. No exame CAM do IMT, esta alternativa responde corretamente à questão «Na profissão de motorista uma alimentação saudável pode contribuir entre outros aspeto s para uma melhoria na produti...».</t>
+          <t>O enunciado pede a afirmação incorreta sobre alimentação do motorista. Horários de refeição irregulares prejudicam energia e concentração; por isso C) («Devem fazer-se horários de refeições irregulares») é a única errada. Pequeno-almoço regular, evitar jejus prolongados e consumir peixe/carnes brancas são boas práticas.</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -22586,7 +22586,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) A afirmação é correta pois drogas e determinados medicamentos como os relaxantes interferem na condução. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os motoristas devem ter especial atenção ao consumo de substâncias, na medida que podem influenciar a tarefa da condução».</t>
+          <t>O procedimento adequado é A afirmação é correta pois drogas e determinados medicamentos como os relaxantes interferem na condução (C)). Por exemplo, D) («A afirmação é correcta apenas relativamente a certos medicamentos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -22646,7 +22646,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Um efeito semelhante ao consumo de bebidas alcoólicas. No exame CAM do IMT, esta alternativa responde corretamente à questão «A fadiga e a sonolência têm sobre a condução».</t>
+          <t>Um efeito semelhante ao consumo de bebidas alcoólicas — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Um efeito negativo sobre o tempo de reação, mas que é ultrapassado se o co…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -22706,7 +22706,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Três tipos de atividades: perceptiva, cognitiva e motora. No exame CAM do IMT, esta alternativa responde corretamente à questão «forte A condução de um veículo comporta».</t>
+          <t>Três tipos de atividades: perceptiva, cognitiva e motora — é o que melhor responde ao enunciado (opção C)). Por exemplo, A) («Uma atividade cognitiva») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -22766,7 +22766,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Com o veículo parado. No exame CAM do IMT, esta alternativa responde corretamente à questão «A inserção de dados num sistema de navegação (GPS) deve ser realizada».</t>
+          <t>O procedimento adequado é Com o veículo parado (A)). Por exemplo, D) («É indiferente uma vez que a realização desta tarefa não interfere com a ac…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -22826,7 +22826,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Um permanente processamento de informação num envolvimento dinâmico e interações com os restantes utentes da via, de modo a permitir a tomada de decisão em tempo útil. No exame CAM do IMT, esta alternativa responde corretamente à questão «A tarefa da condução impõe».</t>
+          <t>Um permanente processamento de informação num envolvimento dinâmico e interações com os restantes utentes da via, de modo a permitir a tomada de decisão em tempo útil — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -22886,7 +22886,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Um permanente processamento de informação num envolvimento dinâmico e interações com os restantes utentes da via, de modo a permitir a tomada de decisão em tempo útil. No exame CAM do IMT, esta alternativa responde corretamente à questão «A tarefa da condução impõe».</t>
+          <t>Um permanente processamento de informação num envolvimento dinâmico e interações com os restantes utentes da via, de modo a permitir a tomada de decisão em tempo útil — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) São da responsabilidade da entidade patronal, devendo os próprios motoristas gerir a sua saúde, adoptando comportamentos em prol de uma vida saudável. No exame CAM do IMT, esta alternativa responde corretamente à questão «As condições para manutenção da saúde física e psicológica dos motoristas».</t>
+          <t>São da responsabilidade da entidade patronal, devendo os próprios motoristas gerir a sua saúde, adoptando comportamentos em prol de uma vida saudável — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («São da responsabilidade do Sistema Nacional de Saúde») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -23006,7 +23006,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Dois tipos de interações: interações sociais e interação homem-máquina. No exame CAM do IMT, esta alternativa responde corretamente à questão «Durante a condução verificam-se».</t>
+          <t>Dois tipos de interações: interações sociais e interação homem-máquina — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -23066,7 +23066,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) De comportamentos habituais, cometidos regularmente e que se torna m práticas automáticas e frequentemente toleradas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Algumas das transgressões cometidas durante a condução resultam».</t>
+          <t>De comportamentos habituais, cometidos regularmente e que se torna m práticas automáticas e frequentemente toleradas — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Apenas de distrações do condutor») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -23126,7 +23126,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Riscos psicossociais, riscos biológicos, riscos físicos ambientais, riscos biológicos e riscos derivados da manutenção da postura sentada. No exame CAM do IMT, esta alternativa responde corretamente à questão «A profissão de motorista tem inerentes».</t>
+          <t>Riscos psicossociais, riscos biológicos, riscos físicos ambientais, riscos biológicos e riscos derivados da manutenção da postura sentada — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Apenas o risco associado à sinistralidade rodoviária») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -23186,7 +23186,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Interferem com a segurança da condução. No exame CAM do IMT, esta alternativa responde corretamente à questão «As distrações e inatenções durante a tarefa de condução são fatores que».</t>
+          <t>Interferem com a segurança da condução — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Interferem com a tarefa da condução apenas se forem ingeridas bebidas alco…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -23246,7 +23246,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Não, qualquer que seja a quantidade ingerida tem efeito negativo na condução. No exame CAM do IMT, esta alternativa responde corretamente à questão «Comente a afirmação: Só quando bebo em excesso é que corro riscos se conduzir».</t>
+          <t>Não, qualquer que seja a quantidade ingerida tem efeito negativo na condução — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Sim, pois o meu metabolismo elimina rapidamente o álcool») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -23306,7 +23306,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Dormir, nem que seja por um pequeno período de tempo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando estou cansado devo».</t>
+          <t>O procedimento adequado é Dormir, nem que seja por um pequeno período de tempo (C)). Por exemplo, D) («Ligar o rádio e ouvir música») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Todas as situações anteriores. No exame CAM do IMT, esta alternativa responde corretamente à questão «Podem ser indicadores de stress».</t>
+          <t>Todas as situações anteriores — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Sentir falhas de memória») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -23426,7 +23426,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Refeições substanciais para não ter que conduzir de “barriga vazia”. No exame CAM do IMT, esta alternativa responde corretamente à questão «Indique quais os fatores que diminuem o risco de fadiga».</t>
+          <t>Refeições substanciais para não ter que conduzir de “barriga vazia” — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Conduzir utilizando o “cruise control”») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -23486,7 +23486,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Dificultar de avaliação das distâncias. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os efeitos do álcool no cérebro são».</t>
+          <t>Dificultar de avaliação das distâncias — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Facilitar a adaptação da visão às mudanças de luminosidade») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>proibido segurar/manipular; permitido em viva-voz/mãos-livres.</t>
+          <t>O Código da Estrada (art. 82.º) proíbe segurar ou manipular o telemóvel enquanto se conduz; o uso em viva-voz ou mãos-livres é o permitido. Por isso A) está correta: Perigosa, pois aumenta o risco de acidente em mais de 4 vezes.</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -23606,7 +23606,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Todas as respostas anteriores estão corretas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quais são os principais sintomas da fadiga?».</t>
+          <t>Todas as respostas anteriores estão corretas — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Sensação de reagir com mais lentidão») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -23666,7 +23666,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) 7 Grupos de Alimentos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Por quantos grupos de alimentos é constituída a Nova Roda de alimentos?».</t>
+          <t>7 Grupos de Alimentos — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (5 Grupos de Alimentos) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -23726,7 +23726,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) O grupo que deve ser consumido em maior quantidade diária é o dos cereais, derivados e tubérculos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Relativamente à Roda dos Alimentos».</t>
+          <t>O grupo que deve ser consumido em maior quantidade diária é o dos cereais, derivados e tubérculos — é o que melhor responde ao enunciado (opção A)). Por exemplo, B) («O álcool aparece no seu centro») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -23786,7 +23786,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Consumir alimentos com muita gordura regularmente. No exame CAM do IMT, esta alternativa responde corretamente à questão «Não é uma recomendação para uma alimentação saudável».</t>
+          <t>Consumir alimentos com muita gordura regularmente — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Reduzir o consumo de sal») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -23846,7 +23846,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Alcoolemia acima de 0,5 g/l é frequentemente mortal. No exame CAM do IMT, esta alternativa responde corretamente à questão «Assinale a afirmação falsa».</t>
+          <t>Alcoolemia acima de 0,5 g/l é frequentemente mortal — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (Alcoolemia entre 0,5 e 0,8 g/l provoca alterações graves, como diminuição …) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -23906,7 +23906,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Aumento do tempo de reação. No exame CAM do IMT, esta alternativa responde corretamente à questão «reação e de concentração Alguns medicamentos podem provocar».</t>
+          <t>Aumento do tempo de reação — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Aumento da capacidade de percepção das velocidades e distâncias») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Igual ou superior a 0,5 g/l. No exame CAM do IMT, esta alternativa responde corretamente à questão «Considera-se condução sob efeito do álcool, quando o condutor apresenta uma taxa de álcool no sangue».</t>
+          <t>Igual ou superior a 0,5 g/l — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (Igual ou superior a 0,3 g/l) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -24026,7 +24026,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Enchidos e carnes fumadas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O colesterol é provocado principalmente pela ingestão de».</t>
+          <t>Enchidos e carnes fumadas — é o que melhor responde ao enunciado (opção D)). Relativamente a «O colesterol é provocado principalmente pela ingestão de», a resposta adequada é D): Enchidos e carnes fumadas.</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -24086,7 +24086,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Técnicas para a prevenção de ac identes de trabalho, quer eliminando condições inseguras do ambiente, quer educando para a prática de atitudes preventivas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Entende-se por segurança no trabalho um conjunto de».</t>
+          <t>Técnicas para a prevenção de ac identes de trabalho, quer eliminando condições inseguras do ambiente, quer educando para a prática de atitudes preventivas — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Medidas de atuação técnica sobre o ambiente de trabalho com o fim de lutar…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -24146,7 +24146,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Triangular, pictograma negro, sobre fundo amarelo e margem negra. No exame CAM do IMT, esta alternativa responde corretamente à questão «profissionais A sinalização de perigo visa advertir para uma situação objeto ou ação susceptível de dano ou lesão pes...».</t>
+          <t>Triangular, pictograma negro, sobre fundo amarelo e margem negra — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Retangular ou quadrada, pictograma branco sobre fundo verde») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -24206,7 +24206,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Contraída por um trabalhador em razão especificamente do seu exercício profissional. No exame CAM do IMT, esta alternativa responde corretamente à questão «Entende-se por doença profissional a doença».</t>
+          <t>Contraída por um trabalhador em razão especificamente do seu exercício profissional — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Resultante de um acontecimento imprevisto») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -24266,7 +24266,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) As interações entre os seres humanos e os outros elementos de um sistema como intuito de otimizar o sistema homem – trabalho. No exame CAM do IMT, esta alternativa responde corretamente à questão «A ergonomia é uma disciplina científica que estuda».</t>
+          <t>As interações entre os seres humanos e os outros elementos de um sistema como intuito de otimizar o sistema homem – trabalho — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («As reações do condutor sob o efeito do álcool A utilização do telemóvel ao…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>permitido em viva-voz/mãos-livres.</t>
+          <t>O Código da Estrada (art. 82.º) proíbe segurar ou manipular o telemóvel enquanto se conduz; o uso em viva-voz ou mãos-livres é o permitido. Por isso B) está correta: Tem efeitos sobre a condução comparáveis aos do álcool.</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Parar 10 a 15 minutos de todas as 2 ou 3 horas de condução, ou então após 150 km. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para evitar a fadiga, aconselha-se».</t>
+          <t>Parar 10 a 15 minutos de todas as 2 ou 3 horas de condução, ou então após 150 km — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Manter os vidros fechados por causa do ruído exterior») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -24446,7 +24446,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Pressões de tempo relacionadas com horário de trabalho ou prazos de entrega de mercadorias. No exame CAM do IMT, esta alternativa responde corretamente à questão «Consideram-se situações indutoras de stress».</t>
+          <t>Pressões de tempo relacionadas com horário de trabalho ou prazos de entrega de mercadorias — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Condução sob boas condições meteorológicas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -24506,7 +24506,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Alargar a base de sustentação, colocar o objeto o mais próximo possível  do corpo e flectir os joelhos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Considera-se como uma boa postura no levantamento de uma carga».</t>
+          <t>Alargar a base de sustentação, colocar o objeto o mais próximo possível  do corpo e flectir os joelhos — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Colocar o objeto afastado do corpo, e fletir os joelhos ao levantá-lo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -24566,7 +24566,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Manter as costas o mais vertical possível fletindo as pernas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Ao fazer o levantamento manual de uma carga deve».</t>
+          <t>O procedimento adequado é Manter as costas o mais vertical possível fletindo as pernas (B)). Por exemplo, C) («Manter a carga na vertical afastada do corpo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -24626,7 +24626,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Na posição sentada, a postura, ligeiramente inclinada para frente, é mais natural e menos fatigante que a ereta. O assento deve permitir mudanças frequente s de postura, para retardar o aparecimento da fadiga. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma má  postura corporal poderá implicar várias consequências no trabalhador. Assinale a afirmação correta».</t>
+          <t>Na posição sentada, a postura, ligeiramente inclinada para frente, é mais natural e menos fatigante que a ereta. O assento deve permitir mudanças frequente s de postura, para retardar o aparecimento da fadiga — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O banco deve estar o mais reclinado para trás possível para que se possa c…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -24686,7 +24686,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) A perda de controlo do veículo, em curva, é, quase sempre, originada por inabilidade do condutor ou por velocidade excessiva para as condições do veículo e da via. No exame CAM do IMT, esta alternativa responde corretamente à questão «Considerando a influência dos fatores humanos na condução, indique qual das seguintes afirmações é verdadeira».</t>
+          <t>A perda de controlo do veículo, em curva, é, quase sempre, originada por inabilidade do condutor ou por velocidade excessiva para as condições do veículo e da via — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A fadiga passiva no decorrer da condução não tem influência no tempo de re…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -24746,7 +24746,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Uma alimentação saudável e equilibrada é fundamental na prevenção de certas doenças (obesidade, doenças cardiovasculares, diabetes, certos tipo de cancro). No exame CAM do IMT, esta alternativa responde corretamente à questão «Indique qual das afirmações é a verdadeira».</t>
+          <t>Uma alimentação saudável e equilibrada é fundamental na prevenção de certas doenças (obesidade, doenças cardiovasculares, diabetes, certos tipo de cancro) — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Mesmo no decorrer do horário de trabal ho recomenda -se a ingestão de álco…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -24806,7 +24806,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Radiações Ópticas (Infra-vermelho, Visível e Ultra Violetas). No exame CAM do IMT, esta alternativa responde corretamente à questão «As principais radiações a que os condutores de veículos pesados de passageiros e de mercadorias estão expostos são».</t>
+          <t>Radiações Ópticas (Infra-vermelho, Visível e Ultra Violetas) — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Somente, as Ultra Violetas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -24866,7 +24866,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Todas as respostas anteriores estão corretas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O assento do motorista deve».</t>
+          <t>O procedimento adequado é Todas as respostas anteriores estão corretas (D)). Por exemplo, C) («Estar posicionado de acordo com o volante, os painéis, pedais e pára-brisas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -24926,7 +24926,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Promover uma convivência pacífica e harmoniosa entre condutores e peões. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para minimizar os efeitos do stress posso».</t>
+          <t>Promover uma convivência pacífica e harmoniosa entre condutores e peões — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («O stress não pode ser minimizado») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -24986,7 +24986,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Implica sempre não comer determinados alimentos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma alimentação saudável e equilibrada».</t>
+          <t>Implica sempre não comer determinados alimentos — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Pode ser constituída apenas por cereais») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -25046,7 +25046,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Provoca redução efetiva das capacidades necessárias para conduzir. No exame CAM do IMT, esta alternativa responde corretamente à questão «O consumo de álcool».</t>
+          <t>Provoca redução efetiva das capacidades necessárias para conduzir — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Não é causa de acidentes») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -25106,7 +25106,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Tem influência na condução, e por isso deve ser regulado por um médico. No exame CAM do IMT, esta alternativa responde corretamente à questão «O uso de medicamentos».</t>
+          <t>Tem influência na condução, e por isso deve ser regulado por um médico — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («É necessário para que se conduza em segurança») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -25166,7 +25166,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Todas as respostas anteriores estão correctas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Sob o efeito de drogas, um motorista».</t>
+          <t>Todas as respostas anteriores estão correctas — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Poderá ficar com as suas capacidades de condução afectadas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -25226,7 +25226,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Devem estar colocados de forma a minimizar os impactos na condução. No exame CAM do IMT, esta alternativa responde corretamente à questão «O uso de sistemas de comunicação e informação embarcados».</t>
+          <t>Devem estar colocados de forma a minimizar os impactos na condução — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Se for um telemóvel, a utilização do auricular é suficiente para evitar ac…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -25286,7 +25286,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Tem impacto na prestação de um serviço de qualidade. No exame CAM do IMT, esta alternativa responde corretamente à questão «A higiene, saúde e segurança no trabalho».</t>
+          <t>Tem impacto na prestação de um serviço de qualidade — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («É a única área relevante na formação dos motoristas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -25346,7 +25346,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Parar o motor sempre que a demora se preveja ser superior a 1 minuto. No exame CAM do IMT, esta alternativa responde corretamente à questão «Na chegada ao terminal do serviço, caso o veículo se encontre sem problemas, a atuação do Motorista deve ser».</t>
+          <t>O procedimento adequado é Parar o motor sempre que a demora se preveja ser superior a 1 minuto (C)). Por exemplo, D) («Não parar o motor para carregar a bateria») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -25406,7 +25406,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) No regime de rotações económicas do motor. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma redução de apenas 5% de consumo de combustível representa poupança energética e evita a emissão de várias tonelad...».</t>
+          <t>No regime de rotações económicas do motor — é o que melhor responde ao enunciado (opção C)). Por exemplo, A) («Sempre com velocidade máxima») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -25466,7 +25466,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Ao binário máximo do motor. No exame CAM do IMT, esta alternativa responde corretamente à questão «O regime de rotações que permite ao motor desenvolver maior força com menor consumo corresponde».</t>
+          <t>Ao binário máximo do motor — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («À potência máxima que o motor pode atingir») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -25526,7 +25526,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Aproveitar a força da inércia nas descidas. No exame CAM do IMT, esta alternativa responde corretamente à questão «É um comportamento de condução económica».</t>
+          <t>Aproveitar a força da inércia nas descidas — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Aproveitar as descidas para desengatar o veículo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -25586,7 +25586,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Todas as afirmações anteriores. No exame CAM do IMT, esta alternativa responde corretamente à questão «Conduzir economicamente significa».</t>
+          <t>Todas as afirmações anteriores — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Proporcionar um maior conforto na tarefa da condução») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -25646,7 +25646,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Todas as causas referidas nas alíneas anteriores “A escolha correcta dos pneus do veículo e a respetiva manutenção, influenciam o consumo de. No exame CAM do IMT, esta alternativa responde corretamente à questão «As principais causas para o aumento do consumo de combustível são».</t>
+          <t>Todas as causas referidas nas alíneas anteriores “A escolha correcta dos pneus do veículo e a respetiva manutenção, influenciam o consumo de — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Altas rotações na engrenagem das velocidades») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -25706,7 +25706,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Sim é importante, pois os dois fatores influenciam os consumos. No exame CAM do IMT, esta alternativa responde corretamente à questão «“A escolha correcta dos pneus do veículo e a respetiva manutenção, influenciam o consumo de combustível”. Identifique...».</t>
+          <t>Sim é importante, pois os dois fatores influenciam os consumos — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («As condições da via são as únicas responsáveis no consumo exagerado de com…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -25766,7 +25766,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) A um menor consumo de combustível. No exame CAM do IMT, esta alternativa responde corretamente à questão «O binário máximo de um automóvel corresponde».</t>
+          <t>A um menor consumo de combustível — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («A um regime máximo de rotações do motor e a um volume médio da potência») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -25826,7 +25826,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Sistema de Escape. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema do veículo que tem por função tratar a emissão de gases poluentes é».</t>
+          <t>Relativamente a «O sistema do veículo que tem por função tratar a emissão de gases poluentes é», a resposta adequada é B): Sistema de Escape.</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -25886,7 +25886,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Conduzir com os vidros abertos, quando se circula a maiores velocidades. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para uma condução económica constitui má prática».</t>
+          <t>Conduzir com os vidros abertos, quando se circula a maiores velocidades — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Manter a pressão de pneus uniforme e nos valores recomendados») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -25946,7 +25946,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) As emissões do veículo, diminuir a eficiência do motor e aumentar o consumo de combustível. No exame CAM do IMT, esta alternativa responde corretamente à questão «Caso o catalisador do sistema de exaustão esteja obstruído, pode influenciar».</t>
+          <t>As emissões do veículo, diminuir a eficiência do motor e aumentar o consumo de combustível — é o que melhor responde ao enunciado (opção C)). Por exemplo, A) («Somente as emissões do veículo automóvel») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -26006,7 +26006,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) 65% do seu curso. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para diminuir o consumo de combustível no início da marcha deve-se pressionar o pedal de acelerador a».</t>
+          <t>O procedimento adequado é 65% do seu curso (A)). Por exemplo, a opção B) indica valores (75% do seu curso) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -26066,7 +26066,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Desacelerar, prevendo o aparecimento de peões. No exame CAM do IMT, esta alternativa responde corretamente à questão «Ao aproximar-se de uma passadeira, o comportamento do motorista deve ser».</t>
+          <t>O procedimento adequado é Desacelerar, prevendo o aparecimento de peões (B)). Por exemplo, D) («Só tirar o pé do acelerador») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -26126,7 +26126,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Conduzir sempre com baixa velocidade. No exame CAM do IMT, esta alternativa responde corretamente à questão «A fim de poder evitar acidentes, o motorista deve».</t>
+          <t>O procedimento adequado é Conduzir sempre com baixa velocidade (A)). Por exemplo, D) («Respeitar rigorosamente a sinalização existente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -26186,7 +26186,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Qualquer uma das respostas anteriores está correta. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um dos cuidados a ter aquando da utilização do espelho retrovisor é».</t>
+          <t>Qualquer uma das respostas anteriores está correta — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Verificar se este se encontra devidamente regulado») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) A afirmação é verdadeira. No exame CAM do IMT, esta alternativa responde corretamente à questão «Em mais de 90 % dos acidentes rodoviários, o erro do condutor é o fator determinante. Comente».</t>
+          <t>A afirmação é verdadeira — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («A afirmação é falsa, porque a maior causa de acidentes é a degradação dos …») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -26306,7 +26306,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) A afirmação é verdadeira. No exame CAM do IMT, esta alternativa responde corretamente à questão «Ter um descanso correto e uma alimentação equilibrada são p rincípios básicos para uma condução mais segura.».</t>
+          <t>A afirmação é verdadeira — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A afirmação é falsa, porque nem o descanso correto nem a alimentação equil…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -26366,7 +26366,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) O coeficiente de atrito no eixo dianteiro é menor que no eixo traseiro. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma situação de sobreviragem surge quando».</t>
+          <t>O coeficiente de atrito no eixo dianteiro é menor que no eixo traseiro — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O veículo entra em derrapagem») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -26426,7 +26426,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Ligar as luzes de cruzamento. No exame CAM do IMT, esta alternativa responde corretamente à questão «De noite, sempre que o condutor circule a menos de 100 metros do veículo da frente deve».</t>
+          <t>Ligar as luzes de cruzamento — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Ligar os quatro piscas em simultâneo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -26486,7 +26486,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) No máximo do binário. No exame CAM do IMT, esta alternativa responde corretamente à questão «A engrenagem das mudanças deve ser feita».</t>
+          <t>O procedimento adequado é No máximo do binário (A)). Por exemplo, D) («No mínimo das rotações») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -26546,7 +26546,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Não, o sistema de travagem dos veículos pesados corresponde a uma forma de segurança ativa, enquanto que o capacete de proteção corresponde a uma medida de segurança passiva. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema de travagem dos veículos pesados de passageiros e o capacete de protecção dos motociclistas correspondem am...».</t>
+          <t>Não, o sistema de travagem dos veículos pesados corresponde a uma forma de segurança ativa, enquanto que o capacete de proteção corresponde a uma medida de segurança passiva — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Sim, ambos são medidas de segurança passiva») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -26606,7 +26606,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Cerca de 1 segundos. No exame CAM do IMT, esta alternativa responde corretamente à questão «O tempo médio de reação de um condutor é, em condições normais».</t>
+          <t>Cerca de 1 segundos — é o que melhor responde ao enunciado (opção A)). Por exemplo, a opção B) indica valores (Cerca de 2 ou 3 segundos) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -26666,7 +26666,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Análise, Percepção, Decisão, Ação. No exame CAM do IMT, esta alternativa responde corretamente à questão «A função “condução” divide-se em 4 fases, sendo a ordem correcta».</t>
+          <t>Análise, Percepção, Decisão, Ação — é o que melhor responde ao enunciado (opção A)). Relativamente a «A função “condução” divide-se em 4 fases, sendo a ordem correcta», a resposta adequada é A): Análise, Percepção, Decisão, Ação.</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -26726,7 +26726,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Espelho – Sinal – Espelho – Manobra. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nas manobras que implicam deslocação lateral dos veículos devo verificar o seguinte procedimento».</t>
+          <t>Antes de qualquer deslocação lateral, o condutor deve observar o espelho, sinalizar a intenção, voltar a consultar o espelho e só então executar a manobra. É a sequência «Espelho – Sinal – Espelho – Manobra» indicada em A).</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -26786,7 +26786,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) 4 Vezes mais. No exame CAM do IMT, esta alternativa responde corretamente à questão «A distância necessária para assegurar uma travagem forte num piso de alcatrão molhado de um veículo à velocidade de 6...».</t>
+          <t>4 Vezes mais — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (2 Vezes mais) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -26846,7 +26846,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Abdicar da prioridade para evitar o acidente. No exame CAM do IMT, esta alternativa responde corretamente à questão «Fazer uma condução defensiva é».</t>
+          <t>Abdicar da prioridade para evitar o acidente — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Não exceder dentro das localidades a velocidade de 50km/h») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -26906,7 +26906,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) A visão. No exame CAM do IMT, esta alternativa responde corretamente à questão «Qual é o órgão dos sentidos que é mais importante para desempenharmos corretamente a tarefa da condução?».</t>
+          <t>Relativamente a «Qual é o órgão dos sentidos que é mais importante para desempenharmos corretamente a…», a resposta adequada é C): A visão.</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -26966,7 +26966,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) A velocidade. No exame CAM do IMT, esta alternativa responde corretamente à questão «Dos fatores que se seguem, o mais determinante para o capotamento de veículos pesados é».</t>
+          <t>A velocidade — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («O pavimento escorregadio “A distribuição do peso na caixa de carga influen…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Adapta a marcha do veículo às condições do tráfego. No exame CAM do IMT, esta alternativa responde corretamente à questão «A condução económica ocorre quando o motorista».</t>
+          <t>Adapta a marcha do veículo às condições do tráfego — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Desrespeita as leis do trânsito») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -27086,7 +27086,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Antecipar as situações de trânsito, guardando a distância de segurança, de modo a evitar as acelerações e as travagens bruscas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma condução económica caracteriza-se por».</t>
+          <t>Antecipar as situações de trânsito, guardando a distância de segurança, de modo a evitar as acelerações e as travagens bruscas — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Acelerar com o motor frio») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -27146,7 +27146,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Ajustar, ao máximo, a velocidade à circulação viária existente no momento. No exame CAM do IMT, esta alternativa responde corretamente à questão «A forma de condução que devemos utilizar para reduzir o número de “pára -arranca”, mesmo estando numa fila de trânsit...».</t>
+          <t>O procedimento adequado é Ajustar, ao máximo, a velocidade à circulação viária existente no momento (A)). Por exemplo, D) («Circular de forma a ultrapassar pela esquerda e pela direita») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Deixar o motor ao ralenti. No exame CAM do IMT, esta alternativa responde corretamente à questão «Com o motor em funcionamento, a fim de carregar o sistema pneumático, o motorista deve».</t>
+          <t>O procedimento adequado é Deixar o motor ao ralenti (D)). Por exemplo, C) («Acelerar sem ultrapassar o regime de binário») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -27266,7 +27266,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Diminuir a resistência aerodinâmica.. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os reboques e/ou semi-reboques acoplados possuem dimensão, em altura, superior ao do trator. A colocação de deflector...».</t>
+          <t>Quando o reboque/semi-reboque é mais alto que o trator, o ar turbulento aumenta o consumo. Os deflectores no tejadilho do trator orientam o fluxo de ar e diminuir a resistência aerodinâmica, poupando combustível. Aumentar a resistência aerodinâmica seria o efeito oposto.</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -27326,7 +27326,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Utilização da inércia do veículo o que i rá traduzir-se numa menor necessidade de usar o acelerador, logo, menores consumos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Como exemplo de algumas das regras para a prática de uma cond ução económica e mais amiga do ambiente pode referir-se».</t>
+          <t>Utilização da inércia do veículo o que i rá traduzir-se numa menor necessidade de usar o acelerador, logo, menores consumos — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Condução a alta velocidade se as condições de trânsito o permitir») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -27386,7 +27386,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Em subida, selecione a relação da caixa de velocidades que permite subir conservando um regime de motor entre 1300 e 1400 rpm;. No exame CAM do IMT, esta alternativa responde corretamente à questão «A utilização correta da caixa de velocidades, irá permitir um menor consumo de combustível e menor desgaste de pneus ...».</t>
+          <t>Em subida, selecione a relação da caixa de velocidades que permite subir conservando um regime de motor entre 1300 e 1400 rpm; — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Em descida aumente a velocidade mantendo a rotação do motor para além da z…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -27446,7 +27446,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Determinar a massa de carga máxima que pode ser carregada no veículo, ao longo da plataforma. No exame CAM do IMT, esta alternativa responde corretamente à questão «A elaboração de um plano de distribuição da carga serve para».</t>
+          <t>Determinar a massa de carga máxima que pode ser carregada no veículo, ao longo da plataforma — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Determinar as forças de aceleração exercidas pela carga») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -27506,7 +27506,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Amarração de topo. No exame CAM do IMT, esta alternativa responde corretamente à questão «As cintas são frequentemente utilizadas para».</t>
+          <t>Amarração de topo — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Amarração directa de máquinas de estaleiro») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -27566,7 +27566,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Num sistema de fixação em que as amarrações são posicionadas por cima da parte superior das mercadorias e fixas a dois pontos de amarração do veículo (opostos). No exame CAM do IMT, esta alternativa responde corretamente à questão «A amarração de topo consiste».</t>
+          <t>Trata-se de uma definição: Num sistema de fixação em que as amarrações são posicionadas por cima da parte superior das mercadorias e fixas a dois pontos de amarração do veículo (opostos) (opção D)).  Por exemplo, C) («Na amarração direta entre os olhais de amarração da carga e os pontos de a…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -27626,7 +27626,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Desacelerar prevendo o aparecimento de peões. No exame CAM do IMT, esta alternativa responde corretamente à questão «mercadorias e fixas a dois pontos de amarração do veículo (opostos) Ao aproximar-se de uma passadeira, o comportament...».</t>
+          <t>O procedimento adequado é Desacelerar prevendo o aparecimento de peões (B)). Por exemplo, D) («Só tirar o pé do acelerador») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -27686,7 +27686,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Fadiga e sonolência. No exame CAM do IMT, esta alternativa responde corretamente à questão «Dos factores abaixo indicados, assinale aquele que pode contribuir para a ocorrência de acidentes».</t>
+          <t>Fadiga e sonolência — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Respeito pelos utentes da via») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -27746,7 +27746,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Aumentar a distância de segurança em relação ao veículo da frente. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para conduzir com antecipação, deve».</t>
+          <t>O procedimento adequado é Aumentar a distância de segurança em relação ao veículo da frente (D)). Por exemplo, C) («Aumentar a distância de paragem») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -27806,7 +27806,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Levantar o pé do pedal do acelerador. No exame CAM do IMT, esta alternativa responde corretamente à questão «Numa curva, deve».</t>
+          <t>Na situação «Numa curva, deve», o procedimento correto é Levantar o pé do pedal do acelerador (opção B)).</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -27866,7 +27866,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Reduzir a velocidade. No exame CAM do IMT, esta alternativa responde corretamente à questão «Ao aproximar-se de uma rotunda, a forma mais adequada de proceder é».</t>
+          <t>Reduzir a velocidade — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Entrar na logo rotunda pois, enquanto veículo pesado, temos sempre priorid…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -27926,7 +27926,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Travamento ou bloqueio. No exame CAM do IMT, esta alternativa responde corretamente à questão «O acondicionamento da carga pode ser feito através do método de».</t>
+          <t>Travamento ou bloqueio — é o que melhor responde ao enunciado (opção C)). Relativamente a «O acondicionamento da carga pode ser feito através do método de», a resposta adequada é C): Travamento ou bloqueio.</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -27986,7 +27986,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) O conjunto do peso da tara e da carga que o veículo pode transportar. No exame CAM do IMT, esta alternativa responde corretamente à questão «O peso bruto de um veículo é».</t>
+          <t>O conjunto do peso da tara e da carga que o veículo pode transportar — é o que melhor responde ao enunciado (opção A)). Por exemplo, B) («O peso do veículo vazio») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -28046,7 +28046,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) 29 toneladas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O peso bruto máximo de um conjunto veículo trator-semi-reboque de três eixos é».</t>
+          <t>O valor ou limite legal aplicável é 29 toneladas, indicado em A).  Por exemplo, a opção B) indica valores (32 toneladas) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -28106,7 +28106,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) De topo, em laço, com lançantes, envolvente e directa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os tipos de amarração que existem são».</t>
+          <t>De topo, em laço, com lançantes, envolvente e directa — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («De topo, de base, directa e indirecta») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -28166,7 +28166,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Proteção de cargas que soltem grãos ou poeiras. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os toldos a colocar nos veículos de caixa aberta, devem ser utilizados para».</t>
+          <t>O procedimento adequado é Proteção de cargas que soltem grãos ou poeiras (C)). Por exemplo, D) («Criação de bolsas de ar») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -28226,7 +28226,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) O trator deve iniciar o processo de travagem primeiro que o reboque e / ou semi-reboque.. No exame CAM do IMT, esta alternativa responde corretamente à questão «No processo de travagem de veículos pe sados com reboque ou semi -reboque, indique a afirmação verdadeira».</t>
+          <t>O trator deve iniciar o processo de travagem primeiro que o reboque e / ou semi-reboque. — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («É mais seguro ser só o veículo trator a proceder à travagem.») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Força que se opõe à deslocação do veículo, tendo este que a vencer para se deslocar. No exame CAM do IMT, esta alternativa responde corretamente à questão «Sobre o veículo automóvel pesado incidem um conjunto de forças que poderão colocar em causa a sua segurança. Entende-...».</t>
+          <t>Força que se opõe à deslocação do veículo, tendo este que a vencer para se deslocar — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («Forças geradas pela deslocação do veículo à retaguarda») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Diminuir a velocidade de cada um dos veículos, encostando-os o mais à direita possível.. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando ocorre o cruzamento de dois veículos pesados com mais do que 8 metros de comprimento, que circulam em sentido ...».</t>
+          <t>Diminuir a velocidade de cada um dos veículos, encostando-os o mais à direita possível. — é o que melhor responde ao enunciado (opção D)). Por exemplo, A) («Aumentar a velocidade.») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -28406,7 +28406,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Maior for a distância entre eixos.. No exame CAM do IMT, esta alternativa responde corretamente à questão «A amplitude de raio de viragem de um veículo pesado de mercadorias é tanto maior quanto».</t>
+          <t>Maior for a distância entre eixos. — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Menor for o peso bruto.») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -28466,7 +28466,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) No transporte com depósito não completamente atestado, o motorista deve ter especial atenção ao efetuar uma curva e ao travar. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os veículos automóveis pesados de mercadorias que transportem cargas móveis (ex: líquido em cisternas) devem ter dete...».</t>
+          <t>O procedimento adequado é No transporte com depósito não completamente atestado, o motorista deve ter especial atenção ao efetuar uma curva e ao travar (C)). Por exemplo, D) («A travagem de veículo com carga móvel nunca irá provocar impulsos no veícu…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -28526,7 +28526,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Posição inadequada ao volante. No exame CAM do IMT, esta alternativa responde corretamente à questão «Como causas potenciadoras de fadiga pode referir-se».</t>
+          <t>Posição inadequada ao volante — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Ventilação regular do habitáculo do veículo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -28586,7 +28586,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) 4 m. No exame CAM do IMT, esta alternativa responde corretamente à questão «A altura máxima permitida para os veículos de mercadorias (carga geral) é de».</t>
+          <t>4 m — é o que melhor responde ao enunciado (opção A)). Por exemplo, a opção B) indica valores (4,2 m) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -28646,7 +28646,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Inclinar-se quando sujeita a forças horizontais. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quanto mais elevado for o centro de gravidade de uma carga mais esta tenderá a».</t>
+          <t>Inclinar-se quando sujeita a forças horizontais — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Estabilizar o comportamento dinâmico do veículo;») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Desacelerar à distância conveniente, reduzindo a carga no acelerador. No exame CAM do IMT, esta alternativa responde corretamente à questão «Num piso irregular e com pouca aderência, o motorista deve».</t>
+          <t>O procedimento adequado é Desacelerar à distância conveniente, reduzindo a carga no acelerador (B)). Por exemplo, D) («Desacelerar e travar logo de seguida») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -28766,7 +28766,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Evitar o deslocamento de objetos cilíndricos ao longo da plataforma de carga. No exame CAM do IMT, esta alternativa responde corretamente à questão «O travamento com calços é utilizado para».</t>
+          <t>Evitar o deslocamento de objetos cilíndricos ao longo da plataforma de carga — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Imobilizar a m ercadoria quando há folgas muito grandes entre a carga e os…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Ensaio da embraiagem e sistema de travagem. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para a salvaguarda da sua segurança, e dos outros utentes da via o motorista deve fazer diariamente antes de iniciar ...».</t>
+          <t>O procedimento adequado é Ensaio da embraiagem e sistema de travagem (D)). Por exemplo, C) («Nível do óleo de lubrificação do motor e indicador de colmatagem do filtro…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -28886,7 +28886,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Sim, sempre. No exame CAM do IMT, esta alternativa responde corretamente à questão «Comente a afirmação: “A distribuição do peso na caixa de carga pode influenciar o consumo de combustível”».</t>
+          <t>Sim, sempre — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A distribuição é importante só para objetos pesados») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -28946,7 +28946,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) A comodidade dos passageiros que transporta. No exame CAM do IMT, esta alternativa responde corretamente à questão «A correta utilização do acelerador por um motorista contribui para».</t>
+          <t>A comodidade dos passageiros que transporta — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O aumento do consumo de combustível») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -29006,7 +29006,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) 61% dos assaltos ocorreram nos parques ou áreas de serviço. No exame CAM do IMT, esta alternativa responde corretamente à questão «De acordo com a IRU».</t>
+          <t>61% dos assaltos ocorreram nos parques ou áreas de serviço — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («61% dos assaltos ocorreram com os veículos imobilizados por avaria») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -29066,7 +29066,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) A maior parte são urbanas ou fronteiriças. A Roménia, a Hungria, a Polónia e a Rússia têm as mais elevadas taxas de agressões. No exame CAM do IMT, esta alternativa responde corretamente à questão «No que respeita a criminalidade, as zonas sensíveis na Europa são».</t>
+          <t>A questão relaciona-se com condução segura, prevenção de acidentes e comportamento ao volante. No caso «No que respeita a criminalidade, as zonas sensíveis na Europa são», a opção C) é a alternativa que melhor se aplica ao caso: A maior parte são urbanas ou fronteiriças. A Roménia, a Hungria, a Polónia e a Rússia têm as mais elevadas taxas de agressões.</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -29126,7 +29126,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) A planificação detalhada do itinerário. No exame CAM do IMT, esta alternativa responde corretamente à questão «Antes de iniciar o transporte, entende -se como uma boa prática, com vista a evitar situações de criminalidade e vand...».</t>
+          <t>A planificação detalhada do itinerário — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Nenhuma das hipóteses anteriores pode ser considerada boa prática») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -29186,7 +29186,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Antes de iniciar a viagem. No exame CAM do IMT, esta alternativa responde corretamente à questão «A verificação do correcto funcionamento dos dispositivos de alarme da viatura deve ser feita».</t>
+          <t>O procedimento adequado é Antes de iniciar a viagem (A)). Por exemplo, C) («Apenas quando vai fazer uma viagem para fora de território nacional») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -29246,7 +29246,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) A prevenção. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma das características fundamentais para a segurança de um condutor e».</t>
+          <t>A prevenção — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O alheamento de comportamentos que visam a promoção da proteção dos bens e…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -29306,7 +29306,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Evitar falar do conteúdo e valor do transporte e dos itinerários escolhidos, com pessoas estranhas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Entende-se como uma boa prática, durante o abastecimento da viatura, com vista a evitar situações de criminalidade e ...».</t>
+          <t>Evitar falar do conteúdo e valor do transporte e dos itinerários escolhidos, com pessoas estranhas — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Basta efetuar o abastecimento em postos com sistema de vigilância») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -29366,7 +29366,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Evitar parques de estacionamento isolados. No exame CAM do IMT, esta alternativa responde corretamente à questão «Durante o estacionamento da viatura, o condutor deve».</t>
+          <t>O procedimento adequado é Evitar parques de estacionamento isolados (B)). Por exemplo, D) («Procurar locais de estacionamento grátis») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -29426,7 +29426,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Avisar as autoridades e o proprietário do veículo em causa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Em caso de desaparecimento da viatura o condutor deve».</t>
+          <t>O procedimento adequado é Avisar as autoridades e o proprietário do veículo em causa (A)). Por exemplo, C) («Apenas avisar as autoridades do sucedido») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -29486,7 +29486,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Avisar as autoridades e o proprietário do veículo em causa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se a viatura que conduz for sujeita a atos de vandalismo, deve».</t>
+          <t>O procedimento adequado é Avisar as autoridades e o proprietário do veículo em causa (A)). Por exemplo, C) («Apenas avisar as autoridades do sucedido») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -29546,7 +29546,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Possua vigilância e os veículos sejam controlados à entrada e à saída. No exame CAM do IMT, esta alternativa responde corretamente à questão «Parque de estacionamento seguro é o que».</t>
+          <t>Possua vigilância e os veículos sejam controlados à entrada e à saída — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Careça de pagamento, não sendo necessária vídeo vigilância») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -29606,7 +29606,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Roménia, Hungria, Polónia e Rússia. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os países europeus que representam maior risco por possuírem taxas elevadas no que diz respeito a índices de agressão...».</t>
+          <t>Roménia, Hungria, Polónia e Rússia — é o que melhor responde ao enunciado (opção D)). Relativamente a «Os países europeus que representam maior risco por possuírem taxas elevadas no que diz…», a resposta adequada é D): Roménia, Hungria, Polónia e Rússia.</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -29666,7 +29666,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) A afirmação é verdadeira. No exame CAM do IMT, esta alternativa responde corretamente à questão «As entradas e saídas de um parque de estacionamento seguro são, regra geral, controladas por vídeo vigilância e apena...».</t>
+          <t>A afirmação é verdadeira — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A afirmação é parcialmente falsa») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -29726,7 +29726,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Da polícia, autoridade anti-terrorismo e proteção civil e da embaixada. No exame CAM do IMT, esta alternativa responde corretamente à questão «No que se refere a segurança, o condutor que se desloque a outro país  deve conhecer sempre os números de contacto».</t>
+          <t>O procedimento adequado é Da polícia, autoridade anti-terrorismo e proteção civil e da embaixada (B)). Por exemplo, D) («Dos melhores hotéis e áreas de lazer») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -29786,7 +29786,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Transportar consigo objetos de valor e grandes quantias de dinheiro. No exame CAM do IMT, esta alternativa responde corretamente à questão «O motorista deve evitar».</t>
+          <t>O procedimento adequado é Transportar consigo objetos de valor e grandes quantias de dinheiro (A)). Por exemplo, D) («Falar com as pessoas que conhece») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -29846,7 +29846,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Saber onde são os parques de estacionamento mais seguros para estacionar a viatura e descansar em segurança.. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nas viagens internacionais deve».</t>
+          <t>O procedimento adequado é Saber onde são os parques de estacionamento mais seguros para estacionar a viatura e descansar em segurança. (D)). Por exemplo, C) («Estacionar a viatura em qualquer local») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -29906,7 +29906,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Preferir os parques de estacionamento bem iluminados e onde já estejam algumas viaturas também. No exame CAM do IMT, esta alternativa responde corretamente à questão «em segurança. Durante a noite, quando tiver de parar para descansar, o motorista deve».</t>
+          <t>O procedimento adequado é Preferir os parques de estacionamento bem iluminados e onde já estejam algumas viaturas também (D)). Por exemplo, C) («Deixar as janelas da viatura abertas para arejar o habitáculo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -29966,7 +29966,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Voltaram todos a entrar e verificar através de uma listagem se são as mesmas pessoas. No exame CAM do IMT, esta alternativa responde corretamente à questão «estacionadas Numa viagem internacional, após uma paragem, o motorista deve, antes de dar continuidade à viagem, verif...».</t>
+          <t>O procedimento adequado é Voltaram todos a entrar e verificar através de uma listagem se são as mesmas pessoas (A)). Por exemplo, D) («Descansaram um pouco.») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -30026,7 +30026,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Entrega as bagagens certas aos respetivos passageiros e que não existe nada de estranho entre elas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando se dirigir à bagageira para retirar ou colocar as bagagens o motorista deve certificar-se que».</t>
+          <t>O procedimento adequado é Entrega as bagagens certas aos respetivos passageiros e que não existe nada de estranho entre elas (D)). Por exemplo, C) («As bagagens têm todas mais ou menos o mesmo peso») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -30086,7 +30086,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Os dispositivos de segurança estão todos a funcionar corretamente. No exame CAM do IMT, esta alternativa responde corretamente à questão «veículo qualquer pessoa estranha Antes de iniciar uma viagem internacional o motorista deve certificar-se que».</t>
+          <t>O procedimento adequado é Os dispositivos de segurança estão todos a funcionar corretamente (A)). Por exemplo, D) («Os passageiros falam todos português corretamente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -30146,7 +30146,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Todas as alíneas anteriores estão certas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Durante uma viagem, a bordo da viatura deve estar uma lista de verificações que serve para».</t>
+          <t>O procedimento adequado é Todas as alíneas anteriores estão certas (D)). Por exemplo, C) («O motorista colocar os dados relativos às mercadorias transportadas ou bag…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -30206,7 +30206,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Chamar de imediato as autoridades competentes. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se o motorista se aperceber que leva um clandestino a bordo qual o procedimento adequado».</t>
+          <t>O procedimento adequado é Chamar de imediato as autoridades competentes (B)). Por exemplo, D) («Fazer de conta que não o viu») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -30266,7 +30266,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Pela via rodoviária, marítima e raramente por via aérea. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os clandestinos procuram introduzir-se na Europa por uma ou mais vias. Indique quais».</t>
+          <t>Pela via rodoviária, marítima e raramente por via aérea — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -30326,7 +30326,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Necessidade de ligação constante com a empresa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nas deslocações em território nacional deve ter sempre presente».</t>
+          <t>O procedimento adequado é Necessidade de ligação constante com a empresa (A)). Por exemplo, D) («Que o serviço começa e termina com o início da viagem») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -30386,7 +30386,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Antes de entrar no veículo verifique se há pessoas a passear na área. No exame CAM do IMT, esta alternativa responde corretamente à questão «Relativamente à segurança passiva, quais as ações que preventivamente deve tomar».</t>
+          <t>O procedimento adequado é Antes de entrar no veículo verifique se há pessoas a passear na área (A)). Por exemplo, D) («Estacione em qualquer parque») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -30446,7 +30446,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Busca sumária ao exterior depois ao interior, em todos os locais susceptíveis de esconder um objeto ou pessoa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Antes e depois de entrar no veículo qual é a tarefa que deve dar especial atenção à».</t>
+          <t>O procedimento adequado é Busca sumária ao exterior depois ao interior, em todos os locais susceptíveis de esconder um objeto ou pessoa (C)). Por exemplo, D) («Verificar se a viatura tem riscos e vidros partidos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -30506,7 +30506,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Manter bom relacionamento e controlo dos passageiros, capacidade do saber ouvir para assim, responder adequadamente e evitar a discussão. No exame CAM do IMT, esta alternativa responde corretamente à questão «Durante o percurso para evitar e prevenir situações de risco, sobretudo, em situações de conflito violento, deve».</t>
+          <t>O procedimento adequado é Manter bom relacionamento e controlo dos passageiros, capacidade do saber ouvir para assim, responder adequadamente e evitar a discussão (B)). Por exemplo, D) («Informar os passageiros que em caso de conflito está autorizado a usar a f…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -30566,7 +30566,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Tráfico e consumo de estupefacientes e substâncias psicotrópicas tipificados no Dec-Lei n.º 15/93 de 22 de Janeiro. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os motoristas estão sujeitos a determinadas consequências por cometerem determinados tipos de crime relativamente à s...».</t>
+          <t>Tráfico e consumo de estupefacientes e substâncias psicotrópicas tipificados no Dec-Lei n.º 15/93 de 22 de Janeiro — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Dar bebidas alcoólicas ao seu colega e/ou a desconhecidos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -30626,7 +30626,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Nos locais de estacionamento e áreas de serviço. No exame CAM do IMT, esta alternativa responde corretamente à questão «De acordo com os dados do International Road Transport Union, a maioria dos ataques aos veículos de transporte ocorrem».</t>
+          <t>Nos locais de estacionamento e áreas de serviço — é o que melhor responde ao enunciado (opção D)). Por exemplo, B) («No local de descarga, no destinatário.») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -30686,7 +30686,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) De noite. No exame CAM do IMT, esta alternativa responde corretamente à questão «Mais de 50 % dos ataques aos veículos de transporte ocorrem».</t>
+          <t>De noite — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Entre as 9h00 e as 12h00») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -30746,7 +30746,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Estacionar em locais isolados, com o menor número de veículos pesados possíveis. No exame CAM do IMT, esta alternativa responde corretamente à questão «Na paragem para descanso, no decorrer do transporte, indique que medida não adoptaria».</t>
+          <t>Estacionar em locais isolados, com o menor número de veículos pesados possíveis — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Não estacionar o veículo de modo a que as portas de carga e descarga se en…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -30806,7 +30806,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Verificar os danos provocados no veículo, avaliar as perdas da carga e comunicar imediatamente á entidade patronal e à polícia, ajudando no relatório do roubo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Diga o que fazer em caso de emergência de roubo ou assalto».</t>
+          <t>Em roubo ou assalto à carga, o condutor deve preservar a segurança, avaliar danos e perdas, comunicar de imediato ao empregador e à polícia e colaborar no registo do incidente. Isso corresponde a B): Verificar os danos provocados no veículo, avaliar as perdas da carga e comunicar imediatamente á entidade patronal e à polícia, ajudando no relatório do roubo.</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Verificar os danos provocados no veículo, avaliar as perdas da carga e comunicar imediatamente á entidade patronal e à polícia, ajudando no relatório do roubo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Diga o que fazer em caso de emergência de roubo ou assalto».</t>
+          <t>Em roubo ou assalto à carga, o condutor deve preservar a segurança, avaliar danos e perdas, comunicar de imediato ao empregador e à polícia e colaborar no registo do incidente. Isso corresponde a B): Verificar os danos provocados no veículo, avaliar as perdas da carga e comunicar imediatamente á entidade patronal e à polícia, ajudando no relatório do roubo.</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -30926,7 +30926,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Entrar na cabine do veículo e sair do local o mais rápido possível. No exame CAM do IMT, esta alternativa responde corretamente à questão «No caso de sofrer uma agressão, indique quais dos seguintes procedimentos não adotaria».</t>
+          <t>O procedimento adequado é Entrar na cabine do veículo e sair do local o mais rápido possível (D)). Por exemplo, C) («Comunicar de imediato à entidade empregadora») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -30986,7 +30986,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Mantenha a calma, não abra o vidro, e se necessário contacte a polícia. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se durante uma paragem na via for abordado por um estranho, qual dos procedimentos adotaria».</t>
+          <t>O procedimento adequado é Mantenha a calma, não abra o vidro, e se necessário contacte a polícia (A)). Por exemplo, D) («Sair do veículo e afaste o estranho») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -31046,7 +31046,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Se no decorrer de um transporte, um utente i nsistir entrar sem documento de embarque, deixar entrar, se houver lugares disponíveis. No exame CAM do IMT, esta alternativa responde corretamente à questão «No transporte de pesados de passageiros, indique que procedimento não adoptaria».</t>
+          <t>O procedimento adequado é Se no decorrer de um transporte, um utente i nsistir entrar sem documento de embarque, deixar entrar, se houver lugares disponíveis (D)). Por exemplo, C) («Verificar, no decorrer de uma pausa de descanso, a eventual entrada de pes…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -31106,7 +31106,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Descansar e aguardar que seja efetuada a descarga. No exame CAM do IMT, esta alternativa responde corretamente à questão «entrar, se houver lugares disponíveis Quando da chegada ao destinatário, o motorista não deve».</t>
+          <t>O procedimento adequado é Descansar e aguardar que seja efetuada a descarga (A)). Por exemplo, D) («Verificar se o lacre colocado no compartimento de carga ainda está intacto…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -31166,7 +31166,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Planear os detalhes do itinerário e não seguir sempre o mesmo percurso. No exame CAM do IMT, esta alternativa responde corretamente à questão «todas retiradas Uma das formas de prevenir a criminalidade é, antes da viagem».</t>
+          <t>Planear os detalhes do itinerário e não seguir sempre o mesmo percurso — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Assegurar-se que a entrega da mercadoria é feita no local correcto ou os p…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -31226,7 +31226,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) O norte de França. No exame CAM do IMT, esta alternativa responde corretamente à questão «no local programado Das zonas abaixo referidas, uma das mais sensíveis da Europa no que respeita a segurança é».</t>
+          <t>Relativamente a «no local programado Das zonas abaixo referidas, uma das mais sensíveis da Europa no que…», a resposta adequada é C): O norte de França.</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -31286,7 +31286,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Legumes. No exame CAM do IMT, esta alternativa responde corretamente à questão «No que se refere a segurança, não é considerada uma “mercadoria sensível”».</t>
+          <t>Relativamente a «No que se refere a segurança, não é considerada uma “mercadoria sensível”», a resposta adequada é C): Legumes.</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -31346,7 +31346,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Hungria. No exame CAM do IMT, esta alternativa responde corretamente à questão «Dos países abaixo referidos, a taxa de agressão a motoristas é maior na».</t>
+          <t>Relativamente a «Dos países abaixo referidos, a taxa de agressão a motoristas é maior na», a resposta adequada é A): Hungria.</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -31406,7 +31406,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Colocar cintas de segurança, trancas/fechaduras e o cabo de segurança TIR ou fechar bem o veículo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para impedir o roubo do veículo ou da carga, deve».</t>
+          <t>O procedimento adequado é Colocar cintas de segurança, trancas/fechaduras e o cabo de segurança TIR ou fechar bem o veículo (B)). Por exemplo, D) («Possuir uma arma de defesa pessoal») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -31466,7 +31466,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Deve observar todas as anteriores respostas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando estaciona o veículo num parque deve».</t>
+          <t>O procedimento adequado é Deve observar todas as anteriores respostas (D)). Por exemplo, C) («Fechar todas as portas à chave e levar todas as chaves, desde que os regul…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -31526,7 +31526,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Três anos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quem favorecer ou facilitar a entrada ou o trânsito ilegais de cidadão estrangeiro em território português, incorre n...».</t>
+          <t>Relativamente a «Quem favorecer ou facilitar a entrada ou o trânsito ilegais de cidadão estrangeiro em…», a resposta adequada é C): Três anos.</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -31586,7 +31586,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Revela comportamento negligente ao não empreender pessoalmente quaisquer verificações do veículo durante a viagem. No exame CAM do IMT, esta alternativa responde corretamente à questão «Perante o transporte de passageiros clandestinos, as autoridades britânicas aplicarão a sanção máxima ao motorista que».</t>
+          <t>Trata-se de uma definição: Revela comportamento negligente ao não empreender pessoalmente quaisquer verificações do veículo durante a viagem (opção D)).  Por exemplo, C) («Procedeu a verificações do exterior do veículo antes de embarcar para o Re…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -31646,7 +31646,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Lista de Verificações do Home Office. No exame CAM do IMT, esta alternativa responde corretamente à questão «A Lista de Verificações que dá mais gar antias de evitar a aplicação de coimas, caso o motorista transporte clandesti...».</t>
+          <t>Lista de Verificações do Home Office — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Lista de Verificações da associação de transportadores inglesa») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -31706,7 +31706,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) O motorista. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quem é o principal responsável pela implementação prática de um sistema eficaz de prevenção do transporte de clandest...».</t>
+          <t>O motorista — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Os agentes fiscalizadores do porto de embarque para o Reino Unido») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -31766,7 +31766,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Antecipar eventuais situações de risco para poder reagir adequadamente. No exame CAM do IMT, esta alternativa responde corretamente à questão «A utilização responsável da rede de estradas implica».</t>
+          <t>Antecipar eventuais situações de risco para poder reagir adequadamente — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Sempre que possível utilizar os trajetos mais curtos, mesmo que não sejam …») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -31826,7 +31826,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Sinalizar o veículo, alertar as autoridades e parar o motor do veículo. No exame CAM do IMT, esta alternativa responde corretamente à questão «As regras gerais de actuação em caso de acidente são».</t>
+          <t>O procedimento adequado é Sinalizar o veículo, alertar as autoridades e parar o motor do veículo (A)). Por exemplo, D) («Nenhuma das respostas anteriores está correcta») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -31886,7 +31886,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) 112. No exame CAM do IMT, esta alternativa responde corretamente à questão «Em caso de acidente e suspeita de vítimas acidentadas com lesões deverá ligar para o».</t>
+          <t>O procedimento adequado é 112 (B)). Por exemplo, a opção A) indica valores (113) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -31946,7 +31946,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Entre o combustível e o oxigénio do ar (comburente), face a uma fonte de calor. No exame CAM do IMT, esta alternativa responde corretamente à questão «Fogo é uma reação química».</t>
+          <t>Entre o combustível e o oxigénio do ar (comburente), face a uma fonte de calor — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Que ocorre em determinados materiais provocado pelo aumento da temperatura») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -32006,7 +32006,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Todas as respostas anteriores estão correctas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O 1º Socorro é a primeira assistência ou ajuda prestada a qualquer indivíduo vítima de acidente ou doença súbita, com...».</t>
+          <t>Todas as respostas anteriores estão correctas — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Promover a recuperação») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -32066,7 +32066,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Pode ser realizado apenas por um condutor. No exame CAM do IMT, esta alternativa responde corretamente à questão «O preenchimento da Declaração Amigável de Acidente Automóvel (DAAA)».</t>
+          <t>Pode ser realizado apenas por um condutor — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Pode omitir o esquema de acidente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -32126,7 +32126,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Convenção internacional, denominada Convenção Multilateral de Garantias. No exame CAM do IMT, esta alternativa responde corretamente à questão «“Carta Verde” é uma».</t>
+          <t>Convenção internacional, denominada Convenção Multilateral de Garantias — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Carta que substitui a Carta de Condução») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -32186,7 +32186,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Escolho áreas de estacionamento vigiadas e seguras. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para prevenir atos de vandalismo, roubo ou sequestro num veículo».</t>
+          <t>Escolho áreas de estacionamento vigiadas e seguras — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Todas as anteriores respostas estão correctas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -32246,7 +32246,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Sim. No exame CAM do IMT, esta alternativa responde corretamente à questão «O seguro obrigatório automóvel garante as indemnizações devidas por danos pessoais ou materiais causados a terceiros ...».</t>
+          <t>Sim — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Todas as respostas estão incorretas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -32306,7 +32306,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) 30 compressões para 2 insuflações (30:2). No exame CAM do IMT, esta alternativa responde corretamente à questão «Na Reanimação Cardio-Respiratória, a razão entre as compressões torácicas e as insuflações é».</t>
+          <t>A questão relaciona-se com condução segura, prevenção de acidentes e comportamento ao volante. No caso «Na Reanimação Cardio-Respiratória, a razão entre as compressões torácicas e as insuflações é», a opção C) é a alternativa que melhor se aplica ao caso: 30 compressões para 2 insuflações (30:2). A opção A) («15 compressões para 3 insuflações (15:3)») apresenta valores diferentes dos exigidos nesta situação A opção B) («20 compressões para 5 insuflações (20:5)») apresenta valores diferentes dos exigidos nesta situação.</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -32366,7 +32366,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Mulheres grávidas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Não devem ser aplicadas compressões abdominais em».</t>
+          <t>O procedimento adequado é Mulheres grávidas (A)). Por exemplo, D) («Idosos com mais de 70 anos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -32426,7 +32426,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Deve ser provocada nas vítimas que respiram normalmente. No exame CAM do IMT, esta alternativa responde corretamente à questão «A posição lateral de segurança».</t>
+          <t>Deve ser provocada nas vítimas que respiram normalmente — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A posição lateral nunca deve ser provocada») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -32486,7 +32486,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Não tocar na lesão. No exame CAM do IMT, esta alternativa responde corretamente à questão «Em caso de queimadura deve-se».</t>
+          <t>O procedimento adequado é Não tocar na lesão (B)). Por exemplo, D) («Colocar sobre a lesão soluções ou pomadas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -32546,7 +32546,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Se a vítima estiver contaminada com tóxicos ou venenos o socorrista deve usar proteções do corpo e da roupa (luvas e avental). No exame CAM do IMT, esta alternativa responde corretamente à questão «Em caso de intoxicação».</t>
+          <t>O procedimento adequado é Se a vítima estiver contaminada com tóxicos ou venenos o socorrista deve usar proteções do corpo e da roupa (luvas e avental) (B)). Por exemplo, D) («Deve ser fornecido álcool à vítima») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -32606,7 +32606,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Deve ser sucinto e relatar resumidamente o que aconteceu. No exame CAM do IMT, esta alternativa responde corretamente à questão «No preenchimento da Declaração Amigável de Acidente Automóvel».</t>
+          <t>Deve ser sucinto e relatar resumidamente o que aconteceu — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («É obrigatório o preenchimento do verso do impresso na hora do acidente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -32666,7 +32666,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Não movimentar a vítima, exceto se existir perigo iminente de incêndio, explosão ou qualquer outra situação que ponha em risco a vida da vítima. No exame CAM do IMT, esta alternativa responde corretamente à questão «Perante uma vítima de acidente o procedimento adequado é».</t>
+          <t>O procedimento adequado é Não movimentar a vítima, exceto se existir perigo iminente de incêndio, explosão ou qualquer outra situação que ponha em risco a vida da vítima (B)). Por exemplo, D) («Ajudar a vítima a sair do veículo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -32726,7 +32726,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Prevenir, alertar e socorrer. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os princípios gerais de socorrismo são».</t>
+          <t>Prevenir, alertar e socorrer — é o que melhor responde ao enunciado (opção D)). Por exemplo, A) («Prever, ajudar e socorrer») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -32786,7 +32786,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Com realização de pancadas interescapulares ou manobra de Heimlich. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma vítima de asfixia por obstr ução das vias respiratórias devido à presença de um corpo estranho deve ser socorrida».</t>
+          <t>O procedimento adequado é Com realização de pancadas interescapulares ou manobra de Heimlich (C)). Por exemplo, D) («Através da colocação em decúbito dorsal») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -32846,7 +32846,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Desobstruir as vias aéreas, fazer a extensão da cabeça, pedir ajuda e verificar se está a respirar. No exame CAM do IMT, esta alternativa responde corretamente à questão «No caso da vítima não responder aos estímulos do socorrista, o procedimento correto é».</t>
+          <t>O procedimento adequado é Desobstruir as vias aéreas, fazer a extensão da cabeça, pedir ajuda e verificar se está a respirar (C)). Por exemplo, D) («Colocar em decúbito dorsal») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -32906,7 +32906,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Estacionar o veículo depois do local do acidente, ligar as luzes de perigo, vestir o colete e colocar o sinal de pré-sinalização de perigo a pelo menos 30m da retaguarda do veículo ou da carga a sinalizar.. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para sinalizar corretamente o local do acidente o motorista deve».</t>
+          <t>Estacionar o veículo depois do local do acidente, ligar as luzes de perigo, vestir o colete e colocar o sinal de pré-sinalização de perigo a pelo menos 30m da retaguarda do veículo ou da carga a sinalizar. — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção C) indica valores (Estacionar o veículo antes do local do acidente, ligar as luzes de perigo,…) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -32966,7 +32966,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Estacionar o veículo antes do local do acidente, ligar as luzes de perigo, vestir o colet e e colocar o sinal de pré-sinalização de perigo a pelo menos 30m da retaguarda do veículo ou da carga a sinalizar.. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para sinalizar corretamente o local do acidente o motorista deve».</t>
+          <t>Estacionar o veículo antes do local do acidente, ligar as luzes de perigo, vestir o colet e e colocar o sinal de pré-sinalização de perigo a pelo menos 30m da retaguarda do veículo ou da carga a sinalizar. — é o que melhor responde ao enunciado (opção A)). Por exemplo, a opção C) indica valores (Estacionar o veículo antes do local do acidente, ligar as luzes de perigo,…) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -33026,7 +33026,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Colocar a vítima sentada com a cabeça direita e fazer compressão com o polegar e o indicador em pinça apertando as extremidades do nariz. No exame CAM do IMT, esta alternativa responde corretamente à questão «Numa situação de epistaxis (hemorragia pelo nariz), o socorrista deve».</t>
+          <t>O procedimento adequado é Colocar a vítima sentada com a cabeça direita e fazer compressão com o polegar e o indicador em pinça apertando as extremidades do nariz (D)).</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -33086,7 +33086,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Todas as respostas anteriores estão correctas. No exame CAM do IMT, esta alternativa responde corretamente à questão «pinça apertando as extremidades do nariz Quando se liga 112».</t>
+          <t>Todas as respostas anteriores estão correctas — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Estamos a ligar diretamente para os bombeiros») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -33146,7 +33146,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Devem ser referidas todas as informações anteriores. No exame CAM do IMT, esta alternativa responde corretamente à questão «Ao ligar 112, o mais importante é».</t>
+          <t>Devem ser referidas todas as informações anteriores — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Fornecer o número de telefone de onde se está a efetuar o pedido de socorro») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -33206,7 +33206,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Deve-se esperar durante 10 segundos para ver se a vítima respira ou não. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para perceber se alguém está em paragem cardio-respiratória».</t>
+          <t>Deve-se esperar durante 10 segundos para ver se a vítima respira ou não — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Nenhuma das respostas anteriores está correcta») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -33266,7 +33266,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) O melhor método é fazer compressão direta. No exame CAM do IMT, esta alternativa responde corretamente à questão «Perante uma ferida simples numa zona sem fraturas».</t>
+          <t>O melhor método é fazer compressão direta — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Uma hemorragia não é grave e por isso não é necessário fazer nada») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -33326,7 +33326,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Todas as respostas anteriores estão corretas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Numa situação de queimadura, os cuidados de emergência visam».</t>
+          <t>Todas as respostas anteriores estão corretas — é o que melhor responde ao enunciado (opção D)). Relativamente a «Numa situação de queimadura, os cuidados de emergência visam», a resposta adequada é D): Todas as respostas anteriores estão corretas.</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -33386,7 +33386,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Todas as respostas anteriores estão correctas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Em caso de incêndio, um motorista».</t>
+          <t>O procedimento adequado é Todas as respostas anteriores estão correctas (D)). Por exemplo, C) («Deve garantir a evacuação dos ocupantes do veículo para uma zona segura») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -33446,7 +33446,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Os atos do motorista devem basear-se em evitar sempre o confronto. No exame CAM do IMT, esta alternativa responde corretamente à questão «Em caso de tentativa de agressão ou agressão ao motorista».</t>
+          <t>O procedimento adequado é Os atos do motorista devem basear-se em evitar sempre o confronto (C)). Por exemplo, D) («O motorista deve reagir violentamente e se possível imobilizar o agressor») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -33506,7 +33506,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Não desligar a ignição dos veículos acidentados. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um condutor que assista a um acidente no qual existam pessoas ou haja veículos danificados tem o dever de prestar o a...».</t>
+          <t>O procedimento adequado é Não desligar a ignição dos veículos acidentados (D)). Por exemplo, C) («Descrever corretamente qual a situação e responder às perguntas que a cent…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -33566,7 +33566,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Abandonar o local. No exame CAM do IMT, esta alternativa responde corretamente à questão «preparados para dar resposta e prestar primeiros socorros aos que deles necessitam Em caso de acidente com a sua viat...».</t>
+          <t>O procedimento adequado é Abandonar o local (D)). Por exemplo, C) («Efetuar uma rápida avaliação da vítima») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -33626,7 +33626,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Manter o veículo em funcionamento. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando ocorre um incêndio num veículo, o motorista deve adotar certos procedimentos. Das seguintes hipóteses, qual é ...».</t>
+          <t>O procedimento adequado é Manter o veículo em funcionamento (D)). Por exemplo, A) («Ligar os 4 indicadores de mudança de direção») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -33686,7 +33686,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) 8 Dias. No exame CAM do IMT, esta alternativa responde corretamente à questão «A participação da declaração amigável de acidente deve ser entregue ou enviada à seguradora no período de».</t>
+          <t>O procedimento adequado é 8 Dias (C)). Por exemplo, a opção A) indica valores (5 Dias) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -33746,7 +33746,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Não, apenas quando os condutores estiverem de acordo. No exame CAM do IMT, esta alternativa responde corretamente à questão «A participação da declaração amigável de acidente deve ser sempre preenchida».</t>
+          <t>O procedimento adequado é Não, apenas quando os condutores estiverem de acordo (B)). Por exemplo, C) («Não, apenas só quando é chamada a polícia») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -33806,7 +33806,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Avaliar se a vítima está consciente/inconsciente. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para iniciar o socorro das vítimas é necessária a avaliaç ão desta, através do exame primário, o qual consiste em».</t>
+          <t>Trata-se de uma definição: Avaliar se a vítima está consciente/inconsciente (opção A)).  Por exemplo, D) («Avaliar somente a circulação e temperatura») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -33866,7 +33866,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Tentar prever potenciais situações de conflito e identificar potenciais agressores, assim como controlar as emoções e tomar decisões. No exame CAM do IMT, esta alternativa responde corretamente à questão «No contexto do transporte  rodoviário os riscos de agressão e violência aos motoristas e respetivos veículos tem vind...».</t>
+          <t>O procedimento adequado é Tentar prever potenciais situações de conflito e identificar potenciais agressores, assim como controlar as emoções e tomar decisões (D)). Por exemplo, C) («Saber identificar potenciais agressores perante a autoridade») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -33926,7 +33926,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Avaliação em primeiro lugar do estado de consciência da vítima. No exame CAM do IMT, esta alternativa responde corretamente à questão «O exame primário da vítima consiste na».</t>
+          <t>Trata-se de uma definição: Avaliação em primeiro lugar do estado de consciência da vítima (opção D)).  Por exemplo, B) («Verificação em primeiro lugar da existência de ventilação.») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -33986,7 +33986,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Deteção Alerta e Pré-socorro. No exame CAM do IMT, esta alternativa responde corretamente à questão «Perante uma situação de acidente, a sequência adequada na aplicação nas diversas fases do Sistema Integrado de Emergê...».</t>
+          <t>Deteção Alerta e Pré-socorro — é o que melhor responde ao enunciado (opção D)). Relativamente a «Perante uma situação de acidente, a sequência adequada na aplicação nas diversas fases…», a resposta adequada é D): Deteção Alerta e Pré-socorro.</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Utilizar água para lavar os olhos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se um produto tóxico atingir o condutor nos olhos, este deverá imediatamente».</t>
+          <t>O procedimento adequado é Utilizar água para lavar os olhos (B)). Por exemplo, D) («Não é necessário tomar precauções especiais porque um produto tóxico não e…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -34106,7 +34106,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Envolver a vítima com um cobertor ou rolá-la pelo chão. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se numa situação de incêndio a roupa da vítima estiver a arder deve-se».</t>
+          <t>O procedimento adequado é Envolver a vítima com um cobertor ou rolá-la pelo chão (C)). Por exemplo, D) («Chamar de imediato o 112») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -34166,7 +34166,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Custo de reparação ou perda total, e reboque. No exame CAM do IMT, esta alternativa responde corretamente à questão «A “Convenção IDS” (indemnização direta ao segurado), assinada por quase todas as seguradoras que operam em Portugal a...».</t>
+          <t>Custo de reparação ou perda total, e reboque — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Danos em muros e animais») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -34226,7 +34226,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Humana, material e financeira. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes rodoviários com veículos pesados de passageiros têm consequências de ordem».</t>
+          <t>Humana, material e financeira — é o que melhor responde ao enunciado (opção B)). Relativamente a «Os acidentes rodoviários com veículos pesados de passageiros têm consequências de ordem», a resposta adequada é B): Humana, material e financeira.</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -34286,7 +34286,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Dentro das localidades. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes com veículos pesados de passageiros ocorrem, sobretudo».</t>
+          <t>Dentro das localidades — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Na circulação nas faixas BUS») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -34346,7 +34346,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) 50 metros. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes rodoviários envolvendo veículos pesados de passageiros traduzem-se fundamentalmente em colisões, despist...».</t>
+          <t>A questão relaciona-se com condução segura, prevenção de acidentes e comportamento ao volante. No caso «Os acidentes rodoviários envolvendo veículos pesados de passageiros traduzem-se fundamentalmente em…», a opção D) é a alternativa que melhor se aplica ao caso: 50 metros. A opção A) («Corresponder à distância que o veículo percorre durante um lapso de…») apresenta valores diferentes dos exigidos nesta situação A opção B) («40 metros») apresenta valores diferentes dos exigidos nesta situação.</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -34406,7 +34406,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Iniciar encostado ao eixo da via, curvando próximo do mesmo; ao sair da curva manter o veículo mais próximo do eixo da via. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para evitar alguns acidentes, os condutores de veículos pesados de passageiros deverão proceder da seguinte forma par...».</t>
+          <t>O procedimento adequado é Iniciar encostado ao eixo da via, curvando próximo do mesmo; ao sair da curva manter o veículo mais próximo do eixo da via (A)). Por exemplo, D) («Iniciar encostado à direita, curvando progressivamente para o lado esquerd…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -34466,7 +34466,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Maior velocidade de circulação. No exame CAM do IMT, esta alternativa responde corretamente à questão «curva, onde as rodas esquerdas devem estar pró ximas do eixo da via; ao sair da curva deve afastar - se do eixo da vi...».</t>
+          <t>O procedimento adequado é Maior velocidade de circulação (C)). Por exemplo, D) («Maior distracção do condutor provocada pelos passageiros») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Colisões. No exame CAM do IMT, esta alternativa responde corretamente à questão «A maior incidência de mortes envolvendo veículos pesados de passageiros é devida».</t>
+          <t>Colisões — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Queda de pessoas do veículo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -34586,7 +34586,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Os acidentes envolvendo veículos pesados de passageiros têm consequências mais graves para terceiros do que para os utentes. No exame CAM do IMT, esta alternativa responde corretamente à questão «Atendendo aos dados estatísticos da sinistralidade rodoviária, indique qual das afirmações é verdadeira».</t>
+          <t>Os acidentes envolvendo veículos pesados de passageiros têm consequências mais graves para terceiros do que para os utentes — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Os acidentes com índice de gravidade mais elevado ocorrem no período de ma…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -34646,7 +34646,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Que o retrator ajuste automaticamente o comprimento do cinto, e em caso de aceleração brusca o mesmo seja bloqueado. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os cintos de segurança equipados com retrator de bloqueio automático de emergência por inércia permitem».</t>
+          <t>Que o retrator ajuste automaticamente o comprimento do cinto, e em caso de aceleração brusca o mesmo seja bloqueado — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Maior segurança ao utilizador») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -34706,7 +34706,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Sinalizar a eventual s úbita redução de velocidade, procurar uma escapatória possível, parar em segurança, sinalizar o acidente e solicitar auxílio. No exame CAM do IMT, esta alternativa responde corretamente à questão «O condutor de um automóvel pesado que assista a um acidente na via em que circula, deve».</t>
+          <t>O procedimento adequado é Sinalizar a eventual s úbita redução de velocidade, procurar uma escapatória possível, parar em segurança, sinalizar o acidente e solicitar auxílio (A)). Por exemplo, D) («Manter a mesma velocidade e manter o veículo na mesma direcção») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -34766,7 +34766,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Reduzir a velocidade, encostar-se o mais à direita possível e ligar os quatro indicadores de mudança de direção em funcionamento simultâneo. No exame CAM do IMT, esta alternativa responde corretamente à questão «O condutor que ao circular em auto-estrada veja que 200 m à sua frente ocorreu um acidente, deve, como procedimento m...».</t>
+          <t>O procedimento adequado é Reduzir a velocidade, encostar-se o mais à direita possível e ligar os quatro indicadores de mudança de direção em funcionamento simultâneo (A)). Por exemplo, D) («Aumentar a velocidade para sair rapidamente da zona do acidente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -34826,7 +34826,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Aumentar a distância do veículo da frente de forma a, se necessário, conseguir parar em segurança. No exame CAM do IMT, esta alternativa responde corretamente à questão «Sempre que a faixa de rodagem se encontre molhada o condutor deve».</t>
+          <t>O procedimento adequado é Aumentar a distância do veículo da frente de forma a, se necessário, conseguir parar em segurança (D)). Por exemplo, C) («Só travar o veículo com a caixa de velocidades») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -34886,7 +34886,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Certificar-se de que a visibilidade para a condução não é afetada e circular só nestas condições. No exame CAM do IMT, esta alternativa responde corretamente à questão «Sempre que o condutor verifique que o sistema de limpa para - brisas apresente deficiências no seu funcionamento o co...».</t>
+          <t>O procedimento adequado é Certificar-se de que a visibilidade para a condução não é afetada e circular só nestas condições (B)). Por exemplo, D) («Esperar pelo verão para reparar a avaria») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -34946,7 +34946,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Reduzir a velocidade e aumentar a distância de segurança do veículo que circula à sua frente. No exame CAM do IMT, esta alternativa responde corretamente à questão «Sempre que as condições atmosféricas sejam adversas o condutor deve».</t>
+          <t>O procedimento adequado é Reduzir a velocidade e aumentar a distância de segurança do veículo que circula à sua frente (A)). Por exemplo, D) («Verificar se os líquidos do motor estão ao nível») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -35006,7 +35006,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Deve-se a um conjunto de medidas concertadas, associadas à evolução do parque automóvel, à qualidade das vias e, essencialmente, às alterações de atitudes e comportamentos que se têm vindo a verificar nos utentes. No exame CAM do IMT, esta alternativa responde corretamente à questão «A redução da sinistralidade rodoviária em Portugal nos últimos anos».</t>
+          <t>Deve-se a um conjunto de medidas concertadas, associadas à evolução do parque automóvel, à qualidade das vias e, essencialmente, às alterações de atitudes e comportamentos que se têm vindo a verificar nos utentes — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («É insignificante, o número de acidentes manteve-se quase inalterado nas du…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -35066,7 +35066,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) As consequências dos acidentes envolvendo veículos pesados são superiores às consequências dos acidentes que não envolvem este tipo de veículos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando observamos as estatísticas de sinistralidade podemos concluir que».</t>
+          <t>As consequências dos acidentes envolvendo veículos pesados são superiores às consequências dos acidentes que não envolvem este tipo de veículos — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -35126,7 +35126,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Menor volume de tráfego e menor número de acidentes. No exame CAM do IMT, esta alternativa responde corretamente à questão «relativamente às consequências dos acidentes que não envolvem este tipo de veículos Os períodos do dia que apresenta ...».</t>
+          <t>A questão relaciona-se com condução segura, prevenção de acidentes e comportamento ao volante. No caso «relativamente às consequências dos acidentes que não envolvem este tipo de veículos Os períodos do…», a opção D) é a alternativa que melhor se aplica ao caso: Menor volume de tráfego e menor número de acidentes.</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -35186,7 +35186,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Têm consequências mais graves para terceiros do que para os utentes dos veículos pesados. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes que envolvem veículos pesados».</t>
+          <t>Têm consequências mais graves para terceiros do que para os utentes dos veículos pesados — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -35246,7 +35246,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Baixou substancialmente nos últimos anos, sendo a mais baixa quando comparada com a dos restantes veículos. No exame CAM do IMT, esta alternativa responde corretamente à questão «A taxa de implicação de veículos pesados de passageiros em acidentes com vítimas».</t>
+          <t>Baixou substancialmente nos últimos anos, sendo a mais baixa quando comparada com a dos restantes veículos — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -35306,7 +35306,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Sim, de acordo com os resultados apresentados o nú mero de mortos e feridos graves diminuiu consideravelmente.. No exame CAM do IMT, esta alternativa responde corretamente à questão «De acordo com o Observatório de Segurança Rodoviária o nosso país tem vindo a diminuir o número de mortos e feridos g...».</t>
+          <t>Sim, de acordo com os resultados apresentados o nú mero de mortos e feridos graves diminuiu consideravelmente. — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («Não, estes números não param de aumentar e os acidentes com pesados são ca…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -35366,7 +35366,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) A apneia do sono tem efeitos muito graves na condução, porque os  condutores não se apercebem de que estão com a vigilância diminuída e, devido a esse facto, com a atenção, a concentração e os reflexos diminuídos. No exame CAM do IMT, esta alternativa responde corretamente à questão «A apneia do sono é um problema que tem efeitos muito graves na condução».</t>
+          <t>A apneia do sono tem efeitos muito graves na condução, porque os  condutores não se apercebem de que estão com a vigilância diminuída e, devido a esse facto, com a atenção, a concentração e os reflexos diminuídos — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A apneia do sono tal como a sonolência ou a fadiga não interferem na condu…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -35426,7 +35426,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) A apneia do sono tem efeitos muito graves na condução, porque os  condutores não se apercebem de que estão com a vigilância diminuída e, devido a esse facto, com a atenção, a concentração e os reflexos diminuídos. No exame CAM do IMT, esta alternativa responde corretamente à questão «A apneia do sono é um problema que tem efeitos muito graves na condução».</t>
+          <t>A apneia do sono tem efeitos muito graves na condução, porque os  condutores não se apercebem de que estão com a vigilância diminuída e, devido a esse facto, com a atenção, a concentração e os reflexos diminuídos — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A apneia do sono tal como a sonolência ou a fadiga não interferem na condu…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -35486,7 +35486,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Sim, usando o cinto de segurança, o condutor, em caso de acidente, tem mais probabilidades de não sofrer lesões graves. No exame CAM do IMT, esta alternativa responde corretamente à questão «O uso do cinto de segurança, usado pelos condutores dos veículos pesados, diminui o número de condutores mortos. Comente».</t>
+          <t>Sim, usando o cinto de segurança, o condutor, em caso de acidente, tem mais probabilidades de não sofrer lesões graves — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («O condutor de veículos pesados não deve utilizar o cinto de segurança») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -35546,7 +35546,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Sim, os acidentes por despiste nos ligeiros de passageiros foi de bastante superior aos despistes de veículos pesados de passageiros. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes, por despiste, são, segundo o Observatório de Segurança Rodoviário de 2009, em número superior nos ligeiros».</t>
+          <t>Sim, os acidentes por despiste nos ligeiros de passageiros foi de bastante superior aos despistes de veículos pesados de passageiros — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Não os pesados despistam-se mais que os ligeiros») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -35606,7 +35606,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Sim, além dos custos ma teriais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos autocarros estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes rodoviários envolvendo pesados de passageiros têm custos para as próprias empresas».</t>
+          <t>Sim, além dos custos ma teriais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos autocarros estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Sim, pois podem perder o alvará») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -35666,7 +35666,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Sim, além dos custos ma teriais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos autocarros estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes rodoviários envolvendo pesados de passageiros têm custos para as próprias empresas».</t>
+          <t>Sim, além dos custos ma teriais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos autocarros estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Sim, pois podem perder o alvará») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -35726,7 +35726,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Sim, além dos custos materiais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos veículos estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes rodoviários envolvendo pesados de mercadorias têm custos para as próprias empresas».</t>
+          <t>Sim, além dos custos materiais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos veículos estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Sim, pois podem perder o alvará») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -35786,7 +35786,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Sim, além dos custos materiais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos veículos estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes rodoviários envolvendo pesados de mercadorias têm custos para as próprias empresas».</t>
+          <t>Sim, além dos custos materiais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos veículos estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Sim, pois podem perder o alvará») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -35846,7 +35846,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Envolve grande diversidade de riscos, para além dos associados à condução. No exame CAM do IMT, esta alternativa responde corretamente à questão «A profissão de motoristas de veículos pesados de passageiros».</t>
+          <t>Envolve grande diversidade de riscos, para além dos associados à condução — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Certa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Pode considerar-se que o risco químico se encontra associado à profissão de condução. A afirmação está».</t>
+          <t>Certa — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A afirmação está certa apenas se o condutor se socorrer do GPS») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -35966,7 +35966,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Pode ser uma medida correta, desde que não incentive a prática de velocidades mais elevadas e de menores tempos de descanso. No exame CAM do IMT, esta alternativa responde corretamente à questão «A existência nas empresas empregadoras de sistemas de prémios de desempenho que tenham em conta o tempo que o motoris...».</t>
+          <t>Pode ser uma medida correta, desde que não incentive a prática de velocidades mais elevadas e de menores tempos de descanso — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -36026,7 +36026,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) É sempre um fator de risco para o motorista. No exame CAM do IMT, esta alternativa responde corretamente à questão «A existência de deficiências ao nível da manutenção e equipamentos do veículo».</t>
+          <t>É sempre um fator de risco para o motorista — é o que melhor responde ao enunciado (opção A)). Relativamente a «A existência de deficiências ao nível da manutenção e equipamentos do veículo», a resposta adequada é A): É sempre um fator de risco para o motorista.</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -36086,7 +36086,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Traduzem-se num aumento da gravidade em caso de acidente. No exame CAM do IMT, esta alternativa responde corretamente à questão «tráfego As características dos veículos pesados de passageiros relacionadas com o seu peso».</t>
+          <t>Traduzem-se num aumento da gravidade em caso de acidente — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -36146,7 +36146,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Traduzem-se num aumento da gravidade em caso de acidente. No exame CAM do IMT, esta alternativa responde corretamente à questão «completamente lotado As características dos veículos pesados de mercadorias relacionadas com o seu peso».</t>
+          <t>Traduzem-se num aumento da gravidade em caso de acidente — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -36206,7 +36206,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) A afirmação está certa apenas se se referir a condução noturna. No exame CAM do IMT, esta alternativa responde corretamente à questão «As ultrapassagens efetuadas por veículos pesados de passageiros oferecem maior risco relativame nte às realizadas por...».</t>
+          <t>A afirmação está certa apenas se se referir a condução noturna — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («A afirmação está errada») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -36266,7 +36266,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Não é permitido ao motorista ´dar boleias´. No exame CAM do IMT, esta alternativa responde corretamente à questão «Das afirmações abaixo referidas, identifique uma normas de segurança ativa».</t>
+          <t>Não é permitido ao motorista ´dar boleias´ — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O motorista não deve identificar passageiros em caso de conflito declarado») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -36326,7 +36326,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Cobrir todas as consequências dos acidentes de viação (materiais, físicos, psicológicos e sociais). No exame CAM do IMT, esta alternativa responde corretamente à questão «A avaliação efetuada pelas seguradoras e sentenças dos tribunais em caso de acidente de viação, permite».</t>
+          <t>O procedimento adequado é Cobrir todas as consequências dos acidentes de viação (materiais, físicos, psicológicos e sociais) (A)).</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -36386,7 +36386,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Morte de passageiros. No exame CAM do IMT, esta alternativa responde corretamente à questão «São consequências materiais de acidentes de viação».</t>
+          <t>Morte de passageiros — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Danos no veículo acidentado») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -36446,7 +36446,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Colisões. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os acidentes rodoviários com veículos pesados de mercadorias são, principalmente, devidos a».</t>
+          <t>Relativamente a «Os acidentes rodoviários com veículos pesados de mercadorias são, principalmente,…», a resposta adequada é A): Colisões.</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -36506,7 +36506,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Nas ultrapassagens indevidas. No exame CAM do IMT, esta alternativa responde corretamente à questão «A colisão com um veículo em sentido contrário ocorre, de modo geral».</t>
+          <t>Nas ultrapassagens indevidas — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («Pelo respeito pelo traço contínuo no eixo da via») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -36566,7 +36566,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Circula demasiado perto do veículo da frente. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma colisão com o veículo da frente pode ocorrer quando o condutor».</t>
+          <t>Circula demasiado perto do veículo da frente — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Observa o comportamento do condutor à sua frente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -36626,7 +36626,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Desrespeito da regra de cedência de passagem. No exame CAM do IMT, esta alternativa responde corretamente à questão «As colisões num cruzamento ocorrem fundamentalmente por».</t>
+          <t>Desrespeito da regra de cedência de passagem — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Respeitar a sinalização luminosa») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -36686,7 +36686,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Fazer sinal com o indicador de mudança de direção à esquerda. No exame CAM do IMT, esta alternativa responde corretamente à questão «A realização de uma ultrapassagem em segurança, implica».</t>
+          <t>Fazer sinal com o indicador de mudança de direção à esquerda — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Buzinar ao veículo da frente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -36746,7 +36746,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) À velocidade de impacto dos veículos. No exame CAM do IMT, esta alternativa responde corretamente à questão «A gravidade dos acidentes com veículos pesados de mercadorias está associada».</t>
+          <t>À velocidade de impacto dos veículos — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («À construção dos veículos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -36806,7 +36806,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) À velocidade a que o veículo circula. No exame CAM do IMT, esta alternativa responde corretamente à questão «A gravidade dos acidentes com veículos pesados de passageiros está associada».</t>
+          <t>À velocidade a que o veículo circula — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («À construção dos veículos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -36866,7 +36866,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Consequências de acidentes. No exame CAM do IMT, esta alternativa responde corretamente à questão «No contexto de acidentes de viação, quando se fala de mortos, feridos, derrames ou custos, referimo -nos a».</t>
+          <t>Consequências de acidentes — é o que melhor responde ao enunciado (opção C)). Relativamente a «No contexto de acidentes de viação, quando se fala de mortos, feridos, derrames ou…», a resposta adequada é C): Consequências de acidentes.</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -36926,7 +36926,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Suécia. No exame CAM do IMT, esta alternativa responde corretamente à questão «O país que regista menor sinistralidade rodoviária com veículos pesados de mercadorias é a».</t>
+          <t>Relativamente a «O país que regista menor sinistralidade rodoviária com veículos pesados de mercadorias é a», a resposta adequada é C): Suécia.</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -36986,7 +36986,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) No veículo, na via e no homem. No exame CAM do IMT, esta alternativa responde corretamente à questão «As condições ambientais têm impacto».</t>
+          <t>No veículo, na via e no homem — é o que melhor responde ao enunciado (opção D)). Por exemplo, B) («Na via, no homem e na intensidade de tráfego») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -37046,7 +37046,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Sim, sempre. No exame CAM do IMT, esta alternativa responde corretamente à questão «A distribuição do peso na caixa de carga pode influenciar o domínio do veículo em segurança».</t>
+          <t>Sim, sempre — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Não, apenas tem impacto no consumo de combustível») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -37106,7 +37106,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) O uso do corta-vento na janela do condutor e a condução, sempre que possível, com o vidro fechado. No exame CAM do IMT, esta alternativa responde corretamente à questão «Algumas das medidas tendentes a reduzir o aparecim ento de otites e doenças das vias respiratórias nos motoristas são».</t>
+          <t>O uso do corta-vento na janela do condutor e a condução, sempre que possível, com o vidro fechado — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («A condução com as janelas abertas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -37166,7 +37166,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) 10 kg por passageiro. No exame CAM do IMT, esta alternativa responde corretamente à questão «É obrigatório o transporte gratuito da bagagem pessoal do passageiro, em veículos afetos a carreiras interurbanas e a...».</t>
+          <t>10 kg por passageiro — é o que melhor responde ao enunciado (opção A)). Por exemplo, a opção B) indica valores (20 kg por passageiro) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -37226,7 +37226,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Sim, pois uma boa rede de transportes públicos eficiente e pontual, fazia com que as pessoas a utilizassem mais e isto iria contribuir para um decréscimo da poluição atmosférica e diminuição dos engarrafamentos de trânsito. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma boa rede de transportes públicos de passageiros pode evitar as deslocações em viaturas particulares e melhoria da...».</t>
+          <t>Sim, pois uma boa rede de transportes públicos eficiente e pontual, fazia com que as pessoas a utilizassem mais e isto iria contribuir para um decréscimo da poluição atmosférica e diminuição dos engarrafamentos de trânsito — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Não, pois ninguém está interessado em utilizar os transportes públicos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -37286,7 +37286,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Alvará ou licença comunitária válida até 5 anos.</t>
+          <t>Um alvará ou licença comunitária emitidos por um prazo não superior a cinco anos. — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A atividade de transporte rodoviário de passageiros em autocarro não neces…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -37346,7 +37346,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Transportes públicos = por conta de outrem.</t>
+          <t>Transportes públicos ou por conta de outrem — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Transportes interurbanos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -37406,7 +37406,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Os transportes regulares e ocasionais. No exame CAM do IMT, esta alternativa responde corretamente à questão «metropolitana de transportes Constituem categorias do transporte interno».</t>
+          <t>Os transportes regulares e ocasionais — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Os transportes particulares») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -37466,7 +37466,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Sociedades comerciais, cooperativas e empresas públicas ou de capitais públicos que comprovem reunir os requisitos de acesso à actividade. No exame CAM do IMT, esta alternativa responde corretamente à questão «A ativid ade de transporte público rodoviário de passageiros ou por conta de outrem nacional  ou internacional pode s...».</t>
+          <t>Sociedades comerciais, cooperativas e empresas públicas ou de capitais públicos que comprovem reunir os requisitos de acesso à actividade — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Empresários em nome individual») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -37526,7 +37526,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Sociedades anónimas. No exame CAM do IMT, esta alternativa responde corretamente à questão «O capital social está dividido em ações num dos seguintes tipos de sociedades».</t>
+          <t>Sociedades anónimas — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Sociedades em comandita simples») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -37586,7 +37586,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Empresas públicas de transporte rodoviário. No exame CAM do IMT, esta alternativa responde corretamente à questão «As empresas de transportes rodoviários de passgeiros cujo capital social é detido maioritariamente pelo Estado ou por...».</t>
+          <t>Empresas públicas de transporte rodoviário — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Sociedades comerciais») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -37646,7 +37646,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) O “Aluguer ocasional” é um serviço prestado mediante a cedência de um autocarro com um condutor para a realização de uma deslocação de um grupo de passageiros.. No exame CAM do IMT, esta alternativa responde corretamente à questão «Em relação ao transporte rodoviário de passageiros, assinale a afirmação verdadeira».</t>
+          <t>O “Aluguer ocasional” é um serviço prestado mediante a cedência de um autocarro com um condutor para a realização de uma deslocação de um grupo de passageiros. — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Serviços “expresso” são aqueles cuja distância a percorrer são inferiores …») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -37706,7 +37706,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Em carreiras regulares, com origem, destino, pontos de passagem e horários previamente estabelecidos, devidamente autorizados e divulgados junto dos utentes. No exame CAM do IMT, esta alternativa responde corretamente à questão «O serviço público de transporte de passageiros é um serviço prestado».</t>
+          <t>Em carreiras regulares, com origem, destino, pontos de passagem e horários previamente estabelecidos, devidamente autorizados e divulgados junto dos utentes — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («Por carreiras regulares, não necessitando de autorização, nem os utentes t…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -37766,7 +37766,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Mais rápido que o transporte público, com menor número de paragens, normalmente aplicável a médio-longo curso. No exame CAM do IMT, esta alternativa responde corretamente à questão «O serviço “Expresso” é um serviço».</t>
+          <t>Mais rápido que o transporte público, com menor número de paragens, normalmente aplicável a médio-longo curso — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Mais lento que o transporte público, utilizados somente em transporte inte…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -37826,7 +37826,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Estes serviços asseguram o transporte de grupos constituídos por iniciativa de um comitente ou do próprio transportador e estão isentos de qualquer autorização, sendo efetuados ao abri go de folhas de itinerário. No exame CAM do IMT, esta alternativa responde corretamente à questão «Considerando as caraterísticas de transporte dos «serviços ocasionais», indique qual das seguintes afirmações é verda...».</t>
+          <t>Estes serviços asseguram o transporte de grupos constituídos por iniciativa de um comitente ou do próprio transportador e estão isentos de qualquer autorização, sendo efetuados ao abri go de folhas de itinerário — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («As empresas que explorem serv iços internacionais estão autorizadas a efet…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -37886,7 +37886,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Exige condições físicas, psíquicas, humanas específicas ao candidato a motorista. No exame CAM do IMT, esta alternativa responde corretamente à questão «transportes nacionais no território de outro Estado A profissão de motorista de pesados».</t>
+          <t>Exige condições físicas, psíquicas, humanas específicas ao candidato a motorista — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Exige apenas qualidade humanas para o exercício da função») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) A visão global do público dos serviços da empresa. No exame CAM do IMT, esta alternativa responde corretamente à questão «A imagem de uma empresa é».</t>
+          <t>A visão global do público dos serviços da empresa — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Os anúncios e slogans da empresa») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -38006,7 +38006,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Preservar a imagem da viatura como a limpeza e adequação dos equipamentos. No exame CAM do IMT, esta alternativa responde corretamente à questão «O motorista deverá ter como características pessoais».</t>
+          <t>O procedimento adequado é Preservar a imagem da viatura como a limpeza e adequação dos equipamentos (B)). Por exemplo, D) («Conhecer bem os seus colegas motoristas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -38066,7 +38066,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Todas as respostas anteriores estão corretas. No exame CAM do IMT, esta alternativa responde corretamente à questão «As necessidades essenciais do cliente são».</t>
+          <t>Todas as respostas anteriores estão corretas — é o que melhor responde ao enunciado (opção D)). Por exemplo, B) («Sentir-se seguro e esclarecido») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -38126,7 +38126,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Estabilidade emocional e manter uma comunicação assertiva com os interlocutores. No exame CAM do IMT, esta alternativa responde corretamente à questão «O motorista deve ter como sua característica».</t>
+          <t>O procedimento adequado é Estabilidade emocional e manter uma comunicação assertiva com os interlocutores (D)). Por exemplo, C) («Idoneidade e responsabilidade de forma a assegurar o respeito pelas normas…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -38186,7 +38186,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Estabilidade emocional e manter uma comunicação assertiva com os interlocutores. No exame CAM do IMT, esta alternativa responde corretamente à questão «O motorista deve ter como sua característica».</t>
+          <t>O procedimento adequado é Estabilidade emocional e manter uma comunicação assertiva com os interlocutores (D)). Por exemplo, C) («Idoneidade e responsabilidade de forma a assegurar o respeito pelas normas…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Falta de organização gerando pouco trabalho e produtividade assim como aspetos físicos ambientais. No exame CAM do IMT, esta alternativa responde corretamente à questão «para o exercício da função e ético Um dos fatores que prejudica o bom relacionamento interpessoal nas empresas é».</t>
+          <t>Falta de organização gerando pouco trabalho e produtividade assim como aspetos físicos ambientais — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Consciencialização dos objetivos e metas a atingir como profissional da em…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -38306,7 +38306,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) O conjunto de deveres, princípios e normas adoptadas por um determinado grupo profissional. No exame CAM do IMT, esta alternativa responde corretamente à questão «A deontologia profissional é».</t>
+          <t>O conjunto de deveres, princípios e normas adoptadas por um determinado grupo profissional — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Um conjunto de fatores que prejudicam o desempenho profissional do motoris…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -38366,7 +38366,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Ser independente no trabalho com os colegas/ colaboradores. No exame CAM do IMT, esta alternativa responde corretamente à questão «No trabalho em equipa, o profissional não deve».</t>
+          <t>O procedimento adequado é Ser independente no trabalho com os colegas/ colaboradores (B)). Por exemplo, D) («Mostrar uma atitude de empatia, disponibilidade e ter capacidade de delegar») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -38426,7 +38426,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Emissor, mensagem, canal e recetor. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os elementos do processo de comunicação são».</t>
+          <t>Emissor, mensagem, canal e recetor — é o que melhor responde ao enunciado (opção D)). Relativamente a «Os elementos do processo de comunicação são», a resposta adequada é D): Emissor, mensagem, canal e recetor.</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -38486,7 +38486,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Assertivo, agressivo, manipulador e passivo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Podemos identificar quatro estilos de comunicação no relacionamento interpessoal».</t>
+          <t>Assertivo, agressivo, manipulador e passivo — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Nenhumas das anteriores está correta») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -38546,7 +38546,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Há uma atitude de auto-afirmação. No exame CAM do IMT, esta alternativa responde corretamente à questão «Na comunicação assertiva».</t>
+          <t>Há uma atitude de auto-afirmação — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A assertividade implica considerar os interesses apenas de uma das partes») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -38606,7 +38606,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Verdadeiro. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um dos problemas inerentes ao processo de comunicação reside no facto de o recetor atribuir à mensagem um significado...».</t>
+          <t>Verdadeiro — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Só será um problema ao nível da comunicação não verbal») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -38666,7 +38666,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) O olhar para o chão. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um dos erros mais comuns quando falamos é».</t>
+          <t>O olhar para o chão — é o que melhor responde ao enunciado (opção B)). Por exemplo, A) («A postura física correta») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -38726,7 +38726,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Todas as outras respostas estão corretas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Ao prestar um serviço, deve».</t>
+          <t>O procedimento adequado é Todas as outras respostas estão corretas (D)). Por exemplo, B) («Ser delicado, amável e despedir-se cordialmente do cliente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -38786,7 +38786,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Todas as outras respostas estão corretas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Perante uma reclamação do cliente devo».</t>
+          <t>Perante uma reclamação, o profissional deve ouvir, validar o sentimento do cliente, explicar a solução e agradecer o feedback. Como A), B) e C) são atitudes corretas isoladamente, a resposta D) resume que todas estão corretas.</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -38846,7 +38846,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Todas as outras respostas estão corretas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Perante uma reclamação do cliente devo».</t>
+          <t>Perante uma reclamação, o profissional deve ouvir, validar o sentimento do cliente, explicar a solução e agradecer o feedback. Como A), B) e C) são atitudes corretas isoladamente, a resposta D) resume que todas estão corretas.</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -38906,7 +38906,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) O nosso comportamento vai influenciar o comportamento daqueles que interagem connosco. No exame CAM do IMT, esta alternativa responde corretamente à questão «Numa correta conduta».</t>
+          <t>O nosso comportamento vai influenciar o comportamento daqueles que interagem connosco — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Deve-se interromper o emissor quando este expõe as suas ideias») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -38966,7 +38966,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Ter o cliente como a razão de ser do seu desempenho. No exame CAM do IMT, esta alternativa responde corretamente à questão «Desenvolver uma postura comercial junto do cliente significa».</t>
+          <t>Ter o cliente como a razão de ser do seu desempenho — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Evitar revelar os aspetos menos positivos do serviço face ao cliente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -39026,7 +39026,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Ajuda os clientes com dificuldade de mobilização (grávidas, idosos). No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma das maneiras de aferir a competência relacional do motorista é verificar se o mesmo».</t>
+          <t>Ajuda os clientes com dificuldade de mobilização (grávidas, idosos) — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Facilita as saídas dos clientes em locais não autorizados ou altera o loca…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -39086,7 +39086,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Uma oportunidade para poder melhorar o serviço e o desempenho. No exame CAM do IMT, esta alternativa responde corretamente à questão «As reclamações dos clientes devem ser entendidas como».</t>
+          <t>O procedimento adequado é Uma oportunidade para poder melhorar o serviço e o desempenho (C)). Por exemplo, D) («Situações que não devem ser muito valorizadas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -39146,7 +39146,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Ter a capacidade de escutar o cliente dando informações corretas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Perante a manifestação de insatisfação do cliente, é mais eficaz».</t>
+          <t>Ter a capacidade de escutar o cliente dando informações corretas — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Ficar em silêncio para não correr o risco de aborrecer o cliente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -39206,7 +39206,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Facilitar a comunicação e cordialidade. No exame CAM do IMT, esta alternativa responde corretamente à questão «Comunicar de forma assertiva é».</t>
+          <t>Facilitar a comunicação e cordialidade — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Estar centrado somente nos seus sentimentos e necessidades») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -39266,7 +39266,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Aproveitar a situação para trocar impressões com o colega. No exame CAM do IMT, esta alternativa responde corretamente à questão «No acto de rendição o motorista deve».</t>
+          <t>O procedimento adequado é Aproveitar a situação para trocar impressões com o colega (A)). Por exemplo, D) («Abandonar o veículo, antes da chegada do colega») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -39326,7 +39326,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) É um dever do motorista. No exame CAM do IMT, esta alternativa responde corretamente à questão «A manutenção do veículo por parte do motorista».</t>
+          <t>É um dever do motorista — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Faz perder tempo, porque os clientes só valorizam a rapidez do transporte») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -39386,7 +39386,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Procurar perceber o que está realmente em causa, sem personalizar ou julgar. No exame CAM do IMT, esta alternativa responde corretamente à questão «A melhor forma de gerir um conflito entre colegas é».</t>
+          <t>Procurar perceber o que está realmente em causa, sem personalizar ou julgar — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Confrontar e fazer valer o ponto de vista quando se tem razão») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -39446,7 +39446,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Sentir-se bloqueado e paralisado quando é apresentado um problema para resolver. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um tipo de comportamento passivo é».</t>
+          <t>Sentir-se bloqueado e paralisado quando é apresentado um problema para resolver — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Impor as suas decisões aos outros») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -39506,7 +39506,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Os motoristas devem estar conscientes da importância do cargo que ocupam e o significado que seu trabalho tem para a organização. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os serviços de uma organização alcançam vantagens competitivas quando a qualid ade é definida como uma questão estrat...».</t>
+          <t>Os motoristas devem estar conscientes da importância do cargo que ocupam e o significado que seu trabalho tem para a organização — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Os transportes devem ser efectuados o mais célere possível, mesmo não resp…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -39566,7 +39566,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Formar um grupo coeso, eficiente e motivado. No exame CAM do IMT, esta alternativa responde corretamente à questão «tempos e condução aplicáveis A boa comunicação é importante entre os membros dentro de uma organização para».</t>
+          <t>Formar um grupo coeso, eficiente e motivado — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Que o nosso comportamento possa depender do nosso estado de espírito») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -39626,7 +39626,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Dar a confiança e satisfação aos clientes. No exame CAM do IMT, esta alternativa responde corretamente à questão «A qualidade do serviço serve para».</t>
+          <t>Dar a confiança e satisfação aos clientes — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Reduzir a satisfação do cliente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -39686,7 +39686,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Técnicas, de relacionamento e organizacionais. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os três tipos de competências do motorista são».</t>
+          <t>Técnicas, de relacionamento e organizacionais — é o que melhor responde ao enunciado (opção A)). Relativamente a «Os três tipos de competências do motorista são», a resposta adequada é A): Técnicas, de relacionamento e organizacionais.</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -39746,7 +39746,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Aumento da fadiga. No exame CAM do IMT, esta alternativa responde corretamente à questão «Qual a principal dificuldade da condução noturna é».</t>
+          <t>Aumento da fadiga — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Diminuição do tempo de reação») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -39806,7 +39806,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) A qualidade de serviço implica obrigatoriamente aumentar os custos da empresa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Não está correto afirmar que».</t>
+          <t>A qualidade de serviço implica obrigatoriamente aumentar os custos da empresa — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A qualidade de serviço é uma forma da empresa de transportes se diferencia…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -39866,7 +39866,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Organizacional. No exame CAM do IMT, esta alternativa responde corretamente à questão «A capacidade de integração na estrutura de uma empresa é uma competência do tipo».</t>
+          <t>Organizacional — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Nenhuma das referidas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -39926,7 +39926,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Tangibilidade, fiabilidade, confiança, pró atividade, e empatia. No exame CAM do IMT, esta alternativa responde corretamente à questão «As características de um serviço de qualidade são».</t>
+          <t>Tangibilidade, fiabilidade, confiança, pró atividade, e empatia — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -39986,7 +39986,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) O motorista. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para os clientes de uma firma de transportes, a face visível da empresa é».</t>
+          <t>Relativamente a «Para os clientes de uma firma de transportes, a face visível da empresa é», a resposta adequada é B): O motorista.</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -40046,7 +40046,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Estão insatisfeitos com a qualidade do atendimento. No exame CAM do IMT, esta alternativa responde corretamente à questão «Estudos indicam que, na maior parte dos casos, os clientes abandonam uma empresa ou serviço, porque».</t>
+          <t>Estão insatisfeitos com a qualidade do atendimento — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Desejam experimentar novos produtos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -40106,7 +40106,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Afastando-se do cliente, deixando-o a falar sozinho. No exame CAM do IMT, esta alternativa responde corretamente à questão «serviço Um dos seguintes comportamentos deve ser evitado, pois prejudica a comunicação com o cliente. Indique qual».</t>
+          <t>O procedimento adequado é Afastando-se do cliente, deixando-o a falar sozinho (C)). Por exemplo, D) («Informar o cliente sobre o funcionamento do serviço, para que ele compreen…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -40166,7 +40166,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Processos de tratamento, controlo e comunicação de informação. No exame CAM do IMT, esta alternativa responde corretamente à questão «fazemos As Tecnologias de Informação e Comunicação dizem respeito a».</t>
+          <t>Processos de tratamento, controlo e comunicação de informação — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Processos de transferência de dados entre equipamentos electrónicos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -40226,7 +40226,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Os clientes que reclamam só causam problemas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma reclamação pode ser vista como uma oportunidade”. Uma das frases seguintes é falsa. Indique qual».</t>
+          <t>Os clientes que reclamam só causam problemas — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Ele irá contar a sua satisfação aos seus conhecidos, ajudando-nos a alarga…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -40286,7 +40286,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Os clientes que reclamam só causam problemas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma reclamação pode ser vista como uma oportunidade”. Uma das frases seguintes é falsa. Indique qual».</t>
+          <t>Os clientes que reclamam só causam problemas — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Ele irá contar a sua satisfação aos seus conhecidos, ajudando-nos a alarga…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -40346,7 +40346,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Um conjunto de veículos pertencentes a uma mesma empresa. No exame CAM do IMT, esta alternativa responde corretamente à questão «Gestão de frota significa administrar ou gerir».</t>
+          <t>Um conjunto de veículos pertencentes a uma mesma empresa — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -40406,7 +40406,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Poupar tempo, dinheiro e aumentar a satisfação dos clientes. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema de bilhética permite aos operadores de transporte público».</t>
+          <t>Poupar tempo, dinheiro e aumentar a satisfação dos clientes — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Utilizar circuitos turísticos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -40466,7 +40466,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Telemóveis. No exame CAM do IMT, esta alternativa responde corretamente à questão «A utilização do Sistema SOS reduziu significativamente, após o aparecimento de».</t>
+          <t>Relativamente a «A utilização do Sistema SOS reduziu significativamente, após o aparecimento de», a resposta adequada é A): Telemóveis.</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -40526,7 +40526,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Móveis. No exame CAM do IMT, esta alternativa responde corretamente à questão «GSM é o Sistema Global para Comunicações».</t>
+          <t>Relativamente a «GSM é o Sistema Global para Comunicações», a resposta adequada é B): Móveis.</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -40586,7 +40586,7 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Posicionamento Global. No exame CAM do IMT, esta alternativa responde corretamente à questão «O GPS é um Sistema de».</t>
+          <t>Posicionamento Global — é o que melhor responde ao enunciado (opção C)). Relativamente a «O GPS é um Sistema de», a resposta adequada é C): Posicionamento Global.</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -40646,7 +40646,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) O tempo estimado para a chegada do próximo veículo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os painéis de informação destinam-se a apresentar, em cada instante, informação sobre».</t>
+          <t>O tempo estimado para a chegada do próximo veículo — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («O tempo médio de passagem entre veículos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -40706,7 +40706,7 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Bilhética Electrónica e SMS. No exame CAM do IMT, esta alternativa responde corretamente à questão «O SAE permite a interligação entre outros sistemas, como».</t>
+          <t>Bilhética Electrónica e SMS — é o que melhor responde ao enunciado (opção A)). Por exemplo, B) («SMS e Rede Multibanco») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -40766,7 +40766,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Altitude, longitude e latitude. No exame CAM do IMT, esta alternativa responde corretamente à questão «O principio de funcionamento do GPS baseia-se em ».</t>
+          <t>Altitude, longitude e latitude — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Altura, largura e longitude») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -40826,7 +40826,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) A coleção de documentos electrónicos interligados por uma infindável  rede ou teia (Web) de aranha, armazenados em computadores designados por servidores Web espalhados por todo o mundo. No exame CAM do IMT, esta alternativa responde corretamente à questão «A World Wide Web (WWW) é».</t>
+          <t>A coleção de documentos electrónicos interligados por uma infindável  rede ou teia (Web) de aranha, armazenados em computadores designados por servidores Web espalhados por todo o mundo — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Um sistema de partilha de documentos que funciona i ndependentemente da ut…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -40886,7 +40886,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Permite aos motoristas estar em contacto com a empresa, colegas, clientes e outros contactos, tais como serviços de manutenção e reparação e centros de controlo de tráfego. No exame CAM do IMT, esta alternativa responde corretamente à questão «A evolução da s tecnologias de informação e comunicação tem tido influência nos transportes de pesados de passageiros...».</t>
+          <t>Permite aos motoristas estar em contacto com a empresa, colegas, clientes e outros contactos, tais como serviços de manutenção e reparação e centros de controlo de tráfego — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Obriga o condutor a obter certificados e autorizações adicionais para o ex…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -40946,7 +40946,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) O processamento de informação, mapas, bases de dados, comunicações e dados em tempo real recolhidos a partir de uma variedade de sensores. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os sistemas inteligentes de transportes (ITS) permitem».</t>
+          <t>O processamento de informação, mapas, bases de dados, comunicações e dados em tempo real recolhidos a partir de uma variedade de sensores — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Aumentar o conforto dos passageiros, apesar do tempo de viagem aumentar») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -41006,7 +41006,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Proporcionam o acesso a informação em tempo real relativa à viagem e ao tráfego. No exame CAM do IMT, esta alternativa responde corretamente à questão «As tecnologias de informação e comunicação contribuem para a segurança rodoviária porque».</t>
+          <t>Proporcionam o acesso a informação em tempo real relativa à viagem e ao tráfego — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Aumentam a segurança na condução, o que permite o aumento da velocidade má…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -41066,7 +41066,7 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Permite fiscalizar os passageiros no veículo. No exame CAM do IMT, esta alternativa responde corretamente à questão «A bilhética sem contacto (indique a afirmação verdadeira)».</t>
+          <t>A bilhética sem contacto permite validar títulos de transporte sem contacto físico prolongado, facilitando a fiscalização em bordo. A afirmação verdadeira é A): Permite fiscalizar os passageiros no veículo.</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -41126,7 +41126,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Os custos de manutenção do sistema são mais altos comparativamente com outros sistemas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Relativamente à bilhética sem contacto, indique qual das seguintes afirmações é falsa».</t>
+          <t>A bilhética sem contacto permite validar títulos de transporte sem contacto físico prolongado, facilitando a fiscalização em bordo. A afirmação verdadeira é C): Os custos de manutenção do sistema são mais altos comparativamente com outros sistemas.</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -41186,7 +41186,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Ter permanentemente a bordo informação sobre o estado da via e condições do tráfego. No exame CAM do IMT, esta alternativa responde corretamente à questão «As tecnologias de informação permitem ao condutor».</t>
+          <t>Ter permanentemente a bordo informação sobre o estado da via e condições do tráfego — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Apenas evitar a possibilidade de engano no trajecto») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -41246,7 +41246,7 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) O condutor possa agir de forma a evitar o acidente. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema de alerta à eminência de colisão permite que».</t>
+          <t>O condutor possa agir de forma a evitar o acidente — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O condutor tenha uma assistência mais rápida em caso de colisão») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
@@ -41306,7 +41306,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Durante um determinado percurso sem que seja necessário pressionar o acelerador do veículo. No exame CAM do IMT, esta alternativa responde corretamente à questão «O regulador de velocidade é um sistema que permite manter uma velocidade constante».</t>
+          <t>Durante um determinado percurso sem que seja necessário pressionar o acelerador do veículo — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Durante 4 h consecutivas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -41366,7 +41366,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Reduzir largamente o congestionamento nessas áreas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os sistemas de pagamento eletrónico de portagens têm como principal vantagem».</t>
+          <t>Reduzir largamente o congestionamento nessas áreas — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Redução do preço da portagem») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -41426,7 +41426,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Reduzir o volume de tráfego e, consequentemente, o correspondente impacto ambiental. No exame CAM do IMT, esta alternativa responde corretamente à questão «A criação de uma taxa de circulação em áreas urbanas congestionadas tem vindo a ser implementada em várias cidades eu...».</t>
+          <t>Reduzir o volume de tráfego e, consequentemente, o correspondente impacto ambiental — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Arrecadar mais receitas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -41486,7 +41486,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Veículos (através da respectiva matrícula). No exame CAM do IMT, esta alternativa responde corretamente à questão «Os sistemas de controlo automático do comportamento em estrada visam a identificação de».</t>
+          <t>Veículos (através da respectiva matrícula) — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Locais regulados por sinalização luminosa») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -41546,7 +41546,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) A promoção da segurança. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma das vantagens da utilização dos sistemas inteligentes de transporte é».</t>
+          <t>A promoção da segurança — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O controlo por parte do condutor dos cruzamentos regulados por sinalização…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -41606,7 +41606,7 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) A emissão de informações aos condutores, permitindo -lhes uma melhor gestão da viagem em função das ocorrências assinaladas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os painéis de mensagens variáveis são painéis eletrónicos que permitem».</t>
+          <t>A emissão de informações aos condutores, permitindo -lhes uma melhor gestão da viagem em função das ocorrências assinaladas — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Apenas informação aos condutores de locais com obras») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -41666,7 +41666,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Evitar o acidente. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema de aviso de aproximação de obstáculos em manobras de marcha-atrás visa».</t>
+          <t>Evitar o acidente — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Dar indicação ao condutor que o caixa de velocidades do veículo se encontr…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -41726,7 +41726,7 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Constitui um útil auxiliar de navegação para o condutor. No exame CAM do IMT, esta alternativa responde corretamente à questão «A correcta utilização do GPS numa viagem pela Europa».</t>
+          <t>Constitui um útil auxiliar de navegação para o condutor — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Permite a melhor manutenção da bagagem dos passageiros») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
@@ -41786,7 +41786,7 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Velocidade média, localização de áreas de serviço e de locais de interesse turístico, bem como o valor da correspondente altitude. No exame CAM do IMT, esta alternativa responde corretamente à questão «O GPS permite que o condutor obtenha, entre outras, as seguintes informações».</t>
+          <t>Velocidade média, localização de áreas de serviço e de locais de interesse turístico, bem como o valor da correspondente altitude — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Apenas a velocidade média») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -41846,7 +41846,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Um recetor GPS. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para um utente receber sinal através dum sistema de navegação GPS, é necessário que possua».</t>
+          <t>Um recetor GPS — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Um aparelho elétrico qualquer») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -41906,7 +41906,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Sintetizadores de voz que permitem a indicação do caminho ou rumo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Sempre que durante a condução se utiliza o GPS, é mais seguro recorrer à função que permite a utilização de».</t>
+          <t>Sintetizadores de voz que permitem a indicação do caminho ou rumo — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («A utilização do GPS é sempre totalmente segura») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -41966,7 +41966,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Deter dados estatísticos mais fiáveis sobre a evolução das necessidades de mobilidade dos cidadãos. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema da bilhética sem contacto permite à entidade transportadora».</t>
+          <t>A bilhética sem contacto permite validar títulos de transporte sem contacto físico prolongado, facilitando a fiscalização em bordo. A afirmação verdadeira é A): Deter dados estatísticos mais fiáveis sobre a evolução das necessidades de mobilidade dos cidadãos.</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -42026,7 +42026,7 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Inteligentes, seguros e com a possibilidade de garantirem serviços transversais. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os Smart Cards são».</t>
+          <t>Inteligentes, seguros e com a possibilidade de garantirem serviços transversais — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Um sistema de utilização mais complicada que o passe normal») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
@@ -42086,7 +42086,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) O conjunto de quaisquer registos quantificáveis relativos a um fenómeno ou acontecimento. No exame CAM do IMT, esta alternativa responde corretamente à questão «O conceito de “dados” representa».</t>
+          <t>O conjunto de quaisquer registos quantificáveis relativos a um fenómeno ou acontecimento — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Qualquer sistema automatizado») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -42146,7 +42146,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) A aplicação das tecnologias de informação e comunicação aos transportes. No exame CAM do IMT, esta alternativa responde corretamente à questão «Sistemas  Inteligentes de Transportes são».</t>
+          <t>A aplicação das tecnologias de informação e comunicação aos transportes — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («A aplicação do tacógrafo digital à infra-estrutura de transporte de veícul…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -42206,7 +42206,7 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Não, cada vez há mais sistemas de informática embarcada, fáceis de utilizar e amigos do ambiente. No exame CAM do IMT, esta alternativa responde corretamente à questão «A gestão da frota só é possível com recurso a complicados sistemas informáticos».</t>
+          <t>Não, cada vez há mais sistemas de informática embarcada, fáceis de utilizar e amigos do ambiente — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Não, mesmo grandes frotas conseguem ser adequadamente geridas sem exigir e…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
@@ -42266,7 +42266,7 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Internet. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma rede de computadores, pública, global, de uso múltiplo é denominada».</t>
+          <t>Internet — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Electronic Data Interchange (EDI)») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
@@ -42326,7 +42326,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Aumentar a produtividade e a competitividade. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um sistema de informação para fins operacionais e fins de gestão pode».</t>
+          <t>Aumentar a produtividade e a competitividade — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Não influencia a eficiência da empresa») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -42386,7 +42386,7 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Registar os tempos de condução e de repouso. No exame CAM do IMT, esta alternativa responde corretamente à questão «O tacógrafo digital tem a função de».</t>
+          <t>Registar os tempos de condução e de repouso — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Controlar a distância entre veículos») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -42446,7 +42446,7 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Este equipamento requer a inserção de u m cartão inteligente (com um chip incorporado), que tem carácter pessoal, contém a identificação do condutor e permite a memorização dos dados relativos às suas actividades. No exame CAM do IMT, esta alternativa responde corretamente à questão «Relativamente ao tacógrafo digital, indique qual é a afirmação verdadeira».</t>
+          <t>Este equipamento requer a inserção de u m cartão inteligente (com um chip incorporado), que tem carácter pessoal, contém a identificação do condutor e permite a memorização dos dados relativos às suas actividades — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («O tacógrafo permite limitar a velocidade máxima do veículo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
@@ -42506,7 +42506,7 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Cada condutor poderá ser titular de um ou mais cartões. No exame CAM do IMT, esta alternativa responde corretamente à questão «Relativamente ao tacógrafo digital, indique qual é a afirmação verdadeira».</t>
+          <t>Cada condutor poderá ser titular de um ou mais cartões — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («O tacógrafo permite limitar a velocidade máxima do veículo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -42566,7 +42566,7 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Sistemas inteligentes de transportes. No exame CAM do IMT, esta alternativa responde corretamente à questão «As siglas ITS significam».</t>
+          <t>Sistemas inteligentes de transportes — é o que melhor responde ao enunciado (opção A)). Relativamente a «As siglas ITS significam», a resposta adequada é A): Sistemas inteligentes de transportes.</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -42626,7 +42626,7 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Falsa, uma vez que o dispositivo que permite manter a velocidade constante é o regulador activo de velocidade. No exame CAM do IMT, esta alternativa responde corretamente à questão «O limitador de velocidade permite manter uma velocidade constante sem que seja necessário pressionar o acelerador do ...».</t>
+          <t>Falsa, uma vez que o dispositivo que permite manter a velocidade constante é o regulador activo de velocidade — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -42686,7 +42686,7 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) GPS/Telemap. No exame CAM do IMT, esta alternativa responde corretamente à questão «As aplicações operacionais são sistemas de informação dedicados às necessidades específicas das empresas. São daquela...».</t>
+          <t>A questão relaciona-se com condução segura, prevenção de acidentes e comportamento ao volante. No caso «As aplicações operacionais são sistemas de informação dedicados às necessidades específicas das…», a opção A) é a alternativa que melhor se aplica ao caso: GPS/Telemap.</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
@@ -42746,7 +42746,7 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) A obtenção de informação em tempo real sobre a localização dos produtos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma das vantagens do RFID na área da logística é».</t>
+          <t>A obtenção de informação em tempo real sobre a localização dos produtos — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A prevenção dos acidentes») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -42806,7 +42806,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Sistema de comunicação “wireless” (sem fios). No exame CAM do IMT, esta alternativa responde corretamente à questão «O RFID (Radio Frequency Identification) é um».</t>
+          <t>Sistema de comunicação “wireless” (sem fios) — é o que melhor responde ao enunciado (opção B)). Relativamente a «O RFID (Radio Frequency Identification) é um», a resposta adequada é B): Sistema de comunicação “wireless” (sem fios).</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -42866,7 +42866,7 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Europeu de radionavegação e de posicionamento por satélite. No exame CAM do IMT, esta alternativa responde corretamente à questão «O “Programa GALILEO” é um programa».</t>
+          <t>Europeu de radionavegação e de posicionamento por satélite — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Norte americano de radionavegação, composto por 24 satélites.») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -42926,7 +42926,7 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) 80%. No exame CAM do IMT, esta alternativa responde corretamente à questão «Nos transportes nacionais por rodoviária a percentagem das cargas que viaja apenas até 100 km é».</t>
+          <t>80% — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (60%) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -42986,7 +42986,7 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Sim, mas nem sempre foi assim. No exame CAM do IMT, esta alternativa responde corretamente à questão «O modo rodoviário é o maior elo de ligação do nosso país ao espaço europeu».</t>
+          <t>Sim, mas nem sempre foi assim — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Não, o maior elo é o caminho-de-ferro») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -43046,7 +43046,7 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) O centro da gravidade da carga (total de passageiros e bagagem) e superfície da caixa de carga coincidirem. No exame CAM do IMT, esta alternativa responde corretamente à questão «O equilíbrio de um veículo pesado de passageiros esta relacionado com o respetivo centro de gravidade. A estabilidade...».</t>
+          <t>O centro da gravidade da carga (total de passageiros e bagagem) e superfície da caixa de carga coincidirem — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («O motorista conseguir determinar o centro de gravidade de todos os passage…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -43106,7 +43106,7 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Encontrar-se em boas condições físicas como psíquicas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para a prática de uma condução correta, cómoda e segura, o motorista de um pesado de passageiro deve».</t>
+          <t>Encontrar-se em boas condições físicas como psíquicas — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Ser frequentemente submetido apenas a avaliações psicológicas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -43166,7 +43166,7 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Submeter-se a prévio controlo médico e a acompanhamento adequado para monitoriz ação de eventuais efeitos negativos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Perante a necessidade de um profissional da condução recorrer a medicamentos que possam atuar sobre o sistema nervoso...».</t>
+          <t>O procedimento adequado é Submeter-se a prévio controlo médico e a acompanhamento adequado para monitoriz ação de eventuais efeitos negativos (A)). Por exemplo, D) («Não tomar qualquer atitude») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -43226,7 +43226,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>Capacidade de resposta = rapidez e precisão.</t>
+          <t>Trata-se de uma definição: Capacidade de resposta (opção D)).  Por exemplo, B) («Condicionantes da condução») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -43286,7 +43286,7 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) ABS. No exame CAM do IMT, esta alternativa responde corretamente à questão «O sistema antibloqueio das rodas de uma viatura é conhecido através das siglas».</t>
+          <t>Relativamente a «O sistema antibloqueio das rodas de uma viatura é conhecido através das siglas», a resposta adequada é C): ABS.</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -43346,7 +43346,7 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Em condições normais, o gasto de combustível não depende do tipo de caixa de velocidades mas do tipo de condução. No exame CAM do IMT, esta alternativa responde corretamente à questão «É gasto mais combustível com uma caixa de velocidades do tipo».</t>
+          <t>Em condições normais, o gasto de combustível não depende do tipo de caixa de velocidades mas do tipo de condução — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Sempre com caixa de velocidades automática nas subidas e descidas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -43406,7 +43406,7 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) As três hipóteses estão corretas, dependendo da situação concreta. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para otimizar o gasto de combustível, o motorista deve».</t>
+          <t>O procedimento adequado é As três hipóteses estão corretas, dependendo da situação concreta (D)). Por exemplo, C) («Usar devidamente o motor da viatura») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -43466,7 +43466,7 @@
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Nas descidas, utilizar o ponto morto. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para racionalizar o consumo de combustível, o motorista não deve».</t>
+          <t>O procedimento adequado é Nas descidas, utilizar o ponto morto (B)). Por exemplo, D) («Nas descidas e subidas mudar a velocidade sempre que necessário») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -43526,7 +43526,7 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Guiar com os vidros abertos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Indique qual o fator indicativo de má prática em termos de condução económica».</t>
+          <t>Guiar com os vidros abertos — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Guiar com antecipação») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -43586,7 +43586,7 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Os atrasos e maior consumo de energia. No exame CAM do IMT, esta alternativa responde corretamente à questão «O principais custos dos congestionamentos de trânsito, são».</t>
+          <t>Os atrasos e maior consumo de energia — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («A maior exposição ao frio ou ao calor») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -43646,7 +43646,7 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) É todo o transporte que se realiza entre locais de um mesmo país estrangeiro. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para um veículo de matrícula portuguesa, cabotagem é».</t>
+          <t>É todo o transporte que se realiza entre locais de um mesmo país estrangeiro — é o que melhor responde ao enunciado (opção B)). Por exemplo, A) («É todo o transporte em que o ponto de origem ou o ponto de destino se situ…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
@@ -43706,7 +43706,7 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Que se realiza entre locais de países diferentes, distintos de Portugal. No exame CAM do IMT, esta alternativa responde corretamente à questão «Para um veículo de matrícula portuguesa o transporte de cross-trade é o transporte».</t>
+          <t>Que se realiza entre locais de países diferentes, distintos de Portugal — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Entre portos de um mesmo país») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -43766,7 +43766,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Serve a empresa proprietária do veículo no exercício das suas atividades. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um veículo que efetua transporte por conta própria».</t>
+          <t>Serve a empresa proprietária do veículo no exercício das suas atividades — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Realiza serviços a qualquer hora») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -43826,7 +43826,7 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Mais de 95% das toneladas movimentadas e a ferrovia menos de 5%. No exame CAM do IMT, esta alternativa responde corretamente à questão «Analisando a produção dos vários modos de transporte de mercadorias observamos que, nos tráfegos nacionais os transpo...».</t>
+          <t>Mais de 95% das toneladas movimentadas e a ferrovia menos de 5% — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção C) indica valores (Cerca de 80% das toneladas movimentadas e os caminhos-de-ferro cerca de 20%) diferentes do aplicável.</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -43886,7 +43886,7 @@
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) A massa de carga máxima que pode ser carregada no veículo, ao longo da plataforma. No exame CAM do IMT, esta alternativa responde corretamente à questão «A elaboração de um plano de distribuição da carga serve para determinar».</t>
+          <t>A massa de carga máxima que pode ser carregada no veículo, ao longo da plataforma — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («As forças de aceleração exercidas pela carga») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -43946,7 +43946,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Reduzir o consumo de combustível, as emissões poluentes e aumentar a segurança rodoviária. No exame CAM do IMT, esta alternativa responde corretamente à questão «e fixas a dois pontos de amarração do veículo (opostos) A condução económica possibilita».</t>
+          <t>Reduzir o consumo de combustível, as emissões poluentes e aumentar a segurança rodoviária — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Aumentar o consumo de óleo e a um menor conforto na condução») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -44006,7 +44006,7 @@
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Maior for a velocidade a que se circula assim como no caso de má visibilidade ou piso escorregadio. No exame CAM do IMT, esta alternativa responde corretamente à questão «A distância de segurança em relação ao veículo da frente deve ser maior quando».</t>
+          <t>O procedimento adequado é Maior for a velocidade a que se circula assim como no caso de má visibilidade ou piso escorregadio (B)). Por exemplo, D) («O veículo da frente é um veículo pesado») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
@@ -44066,7 +44066,7 @@
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Poliéster, poliamida ou polipropileno. No exame CAM do IMT, esta alternativa responde corretamente à questão «As cintas de amarração são normalmente feitas de».</t>
+          <t>Poliéster, poliamida ou polipropileno — é o que melhor responde ao enunciado (opção C)). Relativamente a «As cintas de amarração são normalmente feitas de», a resposta adequada é C): Poliéster, poliamida ou polipropileno.</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
@@ -44126,7 +44126,7 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Numa forma de amarração da carga com ligação a um dos lados da carroçaria do veículo, a fim de evitar o deslizamento e a inclinação da carga para o lado oposto. No exame CAM do IMT, esta alternativa responde corretamente à questão «A amarração em laço consiste».</t>
+          <t>amarração em laço liga a carga a um dos lados da carroçaria (manual IMT Acondicionamento de Carga, sec. 3.2.2).</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
@@ -44186,7 +44186,7 @@
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) A carga máxima admissível, determinada pelo peso ou cubicagem máxima admitida. No exame CAM do IMT, esta alternativa responde corretamente à questão «No planeamento do enchimento da caixa de carga do veículo é imperativo considerar-se».</t>
+          <t>A carga máxima admissível, determinada pelo peso ou cubicagem máxima admitida — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O espaço entre os lotes da mercadoria a fim de garantir o equilíbrio do ve…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
@@ -44246,7 +44246,7 @@
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Pneumático. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os veículos de elevado peso bruto utilizam sistema de travagem».</t>
+          <t>Relativamente a «Os veículos de elevado peso bruto utilizam sistema de travagem», a resposta adequada é B): Pneumático.</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
@@ -44306,7 +44306,7 @@
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) A atividade transitária só pode ser exercida por empresas titulares de alvará emitido pelo IMT. No exame CAM do IMT, esta alternativa responde corretamente à questão «Assinale a afirmação verdadeira».</t>
+          <t>A atividade transitária só pode ser exercida por empresas titulares de alvará emitido pelo IMT — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («As empresas que realizam transporte rodoviário de mercadorias perigosas ca…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
@@ -44366,7 +44366,7 @@
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Uma forma de cooperação ao nível da actividade de uma empresa (contratante ou empresa principal) que entrega a outra (subcontratada ou empresa auxiliar) a execução da totalidade ou de uma parte da sua actividade dentro de determinadas condições. No exame CAM do IMT, esta alternativa responde corretamente à questão «A subcontratação nas empresas de transporte rodoviário é».</t>
+          <t>Uma forma de cooperação ao nível da actividade de uma empresa (contratante ou empresa principal) que entrega a outra (subcontratada ou empresa auxiliar) a execução da totalidade ou de uma parte da sua actividade dentro de determinadas condições — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A perda de controlo na execução das actividades e maior necessidade de con…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
@@ -44426,7 +44426,7 @@
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Não coloca em perigo a saúde pública e os ecossistemas e que respeita as necessidades de mobilidade. No exame CAM do IMT, esta alternativa responde corretamente à questão «Transporte sustentável é o que».</t>
+          <t>Não coloca em perigo a saúde pública e os ecossistemas e que respeita as necessidades de mobilidade — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Apenas é bom para o meio ambiente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
@@ -44486,7 +44486,7 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Alvará, emitido pelo IMTT. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma empresa de aluguer de veículos sem condutor é titulada por».</t>
+          <t>Alvará, emitido pelo IMTT — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Não carece de qualquer alvará») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -44546,7 +44546,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Maior rapidez (porta-a-porta). No exame CAM do IMT, esta alternativa responde corretamente à questão «Das vantagens do transporte rodoviário de mercadorias, pode-se assinalar».</t>
+          <t>Maior rapidez (porta-a-porta) — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Maior competitividade para produtos com baixo custo de tonelada por quilóm…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -44606,7 +44606,7 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Um dos principais fatores encontrados na origem de acidentes rodoviários. No exame CAM do IMT, esta alternativa responde corretamente à questão «A perda de controlo associada à fadiga é».</t>
+          <t>Um dos principais fatores encontrados na origem de acidentes rodoviários — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Significativa apenas se o condutor ingerir bebidas alcoólicas») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -44666,7 +44666,7 @@
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Aumento do tempo de reação. No exame CAM do IMT, esta alternativa responde corretamente à questão «Alguns medicamentos podem provocar».</t>
+          <t>Aumento do tempo de reação — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Aumento da capacidade de percepção das velocidades e distâncias») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
@@ -44726,7 +44726,7 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Aos veículos de duas rodas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Sob a influência de vento lateral o condutor deve dar especial atenção».</t>
+          <t>O procedimento adequado é Aos veículos de duas rodas (A)). Por exemplo, D) («Às marcas rodoviárias») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -44786,7 +44786,7 @@
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Os dispositivos de segurança estão todos a funcionar corretamente. No exame CAM do IMT, esta alternativa responde corretamente à questão «Antes de iniciar uma viagem internacional o motorista deve certificar-se que».</t>
+          <t>O procedimento adequado é Os dispositivos de segurança estão todos a funcionar corretamente (A)). Por exemplo, D) («Os passageiros falam todos português corretamente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
@@ -44846,7 +44846,7 @@
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) Verificar os danos provocados no veículo, avaliar as perdas da carga e comunicar imediatamente á entidade patronal e à polícia, ajudando no relatório do roubo. No exame CAM do IMT, esta alternativa responde corretamente à questão «Diga o que fazer em caso de emergência de roubo ou assalto».</t>
+          <t>Em roubo ou assalto à carga, o condutor deve preservar a segurança, avaliar danos e perdas, comunicar de imediato ao empregador e à polícia e colaborar no registo do incidente. Isso corresponde a B): Verificar os danos provocados no veículo, avaliar as perdas da carga e comunicar imediatamente á entidade patronal e à polícia, ajudando no relatório do roubo.</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">
@@ -44906,7 +44906,7 @@
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Descansar e aguardar que seja efetuada a descarga. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando da chegada ao destinatário, o motorista não deve».</t>
+          <t>O procedimento adequado é Descansar e aguardar que seja efetuada a descarga (A)). Por exemplo, D) («Verificar se o lacre colocado no compartimento de carga ainda está intacto…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
@@ -44966,7 +44966,7 @@
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Planear os detalhes do itinerário e não seguir sempre o mesmo percurso. No exame CAM do IMT, esta alternativa responde corretamente à questão «Uma das formas de prevenir a criminalidade é, antes da viagem».</t>
+          <t>Planear os detalhes do itinerário e não seguir sempre o mesmo percurso — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Assegurar-se que a entrega da mercadoria é feita no local correcto ou os p…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
@@ -45026,7 +45026,7 @@
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Contactar imediatamente as autoridades locais e identificar -se, b em como ao veículo, dando referências da localização. No exame CAM do IMT, esta alternativa responde corretamente à questão «Se suspeitar que transporta um passageiro clandestino, deve».</t>
+          <t>O procedimento adequado é Contactar imediatamente as autoridades locais e identificar -se, b em como ao veículo, dando referências da localização (A)). Por exemplo, D) («Atacar o passageiro, de forma a saia do veículo») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
@@ -45086,7 +45086,7 @@
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) A base das chamas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Em caso de incêndio, o jacto do extintor deve ser direcionado para».</t>
+          <t>O procedimento adequado é A base das chamas (A)). Por exemplo, D) («O topo e o meio das chamas alternadamente») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
@@ -45146,7 +45146,7 @@
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Todas as respostas anteriores estão correctas. No exame CAM do IMT, esta alternativa responde corretamente à questão «Quando se liga 112».</t>
+          <t>Todas as respostas anteriores estão correctas — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Estamos a ligar diretamente para os bombeiros») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I772" t="inlineStr">
@@ -45206,7 +45206,7 @@
       </c>
       <c r="H773" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Abandonar o local. No exame CAM do IMT, esta alternativa responde corretamente à questão «Em caso de acidente com a sua viatura, qual o procedimento que não deve ser adoptado».</t>
+          <t>O procedimento adequado é Abandonar o local (D)). Por exemplo, C) («Efetuar uma rápida avaliação da vítima») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I773" t="inlineStr">
@@ -45266,7 +45266,7 @@
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Maior velocidade de circulação. No exame CAM do IMT, esta alternativa responde corretamente à questão «A principal causa para o índice de gravidade dos acidentes com veículo pesados de passageiros ser superior fora das l...».</t>
+          <t>Maior velocidade de circulação — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Maior distracção do condutor provocada pelos passageiros») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
@@ -45326,7 +45326,7 @@
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Menor volume de tráfego e menor número de acidentes. No exame CAM do IMT, esta alternativa responde corretamente à questão «Os períodos do dia que apresenta maior gravidade nos acidentes correspondem aos períodos com».</t>
+          <t>A questão relaciona-se com condução segura, prevenção de acidentes e comportamento ao volante. No caso «Os períodos do dia que apresenta maior gravidade nos acidentes correspondem aos períodos com», a opção D) é a alternativa que melhor se aplica ao caso: Menor volume de tráfego e menor número de acidentes.</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
@@ -45386,7 +45386,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Os transportes interurbanos, regionais, locais e urbanos. No exame CAM do IMT, esta alternativa responde corretamente à questão «Constituem categorias do transporte interno».</t>
+          <t>Os transportes interurbanos, regionais, locais e urbanos — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Os transportes particulares») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -45446,7 +45446,7 @@
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção C) Falta de organização gerando pouco trabalho e produtividade assim como aspetos físicos ambientais. No exame CAM do IMT, esta alternativa responde corretamente à questão «Um dos fatores que prejudica o bom relacionamento interpessoal nas empresas é».</t>
+          <t>Falta de organização gerando pouco trabalho e produtividade assim como aspetos físicos ambientais — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Consciencialização dos objetivos e metas a atingir como profissional da em…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">
@@ -45506,7 +45506,7 @@
       </c>
       <c r="H778" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Formar um grupo coeso, eficiente e motivado. No exame CAM do IMT, esta alternativa responde corretamente à questão «A boa comunicação é importante entre os membros dentro de uma organização para».</t>
+          <t>Formar um grupo coeso, eficiente e motivado — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Que o nosso comportamento possa depender do nosso estado de espírito») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I778" t="inlineStr">
@@ -45566,7 +45566,7 @@
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Permite aos motoristas estar em contacto com a empresa, colegas, clientes e outros contactos, tais como serviços de manutenção e reparação e centros de controlo de tráfego. No exame CAM do IMT, esta alternativa responde corretamente à questão «A evolução da s tecnologias de informação e comunicação tem tido influência nos transportes de pesados de passageiros...».</t>
+          <t>Permite aos motoristas estar em contacto com a empresa, colegas, clientes e outros contactos, tais como serviços de manutenção e reparação e centros de controlo de tráfego — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Obriga o condutor a obter certificados e autorizações adicionais para o ex…») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I779" t="inlineStr">
@@ -45626,7 +45626,7 @@
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção A) Permite fiscalizar os passageiros no veículo. No exame CAM do IMT, esta alternativa responde corretamente à questão «A bilhética sem contacto (indique a afirmação verdadeira)».</t>
+          <t>A bilhética sem contacto permite validar títulos de transporte sem contacto físico prolongado, facilitando a fiscalização em bordo. A afirmação verdadeira é A): Permite fiscalizar os passageiros no veículo.</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
@@ -45686,7 +45686,7 @@
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção D) Avaliação em primeiro lugar do estado de consciência da vítima. No exame CAM do IMT, esta alternativa responde corretamente à questão «O exame primário da vítima consiste na».</t>
+          <t>Trata-se de uma definição: Avaliação em primeiro lugar do estado de consciência da vítima (opção D)).  Por exemplo, B) («Verificação em primeiro lugar da existência de ventilação.») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
@@ -45746,7 +45746,7 @@
       </c>
       <c r="H782" t="inlineStr">
         <is>
-          <t>A resposta correta é a opção B) A instalação de televisões na cabine do veículo ou na caixa de carga. No exame CAM do IMT, esta alternativa responde corretamente à questão «A telemática é».</t>
+          <t>A instalação de televisões na cabine do veículo ou na caixa de carga — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («As ferramentas informáticas utilizadas para fazer edição de imagens») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I782" t="inlineStr">
@@ -45806,7 +45806,7 @@
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>Integra localização, dados de condução e gestão de frota.</t>
+          <t>Gestão em tempo real de frota, consumo e rotas — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Apenas controlo de velocidade») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>Cartões ou dispositivos que funcionam por proximidade.</t>
+          <t>A bilhética sem contacto permite validar títulos de transporte sem contacto físico prolongado, facilitando a fiscalização em bordo. A afirmação verdadeira é A): Pagamento rápido sem cartão físico.</t>
         </is>
       </c>
       <c r="I784" t="inlineStr">
@@ -45926,7 +45926,7 @@
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>Permite que as rodas exteriores e interiores girem a velocidades diferentes.</t>
+          <t>Permitir que as rodas girem a velocidades diferentes em curva — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Aumentar o binário do motor») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I785" t="inlineStr">
@@ -45986,7 +45986,7 @@
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>É crime e pode acarretar sanções pesadas.</t>
+          <t>É proibido e pode ter consequências graves — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («É permitido se pagar em dinheiro») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I786" t="inlineStr">
@@ -46046,7 +46046,7 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>Afeta todo o sistema de travagem.</t>
+          <t>As alternativas anteriores são corretas em separado; por isso D) («Todas as anteriores») é a resposta completa. Por exemplo, C) («Aumento da distância de travagem») não corresponde ao pedido do enunciado.</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">

--- a/questoes sem rep.xlsx
+++ b/questoes sem rep.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(DL 257/2007): 9.000 € no 1.º veículo; 5.000 € (pesado) ou 900 € (ligeiro) por veículo adicional. Relativamente a «Durante o exercício da atividade das empresas de transportes públicos de mercadorias por…», a resposta adequada é D): Não pode ser inferior a € 9 000 pelo primeiro veículo automóvel licenciado ou € 5 000 ou € 900 por cada veículo adicional, consoante se trate de veículo pesado ou ligeiro. Por exemplo, a opção A) indica valores (Não pode ser superior a € 8 987,36 pelo primeiro veículo automóvel licenci…) diferentes do aplicável.</t>
+          <t>(DL 257/2007): 9.000 € no 1.º veículo; 5.000 € (pesado) ou 900 € (ligeiro) por veículo adicional. Relativamente a «Durante o exercício da atividade das empresas de transportes públicos de mercadorias por…», a resposta adequada é D): Não pode ser inferior a € 9 000 pelo primeiro veículo automóvel licenciado ou € 5 000 ou € 900 por cada veículo adicional, consoante se trate de veículo pesado ou ligeiro.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>O valor ou limite legal aplicável é 30 dias a contar da data da sua ocorrência, indicado em C).  Por exemplo, a opção A) indica valores (10 dias a contar da sua ocorrência) diferentes do aplicável.</t>
+          <t>O valor ou limite legal aplicável é 30 dias a contar da data da sua ocorrência, indicado em C).</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>O procedimento adequado é No prazo de 30 dias a contar da data da sua ocorrência (A)). Por exemplo, D) («Aquando da renovação da licença ou alvará») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é No prazo de 30 dias a contar da data da sua ocorrência (A)).</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>A certidão do registo comercial é o documento válido para comprovar o capital social. Na situação «Uma sociedade unipessoal por quotas, no início da atividade, deve fazer prova da…», o procedimento correto é Certidão do registo comercial da qual conste o capital social (opção B)). Por exemplo, D) («Declaração do IRC referente ao ano anterior.») não corresponde ao pedido do enunciado.</t>
+          <t>A certidão do registo comercial é o documento válido para comprovar o capital social. Na situação «Uma sociedade unipessoal por quotas, no início da atividade, deve fazer prova da…», o procedimento correto é Certidão do registo comercial da qual conste o capital social (opção B)).</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -834,7 +834,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pelo Instituto da Mobilidade e dos Transportes — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Câmara Municipal da residência do proprietário do veículo») não corresponde ao pedido do enunciado.</t>
+          <t>Pelo Instituto da Mobilidade e dos Transportes — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Mediante comprovação de que se mantêm os requisitos de acesso e de exercício de atividade — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Apenas mediante prova da capacidade profissional») não corresponde ao pedido do enunciado.</t>
+          <t>Mediante comprovação de que se mantêm os requisitos de acesso e de exercício de atividade — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -938,7 +938,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Em qualquer momento porque os requisitos são de verificação permanente — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Só pode fiscalizar mediante participação das autoridades policiais») não corresponde ao pedido do enunciado.</t>
+          <t>Em qualquer momento porque os requisitos são de verificação permanente — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5 anos — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (1 ano) diferentes do aplicável.</t>
+          <t>5 anos — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>O valor ou limite legal aplicável é 18 toneladas, indicado em A).  Por exemplo, a opção B) indica valores (20 toneladas) diferentes do aplicável.</t>
+          <t>O valor ou limite legal aplicável é 18 toneladas, indicado em A).</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>O valor ou limite legal aplicável é 26 toneladas, indicado em B).  Por exemplo, a opção A) indica valores (22 toneladas) diferentes do aplicável.</t>
+          <t>O valor ou limite legal aplicável é 26 toneladas, indicado em B).</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>O valor ou limite legal aplicável é 44 toneladas, indicado em C).  Por exemplo, a opção A) indica valores (38 toneladas) diferentes do aplicável.</t>
+          <t>O valor ou limite legal aplicável é 44 toneladas, indicado em C).</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4 metros — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (3,5 metros) diferentes do aplicável.</t>
+          <t>4 metros — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>13,5 metros — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (12 metros) diferentes do aplicável.</t>
+          <t>13,5 metros — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ADR (Acordo Europeu relativo ao transporte de mercadorias perigosas) — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Certificado de capacidade profissional adicional») não corresponde ao pedido do enunciado.</t>
+          <t>ADR (Acordo Europeu relativo ao transporte de mercadorias perigosas) — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>O limite diário de condução é 9 horas (pode ser estendido para 10 horas duas vezes por semana). Relativamente a «O tempo máximo de condução diária para um condutor profissional (sem interrupções) é de», a resposta adequada é B): 9 horas. Por exemplo, a opção A) indica valores (8 horas) diferentes do aplicável.</t>
+          <t>O limite diário de condução é 9 horas (pode ser estendido para 10 horas duas vezes por semana). Relativamente a «O tempo máximo de condução diária para um condutor profissional (sem interrupções) é de», a resposta adequada é B): 9 horas.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>O limite semanal de condução é de 56 horas (pode chegar a 60 horas em algumas semanas). Relativamente a «O tempo máximo de condução semanal (sem interrupções) para um condutor profissional é de», a resposta adequada é B): 56 horas. Por exemplo, a opção A) indica valores (45 horas) diferentes do aplicável.</t>
+          <t>O limite semanal de condução é de 56 horas (pode chegar a 60 horas em algumas semanas). Relativamente a «O tempo máximo de condução semanal (sem interrupções) para um condutor profissional é de», a resposta adequada é B): 56 horas.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>O descanso diário mínimo é de 11 horas (pode ser reduzido para 9 horas três vezes por semana). Relativamente a «O período mínimo de descanso diário obrigatório para um condutor profissional é de», a resposta adequada é B): 11 horas. Por exemplo, a opção A) indica valores (9 horas) diferentes do aplicável.</t>
+          <t>O descanso diário mínimo é de 11 horas (pode ser reduzido para 9 horas três vezes por semana). Relativamente a «O período mínimo de descanso diário obrigatório para um condutor profissional é de», a resposta adequada é B): 11 horas.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>O valor ou limite legal aplicável é 3,5 toneladas, indicado em B).  Por exemplo, a opção A) indica valores (2,5 toneladas) diferentes do aplicável.</t>
+          <t>O valor ou limite legal aplicável é 3,5 toneladas, indicado em B).</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Escrita ou verbal — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Apenas por tempo indeterminado») não corresponde ao pedido do enunciado.</t>
+          <t>Escrita ou verbal — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Pela entidade patronal no mês seguinte (B)). Por exemplo, A) («Pelo trabalhador mensalmente») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Pela entidade patronal no mês seguinte (B)).</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Reintegração na empresa — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Apenas pagamento de salários em atraso») não corresponde ao pedido do enunciado.</t>
+          <t>Reintegração na empresa — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>40 horas — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (35 horas) diferentes do aplicável.</t>
+          <t>40 horas — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Nunca pode acontecer (é irrenunciável) — é o que melhor responde ao enunciado (opção B)). Por exemplo, A) («Pode acontecer se a entidade pagar em dobro») não corresponde ao pedido do enunciado.</t>
+          <t>Nunca pode acontecer (é irrenunciável) — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>As alternativas anteriores são corretas em separado; por isso D) («Todas as anteriores») é a resposta completa. Por exemplo, C) («Recusar tarefas que não estão no contrato») não corresponde ao pedido do enunciado.</t>
+          <t>As alternativas anteriores são corretas em separado; por isso D) («Todas as anteriores») é a resposta completa.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4 horas e 30 minutos — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (4 horas) diferentes do aplicável.</t>
+          <t>4 horas e 30 minutos — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>O procedimento adequado é 45 horas (C)). Por exemplo, a opção A) indica valores (24 horas) diferentes do aplicável.</t>
+          <t>O procedimento adequado é 45 horas (C)).</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Quadro ou Chassis — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Longarinas ou Travessas») não corresponde ao pedido do enunciado.</t>
+          <t>Quadro ou Chassis — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Com metade da sua capacidade — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Não existe diferença em qualquer dos casos assinalados») não corresponde ao pedido do enunciado.</t>
+          <t>Com metade da sua capacidade — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4 metros a contar do solo — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (3,5 metros a contar do solo) diferentes do aplicável.</t>
+          <t>4 metros a contar do solo — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>O procedimento adequado é O nível do óleo do comando da embraiagem e o do sistema hidráulico da direção assistida (C)). Por exemplo, D) («Nenhum dos itens anteriores») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é O nível do óleo do comando da embraiagem e o do sistema hidráulico da direção assistida (C)).</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Excesso de combustível não queimado devido má mistura de combustível — é o que melhor responde ao enunciado (opção D)). Por exemplo, B) («Fugas de combustível na alta pressão») não corresponde ao pedido do enunciado.</t>
+          <t>Excesso de combustível não queimado devido má mistura de combustível — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Trata-se de uma definição: Num sistema de retenção em que a carga é estivada contra estruturas fixas ou elementos do porta-cargas (opção D)).  Por exemplo, C) («Num sistema para prender vários volumes e deve sempre ser combinada com ou…») não corresponde ao pedido do enunciado.</t>
+          <t>Trata-se de uma definição: Num sistema de retenção em que a carga é estivada contra estruturas fixas ou elementos do porta-cargas (opção D)).</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Parar de 2 em 2 horas e, imperativamente, após os primeiros sintomas de fadiga (A)). Por exemplo, D) («Circular com maior velocidade até encontrar uma área de serviço aberta») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Parar de 2 em 2 horas e, imperativamente, após os primeiros sintomas de fadiga (A)).</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Reduzir as partículas de fuligem no escape — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Aquecer o motor mais rápido») não corresponde ao pedido do enunciado.</t>
+          <t>Reduzir as partículas de fuligem no escape — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Motor de combustão através de correia — é o que melhor responde ao enunciado (opção B)). Por exemplo, A) («Motor elétrico auxiliar») não corresponde ao pedido do enunciado.</t>
+          <t>Motor de combustão através de correia — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>As alternativas anteriores são corretas em separado; por isso D) («Todas as anteriores») é a resposta completa. Por exemplo, C) («Carga mal distribuída») não corresponde ao pedido do enunciado.</t>
+          <t>As alternativas anteriores são corretas em separado; por isso D) («Todas as anteriores») é a resposta completa.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Evitar o movimento longitudinal da carga — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Melhorar a aerodinâmica») não corresponde ao pedido do enunciado.</t>
+          <t>Evitar o movimento longitudinal da carga — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Trata-se de uma definição: Amarras diagonais sobre a carga (opção A)).  Por exemplo, C) («Amarras apenas laterais») não corresponde ao pedido do enunciado.</t>
+          <t>Trata-se de uma definição: Amarras diagonais sobre a carga (opção A)).</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Evitar paragens desnecessárias e escolher rotas seguras (A)). Por exemplo, D) («Ignorar o plano de segurança») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Evitar paragens desnecessárias e escolher rotas seguras (A)).</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Avaliar o estado de consciência — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Colocar em posição lateral de segurança») não corresponde ao pedido do enunciado.</t>
+          <t>Avaliar o estado de consciência — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Fazer compressão direta sobre a ferida (B)). Por exemplo, D) («Deixar sangrar para limpar») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Fazer compressão direta sobre a ferida (B)).</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Está inconsciente mas respira (B)). Por exemplo, D) («Está em paragem cardiorrespiratória») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Está inconsciente mas respira (B)).</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>13 horas — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (10 horas) diferentes do aplicável.</t>
+          <t>13 horas — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>O procedimento adequado é 5 anos (B)). Por exemplo, a opção A) indica valores (3 anos) diferentes do aplicável.</t>
+          <t>O procedimento adequado é 5 anos (B)).</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Produção e entrega com stocks mínimos — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Gestão de combustível») não corresponde ao pedido do enunciado.</t>
+          <t>Produção e entrega com stocks mínimos — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Reduzir o esforço físico e prevenir lesões — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Aumentar o espaço de carga») não corresponde ao pedido do enunciado.</t>
+          <t>Reduzir o esforço físico e prevenir lesões — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Obrigatório sempre que o veículo estiver em movimento — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Obrigatório apenas em cidade») não corresponde ao pedido do enunciado.</t>
+          <t>Obrigatório sempre que o veículo estiver em movimento — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Soltar o acelerador e não travar (C)). Por exemplo, D) («Virar o volante rapidamente») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Soltar o acelerador e não travar (C)).</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>O veículo começa a derrapar ou perder estabilidade — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O condutor usa o travão de mão») não corresponde ao pedido do enunciado.</t>
+          <t>O veículo começa a derrapar ou perder estabilidade — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Reduzir o consumo de combustível e o desgaste — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Chegar mais rápido ao destino») não corresponde ao pedido do enunciado.</t>
+          <t>Reduzir o consumo de combustível e o desgaste — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>O procedimento adequado é 2 anos (B)). Por exemplo, a opção A) indica valores (6 meses) diferentes do aplicável.</t>
+          <t>O procedimento adequado é 2 anos (B)).</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Parar o veículo em local seguro e desligar o motor (B)). Por exemplo, C) («Telefonar imediatamente para o 112») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Parar o veículo em local seguro e desligar o motor (B)).</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Sempre que haja danos materiais e as partes concordem (B)). Por exemplo, D) («Apenas em autoestrada») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Sempre que haja danos materiais e as partes concordem (B)).</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0,2 g/l — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (0,5 g/l) diferentes do aplicável.</t>
+          <t>0,2 g/l — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Sempre que possível em autoestrada (A)). Por exemplo, D) («Nunca em veículos pesados») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Sempre que possível em autoestrada (A)).</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Informar sobre condições de trânsito em tempo real — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Indicar postos de combustível») não corresponde ao pedido do enunciado.</t>
+          <t>Informar sobre condições de trânsito em tempo real — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Como apoio, nunca desviando a atenção da estrada (B)). Por exemplo, D) («Apenas em viagens internacionais») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Como apoio, nunca desviando a atenção da estrada (B)).</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Apoiar a gestão da empresa (rotas, horários, bilhética) — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Substituir o tacógrafo») não corresponde ao pedido do enunciado.</t>
+          <t>Apoiar a gestão da empresa (rotas, horários, bilhética) — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Identificação automática de veículos e cargas — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Controlar a velocidade») não corresponde ao pedido do enunciado.</t>
+          <t>Identificação automática de veículos e cargas — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>O procedimento adequado é 600-800 °C (C)). Por exemplo, a opção A) indica valores (100-200 °C) diferentes do aplicável.</t>
+          <t>O procedimento adequado é 600-800 °C (C)).</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>As alternativas anteriores são corretas em separado; por isso D) («Todas as anteriores») é a resposta completa. Por exemplo, C) («Aumento da distância de travagem») não corresponde ao pedido do enunciado.</t>
+          <t>As alternativas anteriores são corretas em separado; por isso D) («Todas as anteriores») é a resposta completa.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Aumentar a altura da carga — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Melhorar a aerodinâmica») não corresponde ao pedido do enunciado.</t>
+          <t>Aumentar a altura da carga — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>As alternativas anteriores são corretas em separado; por isso D) («Todas as anteriores») é a resposta completa. Por exemplo, B) («Movimento para a frente») não corresponde ao pedido do enunciado.</t>
+          <t>As alternativas anteriores são corretas em separado; por isso D) («Todas as anteriores») é a resposta completa.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Torniquete comercial (A)). Por exemplo, D) («Nada, só esperar ajuda») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Torniquete comercial (A)).</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>O procedimento adequado é 30 compressões torácicas (A)). Por exemplo, a opção B) indica valores (2 insuflações) diferentes do aplicável.</t>
+          <t>O procedimento adequado é 30 compressões torácicas (A)).</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>10 horas — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (9 horas) diferentes do aplicável.</t>
+          <t>10 horas — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>O procedimento adequado é 2 anos (B)). Por exemplo, a opção A) indica valores (1 ano) diferentes do aplicável.</t>
+          <t>O procedimento adequado é 2 anos (B)).</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Condutores com excesso de peso — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Condutores que fazem pausas frequentes») não corresponde ao pedido do enunciado.</t>
+          <t>Condutores com excesso de peso — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>É proibido durante a condução — é o que melhor responde ao enunciado (opção B)). Por exemplo, A) («É permitido se tomar só meio comprimido») não corresponde ao pedido do enunciado.</t>
+          <t>É proibido durante a condução — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Com técnicas corretas (mudanças suaves, uso do retardador, etc.) é possível poupar 15-25 %. Relativamente a «A condução económica permite reduzir o consumo de combustível em até», a resposta adequada é C): 15-25 %. Por exemplo, a opção A) indica valores (5 %) diferentes do aplicável.</t>
+          <t>Com técnicas corretas (mudanças suaves, uso do retardador, etc.) é possível poupar 15-25 %. Relativamente a «A condução económica permite reduzir o consumo de combustível em até», a resposta adequada é C): 15-25 %.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Sempre que possível em autoestrada (A)). Por exemplo, D) («Nunca em veículos pesados») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Sempre que possível em autoestrada (A)).</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>O veículo derrapa ou perde aderência — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O condutor usa o telemóvel») não corresponde ao pedido do enunciado.</t>
+          <t>O veículo derrapa ou perde aderência — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Reduzir velocidade e aumentar distância de segurança (B)). Por exemplo, C) («Usar luzes de máximos») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Reduzir velocidade e aumentar distância de segurança (B)).</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Informar sobre condições de trânsito em tempo real — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Indicar postos de combustível») não corresponde ao pedido do enunciado.</t>
+          <t>Informar sobre condições de trânsito em tempo real — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Trata-se de uma definição: Ativar o botão de alarme e ligar 112 (opção A)).  Por exemplo, C) («Parar e sair do veículo») não corresponde ao pedido do enunciado.</t>
+          <t>Trata-se de uma definição: Ativar o botão de alarme e ligar 112 (opção A)).</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Sempre que haja danos e as partes concordem — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Apenas em autoestrada») não corresponde ao pedido do enunciado.</t>
+          <t>Sempre que haja danos e as partes concordem — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Circular em países do Espaço Económico Europeu — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Apenas em viagens de longa distância») não corresponde ao pedido do enunciado.</t>
+          <t>Circular em países do Espaço Económico Europeu — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Avaliar consciência → Via aérea → Respiração → Circulação — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Nenhuma das anteriores») não corresponde ao pedido do enunciado.</t>
+          <t>Avaliar consciência → Via aérea → Respiração → Circulação — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>O procedimento adequado é 11 horas (B)). Por exemplo, a opção A) indica valores (9 horas) diferentes do aplicável.</t>
+          <t>O procedimento adequado é 11 horas (B)).</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>O procedimento adequado é 2 em 2 anos (B)). Por exemplo, a opção A) indica valores (6 em 6 meses) diferentes do aplicável.</t>
+          <t>O procedimento adequado é 2 em 2 anos (B)).</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Em todas as situações acima — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Após 4 horas de condução contínua») não corresponde ao pedido do enunciado.</t>
+          <t>Em todas as situações acima — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>O veículo derrapa ou perde estabilidade — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O condutor usa o travão de mão») não corresponde ao pedido do enunciado.</t>
+          <t>O veículo derrapa ou perde estabilidade — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Proibido e pode ter consequências graves — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Permitido se pagar em dinheiro») não corresponde ao pedido do enunciado.</t>
+          <t>Proibido e pode ter consequências graves — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Sempre que haja danos e as partes concordem (A)). Por exemplo, C) («Apenas em autoestrada») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Sempre que haja danos e as partes concordem (A)).</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Internacional de seguro automóvel — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («De capacidade profissional») não corresponde ao pedido do enunciado.</t>
+          <t>Internacional de seguro automóvel — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>30 compressões torácicas — é o que melhor responde ao enunciado (opção A)). Por exemplo, a opção B) indica valores (2 insuflações) diferentes do aplicável.</t>
+          <t>30 compressões torácicas — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Torniquete comercial (A)). Por exemplo, B) («Compressa improvisada») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Torniquete comercial (A)).</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Avaliar consciência → Via aérea → Respiração → Circulação — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Nenhuma das anteriores») não corresponde ao pedido do enunciado.</t>
+          <t>Avaliar consciência → Via aérea → Respiração → Circulação — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Alinhamento incorreto das rodas — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Carga bem distribuída») não corresponde ao pedido do enunciado.</t>
+          <t>Alinhamento incorreto das rodas — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>As rodas girem a velocidades diferentes em curva — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O motor aumente o binário») não corresponde ao pedido do enunciado.</t>
+          <t>As rodas girem a velocidades diferentes em curva — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -5950,7 +5950,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Movimento longitudinal da mercadoria — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Melhoria da visibilidade») não corresponde ao pedido do enunciado.</t>
+          <t>Movimento longitudinal da mercadoria — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>As alternativas anteriores são corretas em separado; por isso D) («Todas as anteriores») é a resposta completa. Por exemplo, B) («Movimento para a frente») não corresponde ao pedido do enunciado.</t>
+          <t>As alternativas anteriores são corretas em separado; por isso D) («Todas as anteriores») é a resposta completa.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Em caso algum, porque o direito a férias é irrenunciável — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Desde que o trabalhador concorde») não corresponde ao pedido do enunciado.</t>
+          <t>Em caso algum, porque o direito a férias é irrenunciável — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Com excesso de peso — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Que fazem pausas frequentes») não corresponde ao pedido do enunciado.</t>
+          <t>Com excesso de peso — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Proibido durante a condução — é o que melhor responde ao enunciado (opção B)). Por exemplo, A) («Permitido se tomar meio comprimido») não corresponde ao pedido do enunciado.</t>
+          <t>Proibido durante a condução — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>600-800 °C — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (100-200 °C) diferentes do aplicável.</t>
+          <t>600-800 °C — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Além dos acidentes de viação, o motorista também está exposto a acidentes durante carga/descarga. Relativamente a «O motorista de um veículo pesado de mercadorias está, no âmbito da sua profissão,…», a resposta adequada é B): Acidentes relacionados com a carga e descarga de veículos. Por exemplo, D) («Não está sujeito a acidentes») não corresponde ao pedido do enunciado.</t>
+          <t>Além dos acidentes de viação, o motorista também está exposto a acidentes durante carga/descarga. Relativamente a «O motorista de um veículo pesado de mercadorias está, no âmbito da sua profissão,…», a resposta adequada é B): Acidentes relacionados com a carga e descarga de veículos.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>O procedimento adequado é De costas para a via, utilizando sempre todos os apoios de mãos e de pés (A)). Por exemplo, D) («Não é necessário cumprir qualquer regra para o efeito») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é De costas para a via, utilizando sempre todos os apoios de mãos e de pés (A)).</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>O desconhecimento da via e o excesso de confiança — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («Apenas o desconhecimento da via») não corresponde ao pedido do enunciado.</t>
+          <t>O desconhecimento da via e o excesso de confiança — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Um acontecimento sú bito e imprevisto, sofrido pelo trabalhador que se verifique no local e tempo de trabalho — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Um acidente ocorrido na rua que implique hospitalização») não corresponde ao pedido do enunciado.</t>
+          <t>Um acontecimento sú bito e imprevisto, sofrido pelo trabalhador que se verifique no local e tempo de trabalho — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>O uso do corta-vento na janela do condutor e a condução sempre que possível com o vidro fechado — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («A condução com as janelas abertas») não corresponde ao pedido do enunciado.</t>
+          <t>O uso do corta-vento na janela do condutor e a condução sempre que possível com o vidro fechado — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Na sede ou agente da empresa (B)). Por exemplo, D) («Na residência do condutor da viatura») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Na sede ou agente da empresa (B)).</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Meio de deslocação de pessoas ou bens a partir de um lugar para outro — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Movimentação entre dois modos de transporte») não corresponde ao pedido do enunciado.</t>
+          <t>Meio de deslocação de pessoas ou bens a partir de um lugar para outro — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Envolver apenas um modo de transporte — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Envolver transbordos para veículos da mesma modalidade») não corresponde ao pedido do enunciado.</t>
+          <t>Envolver apenas um modo de transporte — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Apresentar-se devidamente uniformizado e com aspecto cuidado — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Importunar os passageiros com exigências não justificadas») não corresponde ao pedido do enunciado.</t>
+          <t>Apresentar-se devidamente uniformizado e com aspecto cuidado — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Os serviços com distâncias não inferiores a 50 km, com  um número limitado de paragens intermédias e que utilizam exclusivamente veículos de classes II ou III — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Apenas serviços classificados como regulares especializados.») não corresponde ao pedido do enunciado.</t>
+          <t>Os serviços com distâncias não inferiores a 50 km, com  um número limitado de paragens intermédias e que utilizam exclusivamente veículos de classes II ou III — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>20 Kg por passageiro — é o que melhor responde ao enunciado (opção D)). Por exemplo, a opção A) indica valores (40 Kg por passageiro) diferentes do aplicável.</t>
+          <t>20 Kg por passageiro — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>A afirmação é verdadeira — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («A afirmação é falsa, porque a maior causa de acidente são as condições met…») não corresponde ao pedido do enunciado.</t>
+          <t>A afirmação é verdadeira — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Sim, aliados a uma boa rede de infraestruturas viárias — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Sim, se for efetuado por autoestradas») não corresponde ao pedido do enunciado.</t>
+          <t>Sim, aliados a uma boa rede de infraestruturas viárias — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Sim, pois uma boa rede de transportes públicos eficiente e pontual, fazia com que as pessoas a utilizassem mais e isto iria contribuir para um decréscimo da poluição atmosférica e diminuição dos engarrafamentos de trânsito — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Não, pois ninguém está interessado em utilizar os transportes públicos») não corresponde ao pedido do enunciado.</t>
+          <t>Sim, pois uma boa rede de transportes públicos eficiente e pontual, fazia com que as pessoas a utilizassem mais e isto iria contribuir para um decréscimo da poluição atmosférica e diminuição dos engarrafamentos de trânsito — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Por conta própria e por conta de outrem — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Não se encontra regulamentado») não corresponde ao pedido do enunciado.</t>
+          <t>Por conta própria e por conta de outrem — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Económico, social e ambiental (C)). Por exemplo, D) («Não é aplicável o conceito de sustentabilidade») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Económico, social e ambiental (C)).</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Um administrador, diretor ou gerente que dirija a empresa em permanência e efetividade (D)). Por exemplo, B) («Pelo sócio maioritário da empresa») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Um administrador, diretor ou gerente que dirija a empresa em permanência e efetividade (D)).</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Sociedades comerciais, cooperativas e empresas públicas ou de capitais públicos — é o que melhor responde ao enunciado (opção D)). Por exemplo, A) («Apenas sociedades comerciais») não corresponde ao pedido do enunciado.</t>
+          <t>Sociedades comerciais, cooperativas e empresas públicas ou de capitais públicos — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Um alvará ou licença comunitária emitidos por um prazo não superior a cinco anos. — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A atividade de transporte rodoviário de passageiros em autocarro não neces…») não corresponde ao pedido do enunciado.</t>
+          <t>Um alvará ou licença comunitária emitidos por um prazo não superior a cinco anos. — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Um contrato escrito entre a empresa transportadora e a entidade interessada na prestação do serviço — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Um acordo entre duas pessoas: gerente da empresa de transportes e  o Presi…») não corresponde ao pedido do enunciado.</t>
+          <t>Um contrato escrito entre a empresa transportadora e a entidade interessada na prestação do serviço — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Transportes públicos ou por conta de outrem — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Transportes interurbanos») não corresponde ao pedido do enunciado.</t>
+          <t>Transportes públicos ou por conta de outrem — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Os que implicando atravessamento de fronteiras se desenvolvem parcialm ente em território português — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Os que visam satisfazer as necessidades de deslocação dentro de um municíp…») não corresponde ao pedido do enunciado.</t>
+          <t>Os que implicando atravessamento de fronteiras se desenvolvem parcialm ente em território português — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Transportes que asseguram o tr ansporte de passageiros segundo itinerário, frequência, horário e tarifas predeterminadas e em que podem ser tomados e largados passageiros em paragens previamente estabelecidas — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Transportes efetuados sem fins lucrativos») não corresponde ao pedido do enunciado.</t>
+          <t>Transportes que asseguram o tr ansporte de passageiros segundo itinerário, frequência, horário e tarifas predeterminadas e em que podem ser tomados e largados passageiros em paragens previamente estabelecidas — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Uma sociedade por quotas, constituída por um único sócio — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Uma sociedade em que as quotas estão repartidas por uma pessoa singular e …») não corresponde ao pedido do enunciado.</t>
+          <t>Uma sociedade por quotas, constituída por um único sócio — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Sociedades comerciais, cooperativas, empresas públicas e outras entidades que reúnam os requisitos de acesso — é o que melhor responde ao enunciado (opção D)). Por exemplo, B) («Unicamente por sociedades comerciais») não corresponde ao pedido do enunciado.</t>
+          <t>Sociedades comerciais, cooperativas, empresas públicas e outras entidades que reúnam os requisitos de acesso — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Optimizar o funcionamento operacional — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Melhorar a qualidade das paragens») não corresponde ao pedido do enunciado.</t>
+          <t>Optimizar o funcionamento operacional — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>O ângulos mortos são maiores — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A afirmação está certa apenas se se referir à condução nocturna») não corresponde ao pedido do enunciado.</t>
+          <t>O ângulos mortos são maiores — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Danos no veículo acidentado — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Incapacidade parcial definitiva do condutor do veículo») não corresponde ao pedido do enunciado.</t>
+          <t>Danos no veículo acidentado — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>O procedimento adequado é À mesma altura da parte posterior da cabeça do motorista (D)). Por exemplo, B) («Debaixo da nuca do motorista») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é À mesma altura da parte posterior da cabeça do motorista (D)).</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Nem muito largo, nem muito apertado, ajustado ao corpo e bem fechado (C)). Por exemplo, D) («O cinto de segurança não é necessário em veiculos pesados») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Nem muito largo, nem muito apertado, ajustado ao corpo e bem fechado (C)).</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Utilizar o singular e não o plural referindo-se à empresa (C)). Por exemplo, B) («Ter sempre uma atitude respeitosa») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Utilizar o singular e não o plural referindo-se à empresa (C)).</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Trata-se de uma definição: Capacidade de resposta (opção D)).  Por exemplo, B) («Condicionantes da condução») não corresponde ao pedido do enunciado.</t>
+          <t>Trata-se de uma definição: Capacidade de resposta (opção D)).</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Velocidade que permite dominar o veículo perante qualquer obstáculo — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Límite inferior de velocidade permitido para a vía onde se circula») não corresponde ao pedido do enunciado.</t>
+          <t>Velocidade que permite dominar o veículo perante qualquer obstáculo — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Todas as alíneas são verdadeiras (D)). Por exemplo, C) («Facilitar o exame dos documentos relacionados com o transporte») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Todas as alíneas são verdadeiras (D)).</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Durante a condução, os braços do condutor não devem estar ligeiramente flexionados — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Durante a condução, não convém cruzar as mãos quando se gira o volante») não corresponde ao pedido do enunciado.</t>
+          <t>Durante a condução, os braços do condutor não devem estar ligeiramente flexionados — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>O enunciado pede a afirmação errada. C) é a incorreta porque: Deve-se tratar os clientes educadamente, dizendo: “o Senhor”, “a Senhora”, “Obrigado(a)”, “Por favor”. As alternativas A) A apresentação do motorista (higiene pessoal, cuidados com a roupa, etc.) … e B) O olhar amável e o sorriso são dois dos maiores trunfos de que o motorista… são afirmações corretas ou recomendadas.</t>
+          <t>O enunciado pede a afirmação errada. C) é a incorreta porque: Deve-se tratar os clientes educadamente, dizendo: “o Senhor”, “a Senhora”, “Obrigado(a)”, “Por favor”.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Verdadeira, para todos os setores, incluindo o setor de transportes — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Falsa — não existe sanção para a contratação de imigrantes em situação irr…») não corresponde ao pedido do enunciado.</t>
+          <t>Verdadeira, para todos os setores, incluindo o setor de transportes — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Fazer exercício físico (D)). Por exemplo, C) («Consumir exclusivamente alimentos ricos em gordura animal») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Fazer exercício físico (D)).</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Ambiente muito quente no habitáculo do condutor — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Descansar regularmente») não corresponde ao pedido do enunciado.</t>
+          <t>Ambiente muito quente no habitáculo do condutor — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Todas as respostas anteriores estão certas — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Os motoristas profissionais estão expostos a estas lesões») não corresponde ao pedido do enunciado.</t>
+          <t>Todas as respostas anteriores estão certas — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Deve tapá-los com um cobertor, tanto de verão como de inverno para evitar perdas de calor — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Deve evitar cobrir os feridos para não provocar choque térmico») não corresponde ao pedido do enunciado.</t>
+          <t>Deve tapá-los com um cobertor, tanto de verão como de inverno para evitar perdas de calor — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Dar comida aos feridos (A)). Por exemplo, D) («Perguntar como se sentem») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Dar comida aos feridos (A)).</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Produz serviços — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Apenas pode prestar serviços em território internacional») não corresponde ao pedido do enunciado.</t>
+          <t>Produz serviços — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Depois do pavimento estar bem molhado (C)). Por exemplo, D) («A chuva não causa a perda de aderência do pneus») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Depois do pavimento estar bem molhado (C)).</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Desligado e quente, para que o óleo a substituir esteja mais diluído (B)). Por exemplo, D) («Ligado e frio, para o óleo estar mais viscoso») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Desligado e quente, para que o óleo a substituir esteja mais diluído (B)).</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Desligado e frio (C)). Por exemplo, D) («Não importa o motor, o veículo é que deve estar num sítio plano») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Desligado e frio (C)).</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Mercadorias com arestas pontiagudas e pesadas — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Fardos de papel e de algodão») não corresponde ao pedido do enunciado.</t>
+          <t>Mercadorias com arestas pontiagudas e pesadas — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Absorver irregularidades do piso e estabilizar os movimentos — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Diminuir o desgaste dos pneus») não corresponde ao pedido do enunciado.</t>
+          <t>Absorver irregularidades do piso e estabilizar os movimentos — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Um pedal esponjoso na travagem — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Um esforço excessivo na travagem») não corresponde ao pedido do enunciado.</t>
+          <t>Um pedal esponjoso na travagem — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>A quantidade de combustível utilizado para obter uma unidade de potência (kW ou CV) numa unidade de tempo — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O máximo esforço que podemos obter do motor a um determinado número ou fai…») não corresponde ao pedido do enunciado.</t>
+          <t>A quantidade de combustível utilizado para obter uma unidade de potência (kW ou CV) numa unidade de tempo — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>A capacidade de realizar trabalho na unidade de tempo — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Nenhuma das respostas anteriores») não corresponde ao pedido do enunciado.</t>
+          <t>A capacidade de realizar trabalho na unidade de tempo — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Adicionar água destilada (D)). Por exemplo, C) («Adicionar electrólito») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Adicionar água destilada (D)).</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>O valor ou limite legal aplicável é 38 toneladas, indicado em D).  Por exemplo, a opção A) indica valores (26 toneladas) diferentes do aplicável.</t>
+          <t>O valor ou limite legal aplicável é 38 toneladas, indicado em D).</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>O valor ou limite legal aplicável é 85 Kms/hora, indicado em B).  Por exemplo, a opção A) indica valores (50 Kms/hora) diferentes do aplicável.</t>
+          <t>O valor ou limite legal aplicável é 85 Kms/hora, indicado em B).</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -9890,7 +9890,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>O valor ou limite legal aplicável é 32 toneladas, indicado em A).  Por exemplo, a opção B) indica valores (28 toneladas) diferentes do aplicável.</t>
+          <t>O valor ou limite legal aplicável é 32 toneladas, indicado em A).</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Anualmente (C)). Por exemplo, B) («De três em três meses») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Anualmente (C)).</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Cumpre os requisitos de acesso à atividade (idoneidade capacidade profissional e capacidade financeira) (B)). Por exemplo, D) («Não tem dívidas ao fisco nem à Segurança Social») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Cumpre os requisitos de acesso à atividade (idoneidade capacidade profissional e capacidade financeira) (B)).</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Percurso não inferior a 100 kms, veículos da categoria III, número limitado de paragens e assistente de bordo — é o que melhor responde ao enunciado (opção A)). Por exemplo, a opção B) indica valores (Percurso não inferior a 200 kms, sem paragens intermédias e veículos da ca…) diferentes do aplicável.</t>
+          <t>Percurso não inferior a 100 kms, veículos da categoria III, número limitado de paragens e assistente de bordo — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Caduca o alvará para o exercício da atividade — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Caducam as concessões que a empresa seja titular») não corresponde ao pedido do enunciado.</t>
+          <t>Caduca o alvará para o exercício da atividade — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Trata-se de uma definição: Documento descritivo do serviço ou folha de itinerário (opção A)).  Por exemplo, D) («Certificado do serviço») não corresponde ao pedido do enunciado.</t>
+          <t>Trata-se de uma definição: Documento descritivo do serviço ou folha de itinerário (opção A)).</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>O procedimento adequado é No prazo de 30 dias a contar da data da ocorrência (C)). Por exemplo, a opção A) indica valores (No prazo de 20 dias a contar da data da ocorrência) diferentes do aplicável.</t>
+          <t>O procedimento adequado é No prazo de 30 dias a contar da data da ocorrência (C)).</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Por duplicado ou cópia autenticada do último balanço apresentado para efeitos do imposto sob re o rendimento das pessoas coletivas (IRC) ou por garantia bancária — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Pelo extracto da conta bancária de qualquer dos gerentes») não corresponde ao pedido do enunciado.</t>
+          <t>Por duplicado ou cópia autenticada do último balanço apresentado para efeitos do imposto sob re o rendimento das pessoas coletivas (IRC) ou por garantia bancária — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>A caducidade da respetiva licença — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A cessação da exploração da carreira à qual o veículo esteja adstrito») não corresponde ao pedido do enunciado.</t>
+          <t>A caducidade da respetiva licença — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Sociedades comerciais, cooperativas e empresas públicas ou de capitais públicos — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Apenas sociedades em nome colectivo») não corresponde ao pedido do enunciado.</t>
+          <t>Sociedades comerciais, cooperativas e empresas públicas ou de capitais públicos — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Estabelecer um contrato reduzido a escrito com a entidade interessada no serviço (A)). Por exemplo, D) («Preencher previamente uma folha de itinerário») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Estabelecer um contrato reduzido a escrito com a entidade interessada no serviço (A)).</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>O procedimento adequado é No acesso e durante o exercício da atividade (D)). Por exemplo, C) («Somente quando for requerido o acesso à atividade») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é No acesso e durante o exercício da atividade (D)).</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Adquiridos em regime de locação financeira ou outro contrato de locação, ou em regime de propriedade plena. — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Mediante exclusivo financiamento público») não corresponde ao pedido do enunciado.</t>
+          <t>Adquiridos em regime de locação financeira ou outro contrato de locação, ou em regime de propriedade plena. — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -10622,7 +10622,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>O procedimento adequado é A categoria dos passageiros a transportar, itinerário, frequência e paragens (A)). Por exemplo, D) («A origem e destino, número de passageiros e locais da sua tomada e largada») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é A categoria dos passageiros a transportar, itinerário, frequência e paragens (A)).</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Cabotagem — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Transportes combinados») não corresponde ao pedido do enunciado.</t>
+          <t>Cabotagem — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Dístico identificativo do serviço e folha de itinerário (C)). Por exemplo, D) («Cópia do contrato de transporte e cópia certificada de licença comunitária») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Dístico identificativo do serviço e folha de itinerário (C)).</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Com o pedido de acesso à atividade — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Com o pedido de admissão a exame de capacidade profissional») não corresponde ao pedido do enunciado.</t>
+          <t>Com o pedido de acesso à atividade — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>O procedimento adequado é No prazo de trinta dias sob pena de aplicação de uma coima (A)). Por exemplo, D) («No prazo de cinco anos») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é No prazo de trinta dias sob pena de aplicação de uma coima (A)).</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Na medida de interdição do exercício da profissão independentemente da natureza do crime — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Na pena acessória de inibição de conduzir») não corresponde ao pedido do enunciado.</t>
+          <t>Na medida de interdição do exercício da profissão independentemente da natureza do crime — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Serviços regulares especializados — é o que melhor responde ao enunciado (opção D)). Por exemplo, B) («Transportes de cabotagem») não corresponde ao pedido do enunciado.</t>
+          <t>Serviços regulares especializados — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Serviços ocasionais e serviços regulares especializados de âmbito nacional — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Todo o tipo de transportes») não corresponde ao pedido do enunciado.</t>
+          <t>Serviços ocasionais e serviços regulares especializados de âmbito nacional — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Municipais e intermunicipais — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Serviços regulares e serviços expresso») não corresponde ao pedido do enunciado.</t>
+          <t>Municipais e intermunicipais — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>20 kg por passageiro — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (10 kg por passageiro) diferentes do aplicável.</t>
+          <t>20 kg por passageiro — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Caduca o alvará — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («A empresa é obrigada a duplicar o capital social») não corresponde ao pedido do enunciado.</t>
+          <t>Caduca o alvará — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Desde que tenha havido anterior condenação pela prática da mesma infração — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («Desde que não cumpra os requisitos de acesso e exercício da atividade») não corresponde ao pedido do enunciado.</t>
+          <t>Desde que tenha havido anterior condenação pela prática da mesma infração — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Duplicado ou cópia autenticada do último balanço apresentado para efeitos de IRC — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Certificado passado por uma associação de transportadores») não corresponde ao pedido do enunciado.</t>
+          <t>Duplicado ou cópia autenticada do último balanço apresentado para efeitos de IRC — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>O procedimento adequado é A guia de transporte (C)). Por exemplo, A) («O bilhete de identidade /cartão do cidadão») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é A guia de transporte (C)).</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Um transportador celebra com outro transportador um novo contrato baseado nos direitos que lhe advêm de um primeiro contrato — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Não existe a figura do subcontrato») não corresponde ao pedido do enunciado.</t>
+          <t>Um transportador celebra com outro transportador um novo contrato baseado nos direitos que lhe advêm de um primeiro contrato — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Nome ou denominação social, sede e número de alvará — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A identificação do expedidor») não corresponde ao pedido do enunciado.</t>
+          <t>Nome ou denominação social, sede e número de alvará — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -11674,7 +11674,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Estão sujeitos a licenciamento, desde que afetos ao transporte rodoviário de mercadorias por conta de outrem — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Só podem ser licenciados se estiverem afetos à realização de transportes p…») não corresponde ao pedido do enunciado.</t>
+          <t>Estão sujeitos a licenciamento, desde que afetos ao transporte rodoviário de mercadorias por conta de outrem — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Prestação do serviço de transporte com faturação ou recibo em regime de atividade liberal ou existência de contrato para utilização do veículo entre a empresa titular do alvará e um terceiro — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Prestação de serviço de transpor te não acompanhado de fatura, guia de rem…») não corresponde ao pedido do enunciado.</t>
+          <t>Prestação do serviço de transporte com faturação ou recibo em regime de atividade liberal ou existência de contrato para utilização do veículo entre a empresa titular do alvará e um terceiro — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Não é necessário obter qualquer autorização ou licenciamento — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («É suficiente proceder ao licenciamento do veículo») não corresponde ao pedido do enunciado.</t>
+          <t>Não é necessário obter qualquer autorização ou licenciamento — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Quando se trate da recolha de mercadorias destinadas a serem agrupadas no armazém do transportador para posterior distribuição (B)). Por exemplo, D) («Quando o percurso do transporte não for superior a 100 quilómetros») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Quando se trate da recolha de mercadorias destinadas a serem agrupadas no armazém do transportador para posterior distribuição (B)).</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Sancionamento com coima — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Pagamento imediato de coima») não corresponde ao pedido do enunciado.</t>
+          <t>Sancionamento com coima — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -11974,7 +11974,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Caducam todas — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Mantêm-se válidas apenas por um ano») não corresponde ao pedido do enunciado.</t>
+          <t>Caducam todas — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Formular reservas na guia de transporte — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Denunciar os defeitos ao destinatário no ato da entrega») não corresponde ao pedido do enunciado.</t>
+          <t>Formular reservas na guia de transporte — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Forma retangular, inscrição “TP” e indicação do número de alvará do transportador (B)). Por exemplo, A) («Forma retangular, inscrição “TP” e designação da empresa proprietária do v…») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Forma retangular, inscrição “TP” e indicação do número de alvará do transportador (B)).</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Apenas sociedades comerciais — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Qualquer pessoa coletiva ou singular») não corresponde ao pedido do enunciado.</t>
+          <t>Apenas sociedades comerciais — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Tem um prazo de validade não superior a 5 anos, renovável mediante comprovação de que se mantêm os requisitos de acesso e de exercício à atividade — é o que melhor responde ao enunciado (opção A)). Por exemplo, a opção C) indica valores (Tem um prazo de validade de 10 anos, renovável mediante a comprovação de q…) diferentes do aplicável.</t>
+          <t>Tem um prazo de validade não superior a 5 anos, renovável mediante comprovação de que se mantêm os requisitos de acesso e de exercício à atividade — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Por duplicado ou cópia autenticada do último balanço apresentado para efeitos do imposto sobre o rendimento das pessoas colectivas (IRC) ou garantia bancária — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Pelo livro de registo das contas da empresa») não corresponde ao pedido do enunciado.</t>
+          <t>Por duplicado ou cópia autenticada do último balanço apresentado para efeitos do imposto sobre o rendimento das pessoas colectivas (IRC) ou garantia bancária — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Identificação do expedidor, do transportador e do destinatário (C)). Por exemplo, D) («Instruções do expedidor relativamente a procedimentos de manuseamento da m…») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Identificação do expedidor, do transportador e do destinatário (C)).</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Preencher total ou parcialmente a guia de transporte, considerando -se que o faz em nome do expedidor (C)). Por exemplo, D) («Utilizar a guia de um contrato anterior») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Preencher total ou parcialmente a guia de transporte, considerando -se que o faz em nome do expedidor (C)).</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>O procedimento adequado é A guia de transporte (A)). Por exemplo, D) («Os documentos de constituição da empresa») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é A guia de transporte (A)).</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Quando se trate de recolha de mercadorias no armazém do transportador para posterior distribuição — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Nos casos em que haja acordo entre expedidor e destinatário») não corresponde ao pedido do enunciado.</t>
+          <t>Quando se trate de recolha de mercadorias no armazém do transportador para posterior distribuição — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Instituto da Mobilidade e dos Transportes — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Conservatoria do Registo Automovel») não corresponde ao pedido do enunciado.</t>
+          <t>Instituto da Mobilidade e dos Transportes — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Sempre que seja solicitado à empresa (C)). Por exemplo, D) («Apenas de cinco em cinco anos») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Sempre que seja solicitado à empresa (C)).</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>O infrator — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («O Instituto da Mobilidade e dos Transportes») não corresponde ao pedido do enunciado.</t>
+          <t>O infrator — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Não estão abrangidos pelo regime de licenciamento na atividade de transporte rodoviário de mercadorias por conta de outrem — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Só estão sujeitos a licenciame nto obrigatório quando o peso bruto dos veí…») não corresponde ao pedido do enunciado.</t>
+          <t>Não estão abrangidos pelo regime de licenciamento na atividade de transporte rodoviário de mercadorias por conta de outrem — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>O procedimento adequado é € 125 000 (A)). Por exemplo, a opção B) indica valores (€ 50 000) diferentes do aplicável.</t>
+          <t>O procedimento adequado é € 125 000 (A)).</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>€ 254 000 — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (€ 150 000) diferentes do aplicável.</t>
+          <t>€ 254 000 — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -12934,7 +12934,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Sempre que se verificar a caducidade do alvará ou da licença comunitária e no caso de transmissão da propriedade ou posse do veículo — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Quando o veículo completar vinte anos») não corresponde ao pedido do enunciado.</t>
+          <t>Sempre que se verificar a caducidade do alvará ou da licença comunitária e no caso de transmissão da propriedade ou posse do veículo — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Por todos os gerentes, administradores ou diretores da sociedade (D)). Por exemplo, C) («Somente pelos sócios que possuam mais de 30% do capital social») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Por todos os gerentes, administradores ou diretores da sociedade (D)).</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Nos veículos automóveis de mercadorias licenciados para transportes rodoviários de mercadorias por conta de outrem — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Em todo o tipo de veículos, desde que alugados em regime de “aluguer de lo…») não corresponde ao pedido do enunciado.</t>
+          <t>Nos veículos automóveis de mercadorias licenciados para transportes rodoviários de mercadorias por conta de outrem — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Mantendo o veículo dentro das condições e recomendações do fabricante — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Viajando a alta velocidade, de modo a que o tempo de duração da viagem dim…») não corresponde ao pedido do enunciado.</t>
+          <t>Mantendo o veículo dentro das condições e recomendações do fabricante — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>O valor ou limite legal aplicável é 37 toneladas, indicado em B).  Por exemplo, a opção A) indica valores (29 toneladas) diferentes do aplicável.</t>
+          <t>O valor ou limite legal aplicável é 37 toneladas, indicado em B).</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>O valor ou limite legal aplicável é 25% do peso bruto do veículo ou conjunto de veículos, indicado em C).  Por exemplo, a opção A) indica valores (15% do peso bruto do veículo ou conjunto de veículos) diferentes do aplicável.</t>
+          <t>O valor ou limite legal aplicável é 25% do peso bruto do veículo ou conjunto de veículos, indicado em C).</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -13294,7 +13294,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>O valor ou limite legal aplicável é 32 toneladas, indicado em B).  Por exemplo, a opção A) indica valores (38 toneladas) diferentes do aplicável.</t>
+          <t>O valor ou limite legal aplicável é 32 toneladas, indicado em B).</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>O valor ou limite legal aplicável é 32 toneladas, indicado em C).  Por exemplo, a opção A) indica valores (22 toneladas) diferentes do aplicável.</t>
+          <t>O valor ou limite legal aplicável é 32 toneladas, indicado em C).</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>O valor ou limite legal aplicável é 15% do peso bruto total, indicado em A).  Por exemplo, a opção B) indica valores (20% do peso bruto total) diferentes do aplicável.</t>
+          <t>O valor ou limite legal aplicável é 15% do peso bruto total, indicado em A).</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>O valor ou limite legal aplicável é 26 toneladas, indicado em C).  Por exemplo, a opção A) indica valores (18 toneladas) diferentes do aplicável.</t>
+          <t>O valor ou limite legal aplicável é 26 toneladas, indicado em C).</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Verdadeira para todos os veículos pesados — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Falsa porque o peso bruto não está relacionado com o número de eixos») não corresponde ao pedido do enunciado.</t>
+          <t>Verdadeira para todos os veículos pesados — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>O procedimento adequado é A um conjunto de operações regulares, nos termos da manutenção preventiva (A)). Por exemplo, D) («Ao parqueamento dos veículos que apresentem problemas») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é A um conjunto de operações regulares, nos termos da manutenção preventiva (A)).</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Garantir a integridade física dos trabalhadores intervenientes na operação, a segurança rodoviária e evitar avarias nas mercadorias transportadas (D)). Por exemplo, C) («Utilizar os diversos equipamentos existentes no veículo (argolas, ganchos,…») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Garantir a integridade física dos trabalhadores intervenientes na operação, a segurança rodoviária e evitar avarias nas mercadorias transportadas (D)).</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>A carga máxima admissível, determinada pelo peso ou cubicagem máxima admitida — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O espaço entre os lotes da mercadoria a fim de garantir o equilíbrio do ve…») não corresponde ao pedido do enunciado.</t>
+          <t>A carga máxima admissível, determinada pelo peso ou cubicagem máxima admitida — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -13774,7 +13774,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Trata-se de uma definição: Preencher os espaços com madeiras, esferovite, cartão prensado ou outro tipo de materiais que absorvam os choques criados ao longo da viagem (opção A)).  Por exemplo, D) («Voltar a arrumar os volumes, de modo a não deixar espaço entre o topo dos …») não corresponde ao pedido do enunciado.</t>
+          <t>Trata-se de uma definição: Preencher os espaços com madeiras, esferovite, cartão prensado ou outro tipo de materiais que absorvam os choques criados ao longo da viagem (opção A)).</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -13834,7 +13834,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Controlar o seu veículo todos os dias, antes da partida (pneus, luzes, travões, combustível, níveis de óleo, bateria, etc...) (C)). Por exemplo, D) («Verificar todas as semanas a pressão dos pneus») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Controlar o seu veículo todos os dias, antes da partida (pneus, luzes, travões, combustível, níveis de óleo, bateria, etc...) (C)).</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Do expedidor, do transportador e do destinatário (C)). Por exemplo, D) («Apenas do destinatário») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Do expedidor, do transportador e do destinatário (C)).</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>O procedimento adequado é No mês seguinte ao do início do trabalho (C)). Por exemplo, D) («Quando o trabalhador adoecer») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é No mês seguinte ao do início do trabalho (C)).</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Trabalho a termo, certo ou incerto — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Trabalho independente») não corresponde ao pedido do enunciado.</t>
+          <t>Trabalho a termo, certo ou incerto — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -14134,7 +14134,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>A entidade empregadora — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («O próprio trabalhador») não corresponde ao pedido do enunciado.</t>
+          <t>A entidade empregadora — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -14194,7 +14194,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Todo o trabalho efetuado entre as 21 horas de um dia e as 9 horas do dia seguinte — é o que melhor responde ao enunciado (opção D)). Por exemplo, a opção A) indica valores (As 22 horas de um dia e as 7 horas do dia seguinte) diferentes do aplicável.</t>
+          <t>Todo o trabalho efetuado entre as 21 horas de um dia e as 9 horas do dia seguinte — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>25% — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (10%) diferentes do aplicável.</t>
+          <t>25% — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -14314,7 +14314,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Ser um acordo celebrado livremen te entre as partes contratantes, podendo ou não ser reduzido a escrito — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Ser um contrato que pode ser celebrado por pessoa de idade inferior a 16 a…») não corresponde ao pedido do enunciado.</t>
+          <t>Ser um acordo celebrado livremen te entre as partes contratantes, podendo ou não ser reduzido a escrito — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -14374,7 +14374,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Com a celebração do contrato de trabalho — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Após um período de trabalho efetivo a combinar com o empregador») não corresponde ao pedido do enunciado.</t>
+          <t>Com a celebração do contrato de trabalho — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>A uma retribuição igual à que receberia se estivesse a trabalhar, acrescida de um montante igual a essa retribuição — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Ao seu vencimento mensal acrescida de uma gratificação em função do seu de…») não corresponde ao pedido do enunciado.</t>
+          <t>A uma retribuição igual à que receberia se estivesse a trabalhar, acrescida de um montante igual a essa retribuição — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -14494,7 +14494,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Exercer o direito de contratação coletiva em nome dos interesses dos seus associados — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Desenvolver uma qualquer atividade empresarial») não corresponde ao pedido do enunciado.</t>
+          <t>Exercer o direito de contratação coletiva em nome dos interesses dos seus associados — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -14554,7 +14554,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Pela entidade patronal através de guia de pagamento (B)). Por exemplo, D) («Por declaração de rendimentos no final de cada ano civil») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Pela entidade patronal através de guia de pagamento (B)).</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>É controlado através de um livrete individual aprovado pelo organismo responsável pelas condições de trabalho — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Não carece de qualquer controle em virtude do trabalho decorrer fora da em…») não corresponde ao pedido do enunciado.</t>
+          <t>É controlado através de um livrete individual aprovado pelo organismo responsável pelas condições de trabalho — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -14674,7 +14674,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>As férias são interrompidas, desde que o trabalhador participe a doença à entidade patronal — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Os dias de doença são descontados nas férias do ano seguinte») não corresponde ao pedido do enunciado.</t>
+          <t>As férias são interrompidas, desde que o trabalhador participe a doença à entidade patronal — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -14734,7 +14734,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Contrato de trabalho — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Contrato de prestação de serviços») não corresponde ao pedido do enunciado.</t>
+          <t>Contrato de trabalho — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>O termo do prazo — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A falta do trabalhador por mais de três dias consecutivos») não corresponde ao pedido do enunciado.</t>
+          <t>O termo do prazo — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>No caso de ocorrer justa causa — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Se a empresa não pagar as quotas ao seu sindicato») não corresponde ao pedido do enunciado.</t>
+          <t>No caso de ocorrer justa causa — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>O comportamento culposo do trabalh ador que inviabilize  a manutenção da relação de trabalho — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Não existe o conceito de justa causa na legislação laboral nacional») não corresponde ao pedido do enunciado.</t>
+          <t>O comportamento culposo do trabalh ador que inviabilize  a manutenção da relação de trabalho — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>A conversão do contrato em contrato sem termo — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A punição da entidade empregadora através de multa») não corresponde ao pedido do enunciado.</t>
+          <t>A conversão do contrato em contrato sem termo — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -15034,7 +15034,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Pode exercer qualquer outra atividade remunerada se a entidade patronal o autorizar a isso — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Não pode sair do concelho da sede da empresa sem autorização da entidade p…») não corresponde ao pedido do enunciado.</t>
+          <t>Pode exercer qualquer outra atividade remunerada se a entidade patronal o autorizar a isso — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>40 horas — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (36 horas) diferentes do aplicável.</t>
+          <t>40 horas — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Realiza um trabalho autónomo e apresenta o respetivo resultado — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Tem direito ao gozo de férias remuneradas») não corresponde ao pedido do enunciado.</t>
+          <t>Realiza um trabalho autónomo e apresenta o respetivo resultado — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Um conjunto de trabalhadores e um conjunto de entidades patronais, através das respetivas associações sindicais e patronais — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Um trabalhador e uma entidade patronal») não corresponde ao pedido do enunciado.</t>
+          <t>Um conjunto de trabalhadores e um conjunto de entidades patronais, através das respetivas associações sindicais e patronais — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>É considerada falta justificada — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («É considerado trabalho efetivo») não corresponde ao pedido do enunciado.</t>
+          <t>É considerada falta justificada — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>O despedimento for considerado injustificado pelo trabalhador e pelo sindicato — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A ilicitude do despedimento seja declarada por tribunal judicial em ação i…») não corresponde ao pedido do enunciado.</t>
+          <t>O despedimento for considerado injustificado pelo trabalhador e pelo sindicato — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>A realização de transportes nacionais por transportadores não residentes — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («A realização de qualquer transporte desde que o veículo esteja vazio») não corresponde ao pedido do enunciado.</t>
+          <t>A realização de transportes nacionais por transportadores não residentes — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>18 toneladas — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (15 toneladas) diferentes do aplicável.</t>
+          <t>18 toneladas — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -15574,7 +15574,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>O procedimento adequado é 1 ano (D)). Por exemplo, a opção A) indica valores (5 anos) diferentes do aplicável.</t>
+          <t>O procedimento adequado é 1 ano (D)).</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Cuja velocidade máxima autorizada ultrapasse os 40 km/hora — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção C) indica valores (Afetos ao transporte de mercadorias e cujo peso máximo autorizado, incluin…) diferentes do aplicável.</t>
+          <t>Cuja velocidade máxima autorizada ultrapasse os 40 km/hora — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Particular ou por conta própria — é o que melhor responde ao enunciado (opção C)). Por exemplo, A) («Público ou por conta de outrem») não corresponde ao pedido do enunciado.</t>
+          <t>Particular ou por conta própria — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -15754,7 +15754,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Idoneidade, capacidade profissional e capacidade financeira (B)). Por exemplo, D) («Estar obrigatoriamente constituídas como sociedades por quotas») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Idoneidade, capacidade profissional e capacidade financeira (B)).</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>14 dias úteis de férias — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (22 dias úteis de férias) diferentes do aplicável.</t>
+          <t>14 dias úteis de férias — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -15934,7 +15934,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>18 meses — é o que melhor responde ao enunciado (opção D)). Por exemplo, a opção A) indica valores (6 meses) diferentes do aplicável.</t>
+          <t>18 meses — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -15994,7 +15994,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Tiver concluído a escolaridade obrigatória e se tratar de trabalhos leves — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («O contrato for reduzido a escrito») não corresponde ao pedido do enunciado.</t>
+          <t>Tiver concluído a escolaridade obrigatória e se tratar de trabalhos leves — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>90 dias — é o que melhor responde ao enunciado (opção A)). Por exemplo, a opção B) indica valores (180 dias) diferentes do aplicável.</t>
+          <t>90 dias — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Se destinarem ao transporte de determinadas categorias de passageiros, com exclusão de  outros, nomeadamente os estudantes entre o domicílio e a escola — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Assegurarem o transporte de passageiros, quando se revelarem insuficientes…») não corresponde ao pedido do enunciado.</t>
+          <t>Se destinarem ao transporte de determinadas categorias de passageiros, com exclusão de  outros, nomeadamente os estudantes entre o domicílio e a escola — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Estão obrigatoriamente sujeitos à forma escrita — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Só podem ter a forma verbal») não corresponde ao pedido do enunciado.</t>
+          <t>Estão obrigatoriamente sujeitos à forma escrita — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -16294,7 +16294,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Pela entidade patronal, no mês seguinte aquele a que disserem respeito (A)). Por exemplo, B) («Mensalmente, pelo próprio trabalhador») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Pela entidade patronal, no mês seguinte aquele a que disserem respeito (A)).</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -16354,7 +16354,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>É considerada falta justificada — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («É considerado um ilícito») não corresponde ao pedido do enunciado.</t>
+          <t>É considerada falta justificada — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>O tribunal decidir que o despedimento é ilícito — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O trabalhador consentir numa redução da sua remuneração») não corresponde ao pedido do enunciado.</t>
+          <t>O tribunal decidir que o despedimento é ilícito — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Capacidade Profissional — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Admissibilidade de Firma») não corresponde ao pedido do enunciado.</t>
+          <t>Capacidade Profissional — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>2 anos — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (1 ano) diferentes do aplicável.</t>
+          <t>2 anos — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Estar legalmente proibidos do exercício do comércio — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Ter sido condenado por duas infrações ao Código da Estrada») não corresponde ao pedido do enunciado.</t>
+          <t>Estar legalmente proibidos do exercício do comércio — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -16654,7 +16654,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Não está sujeito a licenciamento na atividade de transporte público rodoviário de mercadorias por conta de outrem — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Está sujeito apenas ao licenciamento dos veículos ligeiros») não corresponde ao pedido do enunciado.</t>
+          <t>Não está sujeito a licenciamento na atividade de transporte público rodoviário de mercadorias por conta de outrem — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>O valor ou limite legal aplicável é 15 dias, indicado em B).  Por exemplo, a opção A) indica valores (30 dias) diferentes do aplicável.</t>
+          <t>O valor ou limite legal aplicável é 15 dias, indicado em B).</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Para satisfação de necessidades temporárias da empresa e pelo período estritamente necessário — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Sempre que o prazo seja superior a 5 anos») não corresponde ao pedido do enunciado.</t>
+          <t>Para satisfação de necessidades temporárias da empresa e pelo período estritamente necessário — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -16834,7 +16834,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>O procedimento adequado é 5 dias (A)). Por exemplo, a opção B) indica valores (10 dias) diferentes do aplicável.</t>
+          <t>O procedimento adequado é 5 dias (A)).</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Tem direito a gozar dois dias úteis de férias por cada mês completo de duração do contrato — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Só terá direito a férias se esse direito estiver consignado no contrato») não corresponde ao pedido do enunciado.</t>
+          <t>Tem direito a gozar dois dias úteis de férias por cada mês completo de duração do contrato — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>2 membros — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (5 membros) diferentes do aplicável.</t>
+          <t>2 membros — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -17074,7 +17074,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Entre as 22 horas de um dia e as sete horas do dia seguinte — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (Entre as 0 e as 5 horas) diferentes do aplicável.</t>
+          <t>Entre as 22 horas de um dia e as sete horas do dia seguinte — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>O procedimento adequado é 30 dias por ano (D)). Por exemplo, a opção A) indica valores (20 dias por ano) diferentes do aplicável.</t>
+          <t>O procedimento adequado é 30 dias por ano (D)).</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -17194,7 +17194,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Cinco dias úteis seguidos, obrigatoriamente gozados na primeira semana a seguir ao nascimento do filho — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Quinze dias úteis, só em caso de morte ou incapacidade física da mãe») não corresponde ao pedido do enunciado.</t>
+          <t>Cinco dias úteis seguidos, obrigatoriamente gozados na primeira semana a seguir ao nascimento do filho — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -17254,7 +17254,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Início do período experimental — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Dia acordado pela entidade patronal e trabalhador») não corresponde ao pedido do enunciado.</t>
+          <t>Início do período experimental — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -17314,7 +17314,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Quando se trate de recolha de me rcadoria destinada a ser agrupada no armazém do transportador para posterior distribuição — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Quando não seja possível formular reservas») não corresponde ao pedido do enunciado.</t>
+          <t>Quando se trate de recolha de me rcadoria destinada a ser agrupada no armazém do transportador para posterior distribuição — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Por duplicado ou cópia autenticada do último balanço apresentado para efeitos de IRC — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Pelas atas das reuniões realizadas no ano anterior») não corresponde ao pedido do enunciado.</t>
+          <t>Por duplicado ou cópia autenticada do último balanço apresentado para efeitos de IRC — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -17494,7 +17494,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Cumpre os requisitos de acesso à at ividade (idoneidade, capacidade profissional e capacidade financeira) (B)). Por exemplo, D) («Não tem dívidas ao fisco nem à Segurança Social») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Cumpre os requisitos de acesso à at ividade (idoneidade, capacidade profissional e capacidade financeira) (B)).</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -17554,7 +17554,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>A caducidade da respetiva licença — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A cessação da exploração da carreira à qual o veículo esteja adstrito») não corresponde ao pedido do enunciado.</t>
+          <t>A caducidade da respetiva licença — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -17674,7 +17674,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>O procedimento adequado é A categoria dos passageiros a transportar, itinerário, frequência e paragens (A)). Por exemplo, D) («A origem e destino, número de passageiros e locais da sua tomada e largada») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é A categoria dos passageiros a transportar, itinerário, frequência e paragens (A)).</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -17734,7 +17734,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Cabotagem — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Transportes combinados») não corresponde ao pedido do enunciado.</t>
+          <t>Cabotagem — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Dístico identificativo do serviço e folha de itinerário (C)). Por exemplo, D) («Cópia do contrato de transporte e cópia certificada de licença comunitária») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Dístico identificativo do serviço e folha de itinerário (C)).</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Com o pedido de acesso à atividade — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Com o pedido de admissão a exame de capacidade profissional») não corresponde ao pedido do enunciado.</t>
+          <t>Com o pedido de acesso à atividade — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -17914,7 +17914,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Na medida de interdição do exercício da profissão, independentemente da natureza do crime — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Na pena acessória de inibição de conduzir») não corresponde ao pedido do enunciado.</t>
+          <t>Na medida de interdição do exercício da profissão, independentemente da natureza do crime — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -17974,7 +17974,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Serviços regulares e serviços expresso — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Independentes, concorrentes e afluentes») não corresponde ao pedido do enunciado.</t>
+          <t>Serviços regulares e serviços expresso — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -18094,7 +18094,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>O mais baixo possível — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Qualquer altura, pois não tem interferência no centro de gravidade») não corresponde ao pedido do enunciado.</t>
+          <t>O mais baixo possível — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -18154,7 +18154,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Implica na instabilidade do veículo e diminui a eficácia do seu sistema de travagem — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A carga pode ser colocada em qualquer parte da caixa de carga») não corresponde ao pedido do enunciado.</t>
+          <t>Implica na instabilidade do veículo e diminui a eficácia do seu sistema de travagem — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Suportar o motor, a carroçaria e a caixa de carga do veículo — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Suportar o peso do veículo») não corresponde ao pedido do enunciado.</t>
+          <t>Suportar o motor, a carroçaria e a caixa de carga do veículo — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -18274,7 +18274,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Transformar os gases provenientes do motor em produtos menos poluentes — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Diminuir a temperatura do motor») não corresponde ao pedido do enunciado.</t>
+          <t>Transformar os gases provenientes do motor em produtos menos poluentes — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -18334,7 +18334,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>São muito prejudiciais para meio ambiente e para o ser humano — é o que melhor responde ao enunciado (opção B)). Por exemplo, A) («São absorvidos pela atmosfera sem consequências negativas para o meio ambi…») não corresponde ao pedido do enunciado.</t>
+          <t>São muito prejudiciais para meio ambiente e para o ser humano — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -18394,7 +18394,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>O motor está a poluir mais que o normal, porque está a consumir óleo em excesso — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («O cárter e ou a respetiva junta estão a vedar bem») não corresponde ao pedido do enunciado.</t>
+          <t>O motor está a poluir mais que o normal, porque está a consumir óleo em excesso — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -18454,7 +18454,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Verificar se esta está bem fixa à carroçaria e se o líquido se encontra a cobrir as placas — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Adicionar, se necessário, água destilada até ao enchimento completo da bat…») não corresponde ao pedido do enunciado.</t>
+          <t>Verificar se esta está bem fixa à carroçaria e se o líquido se encontra a cobrir as placas — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Condutor — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Proprietário da viatura») não corresponde ao pedido do enunciado.</t>
+          <t>Condutor — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -18574,7 +18574,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>O valor ou limite legal aplicável é 4 kg sem travar o travão de pé, indicado em B).  Por exemplo, a opção A) indica valores (3 kg sempre que se utilize o travão de pé) diferentes do aplicável.</t>
+          <t>O valor ou limite legal aplicável é 4 kg sem travar o travão de pé, indicado em B).</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Sempre que possível, utilizar com a mudança mais alta engrenada, com o motor no binário máximo (B)). Por exemplo, D) («Nas descidas, desengatar a caixa de velocidades») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Sempre que possível, utilizar com a mudança mais alta engrenada, com o motor no binário máximo (B)).</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -18694,7 +18694,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Verificar se a alavanca da caixa automática se encontra na posição D (D)). Por exemplo, C) («Verificar todas as luzes do veículo») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Verificar se a alavanca da caixa automática se encontra na posição D (D)).</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Gerando um campo magnético com a produção de correntes induzidas que reagindo se opõem ao movimento dos dois discos montados no veio da transmissão — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Através de correntes alternas que provocam um atrito entre os discos e o v…») não corresponde ao pedido do enunciado.</t>
+          <t>Gerando um campo magnético com a produção de correntes induzidas que reagindo se opõem ao movimento dos dois discos montados no veio da transmissão — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -18814,7 +18814,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Obrigatoriamente por ação mecânica — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Por ação dos cabos do travão de mão») não corresponde ao pedido do enunciado.</t>
+          <t>Obrigatoriamente por ação mecânica — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -18874,7 +18874,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Inicia uma longa descida de inclinação acentuada (C)). Por exemplo, B) («Transitando em patamar, efetue uma travagem de emergência») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Inicia uma longa descida de inclinação acentuada (C)).</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -18934,7 +18934,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Fuga na tubagem do circuito hidráulico (B)). Por exemplo, C) («Calços do travão muito gastos») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Fuga na tubagem do circuito hidráulico (B)).</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -18994,7 +18994,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Se o líquido refrigerante está entre os parâmetros recomendados (B)). Por exemplo, D) («O filtro do ar tem impurezas») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Se o líquido refrigerante está entre os parâmetros recomendados (B)).</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>O nível de óleo de lubrificação do motor está muito baixo — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («O nível do líquido de limpeza do pára-brisas está baixo») não corresponde ao pedido do enunciado.</t>
+          <t>O nível de óleo de lubrificação do motor está muito baixo — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -19114,7 +19114,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Não esforçar o motor — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Circular dentro das velocidades recomendadas») não corresponde ao pedido do enunciado.</t>
+          <t>Não esforçar o motor — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -19174,7 +19174,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>4 ciclos — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (2 ciclos) diferentes do aplicável.</t>
+          <t>4 ciclos — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -19234,7 +19234,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Admissão, compressão, explosão/expansão, escape — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Admissão, injecção, ignição, escape») não corresponde ao pedido do enunciado.</t>
+          <t>Admissão, compressão, explosão/expansão, escape — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -19294,7 +19294,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Em caso de falha do sistema, possa ainda existir algum poder de travagem — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Evitar que as rodas bloqueiem») não corresponde ao pedido do enunciado.</t>
+          <t>Em caso de falha do sistema, possa ainda existir algum poder de travagem — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -19354,7 +19354,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Reduzir e utilizar os meios de travagem auxiliar (D)). Por exemplo, C) («Bombear consecutivamente o travão») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Reduzir e utilizar os meios de travagem auxiliar (D)).</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -19414,7 +19414,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Detetar a origem do problema e a atitude a tomar (B)). Por exemplo, D) («Ignorar e evitar declives inclinados») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Detetar a origem do problema e a atitude a tomar (B)).</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Que permite desacoplar o motor do resto da transmissão — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Permite adotar o regime do motor») não corresponde ao pedido do enunciado.</t>
+          <t>Que permite desacoplar o motor do resto da transmissão — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -19594,7 +19594,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Longitudinal e atrás do mesmo — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («Transversalmente ao mesmo») não corresponde ao pedido do enunciado.</t>
+          <t>Longitudinal e atrás do mesmo — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Aumentar a curva de binário do motor — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Definir um modelo da gestão do motor») não corresponde ao pedido do enunciado.</t>
+          <t>Aumentar a curva de binário do motor — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -19714,7 +19714,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Antes do binário máximo — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A partir do encontro das linhas de binário e potência») não corresponde ao pedido do enunciado.</t>
+          <t>Antes do binário máximo — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -19774,7 +19774,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>O uso de velas de ignição — é o que melhor responde ao enunciado (opção D)). Por exemplo, B) («O número de cilindros») não corresponde ao pedido do enunciado.</t>
+          <t>O uso de velas de ignição — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -19834,7 +19834,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Retirar a humidade ao ar — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Manter o ar à temperatura ideal») não corresponde ao pedido do enunciado.</t>
+          <t>Retirar a humidade ao ar — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Sempre que possível, andar com a mudança mais alta engrenada e com o motor no binário máximo — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Esticando o motor logo no início da marcha») não corresponde ao pedido do enunciado.</t>
+          <t>Sempre que possível, andar com a mudança mais alta engrenada e com o motor no binário máximo — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Aumentar o controlo e a eficiência de travagem durante as descidas — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Estabilizar o veículo em situações de condução perigosa») não corresponde ao pedido do enunciado.</t>
+          <t>Aumentar o controlo e a eficiência de travagem durante as descidas — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -20074,7 +20074,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Tirar antecipadamente o pé do acelerador (B)). Por exemplo, D) («Acelerar o veículo de forma agressiva») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Tirar antecipadamente o pé do acelerador (B)).</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Obrigatoriamente por acção mecânica — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Por acção dos cabos do travão de mão») não corresponde ao pedido do enunciado.</t>
+          <t>Obrigatoriamente por acção mecânica — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -20194,7 +20194,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Fuga na tubagem do circuito hidráulico (B)). Por exemplo, C) («Calços do travão muito gastos») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Fuga na tubagem do circuito hidráulico (B)).</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -20254,7 +20254,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Evitar o bloqueio das rodas — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Permitir uma melhor repartição da travagem») não corresponde ao pedido do enunciado.</t>
+          <t>Evitar o bloqueio das rodas — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Radiador, válvula termostática, bomba de água, canais de refrigeração no interior do bloco de cilindros e canais de refrigeração na cabeça do motor — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Apenas por ventoinha, termóstato e alhetas do motor») não corresponde ao pedido do enunciado.</t>
+          <t>Radiador, válvula termostática, bomba de água, canais de refrigeração no interior do bloco de cilindros e canais de refrigeração na cabeça do motor — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -20434,7 +20434,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Ar — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Ar e gás de petróleo liquefeito») não corresponde ao pedido do enunciado.</t>
+          <t>Ar — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -20494,7 +20494,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Ao binário máximo do motor — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («À rotação em que quer o binário quer a potência são máximos») não corresponde ao pedido do enunciado.</t>
+          <t>Ao binário máximo do motor — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -20554,7 +20554,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Bomba injectora, common rail ou injector-bomba — é o que melhor responde ao enunciado (opção B)). Por exemplo, A) («Carburador e sistema injector-bomba») não corresponde ao pedido do enunciado.</t>
+          <t>Bomba injectora, common rail ou injector-bomba — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -20614,7 +20614,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Escape e tem por função a reutilização dos gases de escape para compress ão do ar de admissão — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Distribuição dos gases de escape») não corresponde ao pedido do enunciado.</t>
+          <t>Escape e tem por função a reutilização dos gases de escape para compress ão do ar de admissão — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -20674,7 +20674,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Depende do valor binário e da rotação a que o motor está a trabalhar — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Depende apenas do binário») não corresponde ao pedido do enunciado.</t>
+          <t>Depende do valor binário e da rotação a que o motor está a trabalhar — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Da rotação do motor e da velocidade do veículo e da posição do acelerador — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Apenas da posição do acelerador») não corresponde ao pedido do enunciado.</t>
+          <t>Da rotação do motor e da velocidade do veículo e da posição do acelerador — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -20794,7 +20794,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Monitorizar a rotação de cada roda, a inclinação do veículo e a aceleração, atuando em conformidade a fim de estabilizar o veículo em situações de instabilidade — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Limitar o escorregamento em caso de travagem brusca») não corresponde ao pedido do enunciado.</t>
+          <t>Monitorizar a rotação de cada roda, a inclinação do veículo e a aceleração, atuando em conformidade a fim de estabilizar o veículo em situações de instabilidade — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -20854,7 +20854,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Circular com uma mudança baixa de modo a utilizar o motor como travão (C)). Por exemplo, D) («Circular com o pé sempre em cima do pedal de travão») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Circular com uma mudança baixa de modo a utilizar o motor como travão (C)).</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -20974,7 +20974,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>A responsabilidade social de uma empresa de transportes incide sobre os seus clientes, e não sobre os seus trabalhadores — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Uma boa comunicação, a cortesia, prontidão e a competência são alguns dos …») não corresponde ao pedido do enunciado.</t>
+          <t>A responsabilidade social de uma empresa de transportes incide sobre os seus clientes, e não sobre os seus trabalhadores — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>A atividade transitária só pode ser exercida por empresas titulares de alvará emitido pelo IMT — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («As empresas que realizam transporte rodoviário de mercadorias perigosas ca…») não corresponde ao pedido do enunciado.</t>
+          <t>A atividade transitária só pode ser exercida por empresas titulares de alvará emitido pelo IMT — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Matriculados, que não se encontrem avariados ou sinistrados, nem se destinem a substituir veículos sinistrados ou avariados — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Que se destinem a exposições ou manifestações desportivas») não corresponde ao pedido do enunciado.</t>
+          <t>Matriculados, que não se encontrem avariados ou sinistrados, nem se destinem a substituir veículos sinistrados ou avariados — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>No transporte multimodal há um único documento cont ratual para todo o transporte qualquer que seja o número de modos envolvidos, enquanto no intermodal podem existir vários documentos contratuais mas o transporte é realizado sem rutura de carga — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («No transporte intermodal só participam dois modos de transport e enquanto …») não corresponde ao pedido do enunciado.</t>
+          <t>No transporte multimodal há um único documento cont ratual para todo o transporte qualquer que seja o número de modos envolvidos, enquanto no intermodal podem existir vários documentos contratuais mas o transporte é realizado sem rutura de carga — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Isotérmico, com uma fonte de frio, que permite regular a temperatura até -20º C — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção A) indica valores (Isotérmico, com um mecanismo capaz de produzir frio, reduzindo assim a tem…) diferentes do aplicável.</t>
+          <t>Isotérmico, com uma fonte de frio, que permite regular a temperatura até -20º C — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -21386,7 +21386,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Alvará, emitido pelo IMTT — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Não carece de qualquer alvará») não corresponde ao pedido do enunciado.</t>
+          <t>Alvará, emitido pelo IMTT — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>A poluição atmosférica, os acidentes, os riscos de alterações climatéricas, o ruído e os custos para a natureza e para a paisagem — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Apenas a poluição atmosférica») não corresponde ao pedido do enunciado.</t>
+          <t>A poluição atmosférica, os acidentes, os riscos de alterações climatéricas, o ruído e os custos para a natureza e para a paisagem — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -21506,7 +21506,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Maior rapidez (porta-a-porta) — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Maior competitividade para produtos com baixo custo de tonelada por quilóm…») não corresponde ao pedido do enunciado.</t>
+          <t>Maior rapidez (porta-a-porta) — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -21566,7 +21566,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Necessidade de transbordo para chegar junto do cliente final — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Custos bastante elevados em relação aos outros meios de transporte») não corresponde ao pedido do enunciado.</t>
+          <t>Necessidade de transbordo para chegar junto do cliente final — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Ideal para o envio de mercadorias com pouco peso e volume — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Maior capacidade de carga») não corresponde ao pedido do enunciado.</t>
+          <t>Ideal para o envio de mercadorias com pouco peso e volume — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Prazos e entregas atempadas — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Custos administrativos») não corresponde ao pedido do enunciado.</t>
+          <t>Prazos e entregas atempadas — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -21806,7 +21806,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>O retorno das embalagens vazias, produtos danificados ou obsoletos para recuperação ou reciclagem. — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A chegada da carga ao cliente») não corresponde ao pedido do enunciado.</t>
+          <t>O retorno das embalagens vazias, produtos danificados ou obsoletos para recuperação ou reciclagem. — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -21866,7 +21866,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Redução imediata da necessidade de stock — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Aumento dos tempos de produção») não corresponde ao pedido do enunciado.</t>
+          <t>Redução imediata da necessidade de stock — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -22106,7 +22106,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Grande flexibilidade de carga e de destinos — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Elevados custos de terminal») não corresponde ao pedido do enunciado.</t>
+          <t>Grande flexibilidade de carga e de destinos — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -22166,7 +22166,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>A cada indivíduo o equilíbrio entre as exigências da tarefa e suas capacidades individuais — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Apenas o aumento da produtividade») não corresponde ao pedido do enunciado.</t>
+          <t>A cada indivíduo o equilíbrio entre as exigências da tarefa e suas capacidades individuais — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Sempre que o foco de desvio da atenção é interno — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Quando o foco de desvio da atenção é externo, sendo que o indivíduo está a…») não corresponde ao pedido do enunciado.</t>
+          <t>Sempre que o foco de desvio da atenção é interno — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -22346,7 +22346,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Zonas não urbanas — é o que melhor responde ao enunciado (opção A)). Por exemplo, B) («Vias com perfil sinuoso») não corresponde ao pedido do enunciado.</t>
+          <t>Zonas não urbanas — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -22406,7 +22406,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>O stress, a postura sentada prolongada, a manipulação de cargas e o ruído — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Apenas o stress e o ruído») não corresponde ao pedido do enunciado.</t>
+          <t>O stress, a postura sentada prolongada, a manipulação de cargas e o ruído — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -22466,7 +22466,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Negativamente, uma vez que aumenta o tempo de reacção — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Positivamente, uma vez que diminui o tempo de reacção e permite uma melhor…») não corresponde ao pedido do enunciado.</t>
+          <t>Negativamente, uma vez que aumenta o tempo de reacção — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -22586,7 +22586,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>O procedimento adequado é A afirmação é correta pois drogas e determinados medicamentos como os relaxantes interferem na condução (C)). Por exemplo, D) («A afirmação é correcta apenas relativamente a certos medicamentos») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é A afirmação é correta pois drogas e determinados medicamentos como os relaxantes interferem na condução (C)).</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -22646,7 +22646,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Um efeito semelhante ao consumo de bebidas alcoólicas — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Um efeito negativo sobre o tempo de reação, mas que é ultrapassado se o co…») não corresponde ao pedido do enunciado.</t>
+          <t>Um efeito semelhante ao consumo de bebidas alcoólicas — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -22706,7 +22706,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Três tipos de atividades: perceptiva, cognitiva e motora — é o que melhor responde ao enunciado (opção C)). Por exemplo, A) («Uma atividade cognitiva») não corresponde ao pedido do enunciado.</t>
+          <t>Três tipos de atividades: perceptiva, cognitiva e motora — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -22766,7 +22766,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Com o veículo parado (A)). Por exemplo, D) («É indiferente uma vez que a realização desta tarefa não interfere com a ac…») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Com o veículo parado (A)).</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>São da responsabilidade da entidade patronal, devendo os próprios motoristas gerir a sua saúde, adoptando comportamentos em prol de uma vida saudável — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («São da responsabilidade do Sistema Nacional de Saúde») não corresponde ao pedido do enunciado.</t>
+          <t>São da responsabilidade da entidade patronal, devendo os próprios motoristas gerir a sua saúde, adoptando comportamentos em prol de uma vida saudável — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -23066,7 +23066,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>De comportamentos habituais, cometidos regularmente e que se torna m práticas automáticas e frequentemente toleradas — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Apenas de distrações do condutor») não corresponde ao pedido do enunciado.</t>
+          <t>De comportamentos habituais, cometidos regularmente e que se torna m práticas automáticas e frequentemente toleradas — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -23126,7 +23126,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Riscos psicossociais, riscos biológicos, riscos físicos ambientais, riscos biológicos e riscos derivados da manutenção da postura sentada — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Apenas o risco associado à sinistralidade rodoviária») não corresponde ao pedido do enunciado.</t>
+          <t>Riscos psicossociais, riscos biológicos, riscos físicos ambientais, riscos biológicos e riscos derivados da manutenção da postura sentada — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -23186,7 +23186,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Interferem com a segurança da condução — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Interferem com a tarefa da condução apenas se forem ingeridas bebidas alco…») não corresponde ao pedido do enunciado.</t>
+          <t>Interferem com a segurança da condução — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -23246,7 +23246,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>Não, qualquer que seja a quantidade ingerida tem efeito negativo na condução — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Sim, pois o meu metabolismo elimina rapidamente o álcool») não corresponde ao pedido do enunciado.</t>
+          <t>Não, qualquer que seja a quantidade ingerida tem efeito negativo na condução — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -23306,7 +23306,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Dormir, nem que seja por um pequeno período de tempo (C)). Por exemplo, D) («Ligar o rádio e ouvir música») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Dormir, nem que seja por um pequeno período de tempo (C)).</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Todas as situações anteriores — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Sentir falhas de memória») não corresponde ao pedido do enunciado.</t>
+          <t>Todas as situações anteriores — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -23426,7 +23426,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Refeições substanciais para não ter que conduzir de “barriga vazia” — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Conduzir utilizando o “cruise control”») não corresponde ao pedido do enunciado.</t>
+          <t>Refeições substanciais para não ter que conduzir de “barriga vazia” — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -23486,7 +23486,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Dificultar de avaliação das distâncias — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Facilitar a adaptação da visão às mudanças de luminosidade») não corresponde ao pedido do enunciado.</t>
+          <t>Dificultar de avaliação das distâncias — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -23606,7 +23606,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Todas as respostas anteriores estão corretas — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Sensação de reagir com mais lentidão») não corresponde ao pedido do enunciado.</t>
+          <t>Todas as respostas anteriores estão corretas — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -23666,7 +23666,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>7 Grupos de Alimentos — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (5 Grupos de Alimentos) diferentes do aplicável.</t>
+          <t>7 Grupos de Alimentos — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -23726,7 +23726,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>O grupo que deve ser consumido em maior quantidade diária é o dos cereais, derivados e tubérculos — é o que melhor responde ao enunciado (opção A)). Por exemplo, B) («O álcool aparece no seu centro») não corresponde ao pedido do enunciado.</t>
+          <t>O grupo que deve ser consumido em maior quantidade diária é o dos cereais, derivados e tubérculos — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -23786,7 +23786,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>Consumir alimentos com muita gordura regularmente — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Reduzir o consumo de sal») não corresponde ao pedido do enunciado.</t>
+          <t>Consumir alimentos com muita gordura regularmente — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -23846,7 +23846,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>Alcoolemia acima de 0,5 g/l é frequentemente mortal — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (Alcoolemia entre 0,5 e 0,8 g/l provoca alterações graves, como diminuição …) diferentes do aplicável.</t>
+          <t>Alcoolemia acima de 0,5 g/l é frequentemente mortal — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -23906,7 +23906,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Aumento do tempo de reação — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Aumento da capacidade de percepção das velocidades e distâncias») não corresponde ao pedido do enunciado.</t>
+          <t>Aumento do tempo de reação — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Igual ou superior a 0,5 g/l — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (Igual ou superior a 0,3 g/l) diferentes do aplicável.</t>
+          <t>Igual ou superior a 0,5 g/l — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -24086,7 +24086,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Técnicas para a prevenção de ac identes de trabalho, quer eliminando condições inseguras do ambiente, quer educando para a prática de atitudes preventivas — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Medidas de atuação técnica sobre o ambiente de trabalho com o fim de lutar…») não corresponde ao pedido do enunciado.</t>
+          <t>Técnicas para a prevenção de ac identes de trabalho, quer eliminando condições inseguras do ambiente, quer educando para a prática de atitudes preventivas — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -24146,7 +24146,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Triangular, pictograma negro, sobre fundo amarelo e margem negra — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Retangular ou quadrada, pictograma branco sobre fundo verde») não corresponde ao pedido do enunciado.</t>
+          <t>Triangular, pictograma negro, sobre fundo amarelo e margem negra — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -24206,7 +24206,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>Contraída por um trabalhador em razão especificamente do seu exercício profissional — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Resultante de um acontecimento imprevisto») não corresponde ao pedido do enunciado.</t>
+          <t>Contraída por um trabalhador em razão especificamente do seu exercício profissional — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -24266,7 +24266,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>As interações entre os seres humanos e os outros elementos de um sistema como intuito de otimizar o sistema homem – trabalho — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («As reações do condutor sob o efeito do álcool A utilização do telemóvel ao…») não corresponde ao pedido do enunciado.</t>
+          <t>As interações entre os seres humanos e os outros elementos de um sistema como intuito de otimizar o sistema homem – trabalho — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Parar 10 a 15 minutos de todas as 2 ou 3 horas de condução, ou então após 150 km — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Manter os vidros fechados por causa do ruído exterior») não corresponde ao pedido do enunciado.</t>
+          <t>Parar 10 a 15 minutos de todas as 2 ou 3 horas de condução, ou então após 150 km — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -24446,7 +24446,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Pressões de tempo relacionadas com horário de trabalho ou prazos de entrega de mercadorias — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Condução sob boas condições meteorológicas») não corresponde ao pedido do enunciado.</t>
+          <t>Pressões de tempo relacionadas com horário de trabalho ou prazos de entrega de mercadorias — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -24506,7 +24506,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Alargar a base de sustentação, colocar o objeto o mais próximo possível  do corpo e flectir os joelhos — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Colocar o objeto afastado do corpo, e fletir os joelhos ao levantá-lo») não corresponde ao pedido do enunciado.</t>
+          <t>Alargar a base de sustentação, colocar o objeto o mais próximo possível  do corpo e flectir os joelhos — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -24566,7 +24566,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Manter as costas o mais vertical possível fletindo as pernas (B)). Por exemplo, C) («Manter a carga na vertical afastada do corpo») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Manter as costas o mais vertical possível fletindo as pernas (B)).</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -24626,7 +24626,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Na posição sentada, a postura, ligeiramente inclinada para frente, é mais natural e menos fatigante que a ereta. O assento deve permitir mudanças frequente s de postura, para retardar o aparecimento da fadiga — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O banco deve estar o mais reclinado para trás possível para que se possa c…») não corresponde ao pedido do enunciado.</t>
+          <t>Na posição sentada, a postura, ligeiramente inclinada para frente, é mais natural e menos fatigante que a ereta. O assento deve permitir mudanças frequente s de postura, para retardar o aparecimento da fadiga — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -24686,7 +24686,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>A perda de controlo do veículo, em curva, é, quase sempre, originada por inabilidade do condutor ou por velocidade excessiva para as condições do veículo e da via — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A fadiga passiva no decorrer da condução não tem influência no tempo de re…») não corresponde ao pedido do enunciado.</t>
+          <t>A perda de controlo do veículo, em curva, é, quase sempre, originada por inabilidade do condutor ou por velocidade excessiva para as condições do veículo e da via — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -24746,7 +24746,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Uma alimentação saudável e equilibrada é fundamental na prevenção de certas doenças (obesidade, doenças cardiovasculares, diabetes, certos tipo de cancro) — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Mesmo no decorrer do horário de trabal ho recomenda -se a ingestão de álco…») não corresponde ao pedido do enunciado.</t>
+          <t>Uma alimentação saudável e equilibrada é fundamental na prevenção de certas doenças (obesidade, doenças cardiovasculares, diabetes, certos tipo de cancro) — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -24806,7 +24806,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Radiações Ópticas (Infra-vermelho, Visível e Ultra Violetas) — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Somente, as Ultra Violetas») não corresponde ao pedido do enunciado.</t>
+          <t>Radiações Ópticas (Infra-vermelho, Visível e Ultra Violetas) — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -24866,7 +24866,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Todas as respostas anteriores estão corretas (D)). Por exemplo, C) («Estar posicionado de acordo com o volante, os painéis, pedais e pára-brisas») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Todas as respostas anteriores estão corretas (D)).</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -24926,7 +24926,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Promover uma convivência pacífica e harmoniosa entre condutores e peões — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («O stress não pode ser minimizado») não corresponde ao pedido do enunciado.</t>
+          <t>Promover uma convivência pacífica e harmoniosa entre condutores e peões — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -24986,7 +24986,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Implica sempre não comer determinados alimentos — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Pode ser constituída apenas por cereais») não corresponde ao pedido do enunciado.</t>
+          <t>Implica sempre não comer determinados alimentos — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -25046,7 +25046,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Provoca redução efetiva das capacidades necessárias para conduzir — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Não é causa de acidentes») não corresponde ao pedido do enunciado.</t>
+          <t>Provoca redução efetiva das capacidades necessárias para conduzir — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -25106,7 +25106,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Tem influência na condução, e por isso deve ser regulado por um médico — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («É necessário para que se conduza em segurança») não corresponde ao pedido do enunciado.</t>
+          <t>Tem influência na condução, e por isso deve ser regulado por um médico — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -25166,7 +25166,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Todas as respostas anteriores estão correctas — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Poderá ficar com as suas capacidades de condução afectadas») não corresponde ao pedido do enunciado.</t>
+          <t>Todas as respostas anteriores estão correctas — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -25226,7 +25226,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Devem estar colocados de forma a minimizar os impactos na condução — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Se for um telemóvel, a utilização do auricular é suficiente para evitar ac…») não corresponde ao pedido do enunciado.</t>
+          <t>Devem estar colocados de forma a minimizar os impactos na condução — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -25286,7 +25286,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Tem impacto na prestação de um serviço de qualidade — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («É a única área relevante na formação dos motoristas») não corresponde ao pedido do enunciado.</t>
+          <t>Tem impacto na prestação de um serviço de qualidade — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -25346,7 +25346,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Parar o motor sempre que a demora se preveja ser superior a 1 minuto (C)). Por exemplo, D) («Não parar o motor para carregar a bateria») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Parar o motor sempre que a demora se preveja ser superior a 1 minuto (C)).</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -25406,7 +25406,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>No regime de rotações económicas do motor — é o que melhor responde ao enunciado (opção C)). Por exemplo, A) («Sempre com velocidade máxima») não corresponde ao pedido do enunciado.</t>
+          <t>No regime de rotações económicas do motor — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -25466,7 +25466,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Ao binário máximo do motor — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («À potência máxima que o motor pode atingir») não corresponde ao pedido do enunciado.</t>
+          <t>Ao binário máximo do motor — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -25526,7 +25526,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Aproveitar a força da inércia nas descidas — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Aproveitar as descidas para desengatar o veículo») não corresponde ao pedido do enunciado.</t>
+          <t>Aproveitar a força da inércia nas descidas — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -25586,7 +25586,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Todas as afirmações anteriores — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Proporcionar um maior conforto na tarefa da condução») não corresponde ao pedido do enunciado.</t>
+          <t>Todas as afirmações anteriores — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -25646,7 +25646,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Todas as causas referidas nas alíneas anteriores “A escolha correcta dos pneus do veículo e a respetiva manutenção, influenciam o consumo de — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Altas rotações na engrenagem das velocidades») não corresponde ao pedido do enunciado.</t>
+          <t>Todas as causas referidas nas alíneas anteriores “A escolha correcta dos pneus do veículo e a respetiva manutenção, influenciam o consumo de — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -25706,7 +25706,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>Sim é importante, pois os dois fatores influenciam os consumos — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («As condições da via são as únicas responsáveis no consumo exagerado de com…») não corresponde ao pedido do enunciado.</t>
+          <t>Sim é importante, pois os dois fatores influenciam os consumos — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -25766,7 +25766,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>A um menor consumo de combustível — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («A um regime máximo de rotações do motor e a um volume médio da potência») não corresponde ao pedido do enunciado.</t>
+          <t>A um menor consumo de combustível — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -25886,7 +25886,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>Conduzir com os vidros abertos, quando se circula a maiores velocidades — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Manter a pressão de pneus uniforme e nos valores recomendados») não corresponde ao pedido do enunciado.</t>
+          <t>Conduzir com os vidros abertos, quando se circula a maiores velocidades — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -25946,7 +25946,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>As emissões do veículo, diminuir a eficiência do motor e aumentar o consumo de combustível — é o que melhor responde ao enunciado (opção C)). Por exemplo, A) («Somente as emissões do veículo automóvel») não corresponde ao pedido do enunciado.</t>
+          <t>As emissões do veículo, diminuir a eficiência do motor e aumentar o consumo de combustível — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -26006,7 +26006,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>O procedimento adequado é 65% do seu curso (A)). Por exemplo, a opção B) indica valores (75% do seu curso) diferentes do aplicável.</t>
+          <t>O procedimento adequado é 65% do seu curso (A)).</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -26066,7 +26066,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Desacelerar, prevendo o aparecimento de peões (B)). Por exemplo, D) («Só tirar o pé do acelerador») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Desacelerar, prevendo o aparecimento de peões (B)).</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -26126,7 +26126,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Conduzir sempre com baixa velocidade (A)). Por exemplo, D) («Respeitar rigorosamente a sinalização existente») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Conduzir sempre com baixa velocidade (A)).</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -26186,7 +26186,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Qualquer uma das respostas anteriores está correta — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Verificar se este se encontra devidamente regulado») não corresponde ao pedido do enunciado.</t>
+          <t>Qualquer uma das respostas anteriores está correta — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>A afirmação é verdadeira — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («A afirmação é falsa, porque a maior causa de acidentes é a degradação dos …») não corresponde ao pedido do enunciado.</t>
+          <t>A afirmação é verdadeira — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -26306,7 +26306,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>A afirmação é verdadeira — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A afirmação é falsa, porque nem o descanso correto nem a alimentação equil…») não corresponde ao pedido do enunciado.</t>
+          <t>A afirmação é verdadeira — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -26366,7 +26366,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>O coeficiente de atrito no eixo dianteiro é menor que no eixo traseiro — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O veículo entra em derrapagem») não corresponde ao pedido do enunciado.</t>
+          <t>O coeficiente de atrito no eixo dianteiro é menor que no eixo traseiro — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -26426,7 +26426,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Ligar as luzes de cruzamento — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Ligar os quatro piscas em simultâneo») não corresponde ao pedido do enunciado.</t>
+          <t>Ligar as luzes de cruzamento — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -26486,7 +26486,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>O procedimento adequado é No máximo do binário (A)). Por exemplo, D) («No mínimo das rotações») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é No máximo do binário (A)).</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -26546,7 +26546,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Não, o sistema de travagem dos veículos pesados corresponde a uma forma de segurança ativa, enquanto que o capacete de proteção corresponde a uma medida de segurança passiva — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Sim, ambos são medidas de segurança passiva») não corresponde ao pedido do enunciado.</t>
+          <t>Não, o sistema de travagem dos veículos pesados corresponde a uma forma de segurança ativa, enquanto que o capacete de proteção corresponde a uma medida de segurança passiva — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -26606,7 +26606,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Cerca de 1 segundos — é o que melhor responde ao enunciado (opção A)). Por exemplo, a opção B) indica valores (Cerca de 2 ou 3 segundos) diferentes do aplicável.</t>
+          <t>Cerca de 1 segundos — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -26786,7 +26786,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>4 Vezes mais — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (2 Vezes mais) diferentes do aplicável.</t>
+          <t>4 Vezes mais — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -26846,7 +26846,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Abdicar da prioridade para evitar o acidente — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Não exceder dentro das localidades a velocidade de 50km/h») não corresponde ao pedido do enunciado.</t>
+          <t>Abdicar da prioridade para evitar o acidente — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -26966,7 +26966,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>A velocidade — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («O pavimento escorregadio “A distribuição do peso na caixa de carga influen…») não corresponde ao pedido do enunciado.</t>
+          <t>A velocidade — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Adapta a marcha do veículo às condições do tráfego — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Desrespeita as leis do trânsito») não corresponde ao pedido do enunciado.</t>
+          <t>Adapta a marcha do veículo às condições do tráfego — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -27086,7 +27086,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>Antecipar as situações de trânsito, guardando a distância de segurança, de modo a evitar as acelerações e as travagens bruscas — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Acelerar com o motor frio») não corresponde ao pedido do enunciado.</t>
+          <t>Antecipar as situações de trânsito, guardando a distância de segurança, de modo a evitar as acelerações e as travagens bruscas — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -27146,7 +27146,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Ajustar, ao máximo, a velocidade à circulação viária existente no momento (A)). Por exemplo, D) («Circular de forma a ultrapassar pela esquerda e pela direita») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Ajustar, ao máximo, a velocidade à circulação viária existente no momento (A)).</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Deixar o motor ao ralenti (D)). Por exemplo, C) («Acelerar sem ultrapassar o regime de binário») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Deixar o motor ao ralenti (D)).</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -27326,7 +27326,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Utilização da inércia do veículo o que i rá traduzir-se numa menor necessidade de usar o acelerador, logo, menores consumos — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Condução a alta velocidade se as condições de trânsito o permitir») não corresponde ao pedido do enunciado.</t>
+          <t>Utilização da inércia do veículo o que i rá traduzir-se numa menor necessidade de usar o acelerador, logo, menores consumos — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -27386,7 +27386,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Em subida, selecione a relação da caixa de velocidades que permite subir conservando um regime de motor entre 1300 e 1400 rpm; — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Em descida aumente a velocidade mantendo a rotação do motor para além da z…») não corresponde ao pedido do enunciado.</t>
+          <t>Em subida, selecione a relação da caixa de velocidades que permite subir conservando um regime de motor entre 1300 e 1400 rpm; — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -27446,7 +27446,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Determinar a massa de carga máxima que pode ser carregada no veículo, ao longo da plataforma — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Determinar as forças de aceleração exercidas pela carga») não corresponde ao pedido do enunciado.</t>
+          <t>Determinar a massa de carga máxima que pode ser carregada no veículo, ao longo da plataforma — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -27506,7 +27506,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>Amarração de topo — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Amarração directa de máquinas de estaleiro») não corresponde ao pedido do enunciado.</t>
+          <t>Amarração de topo — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -27566,7 +27566,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Trata-se de uma definição: Num sistema de fixação em que as amarrações são posicionadas por cima da parte superior das mercadorias e fixas a dois pontos de amarração do veículo (opostos) (opção D)).  Por exemplo, C) («Na amarração direta entre os olhais de amarração da carga e os pontos de a…») não corresponde ao pedido do enunciado.</t>
+          <t>Trata-se de uma definição: Num sistema de fixação em que as amarrações são posicionadas por cima da parte superior das mercadorias e fixas a dois pontos de amarração do veículo (opostos) (opção D)).</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -27626,7 +27626,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Desacelerar prevendo o aparecimento de peões (B)). Por exemplo, D) («Só tirar o pé do acelerador») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Desacelerar prevendo o aparecimento de peões (B)).</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -27686,7 +27686,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>Fadiga e sonolência — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Respeito pelos utentes da via») não corresponde ao pedido do enunciado.</t>
+          <t>Fadiga e sonolência — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -27746,7 +27746,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Aumentar a distância de segurança em relação ao veículo da frente (D)). Por exemplo, C) («Aumentar a distância de paragem») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Aumentar a distância de segurança em relação ao veículo da frente (D)).</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -27866,7 +27866,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>Reduzir a velocidade — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Entrar na logo rotunda pois, enquanto veículo pesado, temos sempre priorid…») não corresponde ao pedido do enunciado.</t>
+          <t>Reduzir a velocidade — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -27986,7 +27986,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>O conjunto do peso da tara e da carga que o veículo pode transportar — é o que melhor responde ao enunciado (opção A)). Por exemplo, B) («O peso do veículo vazio») não corresponde ao pedido do enunciado.</t>
+          <t>O conjunto do peso da tara e da carga que o veículo pode transportar — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -28046,7 +28046,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>O valor ou limite legal aplicável é 29 toneladas, indicado em A).  Por exemplo, a opção B) indica valores (32 toneladas) diferentes do aplicável.</t>
+          <t>O valor ou limite legal aplicável é 29 toneladas, indicado em A).</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -28106,7 +28106,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>De topo, em laço, com lançantes, envolvente e directa — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («De topo, de base, directa e indirecta») não corresponde ao pedido do enunciado.</t>
+          <t>De topo, em laço, com lançantes, envolvente e directa — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -28166,7 +28166,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Proteção de cargas que soltem grãos ou poeiras (C)). Por exemplo, D) («Criação de bolsas de ar») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Proteção de cargas que soltem grãos ou poeiras (C)).</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -28226,7 +28226,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>O trator deve iniciar o processo de travagem primeiro que o reboque e / ou semi-reboque. — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («É mais seguro ser só o veículo trator a proceder à travagem.») não corresponde ao pedido do enunciado.</t>
+          <t>O trator deve iniciar o processo de travagem primeiro que o reboque e / ou semi-reboque. — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Força que se opõe à deslocação do veículo, tendo este que a vencer para se deslocar — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («Forças geradas pela deslocação do veículo à retaguarda») não corresponde ao pedido do enunciado.</t>
+          <t>Força que se opõe à deslocação do veículo, tendo este que a vencer para se deslocar — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Diminuir a velocidade de cada um dos veículos, encostando-os o mais à direita possível. — é o que melhor responde ao enunciado (opção D)). Por exemplo, A) («Aumentar a velocidade.») não corresponde ao pedido do enunciado.</t>
+          <t>Diminuir a velocidade de cada um dos veículos, encostando-os o mais à direita possível. — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -28406,7 +28406,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Maior for a distância entre eixos. — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Menor for o peso bruto.») não corresponde ao pedido do enunciado.</t>
+          <t>Maior for a distância entre eixos. — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -28466,7 +28466,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>O procedimento adequado é No transporte com depósito não completamente atestado, o motorista deve ter especial atenção ao efetuar uma curva e ao travar (C)). Por exemplo, D) («A travagem de veículo com carga móvel nunca irá provocar impulsos no veícu…») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é No transporte com depósito não completamente atestado, o motorista deve ter especial atenção ao efetuar uma curva e ao travar (C)).</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -28526,7 +28526,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Posição inadequada ao volante — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Ventilação regular do habitáculo do veículo») não corresponde ao pedido do enunciado.</t>
+          <t>Posição inadequada ao volante — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -28586,7 +28586,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>4 m — é o que melhor responde ao enunciado (opção A)). Por exemplo, a opção B) indica valores (4,2 m) diferentes do aplicável.</t>
+          <t>4 m — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -28646,7 +28646,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Inclinar-se quando sujeita a forças horizontais — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Estabilizar o comportamento dinâmico do veículo;») não corresponde ao pedido do enunciado.</t>
+          <t>Inclinar-se quando sujeita a forças horizontais — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Desacelerar à distância conveniente, reduzindo a carga no acelerador (B)). Por exemplo, D) («Desacelerar e travar logo de seguida») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Desacelerar à distância conveniente, reduzindo a carga no acelerador (B)).</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -28766,7 +28766,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Evitar o deslocamento de objetos cilíndricos ao longo da plataforma de carga — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Imobilizar a m ercadoria quando há folgas muito grandes entre a carga e os…») não corresponde ao pedido do enunciado.</t>
+          <t>Evitar o deslocamento de objetos cilíndricos ao longo da plataforma de carga — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Ensaio da embraiagem e sistema de travagem (D)). Por exemplo, C) («Nível do óleo de lubrificação do motor e indicador de colmatagem do filtro…») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Ensaio da embraiagem e sistema de travagem (D)).</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -28886,7 +28886,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>Sim, sempre — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A distribuição é importante só para objetos pesados») não corresponde ao pedido do enunciado.</t>
+          <t>Sim, sempre — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -28946,7 +28946,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>A comodidade dos passageiros que transporta — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O aumento do consumo de combustível») não corresponde ao pedido do enunciado.</t>
+          <t>A comodidade dos passageiros que transporta — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -29006,7 +29006,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>61% dos assaltos ocorreram nos parques ou áreas de serviço — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («61% dos assaltos ocorreram com os veículos imobilizados por avaria») não corresponde ao pedido do enunciado.</t>
+          <t>61% dos assaltos ocorreram nos parques ou áreas de serviço — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -29126,7 +29126,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>A planificação detalhada do itinerário — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Nenhuma das hipóteses anteriores pode ser considerada boa prática») não corresponde ao pedido do enunciado.</t>
+          <t>A planificação detalhada do itinerário — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -29186,7 +29186,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Antes de iniciar a viagem (A)). Por exemplo, C) («Apenas quando vai fazer uma viagem para fora de território nacional») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Antes de iniciar a viagem (A)).</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -29246,7 +29246,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>A prevenção — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O alheamento de comportamentos que visam a promoção da proteção dos bens e…») não corresponde ao pedido do enunciado.</t>
+          <t>A prevenção — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -29306,7 +29306,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>Evitar falar do conteúdo e valor do transporte e dos itinerários escolhidos, com pessoas estranhas — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Basta efetuar o abastecimento em postos com sistema de vigilância») não corresponde ao pedido do enunciado.</t>
+          <t>Evitar falar do conteúdo e valor do transporte e dos itinerários escolhidos, com pessoas estranhas — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -29366,7 +29366,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Evitar parques de estacionamento isolados (B)). Por exemplo, D) («Procurar locais de estacionamento grátis») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Evitar parques de estacionamento isolados (B)).</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -29426,7 +29426,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Avisar as autoridades e o proprietário do veículo em causa (A)). Por exemplo, C) («Apenas avisar as autoridades do sucedido») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Avisar as autoridades e o proprietário do veículo em causa (A)).</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -29486,7 +29486,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Avisar as autoridades e o proprietário do veículo em causa (A)). Por exemplo, C) («Apenas avisar as autoridades do sucedido») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Avisar as autoridades e o proprietário do veículo em causa (A)).</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -29546,7 +29546,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>Possua vigilância e os veículos sejam controlados à entrada e à saída — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Careça de pagamento, não sendo necessária vídeo vigilância») não corresponde ao pedido do enunciado.</t>
+          <t>Possua vigilância e os veículos sejam controlados à entrada e à saída — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -29666,7 +29666,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>A afirmação é verdadeira — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A afirmação é parcialmente falsa») não corresponde ao pedido do enunciado.</t>
+          <t>A afirmação é verdadeira — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -29726,7 +29726,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Da polícia, autoridade anti-terrorismo e proteção civil e da embaixada (B)). Por exemplo, D) («Dos melhores hotéis e áreas de lazer») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Da polícia, autoridade anti-terrorismo e proteção civil e da embaixada (B)).</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -29786,7 +29786,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Transportar consigo objetos de valor e grandes quantias de dinheiro (A)). Por exemplo, D) («Falar com as pessoas que conhece») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Transportar consigo objetos de valor e grandes quantias de dinheiro (A)).</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -29846,7 +29846,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Saber onde são os parques de estacionamento mais seguros para estacionar a viatura e descansar em segurança. (D)). Por exemplo, C) («Estacionar a viatura em qualquer local») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Saber onde são os parques de estacionamento mais seguros para estacionar a viatura e descansar em segurança. (D)).</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -29906,7 +29906,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Preferir os parques de estacionamento bem iluminados e onde já estejam algumas viaturas também (D)). Por exemplo, C) («Deixar as janelas da viatura abertas para arejar o habitáculo») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Preferir os parques de estacionamento bem iluminados e onde já estejam algumas viaturas também (D)).</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -29966,7 +29966,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Voltaram todos a entrar e verificar através de uma listagem se são as mesmas pessoas (A)). Por exemplo, D) («Descansaram um pouco.») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Voltaram todos a entrar e verificar através de uma listagem se são as mesmas pessoas (A)).</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -30026,7 +30026,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Entrega as bagagens certas aos respetivos passageiros e que não existe nada de estranho entre elas (D)). Por exemplo, C) («As bagagens têm todas mais ou menos o mesmo peso») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Entrega as bagagens certas aos respetivos passageiros e que não existe nada de estranho entre elas (D)).</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -30086,7 +30086,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Os dispositivos de segurança estão todos a funcionar corretamente (A)). Por exemplo, D) («Os passageiros falam todos português corretamente») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Os dispositivos de segurança estão todos a funcionar corretamente (A)).</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -30146,7 +30146,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Todas as alíneas anteriores estão certas (D)). Por exemplo, C) («O motorista colocar os dados relativos às mercadorias transportadas ou bag…») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Todas as alíneas anteriores estão certas (D)).</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -30206,7 +30206,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Chamar de imediato as autoridades competentes (B)). Por exemplo, D) («Fazer de conta que não o viu») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Chamar de imediato as autoridades competentes (B)).</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -30326,7 +30326,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Necessidade de ligação constante com a empresa (A)). Por exemplo, D) («Que o serviço começa e termina com o início da viagem») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Necessidade de ligação constante com a empresa (A)).</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -30386,7 +30386,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Antes de entrar no veículo verifique se há pessoas a passear na área (A)). Por exemplo, D) («Estacione em qualquer parque») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Antes de entrar no veículo verifique se há pessoas a passear na área (A)).</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -30446,7 +30446,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Busca sumária ao exterior depois ao interior, em todos os locais susceptíveis de esconder um objeto ou pessoa (C)). Por exemplo, D) («Verificar se a viatura tem riscos e vidros partidos») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Busca sumária ao exterior depois ao interior, em todos os locais susceptíveis de esconder um objeto ou pessoa (C)).</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -30506,7 +30506,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Manter bom relacionamento e controlo dos passageiros, capacidade do saber ouvir para assim, responder adequadamente e evitar a discussão (B)). Por exemplo, D) («Informar os passageiros que em caso de conflito está autorizado a usar a f…») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Manter bom relacionamento e controlo dos passageiros, capacidade do saber ouvir para assim, responder adequadamente e evitar a discussão (B)).</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -30566,7 +30566,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>Tráfico e consumo de estupefacientes e substâncias psicotrópicas tipificados no Dec-Lei n.º 15/93 de 22 de Janeiro — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Dar bebidas alcoólicas ao seu colega e/ou a desconhecidos») não corresponde ao pedido do enunciado.</t>
+          <t>Tráfico e consumo de estupefacientes e substâncias psicotrópicas tipificados no Dec-Lei n.º 15/93 de 22 de Janeiro — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -30626,7 +30626,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>Nos locais de estacionamento e áreas de serviço — é o que melhor responde ao enunciado (opção D)). Por exemplo, B) («No local de descarga, no destinatário.») não corresponde ao pedido do enunciado.</t>
+          <t>Nos locais de estacionamento e áreas de serviço — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -30686,7 +30686,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>De noite — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Entre as 9h00 e as 12h00») não corresponde ao pedido do enunciado.</t>
+          <t>De noite — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -30746,7 +30746,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Estacionar em locais isolados, com o menor número de veículos pesados possíveis — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Não estacionar o veículo de modo a que as portas de carga e descarga se en…») não corresponde ao pedido do enunciado.</t>
+          <t>Estacionar em locais isolados, com o menor número de veículos pesados possíveis — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -30926,7 +30926,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Entrar na cabine do veículo e sair do local o mais rápido possível (D)). Por exemplo, C) («Comunicar de imediato à entidade empregadora») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Entrar na cabine do veículo e sair do local o mais rápido possível (D)).</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -30986,7 +30986,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Mantenha a calma, não abra o vidro, e se necessário contacte a polícia (A)). Por exemplo, D) («Sair do veículo e afaste o estranho») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Mantenha a calma, não abra o vidro, e se necessário contacte a polícia (A)).</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -31046,7 +31046,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Se no decorrer de um transporte, um utente i nsistir entrar sem documento de embarque, deixar entrar, se houver lugares disponíveis (D)). Por exemplo, C) («Verificar, no decorrer de uma pausa de descanso, a eventual entrada de pes…») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Se no decorrer de um transporte, um utente i nsistir entrar sem documento de embarque, deixar entrar, se houver lugares disponíveis (D)).</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -31106,7 +31106,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Descansar e aguardar que seja efetuada a descarga (A)). Por exemplo, D) («Verificar se o lacre colocado no compartimento de carga ainda está intacto…») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Descansar e aguardar que seja efetuada a descarga (A)).</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -31166,7 +31166,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>Planear os detalhes do itinerário e não seguir sempre o mesmo percurso — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Assegurar-se que a entrega da mercadoria é feita no local correcto ou os p…») não corresponde ao pedido do enunciado.</t>
+          <t>Planear os detalhes do itinerário e não seguir sempre o mesmo percurso — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -31406,7 +31406,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Colocar cintas de segurança, trancas/fechaduras e o cabo de segurança TIR ou fechar bem o veículo (B)). Por exemplo, D) («Possuir uma arma de defesa pessoal») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Colocar cintas de segurança, trancas/fechaduras e o cabo de segurança TIR ou fechar bem o veículo (B)).</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -31466,7 +31466,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Deve observar todas as anteriores respostas (D)). Por exemplo, C) («Fechar todas as portas à chave e levar todas as chaves, desde que os regul…») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Deve observar todas as anteriores respostas (D)).</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -31586,7 +31586,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>Trata-se de uma definição: Revela comportamento negligente ao não empreender pessoalmente quaisquer verificações do veículo durante a viagem (opção D)).  Por exemplo, C) («Procedeu a verificações do exterior do veículo antes de embarcar para o Re…») não corresponde ao pedido do enunciado.</t>
+          <t>Trata-se de uma definição: Revela comportamento negligente ao não empreender pessoalmente quaisquer verificações do veículo durante a viagem (opção D)).</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -31646,7 +31646,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Lista de Verificações do Home Office — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Lista de Verificações da associação de transportadores inglesa») não corresponde ao pedido do enunciado.</t>
+          <t>Lista de Verificações do Home Office — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -31706,7 +31706,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>O motorista — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Os agentes fiscalizadores do porto de embarque para o Reino Unido») não corresponde ao pedido do enunciado.</t>
+          <t>O motorista — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -31766,7 +31766,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>Antecipar eventuais situações de risco para poder reagir adequadamente — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Sempre que possível utilizar os trajetos mais curtos, mesmo que não sejam …») não corresponde ao pedido do enunciado.</t>
+          <t>Antecipar eventuais situações de risco para poder reagir adequadamente — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -31826,7 +31826,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Sinalizar o veículo, alertar as autoridades e parar o motor do veículo (A)). Por exemplo, D) («Nenhuma das respostas anteriores está correcta») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Sinalizar o veículo, alertar as autoridades e parar o motor do veículo (A)).</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -31886,7 +31886,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>O procedimento adequado é 112 (B)). Por exemplo, a opção A) indica valores (113) diferentes do aplicável.</t>
+          <t>O procedimento adequado é 112 (B)).</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -31946,7 +31946,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>Entre o combustível e o oxigénio do ar (comburente), face a uma fonte de calor — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Que ocorre em determinados materiais provocado pelo aumento da temperatura») não corresponde ao pedido do enunciado.</t>
+          <t>Entre o combustível e o oxigénio do ar (comburente), face a uma fonte de calor — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -32006,7 +32006,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Todas as respostas anteriores estão correctas — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Promover a recuperação») não corresponde ao pedido do enunciado.</t>
+          <t>Todas as respostas anteriores estão correctas — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -32066,7 +32066,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>Pode ser realizado apenas por um condutor — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Pode omitir o esquema de acidente») não corresponde ao pedido do enunciado.</t>
+          <t>Pode ser realizado apenas por um condutor — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -32126,7 +32126,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Convenção internacional, denominada Convenção Multilateral de Garantias — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Carta que substitui a Carta de Condução») não corresponde ao pedido do enunciado.</t>
+          <t>Convenção internacional, denominada Convenção Multilateral de Garantias — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -32186,7 +32186,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Escolho áreas de estacionamento vigiadas e seguras — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Todas as anteriores respostas estão correctas») não corresponde ao pedido do enunciado.</t>
+          <t>Escolho áreas de estacionamento vigiadas e seguras — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -32246,7 +32246,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Sim — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Todas as respostas estão incorretas») não corresponde ao pedido do enunciado.</t>
+          <t>Sim — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -32366,7 +32366,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Mulheres grávidas (A)). Por exemplo, D) («Idosos com mais de 70 anos») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Mulheres grávidas (A)).</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -32426,7 +32426,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Deve ser provocada nas vítimas que respiram normalmente — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A posição lateral nunca deve ser provocada») não corresponde ao pedido do enunciado.</t>
+          <t>Deve ser provocada nas vítimas que respiram normalmente — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -32486,7 +32486,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Não tocar na lesão (B)). Por exemplo, D) («Colocar sobre a lesão soluções ou pomadas») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Não tocar na lesão (B)).</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -32546,7 +32546,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Se a vítima estiver contaminada com tóxicos ou venenos o socorrista deve usar proteções do corpo e da roupa (luvas e avental) (B)). Por exemplo, D) («Deve ser fornecido álcool à vítima») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Se a vítima estiver contaminada com tóxicos ou venenos o socorrista deve usar proteções do corpo e da roupa (luvas e avental) (B)).</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -32606,7 +32606,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>Deve ser sucinto e relatar resumidamente o que aconteceu — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («É obrigatório o preenchimento do verso do impresso na hora do acidente») não corresponde ao pedido do enunciado.</t>
+          <t>Deve ser sucinto e relatar resumidamente o que aconteceu — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -32666,7 +32666,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Não movimentar a vítima, exceto se existir perigo iminente de incêndio, explosão ou qualquer outra situação que ponha em risco a vida da vítima (B)). Por exemplo, D) («Ajudar a vítima a sair do veículo») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Não movimentar a vítima, exceto se existir perigo iminente de incêndio, explosão ou qualquer outra situação que ponha em risco a vida da vítima (B)).</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -32726,7 +32726,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Prevenir, alertar e socorrer — é o que melhor responde ao enunciado (opção D)). Por exemplo, A) («Prever, ajudar e socorrer») não corresponde ao pedido do enunciado.</t>
+          <t>Prevenir, alertar e socorrer — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -32786,7 +32786,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Com realização de pancadas interescapulares ou manobra de Heimlich (C)). Por exemplo, D) («Através da colocação em decúbito dorsal») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Com realização de pancadas interescapulares ou manobra de Heimlich (C)).</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -32846,7 +32846,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Desobstruir as vias aéreas, fazer a extensão da cabeça, pedir ajuda e verificar se está a respirar (C)). Por exemplo, D) («Colocar em decúbito dorsal») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Desobstruir as vias aéreas, fazer a extensão da cabeça, pedir ajuda e verificar se está a respirar (C)).</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -32906,7 +32906,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>Estacionar o veículo depois do local do acidente, ligar as luzes de perigo, vestir o colete e colocar o sinal de pré-sinalização de perigo a pelo menos 30m da retaguarda do veículo ou da carga a sinalizar. — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção C) indica valores (Estacionar o veículo antes do local do acidente, ligar as luzes de perigo,…) diferentes do aplicável.</t>
+          <t>Estacionar o veículo depois do local do acidente, ligar as luzes de perigo, vestir o colete e colocar o sinal de pré-sinalização de perigo a pelo menos 30m da retaguarda do veículo ou da carga a sinalizar. — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -32966,7 +32966,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Estacionar o veículo antes do local do acidente, ligar as luzes de perigo, vestir o colet e e colocar o sinal de pré-sinalização de perigo a pelo menos 30m da retaguarda do veículo ou da carga a sinalizar. — é o que melhor responde ao enunciado (opção A)). Por exemplo, a opção C) indica valores (Estacionar o veículo antes do local do acidente, ligar as luzes de perigo,…) diferentes do aplicável.</t>
+          <t>Estacionar o veículo antes do local do acidente, ligar as luzes de perigo, vestir o colet e e colocar o sinal de pré-sinalização de perigo a pelo menos 30m da retaguarda do veículo ou da carga a sinalizar. — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -33086,7 +33086,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>Todas as respostas anteriores estão correctas — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Estamos a ligar diretamente para os bombeiros») não corresponde ao pedido do enunciado.</t>
+          <t>Todas as respostas anteriores estão correctas — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -33146,7 +33146,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>Devem ser referidas todas as informações anteriores — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Fornecer o número de telefone de onde se está a efetuar o pedido de socorro») não corresponde ao pedido do enunciado.</t>
+          <t>Devem ser referidas todas as informações anteriores — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -33206,7 +33206,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>Deve-se esperar durante 10 segundos para ver se a vítima respira ou não — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Nenhuma das respostas anteriores está correcta») não corresponde ao pedido do enunciado.</t>
+          <t>Deve-se esperar durante 10 segundos para ver se a vítima respira ou não — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -33266,7 +33266,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>O melhor método é fazer compressão direta — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Uma hemorragia não é grave e por isso não é necessário fazer nada») não corresponde ao pedido do enunciado.</t>
+          <t>O melhor método é fazer compressão direta — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -33386,7 +33386,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Todas as respostas anteriores estão correctas (D)). Por exemplo, C) («Deve garantir a evacuação dos ocupantes do veículo para uma zona segura») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Todas as respostas anteriores estão correctas (D)).</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -33446,7 +33446,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Os atos do motorista devem basear-se em evitar sempre o confronto (C)). Por exemplo, D) («O motorista deve reagir violentamente e se possível imobilizar o agressor») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Os atos do motorista devem basear-se em evitar sempre o confronto (C)).</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -33506,7 +33506,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Não desligar a ignição dos veículos acidentados (D)). Por exemplo, C) («Descrever corretamente qual a situação e responder às perguntas que a cent…») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Não desligar a ignição dos veículos acidentados (D)).</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -33566,7 +33566,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Abandonar o local (D)). Por exemplo, C) («Efetuar uma rápida avaliação da vítima») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Abandonar o local (D)).</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -33626,7 +33626,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Manter o veículo em funcionamento (D)). Por exemplo, A) («Ligar os 4 indicadores de mudança de direção») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Manter o veículo em funcionamento (D)).</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -33686,7 +33686,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>O procedimento adequado é 8 Dias (C)). Por exemplo, a opção A) indica valores (5 Dias) diferentes do aplicável.</t>
+          <t>O procedimento adequado é 8 Dias (C)).</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -33746,7 +33746,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Não, apenas quando os condutores estiverem de acordo (B)). Por exemplo, C) («Não, apenas só quando é chamada a polícia») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Não, apenas quando os condutores estiverem de acordo (B)).</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -33806,7 +33806,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Trata-se de uma definição: Avaliar se a vítima está consciente/inconsciente (opção A)).  Por exemplo, D) («Avaliar somente a circulação e temperatura») não corresponde ao pedido do enunciado.</t>
+          <t>Trata-se de uma definição: Avaliar se a vítima está consciente/inconsciente (opção A)).</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -33866,7 +33866,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Tentar prever potenciais situações de conflito e identificar potenciais agressores, assim como controlar as emoções e tomar decisões (D)). Por exemplo, C) («Saber identificar potenciais agressores perante a autoridade») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Tentar prever potenciais situações de conflito e identificar potenciais agressores, assim como controlar as emoções e tomar decisões (D)).</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -33926,7 +33926,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Trata-se de uma definição: Avaliação em primeiro lugar do estado de consciência da vítima (opção D)).  Por exemplo, B) («Verificação em primeiro lugar da existência de ventilação.») não corresponde ao pedido do enunciado.</t>
+          <t>Trata-se de uma definição: Avaliação em primeiro lugar do estado de consciência da vítima (opção D)).</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Utilizar água para lavar os olhos (B)). Por exemplo, D) («Não é necessário tomar precauções especiais porque um produto tóxico não e…») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Utilizar água para lavar os olhos (B)).</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -34106,7 +34106,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Envolver a vítima com um cobertor ou rolá-la pelo chão (C)). Por exemplo, D) («Chamar de imediato o 112») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Envolver a vítima com um cobertor ou rolá-la pelo chão (C)).</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -34166,7 +34166,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>Custo de reparação ou perda total, e reboque — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Danos em muros e animais») não corresponde ao pedido do enunciado.</t>
+          <t>Custo de reparação ou perda total, e reboque — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -34286,7 +34286,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>Dentro das localidades — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Na circulação nas faixas BUS») não corresponde ao pedido do enunciado.</t>
+          <t>Dentro das localidades — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -34406,7 +34406,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Iniciar encostado ao eixo da via, curvando próximo do mesmo; ao sair da curva manter o veículo mais próximo do eixo da via (A)). Por exemplo, D) («Iniciar encostado à direita, curvando progressivamente para o lado esquerd…») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Iniciar encostado ao eixo da via, curvando próximo do mesmo; ao sair da curva manter o veículo mais próximo do eixo da via (A)).</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -34466,7 +34466,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Maior velocidade de circulação (C)). Por exemplo, D) («Maior distracção do condutor provocada pelos passageiros») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Maior velocidade de circulação (C)).</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>Colisões — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Queda de pessoas do veículo») não corresponde ao pedido do enunciado.</t>
+          <t>Colisões — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -34586,7 +34586,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>Os acidentes envolvendo veículos pesados de passageiros têm consequências mais graves para terceiros do que para os utentes — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Os acidentes com índice de gravidade mais elevado ocorrem no período de ma…») não corresponde ao pedido do enunciado.</t>
+          <t>Os acidentes envolvendo veículos pesados de passageiros têm consequências mais graves para terceiros do que para os utentes — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -34646,7 +34646,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>Que o retrator ajuste automaticamente o comprimento do cinto, e em caso de aceleração brusca o mesmo seja bloqueado — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Maior segurança ao utilizador») não corresponde ao pedido do enunciado.</t>
+          <t>Que o retrator ajuste automaticamente o comprimento do cinto, e em caso de aceleração brusca o mesmo seja bloqueado — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -34706,7 +34706,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Sinalizar a eventual s úbita redução de velocidade, procurar uma escapatória possível, parar em segurança, sinalizar o acidente e solicitar auxílio (A)). Por exemplo, D) («Manter a mesma velocidade e manter o veículo na mesma direcção») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Sinalizar a eventual s úbita redução de velocidade, procurar uma escapatória possível, parar em segurança, sinalizar o acidente e solicitar auxílio (A)).</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -34766,7 +34766,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Reduzir a velocidade, encostar-se o mais à direita possível e ligar os quatro indicadores de mudança de direção em funcionamento simultâneo (A)). Por exemplo, D) («Aumentar a velocidade para sair rapidamente da zona do acidente») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Reduzir a velocidade, encostar-se o mais à direita possível e ligar os quatro indicadores de mudança de direção em funcionamento simultâneo (A)).</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -34826,7 +34826,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Aumentar a distância do veículo da frente de forma a, se necessário, conseguir parar em segurança (D)). Por exemplo, C) («Só travar o veículo com a caixa de velocidades») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Aumentar a distância do veículo da frente de forma a, se necessário, conseguir parar em segurança (D)).</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -34886,7 +34886,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Certificar-se de que a visibilidade para a condução não é afetada e circular só nestas condições (B)). Por exemplo, D) («Esperar pelo verão para reparar a avaria») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Certificar-se de que a visibilidade para a condução não é afetada e circular só nestas condições (B)).</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -34946,7 +34946,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Reduzir a velocidade e aumentar a distância de segurança do veículo que circula à sua frente (A)). Por exemplo, D) («Verificar se os líquidos do motor estão ao nível») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Reduzir a velocidade e aumentar a distância de segurança do veículo que circula à sua frente (A)).</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -35006,7 +35006,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>Deve-se a um conjunto de medidas concertadas, associadas à evolução do parque automóvel, à qualidade das vias e, essencialmente, às alterações de atitudes e comportamentos que se têm vindo a verificar nos utentes — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («É insignificante, o número de acidentes manteve-se quase inalterado nas du…») não corresponde ao pedido do enunciado.</t>
+          <t>Deve-se a um conjunto de medidas concertadas, associadas à evolução do parque automóvel, à qualidade das vias e, essencialmente, às alterações de atitudes e comportamentos que se têm vindo a verificar nos utentes — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -35306,7 +35306,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>Sim, de acordo com os resultados apresentados o nú mero de mortos e feridos graves diminuiu consideravelmente. — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («Não, estes números não param de aumentar e os acidentes com pesados são ca…») não corresponde ao pedido do enunciado.</t>
+          <t>Sim, de acordo com os resultados apresentados o nú mero de mortos e feridos graves diminuiu consideravelmente. — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -35366,7 +35366,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>A apneia do sono tem efeitos muito graves na condução, porque os  condutores não se apercebem de que estão com a vigilância diminuída e, devido a esse facto, com a atenção, a concentração e os reflexos diminuídos — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A apneia do sono tal como a sonolência ou a fadiga não interferem na condu…») não corresponde ao pedido do enunciado.</t>
+          <t>A apneia do sono tem efeitos muito graves na condução, porque os  condutores não se apercebem de que estão com a vigilância diminuída e, devido a esse facto, com a atenção, a concentração e os reflexos diminuídos — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -35426,7 +35426,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>A apneia do sono tem efeitos muito graves na condução, porque os  condutores não se apercebem de que estão com a vigilância diminuída e, devido a esse facto, com a atenção, a concentração e os reflexos diminuídos — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A apneia do sono tal como a sonolência ou a fadiga não interferem na condu…») não corresponde ao pedido do enunciado.</t>
+          <t>A apneia do sono tem efeitos muito graves na condução, porque os  condutores não se apercebem de que estão com a vigilância diminuída e, devido a esse facto, com a atenção, a concentração e os reflexos diminuídos — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -35486,7 +35486,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>Sim, usando o cinto de segurança, o condutor, em caso de acidente, tem mais probabilidades de não sofrer lesões graves — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («O condutor de veículos pesados não deve utilizar o cinto de segurança») não corresponde ao pedido do enunciado.</t>
+          <t>Sim, usando o cinto de segurança, o condutor, em caso de acidente, tem mais probabilidades de não sofrer lesões graves — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -35546,7 +35546,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>Sim, os acidentes por despiste nos ligeiros de passageiros foi de bastante superior aos despistes de veículos pesados de passageiros — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Não os pesados despistam-se mais que os ligeiros») não corresponde ao pedido do enunciado.</t>
+          <t>Sim, os acidentes por despiste nos ligeiros de passageiros foi de bastante superior aos despistes de veículos pesados de passageiros — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -35606,7 +35606,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>Sim, além dos custos ma teriais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos autocarros estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Sim, pois podem perder o alvará») não corresponde ao pedido do enunciado.</t>
+          <t>Sim, além dos custos ma teriais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos autocarros estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -35666,7 +35666,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>Sim, além dos custos ma teriais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos autocarros estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Sim, pois podem perder o alvará») não corresponde ao pedido do enunciado.</t>
+          <t>Sim, além dos custos ma teriais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos autocarros estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -35726,7 +35726,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Sim, além dos custos materiais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos veículos estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Sim, pois podem perder o alvará») não corresponde ao pedido do enunciado.</t>
+          <t>Sim, além dos custos materiais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos veículos estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -35786,7 +35786,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>Sim, além dos custos materiais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos veículos estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Sim, pois podem perder o alvará») não corresponde ao pedido do enunciado.</t>
+          <t>Sim, além dos custos materiais, também têm custos ao nível da imagem da própria empresa. Uma empresa cujos veículos estejam frequentemente envolvidos em acidentes rodoviários, irá a curto prazo começar a perder os seus clientes — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Certa — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A afirmação está certa apenas se o condutor se socorrer do GPS») não corresponde ao pedido do enunciado.</t>
+          <t>Certa — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -36206,7 +36206,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>A afirmação está certa apenas se se referir a condução noturna — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («A afirmação está errada») não corresponde ao pedido do enunciado.</t>
+          <t>A afirmação está certa apenas se se referir a condução noturna — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -36266,7 +36266,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>Não é permitido ao motorista ´dar boleias´ — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O motorista não deve identificar passageiros em caso de conflito declarado») não corresponde ao pedido do enunciado.</t>
+          <t>Não é permitido ao motorista ´dar boleias´ — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -36386,7 +36386,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>Morte de passageiros — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Danos no veículo acidentado») não corresponde ao pedido do enunciado.</t>
+          <t>Morte de passageiros — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -36506,7 +36506,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>Nas ultrapassagens indevidas — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («Pelo respeito pelo traço contínuo no eixo da via») não corresponde ao pedido do enunciado.</t>
+          <t>Nas ultrapassagens indevidas — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -36566,7 +36566,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>Circula demasiado perto do veículo da frente — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Observa o comportamento do condutor à sua frente») não corresponde ao pedido do enunciado.</t>
+          <t>Circula demasiado perto do veículo da frente — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -36626,7 +36626,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Desrespeito da regra de cedência de passagem — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Respeitar a sinalização luminosa») não corresponde ao pedido do enunciado.</t>
+          <t>Desrespeito da regra de cedência de passagem — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -36686,7 +36686,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Fazer sinal com o indicador de mudança de direção à esquerda — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Buzinar ao veículo da frente») não corresponde ao pedido do enunciado.</t>
+          <t>Fazer sinal com o indicador de mudança de direção à esquerda — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -36746,7 +36746,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>À velocidade de impacto dos veículos — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («À construção dos veículos») não corresponde ao pedido do enunciado.</t>
+          <t>À velocidade de impacto dos veículos — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -36806,7 +36806,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>À velocidade a que o veículo circula — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («À construção dos veículos») não corresponde ao pedido do enunciado.</t>
+          <t>À velocidade a que o veículo circula — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -36986,7 +36986,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>No veículo, na via e no homem — é o que melhor responde ao enunciado (opção D)). Por exemplo, B) («Na via, no homem e na intensidade de tráfego») não corresponde ao pedido do enunciado.</t>
+          <t>No veículo, na via e no homem — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -37046,7 +37046,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>Sim, sempre — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Não, apenas tem impacto no consumo de combustível») não corresponde ao pedido do enunciado.</t>
+          <t>Sim, sempre — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -37106,7 +37106,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>O uso do corta-vento na janela do condutor e a condução, sempre que possível, com o vidro fechado — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («A condução com as janelas abertas») não corresponde ao pedido do enunciado.</t>
+          <t>O uso do corta-vento na janela do condutor e a condução, sempre que possível, com o vidro fechado — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -37166,7 +37166,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>10 kg por passageiro — é o que melhor responde ao enunciado (opção A)). Por exemplo, a opção B) indica valores (20 kg por passageiro) diferentes do aplicável.</t>
+          <t>10 kg por passageiro — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -37226,7 +37226,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>Sim, pois uma boa rede de transportes públicos eficiente e pontual, fazia com que as pessoas a utilizassem mais e isto iria contribuir para um decréscimo da poluição atmosférica e diminuição dos engarrafamentos de trânsito — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Não, pois ninguém está interessado em utilizar os transportes públicos») não corresponde ao pedido do enunciado.</t>
+          <t>Sim, pois uma boa rede de transportes públicos eficiente e pontual, fazia com que as pessoas a utilizassem mais e isto iria contribuir para um decréscimo da poluição atmosférica e diminuição dos engarrafamentos de trânsito — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -37286,7 +37286,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Um alvará ou licença comunitária emitidos por um prazo não superior a cinco anos. — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A atividade de transporte rodoviário de passageiros em autocarro não neces…») não corresponde ao pedido do enunciado.</t>
+          <t>Um alvará ou licença comunitária emitidos por um prazo não superior a cinco anos. — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -37346,7 +37346,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Transportes públicos ou por conta de outrem — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Transportes interurbanos») não corresponde ao pedido do enunciado.</t>
+          <t>Transportes públicos ou por conta de outrem — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -37406,7 +37406,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>Os transportes regulares e ocasionais — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Os transportes particulares») não corresponde ao pedido do enunciado.</t>
+          <t>Os transportes regulares e ocasionais — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -37466,7 +37466,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Sociedades comerciais, cooperativas e empresas públicas ou de capitais públicos que comprovem reunir os requisitos de acesso à actividade — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Empresários em nome individual») não corresponde ao pedido do enunciado.</t>
+          <t>Sociedades comerciais, cooperativas e empresas públicas ou de capitais públicos que comprovem reunir os requisitos de acesso à actividade — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -37526,7 +37526,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>Sociedades anónimas — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Sociedades em comandita simples») não corresponde ao pedido do enunciado.</t>
+          <t>Sociedades anónimas — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -37586,7 +37586,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Empresas públicas de transporte rodoviário — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Sociedades comerciais») não corresponde ao pedido do enunciado.</t>
+          <t>Empresas públicas de transporte rodoviário — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -37646,7 +37646,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>O “Aluguer ocasional” é um serviço prestado mediante a cedência de um autocarro com um condutor para a realização de uma deslocação de um grupo de passageiros. — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Serviços “expresso” são aqueles cuja distância a percorrer são inferiores …») não corresponde ao pedido do enunciado.</t>
+          <t>O “Aluguer ocasional” é um serviço prestado mediante a cedência de um autocarro com um condutor para a realização de uma deslocação de um grupo de passageiros. — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -37706,7 +37706,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>Em carreiras regulares, com origem, destino, pontos de passagem e horários previamente estabelecidos, devidamente autorizados e divulgados junto dos utentes — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («Por carreiras regulares, não necessitando de autorização, nem os utentes t…») não corresponde ao pedido do enunciado.</t>
+          <t>Em carreiras regulares, com origem, destino, pontos de passagem e horários previamente estabelecidos, devidamente autorizados e divulgados junto dos utentes — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -37766,7 +37766,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Mais rápido que o transporte público, com menor número de paragens, normalmente aplicável a médio-longo curso — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Mais lento que o transporte público, utilizados somente em transporte inte…») não corresponde ao pedido do enunciado.</t>
+          <t>Mais rápido que o transporte público, com menor número de paragens, normalmente aplicável a médio-longo curso — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -37826,7 +37826,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>Estes serviços asseguram o transporte de grupos constituídos por iniciativa de um comitente ou do próprio transportador e estão isentos de qualquer autorização, sendo efetuados ao abri go de folhas de itinerário — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («As empresas que explorem serv iços internacionais estão autorizadas a efet…») não corresponde ao pedido do enunciado.</t>
+          <t>Estes serviços asseguram o transporte de grupos constituídos por iniciativa de um comitente ou do próprio transportador e estão isentos de qualquer autorização, sendo efetuados ao abri go de folhas de itinerário — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -37886,7 +37886,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>Exige condições físicas, psíquicas, humanas específicas ao candidato a motorista — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Exige apenas qualidade humanas para o exercício da função») não corresponde ao pedido do enunciado.</t>
+          <t>Exige condições físicas, psíquicas, humanas específicas ao candidato a motorista — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>A visão global do público dos serviços da empresa — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Os anúncios e slogans da empresa») não corresponde ao pedido do enunciado.</t>
+          <t>A visão global do público dos serviços da empresa — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -38006,7 +38006,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Preservar a imagem da viatura como a limpeza e adequação dos equipamentos (B)). Por exemplo, D) («Conhecer bem os seus colegas motoristas») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Preservar a imagem da viatura como a limpeza e adequação dos equipamentos (B)).</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -38066,7 +38066,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Todas as respostas anteriores estão corretas — é o que melhor responde ao enunciado (opção D)). Por exemplo, B) («Sentir-se seguro e esclarecido») não corresponde ao pedido do enunciado.</t>
+          <t>Todas as respostas anteriores estão corretas — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -38126,7 +38126,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Estabilidade emocional e manter uma comunicação assertiva com os interlocutores (D)). Por exemplo, C) («Idoneidade e responsabilidade de forma a assegurar o respeito pelas normas…») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Estabilidade emocional e manter uma comunicação assertiva com os interlocutores (D)).</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -38186,7 +38186,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Estabilidade emocional e manter uma comunicação assertiva com os interlocutores (D)). Por exemplo, C) («Idoneidade e responsabilidade de forma a assegurar o respeito pelas normas…») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Estabilidade emocional e manter uma comunicação assertiva com os interlocutores (D)).</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Falta de organização gerando pouco trabalho e produtividade assim como aspetos físicos ambientais — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Consciencialização dos objetivos e metas a atingir como profissional da em…») não corresponde ao pedido do enunciado.</t>
+          <t>Falta de organização gerando pouco trabalho e produtividade assim como aspetos físicos ambientais — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -38306,7 +38306,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>O conjunto de deveres, princípios e normas adoptadas por um determinado grupo profissional — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Um conjunto de fatores que prejudicam o desempenho profissional do motoris…») não corresponde ao pedido do enunciado.</t>
+          <t>O conjunto de deveres, princípios e normas adoptadas por um determinado grupo profissional — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -38366,7 +38366,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Ser independente no trabalho com os colegas/ colaboradores (B)). Por exemplo, D) («Mostrar uma atitude de empatia, disponibilidade e ter capacidade de delegar») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Ser independente no trabalho com os colegas/ colaboradores (B)).</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -38486,7 +38486,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Assertivo, agressivo, manipulador e passivo — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Nenhumas das anteriores está correta») não corresponde ao pedido do enunciado.</t>
+          <t>Assertivo, agressivo, manipulador e passivo — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -38546,7 +38546,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Há uma atitude de auto-afirmação — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A assertividade implica considerar os interesses apenas de uma das partes») não corresponde ao pedido do enunciado.</t>
+          <t>Há uma atitude de auto-afirmação — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -38606,7 +38606,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>Verdadeiro — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Só será um problema ao nível da comunicação não verbal») não corresponde ao pedido do enunciado.</t>
+          <t>Verdadeiro — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -38666,7 +38666,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>O olhar para o chão — é o que melhor responde ao enunciado (opção B)). Por exemplo, A) («A postura física correta») não corresponde ao pedido do enunciado.</t>
+          <t>O olhar para o chão — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -38726,7 +38726,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Todas as outras respostas estão corretas (D)). Por exemplo, B) («Ser delicado, amável e despedir-se cordialmente do cliente») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Todas as outras respostas estão corretas (D)).</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -38906,7 +38906,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>O nosso comportamento vai influenciar o comportamento daqueles que interagem connosco — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Deve-se interromper o emissor quando este expõe as suas ideias») não corresponde ao pedido do enunciado.</t>
+          <t>O nosso comportamento vai influenciar o comportamento daqueles que interagem connosco — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -38966,7 +38966,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>Ter o cliente como a razão de ser do seu desempenho — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Evitar revelar os aspetos menos positivos do serviço face ao cliente») não corresponde ao pedido do enunciado.</t>
+          <t>Ter o cliente como a razão de ser do seu desempenho — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -39026,7 +39026,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>Ajuda os clientes com dificuldade de mobilização (grávidas, idosos) — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Facilita as saídas dos clientes em locais não autorizados ou altera o loca…») não corresponde ao pedido do enunciado.</t>
+          <t>Ajuda os clientes com dificuldade de mobilização (grávidas, idosos) — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -39086,7 +39086,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Uma oportunidade para poder melhorar o serviço e o desempenho (C)). Por exemplo, D) («Situações que não devem ser muito valorizadas») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Uma oportunidade para poder melhorar o serviço e o desempenho (C)).</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -39146,7 +39146,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>Ter a capacidade de escutar o cliente dando informações corretas — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Ficar em silêncio para não correr o risco de aborrecer o cliente») não corresponde ao pedido do enunciado.</t>
+          <t>Ter a capacidade de escutar o cliente dando informações corretas — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -39206,7 +39206,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Facilitar a comunicação e cordialidade — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Estar centrado somente nos seus sentimentos e necessidades») não corresponde ao pedido do enunciado.</t>
+          <t>Facilitar a comunicação e cordialidade — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -39266,7 +39266,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Aproveitar a situação para trocar impressões com o colega (A)). Por exemplo, D) («Abandonar o veículo, antes da chegada do colega») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Aproveitar a situação para trocar impressões com o colega (A)).</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -39326,7 +39326,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>É um dever do motorista — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Faz perder tempo, porque os clientes só valorizam a rapidez do transporte») não corresponde ao pedido do enunciado.</t>
+          <t>É um dever do motorista — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -39386,7 +39386,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Procurar perceber o que está realmente em causa, sem personalizar ou julgar — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Confrontar e fazer valer o ponto de vista quando se tem razão») não corresponde ao pedido do enunciado.</t>
+          <t>Procurar perceber o que está realmente em causa, sem personalizar ou julgar — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -39446,7 +39446,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Sentir-se bloqueado e paralisado quando é apresentado um problema para resolver — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Impor as suas decisões aos outros») não corresponde ao pedido do enunciado.</t>
+          <t>Sentir-se bloqueado e paralisado quando é apresentado um problema para resolver — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -39506,7 +39506,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Os motoristas devem estar conscientes da importância do cargo que ocupam e o significado que seu trabalho tem para a organização — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Os transportes devem ser efectuados o mais célere possível, mesmo não resp…») não corresponde ao pedido do enunciado.</t>
+          <t>Os motoristas devem estar conscientes da importância do cargo que ocupam e o significado que seu trabalho tem para a organização — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -39566,7 +39566,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Formar um grupo coeso, eficiente e motivado — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Que o nosso comportamento possa depender do nosso estado de espírito») não corresponde ao pedido do enunciado.</t>
+          <t>Formar um grupo coeso, eficiente e motivado — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -39626,7 +39626,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Dar a confiança e satisfação aos clientes — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Reduzir a satisfação do cliente») não corresponde ao pedido do enunciado.</t>
+          <t>Dar a confiança e satisfação aos clientes — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -39746,7 +39746,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Aumento da fadiga — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Diminuição do tempo de reação») não corresponde ao pedido do enunciado.</t>
+          <t>Aumento da fadiga — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -39806,7 +39806,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>A qualidade de serviço implica obrigatoriamente aumentar os custos da empresa — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («A qualidade de serviço é uma forma da empresa de transportes se diferencia…») não corresponde ao pedido do enunciado.</t>
+          <t>A qualidade de serviço implica obrigatoriamente aumentar os custos da empresa — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -39866,7 +39866,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Organizacional — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Nenhuma das referidas») não corresponde ao pedido do enunciado.</t>
+          <t>Organizacional — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -40046,7 +40046,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Estão insatisfeitos com a qualidade do atendimento — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Desejam experimentar novos produtos») não corresponde ao pedido do enunciado.</t>
+          <t>Estão insatisfeitos com a qualidade do atendimento — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -40106,7 +40106,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Afastando-se do cliente, deixando-o a falar sozinho (C)). Por exemplo, D) («Informar o cliente sobre o funcionamento do serviço, para que ele compreen…») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Afastando-se do cliente, deixando-o a falar sozinho (C)).</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -40166,7 +40166,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>Processos de tratamento, controlo e comunicação de informação — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Processos de transferência de dados entre equipamentos electrónicos») não corresponde ao pedido do enunciado.</t>
+          <t>Processos de tratamento, controlo e comunicação de informação — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -40226,7 +40226,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>Os clientes que reclamam só causam problemas — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Ele irá contar a sua satisfação aos seus conhecidos, ajudando-nos a alarga…») não corresponde ao pedido do enunciado.</t>
+          <t>Os clientes que reclamam só causam problemas — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -40286,7 +40286,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>Os clientes que reclamam só causam problemas — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Ele irá contar a sua satisfação aos seus conhecidos, ajudando-nos a alarga…») não corresponde ao pedido do enunciado.</t>
+          <t>Os clientes que reclamam só causam problemas — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -40406,7 +40406,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>Poupar tempo, dinheiro e aumentar a satisfação dos clientes — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Utilizar circuitos turísticos») não corresponde ao pedido do enunciado.</t>
+          <t>Poupar tempo, dinheiro e aumentar a satisfação dos clientes — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -40646,7 +40646,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>O tempo estimado para a chegada do próximo veículo — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («O tempo médio de passagem entre veículos») não corresponde ao pedido do enunciado.</t>
+          <t>O tempo estimado para a chegada do próximo veículo — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -40706,7 +40706,7 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>Bilhética Electrónica e SMS — é o que melhor responde ao enunciado (opção A)). Por exemplo, B) («SMS e Rede Multibanco») não corresponde ao pedido do enunciado.</t>
+          <t>Bilhética Electrónica e SMS — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -40766,7 +40766,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>Altitude, longitude e latitude — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Altura, largura e longitude») não corresponde ao pedido do enunciado.</t>
+          <t>Altitude, longitude e latitude — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -40826,7 +40826,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>A coleção de documentos electrónicos interligados por uma infindável  rede ou teia (Web) de aranha, armazenados em computadores designados por servidores Web espalhados por todo o mundo — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Um sistema de partilha de documentos que funciona i ndependentemente da ut…») não corresponde ao pedido do enunciado.</t>
+          <t>A coleção de documentos electrónicos interligados por uma infindável  rede ou teia (Web) de aranha, armazenados em computadores designados por servidores Web espalhados por todo o mundo — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -40886,7 +40886,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>Permite aos motoristas estar em contacto com a empresa, colegas, clientes e outros contactos, tais como serviços de manutenção e reparação e centros de controlo de tráfego — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Obriga o condutor a obter certificados e autorizações adicionais para o ex…») não corresponde ao pedido do enunciado.</t>
+          <t>Permite aos motoristas estar em contacto com a empresa, colegas, clientes e outros contactos, tais como serviços de manutenção e reparação e centros de controlo de tráfego — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -40946,7 +40946,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>O processamento de informação, mapas, bases de dados, comunicações e dados em tempo real recolhidos a partir de uma variedade de sensores — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Aumentar o conforto dos passageiros, apesar do tempo de viagem aumentar») não corresponde ao pedido do enunciado.</t>
+          <t>O processamento de informação, mapas, bases de dados, comunicações e dados em tempo real recolhidos a partir de uma variedade de sensores — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -41006,7 +41006,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>Proporcionam o acesso a informação em tempo real relativa à viagem e ao tráfego — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Aumentam a segurança na condução, o que permite o aumento da velocidade má…») não corresponde ao pedido do enunciado.</t>
+          <t>Proporcionam o acesso a informação em tempo real relativa à viagem e ao tráfego — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -41186,7 +41186,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>Ter permanentemente a bordo informação sobre o estado da via e condições do tráfego — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Apenas evitar a possibilidade de engano no trajecto») não corresponde ao pedido do enunciado.</t>
+          <t>Ter permanentemente a bordo informação sobre o estado da via e condições do tráfego — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -41246,7 +41246,7 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>O condutor possa agir de forma a evitar o acidente — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O condutor tenha uma assistência mais rápida em caso de colisão») não corresponde ao pedido do enunciado.</t>
+          <t>O condutor possa agir de forma a evitar o acidente — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
@@ -41306,7 +41306,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Durante um determinado percurso sem que seja necessário pressionar o acelerador do veículo — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Durante 4 h consecutivas») não corresponde ao pedido do enunciado.</t>
+          <t>Durante um determinado percurso sem que seja necessário pressionar o acelerador do veículo — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -41366,7 +41366,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>Reduzir largamente o congestionamento nessas áreas — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Redução do preço da portagem») não corresponde ao pedido do enunciado.</t>
+          <t>Reduzir largamente o congestionamento nessas áreas — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -41426,7 +41426,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>Reduzir o volume de tráfego e, consequentemente, o correspondente impacto ambiental — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Arrecadar mais receitas») não corresponde ao pedido do enunciado.</t>
+          <t>Reduzir o volume de tráfego e, consequentemente, o correspondente impacto ambiental — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -41486,7 +41486,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>Veículos (através da respectiva matrícula) — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Locais regulados por sinalização luminosa») não corresponde ao pedido do enunciado.</t>
+          <t>Veículos (através da respectiva matrícula) — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -41546,7 +41546,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>A promoção da segurança — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O controlo por parte do condutor dos cruzamentos regulados por sinalização…») não corresponde ao pedido do enunciado.</t>
+          <t>A promoção da segurança — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -41606,7 +41606,7 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>A emissão de informações aos condutores, permitindo -lhes uma melhor gestão da viagem em função das ocorrências assinaladas — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Apenas informação aos condutores de locais com obras») não corresponde ao pedido do enunciado.</t>
+          <t>A emissão de informações aos condutores, permitindo -lhes uma melhor gestão da viagem em função das ocorrências assinaladas — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -41666,7 +41666,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>Evitar o acidente — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Dar indicação ao condutor que o caixa de velocidades do veículo se encontr…») não corresponde ao pedido do enunciado.</t>
+          <t>Evitar o acidente — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -41726,7 +41726,7 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>Constitui um útil auxiliar de navegação para o condutor — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Permite a melhor manutenção da bagagem dos passageiros») não corresponde ao pedido do enunciado.</t>
+          <t>Constitui um útil auxiliar de navegação para o condutor — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
@@ -41786,7 +41786,7 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>Velocidade média, localização de áreas de serviço e de locais de interesse turístico, bem como o valor da correspondente altitude — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Apenas a velocidade média») não corresponde ao pedido do enunciado.</t>
+          <t>Velocidade média, localização de áreas de serviço e de locais de interesse turístico, bem como o valor da correspondente altitude — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -41846,7 +41846,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>Um recetor GPS — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Um aparelho elétrico qualquer») não corresponde ao pedido do enunciado.</t>
+          <t>Um recetor GPS — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -41906,7 +41906,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>Sintetizadores de voz que permitem a indicação do caminho ou rumo — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («A utilização do GPS é sempre totalmente segura») não corresponde ao pedido do enunciado.</t>
+          <t>Sintetizadores de voz que permitem a indicação do caminho ou rumo — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -42026,7 +42026,7 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>Inteligentes, seguros e com a possibilidade de garantirem serviços transversais — é o que melhor responde ao enunciado (opção B)). Por exemplo, C) («Um sistema de utilização mais complicada que o passe normal») não corresponde ao pedido do enunciado.</t>
+          <t>Inteligentes, seguros e com a possibilidade de garantirem serviços transversais — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
@@ -42086,7 +42086,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>O conjunto de quaisquer registos quantificáveis relativos a um fenómeno ou acontecimento — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Qualquer sistema automatizado») não corresponde ao pedido do enunciado.</t>
+          <t>O conjunto de quaisquer registos quantificáveis relativos a um fenómeno ou acontecimento — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -42146,7 +42146,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>A aplicação das tecnologias de informação e comunicação aos transportes — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («A aplicação do tacógrafo digital à infra-estrutura de transporte de veícul…») não corresponde ao pedido do enunciado.</t>
+          <t>A aplicação das tecnologias de informação e comunicação aos transportes — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -42206,7 +42206,7 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>Não, cada vez há mais sistemas de informática embarcada, fáceis de utilizar e amigos do ambiente — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Não, mesmo grandes frotas conseguem ser adequadamente geridas sem exigir e…») não corresponde ao pedido do enunciado.</t>
+          <t>Não, cada vez há mais sistemas de informática embarcada, fáceis de utilizar e amigos do ambiente — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
@@ -42266,7 +42266,7 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>Internet — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Electronic Data Interchange (EDI)») não corresponde ao pedido do enunciado.</t>
+          <t>Internet — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
@@ -42326,7 +42326,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>Aumentar a produtividade e a competitividade — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Não influencia a eficiência da empresa») não corresponde ao pedido do enunciado.</t>
+          <t>Aumentar a produtividade e a competitividade — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -42386,7 +42386,7 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>Registar os tempos de condução e de repouso — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Controlar a distância entre veículos») não corresponde ao pedido do enunciado.</t>
+          <t>Registar os tempos de condução e de repouso — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -42446,7 +42446,7 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>Este equipamento requer a inserção de u m cartão inteligente (com um chip incorporado), que tem carácter pessoal, contém a identificação do condutor e permite a memorização dos dados relativos às suas actividades — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («O tacógrafo permite limitar a velocidade máxima do veículo») não corresponde ao pedido do enunciado.</t>
+          <t>Este equipamento requer a inserção de u m cartão inteligente (com um chip incorporado), que tem carácter pessoal, contém a identificação do condutor e permite a memorização dos dados relativos às suas actividades — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
@@ -42506,7 +42506,7 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>Cada condutor poderá ser titular de um ou mais cartões — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («O tacógrafo permite limitar a velocidade máxima do veículo») não corresponde ao pedido do enunciado.</t>
+          <t>Cada condutor poderá ser titular de um ou mais cartões — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -42746,7 +42746,7 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>A obtenção de informação em tempo real sobre a localização dos produtos — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A prevenção dos acidentes») não corresponde ao pedido do enunciado.</t>
+          <t>A obtenção de informação em tempo real sobre a localização dos produtos — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -42866,7 +42866,7 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>Europeu de radionavegação e de posicionamento por satélite — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Norte americano de radionavegação, composto por 24 satélites.») não corresponde ao pedido do enunciado.</t>
+          <t>Europeu de radionavegação e de posicionamento por satélite — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -42926,7 +42926,7 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>80% — é o que melhor responde ao enunciado (opção C)). Por exemplo, a opção A) indica valores (60%) diferentes do aplicável.</t>
+          <t>80% — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -42986,7 +42986,7 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>Sim, mas nem sempre foi assim — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Não, o maior elo é o caminho-de-ferro») não corresponde ao pedido do enunciado.</t>
+          <t>Sim, mas nem sempre foi assim — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -43046,7 +43046,7 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>O centro da gravidade da carga (total de passageiros e bagagem) e superfície da caixa de carga coincidirem — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («O motorista conseguir determinar o centro de gravidade de todos os passage…») não corresponde ao pedido do enunciado.</t>
+          <t>O centro da gravidade da carga (total de passageiros e bagagem) e superfície da caixa de carga coincidirem — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -43106,7 +43106,7 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>Encontrar-se em boas condições físicas como psíquicas — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Ser frequentemente submetido apenas a avaliações psicológicas») não corresponde ao pedido do enunciado.</t>
+          <t>Encontrar-se em boas condições físicas como psíquicas — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -43166,7 +43166,7 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Submeter-se a prévio controlo médico e a acompanhamento adequado para monitoriz ação de eventuais efeitos negativos (A)). Por exemplo, D) («Não tomar qualquer atitude») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Submeter-se a prévio controlo médico e a acompanhamento adequado para monitoriz ação de eventuais efeitos negativos (A)).</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -43226,7 +43226,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>Trata-se de uma definição: Capacidade de resposta (opção D)).  Por exemplo, B) («Condicionantes da condução») não corresponde ao pedido do enunciado.</t>
+          <t>Trata-se de uma definição: Capacidade de resposta (opção D)).</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -43346,7 +43346,7 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>Em condições normais, o gasto de combustível não depende do tipo de caixa de velocidades mas do tipo de condução — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Sempre com caixa de velocidades automática nas subidas e descidas») não corresponde ao pedido do enunciado.</t>
+          <t>Em condições normais, o gasto de combustível não depende do tipo de caixa de velocidades mas do tipo de condução — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -43406,7 +43406,7 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>O procedimento adequado é As três hipóteses estão corretas, dependendo da situação concreta (D)). Por exemplo, C) («Usar devidamente o motor da viatura») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é As três hipóteses estão corretas, dependendo da situação concreta (D)).</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -43466,7 +43466,7 @@
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Nas descidas, utilizar o ponto morto (B)). Por exemplo, D) («Nas descidas e subidas mudar a velocidade sempre que necessário») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Nas descidas, utilizar o ponto morto (B)).</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -43526,7 +43526,7 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>Guiar com os vidros abertos — é o que melhor responde ao enunciado (opção A)). Por exemplo, C) («Guiar com antecipação») não corresponde ao pedido do enunciado.</t>
+          <t>Guiar com os vidros abertos — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -43586,7 +43586,7 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>Os atrasos e maior consumo de energia — é o que melhor responde ao enunciado (opção C)). Por exemplo, B) («A maior exposição ao frio ou ao calor») não corresponde ao pedido do enunciado.</t>
+          <t>Os atrasos e maior consumo de energia — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -43646,7 +43646,7 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>É todo o transporte que se realiza entre locais de um mesmo país estrangeiro — é o que melhor responde ao enunciado (opção B)). Por exemplo, A) («É todo o transporte em que o ponto de origem ou o ponto de destino se situ…») não corresponde ao pedido do enunciado.</t>
+          <t>É todo o transporte que se realiza entre locais de um mesmo país estrangeiro — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
@@ -43706,7 +43706,7 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>Que se realiza entre locais de países diferentes, distintos de Portugal — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Entre portos de um mesmo país») não corresponde ao pedido do enunciado.</t>
+          <t>Que se realiza entre locais de países diferentes, distintos de Portugal — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -43766,7 +43766,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>Serve a empresa proprietária do veículo no exercício das suas atividades — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Realiza serviços a qualquer hora») não corresponde ao pedido do enunciado.</t>
+          <t>Serve a empresa proprietária do veículo no exercício das suas atividades — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -43826,7 +43826,7 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>Mais de 95% das toneladas movimentadas e a ferrovia menos de 5% — é o que melhor responde ao enunciado (opção B)). Por exemplo, a opção C) indica valores (Cerca de 80% das toneladas movimentadas e os caminhos-de-ferro cerca de 20%) diferentes do aplicável.</t>
+          <t>Mais de 95% das toneladas movimentadas e a ferrovia menos de 5% — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -43886,7 +43886,7 @@
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>A massa de carga máxima que pode ser carregada no veículo, ao longo da plataforma — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («As forças de aceleração exercidas pela carga») não corresponde ao pedido do enunciado.</t>
+          <t>A massa de carga máxima que pode ser carregada no veículo, ao longo da plataforma — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -43946,7 +43946,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>Reduzir o consumo de combustível, as emissões poluentes e aumentar a segurança rodoviária — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Aumentar o consumo de óleo e a um menor conforto na condução») não corresponde ao pedido do enunciado.</t>
+          <t>Reduzir o consumo de combustível, as emissões poluentes e aumentar a segurança rodoviária — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -44006,7 +44006,7 @@
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Maior for a velocidade a que se circula assim como no caso de má visibilidade ou piso escorregadio (B)). Por exemplo, D) («O veículo da frente é um veículo pesado») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Maior for a velocidade a que se circula assim como no caso de má visibilidade ou piso escorregadio (B)).</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
@@ -44186,7 +44186,7 @@
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>A carga máxima admissível, determinada pelo peso ou cubicagem máxima admitida — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («O espaço entre os lotes da mercadoria a fim de garantir o equilíbrio do ve…») não corresponde ao pedido do enunciado.</t>
+          <t>A carga máxima admissível, determinada pelo peso ou cubicagem máxima admitida — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
@@ -44306,7 +44306,7 @@
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>A atividade transitária só pode ser exercida por empresas titulares de alvará emitido pelo IMT — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («As empresas que realizam transporte rodoviário de mercadorias perigosas ca…») não corresponde ao pedido do enunciado.</t>
+          <t>A atividade transitária só pode ser exercida por empresas titulares de alvará emitido pelo IMT — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
@@ -44366,7 +44366,7 @@
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>Uma forma de cooperação ao nível da actividade de uma empresa (contratante ou empresa principal) que entrega a outra (subcontratada ou empresa auxiliar) a execução da totalidade ou de uma parte da sua actividade dentro de determinadas condições — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («A perda de controlo na execução das actividades e maior necessidade de con…») não corresponde ao pedido do enunciado.</t>
+          <t>Uma forma de cooperação ao nível da actividade de uma empresa (contratante ou empresa principal) que entrega a outra (subcontratada ou empresa auxiliar) a execução da totalidade ou de uma parte da sua actividade dentro de determinadas condições — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
@@ -44426,7 +44426,7 @@
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>Não coloca em perigo a saúde pública e os ecossistemas e que respeita as necessidades de mobilidade — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Apenas é bom para o meio ambiente») não corresponde ao pedido do enunciado.</t>
+          <t>Não coloca em perigo a saúde pública e os ecossistemas e que respeita as necessidades de mobilidade — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
@@ -44486,7 +44486,7 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>Alvará, emitido pelo IMTT — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Não carece de qualquer alvará») não corresponde ao pedido do enunciado.</t>
+          <t>Alvará, emitido pelo IMTT — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -44546,7 +44546,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>Maior rapidez (porta-a-porta) — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Maior competitividade para produtos com baixo custo de tonelada por quilóm…») não corresponde ao pedido do enunciado.</t>
+          <t>Maior rapidez (porta-a-porta) — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -44606,7 +44606,7 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>Um dos principais fatores encontrados na origem de acidentes rodoviários — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Significativa apenas se o condutor ingerir bebidas alcoólicas») não corresponde ao pedido do enunciado.</t>
+          <t>Um dos principais fatores encontrados na origem de acidentes rodoviários — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -44666,7 +44666,7 @@
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>Aumento do tempo de reação — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Aumento da capacidade de percepção das velocidades e distâncias») não corresponde ao pedido do enunciado.</t>
+          <t>Aumento do tempo de reação — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
@@ -44726,7 +44726,7 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Aos veículos de duas rodas (A)). Por exemplo, D) («Às marcas rodoviárias») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Aos veículos de duas rodas (A)).</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -44786,7 +44786,7 @@
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Os dispositivos de segurança estão todos a funcionar corretamente (A)). Por exemplo, D) («Os passageiros falam todos português corretamente») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Os dispositivos de segurança estão todos a funcionar corretamente (A)).</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
@@ -44906,7 +44906,7 @@
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Descansar e aguardar que seja efetuada a descarga (A)). Por exemplo, D) («Verificar se o lacre colocado no compartimento de carga ainda está intacto…») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Descansar e aguardar que seja efetuada a descarga (A)).</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
@@ -44966,7 +44966,7 @@
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>Planear os detalhes do itinerário e não seguir sempre o mesmo percurso — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Assegurar-se que a entrega da mercadoria é feita no local correcto ou os p…») não corresponde ao pedido do enunciado.</t>
+          <t>Planear os detalhes do itinerário e não seguir sempre o mesmo percurso — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
@@ -45026,7 +45026,7 @@
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Contactar imediatamente as autoridades locais e identificar -se, b em como ao veículo, dando referências da localização (A)). Por exemplo, D) («Atacar o passageiro, de forma a saia do veículo») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Contactar imediatamente as autoridades locais e identificar -se, b em como ao veículo, dando referências da localização (A)).</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
@@ -45086,7 +45086,7 @@
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>O procedimento adequado é A base das chamas (A)). Por exemplo, D) («O topo e o meio das chamas alternadamente») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é A base das chamas (A)).</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
@@ -45146,7 +45146,7 @@
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>Todas as respostas anteriores estão correctas — é o que melhor responde ao enunciado (opção D)). Por exemplo, C) («Estamos a ligar diretamente para os bombeiros») não corresponde ao pedido do enunciado.</t>
+          <t>Todas as respostas anteriores estão correctas — é o que melhor responde ao enunciado (opção D)).</t>
         </is>
       </c>
       <c r="I772" t="inlineStr">
@@ -45206,7 +45206,7 @@
       </c>
       <c r="H773" t="inlineStr">
         <is>
-          <t>O procedimento adequado é Abandonar o local (D)). Por exemplo, C) («Efetuar uma rápida avaliação da vítima») não corresponde ao pedido do enunciado.</t>
+          <t>O procedimento adequado é Abandonar o local (D)).</t>
         </is>
       </c>
       <c r="I773" t="inlineStr">
@@ -45266,7 +45266,7 @@
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>Maior velocidade de circulação — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Maior distracção do condutor provocada pelos passageiros») não corresponde ao pedido do enunciado.</t>
+          <t>Maior velocidade de circulação — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
@@ -45386,7 +45386,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>Os transportes interurbanos, regionais, locais e urbanos — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Os transportes particulares») não corresponde ao pedido do enunciado.</t>
+          <t>Os transportes interurbanos, regionais, locais e urbanos — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -45446,7 +45446,7 @@
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>Falta de organização gerando pouco trabalho e produtividade assim como aspetos físicos ambientais — é o que melhor responde ao enunciado (opção C)). Por exemplo, D) («Consciencialização dos objetivos e metas a atingir como profissional da em…») não corresponde ao pedido do enunciado.</t>
+          <t>Falta de organização gerando pouco trabalho e produtividade assim como aspetos físicos ambientais — é o que melhor responde ao enunciado (opção C)).</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">
@@ -45506,7 +45506,7 @@
       </c>
       <c r="H778" t="inlineStr">
         <is>
-          <t>Formar um grupo coeso, eficiente e motivado — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Que o nosso comportamento possa depender do nosso estado de espírito») não corresponde ao pedido do enunciado.</t>
+          <t>Formar um grupo coeso, eficiente e motivado — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I778" t="inlineStr">
@@ -45566,7 +45566,7 @@
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>Permite aos motoristas estar em contacto com a empresa, colegas, clientes e outros contactos, tais como serviços de manutenção e reparação e centros de controlo de tráfego — é o que melhor responde ao enunciado (opção A)). Por exemplo, D) («Obriga o condutor a obter certificados e autorizações adicionais para o ex…») não corresponde ao pedido do enunciado.</t>
+          <t>Permite aos motoristas estar em contacto com a empresa, colegas, clientes e outros contactos, tais como serviços de manutenção e reparação e centros de controlo de tráfego — é o que melhor responde ao enunciado (opção A)).</t>
         </is>
       </c>
       <c r="I779" t="inlineStr">
@@ -45686,7 +45686,7 @@
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t>Trata-se de uma definição: Avaliação em primeiro lugar do estado de consciência da vítima (opção D)).  Por exemplo, B) («Verificação em primeiro lugar da existência de ventilação.») não corresponde ao pedido do enunciado.</t>
+          <t>Trata-se de uma definição: Avaliação em primeiro lugar do estado de consciência da vítima (opção D)).</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
@@ -45746,7 +45746,7 @@
       </c>
       <c r="H782" t="inlineStr">
         <is>
-          <t>A instalação de televisões na cabine do veículo ou na caixa de carga — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («As ferramentas informáticas utilizadas para fazer edição de imagens») não corresponde ao pedido do enunciado.</t>
+          <t>A instalação de televisões na cabine do veículo ou na caixa de carga — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I782" t="inlineStr">
@@ -45806,7 +45806,7 @@
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>Gestão em tempo real de frota, consumo e rotas — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Apenas controlo de velocidade») não corresponde ao pedido do enunciado.</t>
+          <t>Gestão em tempo real de frota, consumo e rotas — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -45926,7 +45926,7 @@
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>Permitir que as rodas girem a velocidades diferentes em curva — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («Aumentar o binário do motor») não corresponde ao pedido do enunciado.</t>
+          <t>Permitir que as rodas girem a velocidades diferentes em curva — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I785" t="inlineStr">
@@ -45986,7 +45986,7 @@
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>É proibido e pode ter consequências graves — é o que melhor responde ao enunciado (opção B)). Por exemplo, D) («É permitido se pagar em dinheiro») não corresponde ao pedido do enunciado.</t>
+          <t>É proibido e pode ter consequências graves — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
       <c r="I786" t="inlineStr">
@@ -46046,7 +46046,7 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>As alternativas anteriores são corretas em separado; por isso D) («Todas as anteriores») é a resposta completa. Por exemplo, C) («Aumento da distância de travagem») não corresponde ao pedido do enunciado.</t>
+          <t>As alternativas anteriores são corretas em separado; por isso D) («Todas as anteriores») é a resposta completa.</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">

--- a/questoes sem rep.xlsx
+++ b/questoes sem rep.xlsx
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4177,8 +4177,16 @@
           <t>Aumentar a altura da carga — é o que melhor responde ao enunciado (opção B)).</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>corrigida</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Gabarito corrigido manualmente: A</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>mercadorias</t>

--- a/questoes sem rep.xlsx
+++ b/questoes sem rep.xlsx
@@ -24985,7 +24985,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -24995,12 +24995,12 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>gabarito_testescam</t>
+          <t>corrigida</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>Importado IMT rel_2 | Gabarito IMT pendente | Gabarito TestesCAM (exato 100%, opcao_texto)</t>
+          <t>Gabarito corrigido manualmente: B</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">

--- a/questoes sem rep.xlsx
+++ b/questoes sem rep.xlsx
@@ -18813,7 +18813,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -18823,12 +18823,12 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>gabarito_testescam</t>
+          <t>corrigida</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>Importado IMT rel_2 | Gabarito IMT pendente | Gabarito TestesCAM (exato 100%, opcao_texto)</t>
+          <t>Gabarito corrigido manualmente: B (ação pneumática)</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -20143,12 +20143,12 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>gabarito_testescam</t>
+          <t>corrigida</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>Importado IMT rel_2 | Gabarito IMT pendente | Gabarito TestesCAM (fuzzy 75%, opcao_texto)</t>
+          <t>Gabarito corrigido manualmente: B (ação pneumática)</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
